--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -5880,7 +5880,7 @@
         <v>121859643</v>
       </c>
       <c r="B46" t="n">
-        <v>98157</v>
+        <v>98159</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5989,10 +5989,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121859629</v>
+        <v>121859644</v>
       </c>
       <c r="B47" t="n">
-        <v>8436</v>
+        <v>98159</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6001,25 +6001,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6029,10 +6029,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>686792</v>
+        <v>686844</v>
       </c>
       <c r="R47" t="n">
-        <v>6563030</v>
+        <v>6563303</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6064,7 +6064,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6085,21 +6085,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6116,10 +6101,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121859639</v>
+        <v>121859640</v>
       </c>
       <c r="B48" t="n">
-        <v>98157</v>
+        <v>98159</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6156,10 +6141,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>686827</v>
+        <v>686837</v>
       </c>
       <c r="R48" t="n">
-        <v>6563296</v>
+        <v>6563297</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6191,7 +6176,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6201,7 +6186,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6228,7 +6213,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121859631</v>
+        <v>121859629</v>
       </c>
       <c r="B49" t="n">
         <v>8436</v>
@@ -6268,10 +6253,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>686934</v>
+        <v>686792</v>
       </c>
       <c r="R49" t="n">
-        <v>6563148</v>
+        <v>6563030</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6303,7 +6288,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6313,7 +6298,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6355,10 +6340,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121859656</v>
+        <v>121859649</v>
       </c>
       <c r="B50" t="n">
-        <v>5193</v>
+        <v>98159</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6367,25 +6352,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6395,10 +6380,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>687094</v>
+        <v>686851</v>
       </c>
       <c r="R50" t="n">
-        <v>6563235</v>
+        <v>6563299</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6430,7 +6415,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6440,7 +6425,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6451,26 +6436,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL50" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6487,10 +6452,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121859651</v>
+        <v>121859637</v>
       </c>
       <c r="B51" t="n">
-        <v>95704</v>
+        <v>98159</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6499,25 +6464,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6527,10 +6492,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>686912</v>
+        <v>686863</v>
       </c>
       <c r="R51" t="n">
-        <v>6563320</v>
+        <v>6563252</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6562,7 +6527,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6572,7 +6537,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6583,11 +6548,6 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Klen fuktig låga.</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6604,10 +6564,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121859646</v>
+        <v>121859638</v>
       </c>
       <c r="B52" t="n">
-        <v>98157</v>
+        <v>98159</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6644,10 +6604,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>686841</v>
+        <v>686826</v>
       </c>
       <c r="R52" t="n">
-        <v>6563303</v>
+        <v>6563286</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6679,7 +6639,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6689,7 +6649,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6716,10 +6676,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121859638</v>
+        <v>121859655</v>
       </c>
       <c r="B53" t="n">
-        <v>98157</v>
+        <v>95706</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6728,25 +6688,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6756,10 +6716,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>686826</v>
+        <v>687027</v>
       </c>
       <c r="R53" t="n">
-        <v>6563286</v>
+        <v>6563279</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6791,7 +6751,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6801,7 +6761,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6812,6 +6772,26 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL53" t="inlineStr">
+        <is>
+          <t>Grov granlåga.</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Picea abies # Grov granlåga.</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6828,10 +6808,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121859655</v>
+        <v>121859647</v>
       </c>
       <c r="B54" t="n">
-        <v>95704</v>
+        <v>98159</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6840,25 +6820,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6868,10 +6848,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>687027</v>
+        <v>686854</v>
       </c>
       <c r="R54" t="n">
-        <v>6563279</v>
+        <v>6563286</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6903,7 +6883,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6913,7 +6893,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6924,26 +6904,6 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL54" t="inlineStr">
-        <is>
-          <t>Grov granlåga.</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Picea abies # Grov granlåga.</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6960,10 +6920,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121859650</v>
+        <v>121859642</v>
       </c>
       <c r="B55" t="n">
-        <v>98157</v>
+        <v>98159</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6994,16 +6954,24 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Öster om Tyresta by, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>686895</v>
+        <v>686834</v>
       </c>
       <c r="R55" t="n">
-        <v>6563306</v>
+        <v>6563305</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7035,7 +7003,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7045,7 +7013,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7054,6 +7022,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -7072,10 +7041,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121859633</v>
+        <v>121859632</v>
       </c>
       <c r="B56" t="n">
-        <v>78712</v>
+        <v>90783</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7084,25 +7053,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>637</v>
+        <v>5442</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7112,10 +7081,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>686873</v>
+        <v>686934</v>
       </c>
       <c r="R56" t="n">
-        <v>6563147</v>
+        <v>6563148</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7147,7 +7116,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7157,7 +7126,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7204,10 +7173,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121859644</v>
+        <v>121859633</v>
       </c>
       <c r="B57" t="n">
-        <v>98157</v>
+        <v>78714</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7220,21 +7189,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>637</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7244,10 +7213,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>686844</v>
+        <v>686873</v>
       </c>
       <c r="R57" t="n">
-        <v>6563303</v>
+        <v>6563147</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7279,7 +7248,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7289,7 +7258,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7300,6 +7269,26 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL57" t="inlineStr">
+        <is>
+          <t>Levande äldre tall.</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Levande äldre tall.</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7316,10 +7305,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121859657</v>
+        <v>121859620</v>
       </c>
       <c r="B58" t="n">
-        <v>90761</v>
+        <v>94681</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7328,25 +7317,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>2818</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7356,10 +7345,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>687094</v>
+        <v>686447</v>
       </c>
       <c r="R58" t="n">
-        <v>6563235</v>
+        <v>6562986</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7391,7 +7380,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7401,7 +7390,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7428,10 +7417,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121859620</v>
+        <v>121859646</v>
       </c>
       <c r="B59" t="n">
-        <v>94679</v>
+        <v>98159</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7440,25 +7429,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2818</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7468,10 +7457,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>686447</v>
+        <v>686841</v>
       </c>
       <c r="R59" t="n">
-        <v>6562986</v>
+        <v>6563303</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7503,7 +7492,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7513,7 +7502,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7540,10 +7529,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121859636</v>
+        <v>121859656</v>
       </c>
       <c r="B60" t="n">
-        <v>94569</v>
+        <v>5193</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7556,21 +7545,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2810</v>
+        <v>105930</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7580,10 +7569,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>686870</v>
+        <v>687094</v>
       </c>
       <c r="R60" t="n">
-        <v>6563252</v>
+        <v>6563235</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7615,7 +7604,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7625,7 +7614,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7636,6 +7625,26 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL60" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7652,10 +7661,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121859632</v>
+        <v>121859636</v>
       </c>
       <c r="B61" t="n">
-        <v>90781</v>
+        <v>94571</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7664,25 +7673,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5442</v>
+        <v>2810</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7692,10 +7701,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>686934</v>
+        <v>686870</v>
       </c>
       <c r="R61" t="n">
-        <v>6563148</v>
+        <v>6563252</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7727,7 +7736,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7737,7 +7746,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7748,26 +7757,6 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL61" t="inlineStr">
-        <is>
-          <t>Levande äldre tall.</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Levande äldre tall.</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7784,10 +7773,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121859654</v>
+        <v>121859657</v>
       </c>
       <c r="B62" t="n">
-        <v>78643</v>
+        <v>90763</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7800,21 +7789,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7824,10 +7813,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>687000</v>
+        <v>687094</v>
       </c>
       <c r="R62" t="n">
-        <v>6563278</v>
+        <v>6563235</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7859,7 +7848,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7869,7 +7858,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7880,21 +7869,6 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7911,10 +7885,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121859642</v>
+        <v>121859651</v>
       </c>
       <c r="B63" t="n">
-        <v>98157</v>
+        <v>95706</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7923,46 +7897,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Öster om Tyresta by, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>686834</v>
+        <v>686912</v>
       </c>
       <c r="R63" t="n">
-        <v>6563305</v>
+        <v>6563320</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7994,7 +7960,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8004,7 +7970,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8013,9 +7979,13 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Klen fuktig låga.</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -8032,10 +8002,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121859637</v>
+        <v>121859650</v>
       </c>
       <c r="B64" t="n">
-        <v>98157</v>
+        <v>98159</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8072,10 +8042,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>686863</v>
+        <v>686895</v>
       </c>
       <c r="R64" t="n">
-        <v>6563252</v>
+        <v>6563306</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8107,7 +8077,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8117,7 +8087,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8144,10 +8114,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121859649</v>
+        <v>121859631</v>
       </c>
       <c r="B65" t="n">
-        <v>98157</v>
+        <v>8436</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8156,25 +8126,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8184,10 +8154,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>686851</v>
+        <v>686934</v>
       </c>
       <c r="R65" t="n">
-        <v>6563299</v>
+        <v>6563148</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8219,7 +8189,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8229,7 +8199,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8240,6 +8210,21 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -8256,10 +8241,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121859640</v>
+        <v>121859639</v>
       </c>
       <c r="B66" t="n">
-        <v>98157</v>
+        <v>98159</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8296,10 +8281,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>686837</v>
+        <v>686827</v>
       </c>
       <c r="R66" t="n">
-        <v>6563297</v>
+        <v>6563296</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8331,7 +8316,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8341,7 +8326,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8368,10 +8353,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121859647</v>
+        <v>121859654</v>
       </c>
       <c r="B67" t="n">
-        <v>98157</v>
+        <v>78645</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8380,25 +8365,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8408,10 +8393,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>686854</v>
+        <v>687000</v>
       </c>
       <c r="R67" t="n">
-        <v>6563286</v>
+        <v>6563278</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8443,7 +8428,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8453,7 +8438,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8464,6 +8449,21 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -8483,7 +8483,7 @@
         <v>121859619</v>
       </c>
       <c r="B68" t="n">
-        <v>94775</v>
+        <v>94777</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8595,7 +8595,7 @@
         <v>122220583</v>
       </c>
       <c r="B69" t="n">
-        <v>98157</v>
+        <v>98159</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         <v>122220670</v>
       </c>
       <c r="B70" t="n">
-        <v>78712</v>
+        <v>78714</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -5877,7 +5877,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121859643</v>
+        <v>121859644</v>
       </c>
       <c r="B46" t="n">
         <v>98159</v>
@@ -5917,10 +5917,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>686834</v>
+        <v>686844</v>
       </c>
       <c r="R46" t="n">
-        <v>6563309</v>
+        <v>6563303</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5952,7 +5952,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5962,7 +5962,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5989,7 +5989,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121859644</v>
+        <v>121859649</v>
       </c>
       <c r="B47" t="n">
         <v>98159</v>
@@ -6029,10 +6029,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>686844</v>
+        <v>686851</v>
       </c>
       <c r="R47" t="n">
-        <v>6563303</v>
+        <v>6563299</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6064,7 +6064,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6101,7 +6101,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121859640</v>
+        <v>121859638</v>
       </c>
       <c r="B48" t="n">
         <v>98159</v>
@@ -6141,10 +6141,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>686837</v>
+        <v>686826</v>
       </c>
       <c r="R48" t="n">
-        <v>6563297</v>
+        <v>6563286</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6186,7 +6186,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6213,10 +6213,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121859629</v>
+        <v>121859640</v>
       </c>
       <c r="B49" t="n">
-        <v>8436</v>
+        <v>98159</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6225,25 +6225,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6253,10 +6253,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>686792</v>
+        <v>686837</v>
       </c>
       <c r="R49" t="n">
-        <v>6563030</v>
+        <v>6563297</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6298,7 +6298,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6309,21 +6309,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6340,7 +6325,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121859649</v>
+        <v>121859642</v>
       </c>
       <c r="B50" t="n">
         <v>98159</v>
@@ -6374,16 +6359,24 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Öster om Tyresta by, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>686851</v>
+        <v>686834</v>
       </c>
       <c r="R50" t="n">
-        <v>6563299</v>
+        <v>6563305</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6415,7 +6408,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6425,7 +6418,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6434,6 +6427,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6452,7 +6446,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121859637</v>
+        <v>121859646</v>
       </c>
       <c r="B51" t="n">
         <v>98159</v>
@@ -6492,10 +6486,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>686863</v>
+        <v>686841</v>
       </c>
       <c r="R51" t="n">
-        <v>6563252</v>
+        <v>6563303</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6527,7 +6521,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6537,7 +6531,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6564,10 +6558,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121859638</v>
+        <v>121859657</v>
       </c>
       <c r="B52" t="n">
-        <v>98159</v>
+        <v>90763</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6576,25 +6570,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6604,10 +6598,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>686826</v>
+        <v>687094</v>
       </c>
       <c r="R52" t="n">
-        <v>6563286</v>
+        <v>6563235</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6639,7 +6633,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6649,7 +6643,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6676,10 +6670,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121859655</v>
+        <v>121859637</v>
       </c>
       <c r="B53" t="n">
-        <v>95706</v>
+        <v>98159</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6688,25 +6682,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6716,10 +6710,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>687027</v>
+        <v>686863</v>
       </c>
       <c r="R53" t="n">
-        <v>6563279</v>
+        <v>6563252</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6751,7 +6745,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6761,7 +6755,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6772,26 +6766,6 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL53" t="inlineStr">
-        <is>
-          <t>Grov granlåga.</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Picea abies # Grov granlåga.</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6808,10 +6782,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121859647</v>
+        <v>121859629</v>
       </c>
       <c r="B54" t="n">
-        <v>98159</v>
+        <v>8436</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6820,25 +6794,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6848,10 +6822,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>686854</v>
+        <v>686792</v>
       </c>
       <c r="R54" t="n">
-        <v>6563286</v>
+        <v>6563030</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6883,7 +6857,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6893,7 +6867,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6904,6 +6878,21 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6920,7 +6909,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121859642</v>
+        <v>121859650</v>
       </c>
       <c r="B55" t="n">
         <v>98159</v>
@@ -6954,24 +6943,16 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Öster om Tyresta by, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>686834</v>
+        <v>686895</v>
       </c>
       <c r="R55" t="n">
-        <v>6563305</v>
+        <v>6563306</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7003,7 +6984,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7013,7 +6994,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7022,7 +7003,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -7041,10 +7021,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121859632</v>
+        <v>121859633</v>
       </c>
       <c r="B56" t="n">
-        <v>90783</v>
+        <v>78714</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7053,25 +7033,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5442</v>
+        <v>637</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7081,10 +7061,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>686934</v>
+        <v>686873</v>
       </c>
       <c r="R56" t="n">
-        <v>6563148</v>
+        <v>6563147</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7116,7 +7096,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7126,7 +7106,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7173,10 +7153,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121859633</v>
+        <v>121859654</v>
       </c>
       <c r="B57" t="n">
-        <v>78714</v>
+        <v>78645</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7185,25 +7165,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>637</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7213,10 +7193,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>686873</v>
+        <v>687000</v>
       </c>
       <c r="R57" t="n">
-        <v>6563147</v>
+        <v>6563278</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7248,7 +7228,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7258,7 +7238,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7280,14 +7260,9 @@
           <t>Pinus sylvestris</t>
         </is>
       </c>
-      <c r="AL57" t="inlineStr">
-        <is>
-          <t>Levande äldre tall.</t>
-        </is>
-      </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # Levande äldre tall.</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7305,10 +7280,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121859620</v>
+        <v>121859636</v>
       </c>
       <c r="B58" t="n">
-        <v>94681</v>
+        <v>94571</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7321,21 +7296,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2818</v>
+        <v>2810</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7345,10 +7320,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>686447</v>
+        <v>686870</v>
       </c>
       <c r="R58" t="n">
-        <v>6562986</v>
+        <v>6563252</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7380,7 +7355,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7390,7 +7365,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7417,10 +7392,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121859646</v>
+        <v>121859620</v>
       </c>
       <c r="B59" t="n">
-        <v>98159</v>
+        <v>94681</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7429,25 +7404,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>2818</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7457,10 +7432,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>686841</v>
+        <v>686447</v>
       </c>
       <c r="R59" t="n">
-        <v>6563303</v>
+        <v>6562986</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7492,7 +7467,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7502,7 +7477,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7529,10 +7504,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121859656</v>
+        <v>121859631</v>
       </c>
       <c r="B60" t="n">
-        <v>5193</v>
+        <v>8436</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7545,21 +7520,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>105930</v>
+        <v>106545</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7569,10 +7544,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>687094</v>
+        <v>686934</v>
       </c>
       <c r="R60" t="n">
-        <v>6563235</v>
+        <v>6563148</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7604,7 +7579,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7614,7 +7589,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7628,22 +7603,17 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL60" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7661,10 +7631,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121859636</v>
+        <v>121859655</v>
       </c>
       <c r="B61" t="n">
-        <v>94571</v>
+        <v>95706</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7673,25 +7643,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2810</v>
+        <v>53</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7701,10 +7671,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>686870</v>
+        <v>687027</v>
       </c>
       <c r="R61" t="n">
-        <v>6563252</v>
+        <v>6563279</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7736,7 +7706,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7746,7 +7716,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7757,6 +7727,26 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL61" t="inlineStr">
+        <is>
+          <t>Grov granlåga.</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Picea abies # Grov granlåga.</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7773,10 +7763,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121859657</v>
+        <v>121859651</v>
       </c>
       <c r="B62" t="n">
-        <v>90763</v>
+        <v>95706</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7789,21 +7779,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7813,10 +7803,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>687094</v>
+        <v>686912</v>
       </c>
       <c r="R62" t="n">
-        <v>6563235</v>
+        <v>6563320</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7848,7 +7838,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7858,7 +7848,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7869,6 +7859,11 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Klen fuktig låga.</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7885,10 +7880,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121859651</v>
+        <v>121859656</v>
       </c>
       <c r="B63" t="n">
-        <v>95706</v>
+        <v>5193</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7897,25 +7892,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>53</v>
+        <v>105930</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7925,10 +7920,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>686912</v>
+        <v>687094</v>
       </c>
       <c r="R63" t="n">
-        <v>6563320</v>
+        <v>6563235</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7960,7 +7955,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7970,7 +7965,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7982,9 +7977,24 @@
       <c r="AG63" t="b">
         <v>0</v>
       </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL63" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Klen fuktig låga.</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8002,7 +8012,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121859650</v>
+        <v>121859647</v>
       </c>
       <c r="B64" t="n">
         <v>98159</v>
@@ -8042,10 +8052,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>686895</v>
+        <v>686854</v>
       </c>
       <c r="R64" t="n">
-        <v>6563306</v>
+        <v>6563286</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8077,7 +8087,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8087,7 +8097,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8114,10 +8124,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121859631</v>
+        <v>121859632</v>
       </c>
       <c r="B65" t="n">
-        <v>8436</v>
+        <v>90783</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8126,25 +8136,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8221,9 +8231,14 @@
           <t>Pinus sylvestris</t>
         </is>
       </c>
+      <c r="AL65" t="inlineStr">
+        <is>
+          <t>Levande äldre tall.</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Pinus sylvestris # Levande äldre tall.</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -8353,10 +8368,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121859654</v>
+        <v>121859643</v>
       </c>
       <c r="B67" t="n">
-        <v>78645</v>
+        <v>98159</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8365,25 +8380,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8393,10 +8408,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>687000</v>
+        <v>686834</v>
       </c>
       <c r="R67" t="n">
-        <v>6563278</v>
+        <v>6563309</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8428,7 +8443,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8438,7 +8453,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8449,21 +8464,6 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -8592,10 +8592,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122220583</v>
+        <v>122220670</v>
       </c>
       <c r="B69" t="n">
-        <v>98159</v>
+        <v>78714</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8608,35 +8608,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>637</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8644,10 +8643,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>686996</v>
+        <v>686813</v>
       </c>
       <c r="R69" t="n">
-        <v>6562864</v>
+        <v>6563023</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8684,7 +8683,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Samma lokal som rapporterats -21 och -22 men en ny klon. Den förra har möjligen haft lite problem med grisbök.</t>
+          <t>På tallstam.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8712,10 +8711,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122220670</v>
+        <v>122220583</v>
       </c>
       <c r="B70" t="n">
-        <v>78714</v>
+        <v>98159</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8728,34 +8727,35 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>637</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8763,10 +8763,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>686813</v>
+        <v>686996</v>
       </c>
       <c r="R70" t="n">
-        <v>6563023</v>
+        <v>6562864</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8803,7 +8803,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På tallstam.</t>
+          <t>Samma lokal som rapporterats -21 och -22 men en ny klon. Den förra har möjligen haft lite problem med grisbök.</t>
         </is>
       </c>
       <c r="AD70" t="b">

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -5877,10 +5877,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121859654</v>
+        <v>121859629</v>
       </c>
       <c r="B46" t="n">
-        <v>78645</v>
+        <v>8436</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5889,25 +5889,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5917,10 +5917,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>687000</v>
+        <v>686792</v>
       </c>
       <c r="R46" t="n">
-        <v>6563278</v>
+        <v>6563030</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5952,7 +5952,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5962,7 +5962,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6004,10 +6004,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121859633</v>
+        <v>121859638</v>
       </c>
       <c r="B47" t="n">
-        <v>78714</v>
+        <v>98175</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6020,21 +6020,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>637</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6044,10 +6044,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>686873</v>
+        <v>686826</v>
       </c>
       <c r="R47" t="n">
-        <v>6563147</v>
+        <v>6563286</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6079,7 +6079,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6100,26 +6100,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL47" t="inlineStr">
-        <is>
-          <t>Levande äldre tall.</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Levande äldre tall.</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6136,10 +6116,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121859656</v>
+        <v>121859644</v>
       </c>
       <c r="B48" t="n">
-        <v>5193</v>
+        <v>98175</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6148,25 +6128,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6176,10 +6156,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>687094</v>
+        <v>686844</v>
       </c>
       <c r="R48" t="n">
-        <v>6563235</v>
+        <v>6563303</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6211,7 +6191,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6221,7 +6201,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6232,26 +6212,6 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL48" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6268,10 +6228,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121859643</v>
+        <v>121859656</v>
       </c>
       <c r="B49" t="n">
-        <v>98175</v>
+        <v>5193</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6280,25 +6240,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6308,10 +6268,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>686834</v>
+        <v>687094</v>
       </c>
       <c r="R49" t="n">
-        <v>6563309</v>
+        <v>6563235</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6343,7 +6303,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6353,7 +6313,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6364,6 +6324,26 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL49" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6380,10 +6360,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121859632</v>
+        <v>121859642</v>
       </c>
       <c r="B50" t="n">
-        <v>90799</v>
+        <v>98175</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6392,38 +6372,46 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Öster om Tyresta by, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>686934</v>
+        <v>686834</v>
       </c>
       <c r="R50" t="n">
-        <v>6563148</v>
+        <v>6563305</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6455,7 +6443,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6465,7 +6453,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6474,28 +6462,9 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL50" t="inlineStr">
-        <is>
-          <t>Levande äldre tall.</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Levande äldre tall.</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6512,10 +6481,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121859657</v>
+        <v>121859637</v>
       </c>
       <c r="B51" t="n">
-        <v>90779</v>
+        <v>98175</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6524,25 +6493,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6552,10 +6521,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>687094</v>
+        <v>686863</v>
       </c>
       <c r="R51" t="n">
-        <v>6563235</v>
+        <v>6563252</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6587,7 +6556,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6597,7 +6566,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6624,7 +6593,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121859638</v>
+        <v>121859649</v>
       </c>
       <c r="B52" t="n">
         <v>98175</v>
@@ -6664,10 +6633,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>686826</v>
+        <v>686851</v>
       </c>
       <c r="R52" t="n">
-        <v>6563286</v>
+        <v>6563299</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6699,7 +6668,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6709,7 +6678,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6736,7 +6705,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121859629</v>
+        <v>121859631</v>
       </c>
       <c r="B53" t="n">
         <v>8436</v>
@@ -6776,10 +6745,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>686792</v>
+        <v>686934</v>
       </c>
       <c r="R53" t="n">
-        <v>6563030</v>
+        <v>6563148</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6811,7 +6780,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6821,7 +6790,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6863,10 +6832,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121859636</v>
+        <v>121859655</v>
       </c>
       <c r="B54" t="n">
-        <v>94587</v>
+        <v>95722</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6875,25 +6844,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2810</v>
+        <v>53</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6903,10 +6872,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>686870</v>
+        <v>687027</v>
       </c>
       <c r="R54" t="n">
-        <v>6563252</v>
+        <v>6563279</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6938,7 +6907,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6948,7 +6917,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6959,6 +6928,26 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL54" t="inlineStr">
+        <is>
+          <t>Grov granlåga.</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Picea abies # Grov granlåga.</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6975,10 +6964,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121859644</v>
+        <v>121859633</v>
       </c>
       <c r="B55" t="n">
-        <v>98175</v>
+        <v>78714</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6991,21 +6980,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>637</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7015,10 +7004,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>686844</v>
+        <v>686873</v>
       </c>
       <c r="R55" t="n">
-        <v>6563303</v>
+        <v>6563147</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7050,7 +7039,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7060,7 +7049,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7071,6 +7060,26 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL55" t="inlineStr">
+        <is>
+          <t>Levande äldre tall.</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Levande äldre tall.</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -7087,10 +7096,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121859631</v>
+        <v>121859651</v>
       </c>
       <c r="B56" t="n">
-        <v>8436</v>
+        <v>95722</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7099,25 +7108,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>53</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7127,10 +7136,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>686934</v>
+        <v>686912</v>
       </c>
       <c r="R56" t="n">
-        <v>6563148</v>
+        <v>6563320</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7162,7 +7171,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7172,7 +7181,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7184,19 +7193,9 @@
       <c r="AG56" t="b">
         <v>0</v>
       </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Klen fuktig låga.</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7214,10 +7213,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121859650</v>
+        <v>121859620</v>
       </c>
       <c r="B57" t="n">
-        <v>98175</v>
+        <v>94697</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7226,25 +7225,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>2818</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7254,10 +7253,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>686895</v>
+        <v>686447</v>
       </c>
       <c r="R57" t="n">
-        <v>6563306</v>
+        <v>6562986</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7289,7 +7288,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7299,7 +7298,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7326,10 +7325,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121859651</v>
+        <v>121859632</v>
       </c>
       <c r="B58" t="n">
-        <v>95722</v>
+        <v>90799</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7342,21 +7341,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>53</v>
+        <v>5442</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7366,10 +7365,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>686912</v>
+        <v>686934</v>
       </c>
       <c r="R58" t="n">
-        <v>6563320</v>
+        <v>6563148</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7401,7 +7400,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7411,7 +7410,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7423,9 +7422,24 @@
       <c r="AG58" t="b">
         <v>0</v>
       </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL58" t="inlineStr">
+        <is>
+          <t>Levande äldre tall.</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Klen fuktig låga.</t>
+          <t>Pinus sylvestris # Levande äldre tall.</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7443,10 +7457,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121859637</v>
+        <v>121859654</v>
       </c>
       <c r="B59" t="n">
-        <v>98175</v>
+        <v>78645</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7455,25 +7469,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7483,10 +7497,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>686863</v>
+        <v>687000</v>
       </c>
       <c r="R59" t="n">
-        <v>6563252</v>
+        <v>6563278</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7518,7 +7532,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7528,7 +7542,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7539,6 +7553,21 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7555,7 +7584,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121859639</v>
+        <v>121859647</v>
       </c>
       <c r="B60" t="n">
         <v>98175</v>
@@ -7595,10 +7624,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>686827</v>
+        <v>686854</v>
       </c>
       <c r="R60" t="n">
-        <v>6563296</v>
+        <v>6563286</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7630,7 +7659,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7640,7 +7669,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7667,7 +7696,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121859647</v>
+        <v>121859640</v>
       </c>
       <c r="B61" t="n">
         <v>98175</v>
@@ -7707,10 +7736,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>686854</v>
+        <v>686837</v>
       </c>
       <c r="R61" t="n">
-        <v>6563286</v>
+        <v>6563297</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7742,7 +7771,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7752,7 +7781,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7779,7 +7808,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121859646</v>
+        <v>121859643</v>
       </c>
       <c r="B62" t="n">
         <v>98175</v>
@@ -7819,10 +7848,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>686841</v>
+        <v>686834</v>
       </c>
       <c r="R62" t="n">
-        <v>6563303</v>
+        <v>6563309</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7854,7 +7883,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7864,7 +7893,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7891,10 +7920,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121859655</v>
+        <v>121859646</v>
       </c>
       <c r="B63" t="n">
-        <v>95722</v>
+        <v>98175</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7903,25 +7932,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7931,10 +7960,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>687027</v>
+        <v>686841</v>
       </c>
       <c r="R63" t="n">
-        <v>6563279</v>
+        <v>6563303</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7966,7 +7995,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7976,7 +8005,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7987,26 +8016,6 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL63" t="inlineStr">
-        <is>
-          <t>Grov granlåga.</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Picea abies # Grov granlåga.</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -8023,10 +8032,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121859620</v>
+        <v>121859650</v>
       </c>
       <c r="B64" t="n">
-        <v>94697</v>
+        <v>98175</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8035,25 +8044,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2818</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8063,10 +8072,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>686447</v>
+        <v>686895</v>
       </c>
       <c r="R64" t="n">
-        <v>6562986</v>
+        <v>6563306</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8098,7 +8107,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8108,7 +8117,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8135,10 +8144,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121859649</v>
+        <v>121859636</v>
       </c>
       <c r="B65" t="n">
-        <v>98175</v>
+        <v>94587</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8147,25 +8156,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>2810</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8175,10 +8184,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>686851</v>
+        <v>686870</v>
       </c>
       <c r="R65" t="n">
-        <v>6563299</v>
+        <v>6563252</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8210,7 +8219,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8220,7 +8229,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8247,10 +8256,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121859642</v>
+        <v>121859657</v>
       </c>
       <c r="B66" t="n">
-        <v>98175</v>
+        <v>90779</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8259,46 +8268,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Öster om Tyresta by, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>686834</v>
+        <v>687094</v>
       </c>
       <c r="R66" t="n">
-        <v>6563305</v>
+        <v>6563235</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8330,7 +8331,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8340,7 +8341,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8349,7 +8350,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -8368,7 +8368,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121859640</v>
+        <v>121859639</v>
       </c>
       <c r="B67" t="n">
         <v>98175</v>
@@ -8408,10 +8408,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>686837</v>
+        <v>686827</v>
       </c>
       <c r="R67" t="n">
-        <v>6563297</v>
+        <v>6563296</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8443,7 +8443,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8453,7 +8453,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD67" t="b">

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY70"/>
+  <dimension ref="A1:AY71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8595,7 +8595,7 @@
         <v>122220670</v>
       </c>
       <c r="B69" t="n">
-        <v>78714</v>
+        <v>78715</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8714,7 +8714,7 @@
         <v>122220583</v>
       </c>
       <c r="B70" t="n">
-        <v>98175</v>
+        <v>98185</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8828,6 +8828,112 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>122435803</v>
+      </c>
+      <c r="B71" t="n">
+        <v>91472</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>SV Norrby Mosse, Srm</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>686469</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6563016</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-02-02</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -8595,7 +8595,7 @@
         <v>122220670</v>
       </c>
       <c r="B69" t="n">
-        <v>78715</v>
+        <v>78720</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8714,7 +8714,7 @@
         <v>122220583</v>
       </c>
       <c r="B70" t="n">
-        <v>98185</v>
+        <v>98197</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8834,7 +8834,7 @@
         <v>122435803</v>
       </c>
       <c r="B71" t="n">
-        <v>91472</v>
+        <v>91484</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -8714,7 +8714,7 @@
         <v>122220583</v>
       </c>
       <c r="B70" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8834,7 +8834,7 @@
         <v>122435803</v>
       </c>
       <c r="B71" t="n">
-        <v>91484</v>
+        <v>91489</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -8595,7 +8595,7 @@
         <v>122220670</v>
       </c>
       <c r="B69" t="n">
-        <v>78720</v>
+        <v>78721</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8609,11 +8609,6 @@
       </c>
       <c r="E69" t="n">
         <v>637</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Ringlav</t>
-        </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -8714,7 +8709,7 @@
         <v>122220583</v>
       </c>
       <c r="B70" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8728,11 +8723,6 @@
       </c>
       <c r="E70" t="n">
         <v>220787</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -8834,7 +8824,7 @@
         <v>122435803</v>
       </c>
       <c r="B71" t="n">
-        <v>91489</v>
+        <v>91494</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8848,11 +8838,6 @@
       </c>
       <c r="E71" t="n">
         <v>3298</v>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Trådticka</t>
-        </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -8595,7 +8595,7 @@
         <v>122220670</v>
       </c>
       <c r="B69" t="n">
-        <v>78721</v>
+        <v>78725</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8609,6 +8609,11 @@
       </c>
       <c r="E69" t="n">
         <v>637</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Ringlav</t>
+        </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -8709,7 +8714,7 @@
         <v>122220583</v>
       </c>
       <c r="B70" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8723,6 +8728,11 @@
       </c>
       <c r="E70" t="n">
         <v>220787</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -8824,7 +8834,7 @@
         <v>122435803</v>
       </c>
       <c r="B71" t="n">
-        <v>91494</v>
+        <v>91507</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8838,6 +8848,11 @@
       </c>
       <c r="E71" t="n">
         <v>3298</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -8714,7 +8714,7 @@
         <v>122220583</v>
       </c>
       <c r="B70" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8834,7 +8834,7 @@
         <v>122435803</v>
       </c>
       <c r="B71" t="n">
-        <v>91507</v>
+        <v>91520</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -8592,10 +8592,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122220670</v>
+        <v>122220583</v>
       </c>
       <c r="B69" t="n">
-        <v>78725</v>
+        <v>98240</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8608,34 +8608,35 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>637</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -8643,10 +8644,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>686813</v>
+        <v>686996</v>
       </c>
       <c r="R69" t="n">
-        <v>6563023</v>
+        <v>6562864</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8683,7 +8684,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>På tallstam.</t>
+          <t>Samma lokal som rapporterats -21 och -22 men en ny klon. Den förra har möjligen haft lite problem med grisbök.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8711,10 +8712,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122220583</v>
+        <v>122220670</v>
       </c>
       <c r="B70" t="n">
-        <v>98237</v>
+        <v>78725</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8727,35 +8728,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>637</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -8763,10 +8763,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>686996</v>
+        <v>686813</v>
       </c>
       <c r="R70" t="n">
-        <v>6562864</v>
+        <v>6563023</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8803,7 +8803,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Samma lokal som rapporterats -21 och -22 men en ny klon. Den förra har möjligen haft lite problem med grisbök.</t>
+          <t>På tallstam.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8834,7 +8834,7 @@
         <v>122435803</v>
       </c>
       <c r="B71" t="n">
-        <v>91520</v>
+        <v>91521</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -8834,7 +8834,7 @@
         <v>122435803</v>
       </c>
       <c r="B71" t="n">
-        <v>91521</v>
+        <v>91522</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -8834,7 +8834,7 @@
         <v>122435803</v>
       </c>
       <c r="B71" t="n">
-        <v>91522</v>
+        <v>91525</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY71"/>
+  <dimension ref="A1:AY72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8935,6 +8935,116 @@
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>122778162</v>
+      </c>
+      <c r="B72" t="n">
+        <v>57631</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>NO Norrby  Mosse, Srm</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>687230</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6563312</v>
+      </c>
+      <c r="S72" t="n">
+        <v>25</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY72"/>
+  <dimension ref="A1:AY74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9045,6 +9045,241 @@
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>122779259</v>
+      </c>
+      <c r="B73" t="n">
+        <v>57631</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Talltita, Srm</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>686999</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6563293</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Hörde talltitan och hann se den för en kort ögonblick</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Jenny Nyholm</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Jenny Nyholm</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>122781008</v>
+      </c>
+      <c r="B74" t="n">
+        <v>98347</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Knärot, Srm</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>686833</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6563215</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Jenny Nyholm</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Jenny Nyholm</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -8834,7 +8834,7 @@
         <v>122435803</v>
       </c>
       <c r="B71" t="n">
-        <v>91525</v>
+        <v>91628</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -9047,10 +9047,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122779259</v>
+        <v>122781008</v>
       </c>
       <c r="B73" t="n">
-        <v>57631</v>
+        <v>98355</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9059,54 +9059,42 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Talltita, Srm</t>
+          <t>Knärot, Srm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>686999</v>
+        <v>686833</v>
       </c>
       <c r="R73" t="n">
-        <v>6563293</v>
+        <v>6563215</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9143,7 +9131,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Hörde talltitan och hann se den för en kort ögonblick</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9152,6 +9140,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -9170,10 +9159,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122781008</v>
+        <v>122779259</v>
       </c>
       <c r="B74" t="n">
-        <v>98347</v>
+        <v>57631</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9182,42 +9171,54 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Knärot, Srm</t>
+          <t>Talltita, Srm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>686833</v>
+        <v>686999</v>
       </c>
       <c r="R74" t="n">
-        <v>6563215</v>
+        <v>6563293</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9254,7 +9255,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Hörde talltitan och hann se den för en kort ögonblick</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9263,7 +9264,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -9047,10 +9047,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122781008</v>
+        <v>122779259</v>
       </c>
       <c r="B73" t="n">
-        <v>98355</v>
+        <v>57631</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9059,42 +9059,54 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Knärot, Srm</t>
+          <t>Talltita, Srm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>686833</v>
+        <v>686999</v>
       </c>
       <c r="R73" t="n">
-        <v>6563215</v>
+        <v>6563293</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9131,7 +9143,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Hörde talltitan och hann se den för en kort ögonblick</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9140,7 +9152,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -9159,10 +9170,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122779259</v>
+        <v>122781008</v>
       </c>
       <c r="B74" t="n">
-        <v>57631</v>
+        <v>98357</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9171,54 +9182,42 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Talltita, Srm</t>
+          <t>Knärot, Srm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>686999</v>
+        <v>686833</v>
       </c>
       <c r="R74" t="n">
-        <v>6563293</v>
+        <v>6563215</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9255,7 +9254,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Hörde talltitan och hann se den för en kort ögonblick</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9264,6 +9263,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY74"/>
+  <dimension ref="A1:AY82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9280,6 +9280,947 @@
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>122930294</v>
+      </c>
+      <c r="B75" t="n">
+        <v>97311</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Norrby mosse, Srm</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>686824</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6562778</v>
+      </c>
+      <c r="S75" t="n">
+        <v>16</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>122929399</v>
+      </c>
+      <c r="B76" t="n">
+        <v>57494</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Norrby mosse, Srm</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>686567</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6562954</v>
+      </c>
+      <c r="S76" t="n">
+        <v>13</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>122930205</v>
+      </c>
+      <c r="B77" t="n">
+        <v>94878</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Norrby mosse, Srm</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>686779</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6562740</v>
+      </c>
+      <c r="S77" t="n">
+        <v>12</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>122929483</v>
+      </c>
+      <c r="B78" t="n">
+        <v>57494</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Norrby mosse, Srm</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>686592</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6562918</v>
+      </c>
+      <c r="S78" t="n">
+        <v>22</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>122930166</v>
+      </c>
+      <c r="B79" t="n">
+        <v>94974</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>210</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Norrby mosse, Srm</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>686762</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6562715</v>
+      </c>
+      <c r="S79" t="n">
+        <v>21</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>122928987</v>
+      </c>
+      <c r="B80" t="n">
+        <v>97311</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Norrby mosse, Srm</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>686389</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6562967</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>122929535</v>
+      </c>
+      <c r="B81" t="n">
+        <v>8441</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Norrby mosse, Srm</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>686612</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6562882</v>
+      </c>
+      <c r="S81" t="n">
+        <v>9</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>122929342</v>
+      </c>
+      <c r="B82" t="n">
+        <v>97314</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Norrby mosse, Srm</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>686569</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6562949</v>
+      </c>
+      <c r="S82" t="n">
+        <v>12</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY82"/>
+  <dimension ref="A1:AY83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9870,10 +9870,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122928987</v>
+        <v>122929535</v>
       </c>
       <c r="B80" t="n">
-        <v>97311</v>
+        <v>8441</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9886,27 +9886,32 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -9914,13 +9919,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>686389</v>
+        <v>686612</v>
       </c>
       <c r="R80" t="n">
-        <v>6562967</v>
+        <v>6562882</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9949,7 +9954,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9959,7 +9964,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9986,10 +9991,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122929535</v>
+        <v>122928987</v>
       </c>
       <c r="B81" t="n">
-        <v>8441</v>
+        <v>97311</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10002,32 +10007,27 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>106545</v>
+        <v>221945</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -10035,13 +10035,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>686612</v>
+        <v>686389</v>
       </c>
       <c r="R81" t="n">
-        <v>6562882</v>
+        <v>6562967</v>
       </c>
       <c r="S81" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10070,7 +10070,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10080,7 +10080,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10221,6 +10221,121 @@
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>122988731</v>
+      </c>
+      <c r="B83" t="n">
+        <v>56688</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Norrby mosse, Tyresta naturreservat, Haninge, Srm</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>686859</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6563274</v>
+      </c>
+      <c r="S83" t="n">
+        <v>50</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Uppe på berget SO om mossen.</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Mats Gothnier</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Mats Gothnier</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -9282,7 +9282,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122930294</v>
+        <v>122928987</v>
       </c>
       <c r="B75" t="n">
         <v>97311</v>
@@ -9326,13 +9326,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>686824</v>
+        <v>686389</v>
       </c>
       <c r="R75" t="n">
-        <v>6562778</v>
+        <v>6562967</v>
       </c>
       <c r="S75" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9398,10 +9398,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122929399</v>
+        <v>122930294</v>
       </c>
       <c r="B76" t="n">
-        <v>57494</v>
+        <v>97311</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9410,35 +9410,31 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -9446,13 +9442,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>686567</v>
+        <v>686824</v>
       </c>
       <c r="R76" t="n">
-        <v>6562954</v>
+        <v>6562778</v>
       </c>
       <c r="S76" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9481,7 +9477,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9491,7 +9487,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9518,10 +9514,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122930205</v>
+        <v>122929342</v>
       </c>
       <c r="B77" t="n">
-        <v>94878</v>
+        <v>97314</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9534,21 +9530,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2818</v>
+        <v>221946</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9562,10 +9558,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>686779</v>
+        <v>686569</v>
       </c>
       <c r="R77" t="n">
-        <v>6562740</v>
+        <v>6562949</v>
       </c>
       <c r="S77" t="n">
         <v>12</v>
@@ -9597,7 +9593,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9607,7 +9603,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9634,10 +9630,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122929483</v>
+        <v>122929535</v>
       </c>
       <c r="B78" t="n">
-        <v>57494</v>
+        <v>8441</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9646,25 +9642,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -9672,6 +9668,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr"/>
@@ -9682,13 +9679,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>686592</v>
+        <v>686612</v>
       </c>
       <c r="R78" t="n">
-        <v>6562918</v>
+        <v>6562882</v>
       </c>
       <c r="S78" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9717,7 +9714,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9727,7 +9724,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9754,10 +9751,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122930166</v>
+        <v>122930205</v>
       </c>
       <c r="B79" t="n">
-        <v>94974</v>
+        <v>94878</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9770,21 +9767,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9798,13 +9795,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>686762</v>
+        <v>686779</v>
       </c>
       <c r="R79" t="n">
-        <v>6562715</v>
+        <v>6562740</v>
       </c>
       <c r="S79" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9833,7 +9830,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9843,7 +9840,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9870,10 +9867,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122929535</v>
+        <v>122929399</v>
       </c>
       <c r="B80" t="n">
-        <v>8441</v>
+        <v>57494</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9882,25 +9879,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -9908,7 +9905,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr"/>
@@ -9919,13 +9915,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>686612</v>
+        <v>686567</v>
       </c>
       <c r="R80" t="n">
-        <v>6562882</v>
+        <v>6562954</v>
       </c>
       <c r="S80" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9954,7 +9950,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9964,7 +9960,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9991,10 +9987,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122928987</v>
+        <v>122930166</v>
       </c>
       <c r="B81" t="n">
-        <v>97311</v>
+        <v>94974</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10007,21 +10003,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221945</v>
+        <v>210</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -10035,13 +10031,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>686389</v>
+        <v>686762</v>
       </c>
       <c r="R81" t="n">
-        <v>6562967</v>
+        <v>6562715</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10070,7 +10066,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10080,7 +10076,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10107,10 +10103,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122929342</v>
+        <v>122929483</v>
       </c>
       <c r="B82" t="n">
-        <v>97314</v>
+        <v>57494</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10119,31 +10115,35 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>221946</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -10151,13 +10151,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>686569</v>
+        <v>686592</v>
       </c>
       <c r="R82" t="n">
-        <v>6562949</v>
+        <v>6562918</v>
       </c>
       <c r="S82" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10196,7 +10196,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD82" t="b">

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -9751,10 +9751,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122930205</v>
+        <v>122929399</v>
       </c>
       <c r="B79" t="n">
-        <v>94878</v>
+        <v>57494</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9763,31 +9763,35 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2818</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -9795,13 +9799,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>686779</v>
+        <v>686567</v>
       </c>
       <c r="R79" t="n">
-        <v>6562740</v>
+        <v>6562954</v>
       </c>
       <c r="S79" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9830,7 +9834,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9840,7 +9844,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9867,7 +9871,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122929399</v>
+        <v>122929483</v>
       </c>
       <c r="B80" t="n">
         <v>57494</v>
@@ -9915,13 +9919,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>686567</v>
+        <v>686592</v>
       </c>
       <c r="R80" t="n">
-        <v>6562954</v>
+        <v>6562918</v>
       </c>
       <c r="S80" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9950,7 +9954,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9960,7 +9964,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9987,10 +9991,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122930166</v>
+        <v>122988731</v>
       </c>
       <c r="B81" t="n">
-        <v>94974</v>
+        <v>56688</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10003,41 +10007,45 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>210</v>
+        <v>100138</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Norrby mosse, Srm</t>
+          <t>Norrby mosse, Tyresta naturreservat, Haninge, Srm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>686762</v>
+        <v>686859</v>
       </c>
       <c r="R81" t="n">
-        <v>6562715</v>
+        <v>6563274</v>
       </c>
       <c r="S81" t="n">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10061,22 +10069,17 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>11:21</t>
+          <t>2025-03-08</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>11:21</t>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Uppe på berget SO om mossen.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10091,59 +10094,55 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Mats Gothnier</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Mats Gothnier</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122929483</v>
+        <v>122930166</v>
       </c>
       <c r="B82" t="n">
-        <v>57494</v>
+        <v>94974</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
+        <v>210</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -10151,13 +10150,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>686592</v>
+        <v>686762</v>
       </c>
       <c r="R82" t="n">
-        <v>6562918</v>
+        <v>6562715</v>
       </c>
       <c r="S82" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10186,7 +10185,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10196,7 +10195,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10223,14 +10222,14 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122988731</v>
+        <v>122930205</v>
       </c>
       <c r="B83" t="n">
-        <v>56688</v>
+        <v>94878</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -10239,45 +10238,41 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100138</v>
+        <v>2818</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Norrby mosse, Tyresta naturreservat, Haninge, Srm</t>
+          <t>Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>686859</v>
+        <v>686779</v>
       </c>
       <c r="R83" t="n">
-        <v>6563274</v>
+        <v>6562740</v>
       </c>
       <c r="S83" t="n">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10301,17 +10296,22 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Uppe på berget SO om mossen.</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10326,12 +10326,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Mats Gothnier</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Mats Gothnier</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -9047,10 +9047,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122779259</v>
+        <v>122781008</v>
       </c>
       <c r="B73" t="n">
-        <v>57631</v>
+        <v>98365</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9059,54 +9059,42 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Talltita, Srm</t>
+          <t>Knärot, Srm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>686999</v>
+        <v>686833</v>
       </c>
       <c r="R73" t="n">
-        <v>6563293</v>
+        <v>6563215</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9143,7 +9131,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Hörde talltitan och hann se den för en kort ögonblick</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9152,6 +9140,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -9170,10 +9159,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122781008</v>
+        <v>122779259</v>
       </c>
       <c r="B74" t="n">
-        <v>98357</v>
+        <v>57631</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9182,42 +9171,54 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Knärot, Srm</t>
+          <t>Talltita, Srm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>686833</v>
+        <v>686999</v>
       </c>
       <c r="R74" t="n">
-        <v>6563215</v>
+        <v>6563293</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9254,7 +9255,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Hörde talltitan och hann se den för en kort ögonblick</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9263,7 +9264,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -9282,10 +9282,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122928987</v>
+        <v>122929483</v>
       </c>
       <c r="B75" t="n">
-        <v>97311</v>
+        <v>57494</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9294,31 +9294,35 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -9326,13 +9330,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>686389</v>
+        <v>686592</v>
       </c>
       <c r="R75" t="n">
-        <v>6562967</v>
+        <v>6562918</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9361,7 +9365,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9371,7 +9375,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9398,10 +9402,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122930294</v>
+        <v>122929535</v>
       </c>
       <c r="B76" t="n">
-        <v>97311</v>
+        <v>8441</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9414,27 +9418,32 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -9442,13 +9451,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>686824</v>
+        <v>686612</v>
       </c>
       <c r="R76" t="n">
-        <v>6562778</v>
+        <v>6562882</v>
       </c>
       <c r="S76" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9477,7 +9486,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9487,7 +9496,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9514,10 +9523,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122929342</v>
+        <v>122930294</v>
       </c>
       <c r="B77" t="n">
-        <v>97314</v>
+        <v>97319</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9530,16 +9539,16 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -9558,13 +9567,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>686569</v>
+        <v>686824</v>
       </c>
       <c r="R77" t="n">
-        <v>6562949</v>
+        <v>6562778</v>
       </c>
       <c r="S77" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9593,7 +9602,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9603,7 +9612,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9630,10 +9639,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122929535</v>
+        <v>122929399</v>
       </c>
       <c r="B78" t="n">
-        <v>8441</v>
+        <v>57494</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9642,25 +9651,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -9668,7 +9677,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr"/>
@@ -9679,13 +9687,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>686612</v>
+        <v>686567</v>
       </c>
       <c r="R78" t="n">
-        <v>6562882</v>
+        <v>6562954</v>
       </c>
       <c r="S78" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9714,7 +9722,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9724,7 +9732,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9751,10 +9759,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122929399</v>
+        <v>122929342</v>
       </c>
       <c r="B79" t="n">
-        <v>57494</v>
+        <v>97322</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9763,35 +9771,31 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>221946</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -9799,13 +9803,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>686567</v>
+        <v>686569</v>
       </c>
       <c r="R79" t="n">
-        <v>6562954</v>
+        <v>6562949</v>
       </c>
       <c r="S79" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9834,7 +9838,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9844,7 +9848,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9871,10 +9875,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122929483</v>
+        <v>122928987</v>
       </c>
       <c r="B80" t="n">
-        <v>57494</v>
+        <v>97319</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9883,35 +9887,31 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -9919,13 +9919,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>686592</v>
+        <v>686389</v>
       </c>
       <c r="R80" t="n">
-        <v>6562918</v>
+        <v>6562967</v>
       </c>
       <c r="S80" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9964,7 +9964,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10109,7 +10109,7 @@
         <v>122930166</v>
       </c>
       <c r="B82" t="n">
-        <v>94974</v>
+        <v>94982</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         <v>122930205</v>
       </c>
       <c r="B83" t="n">
-        <v>94878</v>
+        <v>94886</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -9047,10 +9047,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122781008</v>
+        <v>122779259</v>
       </c>
       <c r="B73" t="n">
-        <v>98365</v>
+        <v>57631</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9059,42 +9059,54 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Knärot, Srm</t>
+          <t>Talltita, Srm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>686833</v>
+        <v>686999</v>
       </c>
       <c r="R73" t="n">
-        <v>6563215</v>
+        <v>6563293</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9131,7 +9143,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Hörde talltitan och hann se den för en kort ögonblick</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9140,7 +9152,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -9159,10 +9170,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122779259</v>
+        <v>122781008</v>
       </c>
       <c r="B74" t="n">
-        <v>57631</v>
+        <v>98365</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9171,54 +9182,42 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Talltita, Srm</t>
+          <t>Knärot, Srm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>686999</v>
+        <v>686833</v>
       </c>
       <c r="R74" t="n">
-        <v>6563293</v>
+        <v>6563215</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9255,7 +9254,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Hörde talltitan och hann se den för en kort ögonblick</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9264,6 +9263,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -9282,10 +9282,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122929483</v>
+        <v>122929342</v>
       </c>
       <c r="B75" t="n">
-        <v>57494</v>
+        <v>97322</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9294,35 +9294,31 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>221946</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -9330,13 +9326,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>686592</v>
+        <v>686569</v>
       </c>
       <c r="R75" t="n">
-        <v>6562918</v>
+        <v>6562949</v>
       </c>
       <c r="S75" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9365,7 +9361,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9375,7 +9371,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9402,10 +9398,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122929535</v>
+        <v>122929399</v>
       </c>
       <c r="B76" t="n">
-        <v>8441</v>
+        <v>57494</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9414,25 +9410,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -9440,7 +9436,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
@@ -9451,13 +9446,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>686612</v>
+        <v>686567</v>
       </c>
       <c r="R76" t="n">
-        <v>6562882</v>
+        <v>6562954</v>
       </c>
       <c r="S76" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9486,7 +9481,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9496,7 +9491,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9523,7 +9518,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122930294</v>
+        <v>122928987</v>
       </c>
       <c r="B77" t="n">
         <v>97319</v>
@@ -9567,13 +9562,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>686824</v>
+        <v>686389</v>
       </c>
       <c r="R77" t="n">
-        <v>6562778</v>
+        <v>6562967</v>
       </c>
       <c r="S77" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9602,7 +9597,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9612,7 +9607,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9639,7 +9634,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122929399</v>
+        <v>122929483</v>
       </c>
       <c r="B78" t="n">
         <v>57494</v>
@@ -9687,13 +9682,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>686567</v>
+        <v>686592</v>
       </c>
       <c r="R78" t="n">
-        <v>6562954</v>
+        <v>6562918</v>
       </c>
       <c r="S78" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9722,7 +9717,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9732,7 +9727,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9759,10 +9754,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122929342</v>
+        <v>122930294</v>
       </c>
       <c r="B79" t="n">
-        <v>97322</v>
+        <v>97319</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9775,16 +9770,16 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -9803,13 +9798,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>686569</v>
+        <v>686824</v>
       </c>
       <c r="R79" t="n">
-        <v>6562949</v>
+        <v>6562778</v>
       </c>
       <c r="S79" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9838,7 +9833,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9848,7 +9843,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9875,10 +9870,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122928987</v>
+        <v>122929535</v>
       </c>
       <c r="B80" t="n">
-        <v>97319</v>
+        <v>8441</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9891,27 +9886,32 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -9919,13 +9919,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>686389</v>
+        <v>686612</v>
       </c>
       <c r="R80" t="n">
-        <v>6562967</v>
+        <v>6562882</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9964,7 +9964,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD80" t="b">

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -9282,10 +9282,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122929342</v>
+        <v>122929483</v>
       </c>
       <c r="B75" t="n">
-        <v>97322</v>
+        <v>57494</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9294,31 +9294,35 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221946</v>
+        <v>100049</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -9326,13 +9330,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>686569</v>
+        <v>686592</v>
       </c>
       <c r="R75" t="n">
-        <v>6562949</v>
+        <v>6562918</v>
       </c>
       <c r="S75" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9361,7 +9365,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9371,7 +9375,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9634,10 +9638,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122929483</v>
+        <v>122930294</v>
       </c>
       <c r="B78" t="n">
-        <v>57494</v>
+        <v>97319</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9646,35 +9650,31 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -9682,13 +9682,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>686592</v>
+        <v>686824</v>
       </c>
       <c r="R78" t="n">
-        <v>6562918</v>
+        <v>6562778</v>
       </c>
       <c r="S78" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9717,7 +9717,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9727,7 +9727,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9754,10 +9754,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122930294</v>
+        <v>122929535</v>
       </c>
       <c r="B79" t="n">
-        <v>97319</v>
+        <v>8441</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9770,27 +9770,32 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -9798,13 +9803,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>686824</v>
+        <v>686612</v>
       </c>
       <c r="R79" t="n">
-        <v>6562778</v>
+        <v>6562882</v>
       </c>
       <c r="S79" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9833,7 +9838,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9843,7 +9848,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9870,10 +9875,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122929535</v>
+        <v>122929342</v>
       </c>
       <c r="B80" t="n">
-        <v>8441</v>
+        <v>97322</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9886,32 +9891,27 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>106545</v>
+        <v>221946</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -9919,13 +9919,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>686612</v>
+        <v>686569</v>
       </c>
       <c r="R80" t="n">
-        <v>6562882</v>
+        <v>6562949</v>
       </c>
       <c r="S80" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9964,7 +9964,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD80" t="b">

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -9047,10 +9047,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122779259</v>
+        <v>122781008</v>
       </c>
       <c r="B73" t="n">
-        <v>57631</v>
+        <v>98365</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9059,54 +9059,42 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Talltita, Srm</t>
+          <t>Knärot, Srm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>686999</v>
+        <v>686833</v>
       </c>
       <c r="R73" t="n">
-        <v>6563293</v>
+        <v>6563215</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9143,7 +9131,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Hörde talltitan och hann se den för en kort ögonblick</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9152,6 +9140,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -9170,10 +9159,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122781008</v>
+        <v>122779259</v>
       </c>
       <c r="B74" t="n">
-        <v>98365</v>
+        <v>57631</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9182,42 +9171,54 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Knärot, Srm</t>
+          <t>Talltita, Srm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>686833</v>
+        <v>686999</v>
       </c>
       <c r="R74" t="n">
-        <v>6563215</v>
+        <v>6563293</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9254,7 +9255,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Hörde talltitan och hann se den för en kort ögonblick</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9263,7 +9264,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -9282,10 +9282,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122929483</v>
+        <v>122929535</v>
       </c>
       <c r="B75" t="n">
-        <v>57494</v>
+        <v>8441</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9294,25 +9294,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -9320,6 +9320,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
       <c r="M75" t="inlineStr"/>
@@ -9330,13 +9331,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>686592</v>
+        <v>686612</v>
       </c>
       <c r="R75" t="n">
-        <v>6562918</v>
+        <v>6562882</v>
       </c>
       <c r="S75" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9365,7 +9366,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9375,7 +9376,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9522,7 +9523,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122928987</v>
+        <v>122930294</v>
       </c>
       <c r="B77" t="n">
         <v>97319</v>
@@ -9566,13 +9567,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>686389</v>
+        <v>686824</v>
       </c>
       <c r="R77" t="n">
-        <v>6562967</v>
+        <v>6562778</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9601,7 +9602,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9611,7 +9612,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9638,10 +9639,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122930294</v>
+        <v>122929483</v>
       </c>
       <c r="B78" t="n">
-        <v>97319</v>
+        <v>57494</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9650,31 +9651,35 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -9682,13 +9687,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>686824</v>
+        <v>686592</v>
       </c>
       <c r="R78" t="n">
-        <v>6562778</v>
+        <v>6562918</v>
       </c>
       <c r="S78" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9717,7 +9722,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9727,7 +9732,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9754,10 +9759,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122929535</v>
+        <v>122929342</v>
       </c>
       <c r="B79" t="n">
-        <v>8441</v>
+        <v>97322</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9770,32 +9775,27 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>106545</v>
+        <v>221946</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -9803,13 +9803,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>686612</v>
+        <v>686569</v>
       </c>
       <c r="R79" t="n">
-        <v>6562882</v>
+        <v>6562949</v>
       </c>
       <c r="S79" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9838,7 +9838,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9848,7 +9848,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9875,10 +9875,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122929342</v>
+        <v>122928987</v>
       </c>
       <c r="B80" t="n">
-        <v>97322</v>
+        <v>97319</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9891,16 +9891,16 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -9919,13 +9919,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>686569</v>
+        <v>686389</v>
       </c>
       <c r="R80" t="n">
-        <v>6562949</v>
+        <v>6562967</v>
       </c>
       <c r="S80" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9964,7 +9964,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10106,10 +10106,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122930166</v>
+        <v>122930205</v>
       </c>
       <c r="B82" t="n">
-        <v>94982</v>
+        <v>94886</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10122,21 +10122,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -10150,13 +10150,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>686762</v>
+        <v>686779</v>
       </c>
       <c r="R82" t="n">
-        <v>6562715</v>
+        <v>6562740</v>
       </c>
       <c r="S82" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10185,7 +10185,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10222,10 +10222,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122930205</v>
+        <v>122930166</v>
       </c>
       <c r="B83" t="n">
-        <v>94886</v>
+        <v>94982</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10238,21 +10238,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10266,13 +10266,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>686779</v>
+        <v>686762</v>
       </c>
       <c r="R83" t="n">
-        <v>6562740</v>
+        <v>6562715</v>
       </c>
       <c r="S83" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10301,7 +10301,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10311,7 +10311,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD83" t="b">

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -8940,7 +8940,7 @@
         <v>122778162</v>
       </c>
       <c r="B72" t="n">
-        <v>57631</v>
+        <v>57634</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9050,7 +9050,7 @@
         <v>122781008</v>
       </c>
       <c r="B73" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9162,7 +9162,7 @@
         <v>122779259</v>
       </c>
       <c r="B74" t="n">
-        <v>57631</v>
+        <v>57634</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9282,10 +9282,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122929535</v>
+        <v>122929342</v>
       </c>
       <c r="B75" t="n">
-        <v>8441</v>
+        <v>97325</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9298,32 +9298,27 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>106545</v>
+        <v>221946</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -9331,13 +9326,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>686612</v>
+        <v>686569</v>
       </c>
       <c r="R75" t="n">
-        <v>6562882</v>
+        <v>6562949</v>
       </c>
       <c r="S75" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9366,7 +9361,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9376,7 +9371,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9403,10 +9398,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122929399</v>
+        <v>122930294</v>
       </c>
       <c r="B76" t="n">
-        <v>57494</v>
+        <v>97322</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9415,35 +9410,31 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -9451,13 +9442,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>686567</v>
+        <v>686824</v>
       </c>
       <c r="R76" t="n">
-        <v>6562954</v>
+        <v>6562778</v>
       </c>
       <c r="S76" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9486,7 +9477,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9496,7 +9487,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9523,10 +9514,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122930294</v>
+        <v>122928987</v>
       </c>
       <c r="B77" t="n">
-        <v>97319</v>
+        <v>97322</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9567,13 +9558,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>686824</v>
+        <v>686389</v>
       </c>
       <c r="R77" t="n">
-        <v>6562778</v>
+        <v>6562967</v>
       </c>
       <c r="S77" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9602,7 +9593,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9612,7 +9603,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9639,10 +9630,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122929483</v>
+        <v>122929535</v>
       </c>
       <c r="B78" t="n">
-        <v>57494</v>
+        <v>8441</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9651,25 +9642,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -9677,6 +9668,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr"/>
@@ -9687,13 +9679,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>686592</v>
+        <v>686612</v>
       </c>
       <c r="R78" t="n">
-        <v>6562918</v>
+        <v>6562882</v>
       </c>
       <c r="S78" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9722,7 +9714,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9732,7 +9724,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9759,10 +9751,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122929342</v>
+        <v>122929483</v>
       </c>
       <c r="B79" t="n">
-        <v>97322</v>
+        <v>57497</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9771,31 +9763,35 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221946</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -9803,13 +9799,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>686569</v>
+        <v>686592</v>
       </c>
       <c r="R79" t="n">
-        <v>6562949</v>
+        <v>6562918</v>
       </c>
       <c r="S79" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9838,7 +9834,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9848,7 +9844,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9875,10 +9871,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122928987</v>
+        <v>122929399</v>
       </c>
       <c r="B80" t="n">
-        <v>97319</v>
+        <v>57497</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9887,31 +9883,35 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -9919,13 +9919,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>686389</v>
+        <v>686567</v>
       </c>
       <c r="R80" t="n">
-        <v>6562967</v>
+        <v>6562954</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9964,7 +9964,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9994,7 +9994,7 @@
         <v>122988731</v>
       </c>
       <c r="B81" t="n">
-        <v>56688</v>
+        <v>56691</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10109,7 +10109,7 @@
         <v>122930205</v>
       </c>
       <c r="B82" t="n">
-        <v>94886</v>
+        <v>94889</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         <v>122930166</v>
       </c>
       <c r="B83" t="n">
-        <v>94982</v>
+        <v>94985</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -9050,7 +9050,7 @@
         <v>122781008</v>
       </c>
       <c r="B73" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9282,10 +9282,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122929342</v>
+        <v>122930294</v>
       </c>
       <c r="B75" t="n">
-        <v>97325</v>
+        <v>97324</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9298,16 +9298,16 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -9326,13 +9326,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>686569</v>
+        <v>686824</v>
       </c>
       <c r="R75" t="n">
-        <v>6562949</v>
+        <v>6562778</v>
       </c>
       <c r="S75" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9398,10 +9398,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122930294</v>
+        <v>122929535</v>
       </c>
       <c r="B76" t="n">
-        <v>97322</v>
+        <v>8441</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9414,27 +9414,32 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -9442,13 +9447,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>686824</v>
+        <v>686612</v>
       </c>
       <c r="R76" t="n">
-        <v>6562778</v>
+        <v>6562882</v>
       </c>
       <c r="S76" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9477,7 +9482,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9487,7 +9492,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9514,10 +9519,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122928987</v>
+        <v>122929342</v>
       </c>
       <c r="B77" t="n">
-        <v>97322</v>
+        <v>97327</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9530,16 +9535,16 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221945</v>
+        <v>221946</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -9558,13 +9563,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>686389</v>
+        <v>686569</v>
       </c>
       <c r="R77" t="n">
-        <v>6562967</v>
+        <v>6562949</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9593,7 +9598,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9603,7 +9608,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9630,10 +9635,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122929535</v>
+        <v>122929399</v>
       </c>
       <c r="B78" t="n">
-        <v>8441</v>
+        <v>57497</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9642,25 +9647,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -9668,7 +9673,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr"/>
@@ -9679,13 +9683,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>686612</v>
+        <v>686567</v>
       </c>
       <c r="R78" t="n">
-        <v>6562882</v>
+        <v>6562954</v>
       </c>
       <c r="S78" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9714,7 +9718,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9724,7 +9728,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9871,10 +9875,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122929399</v>
+        <v>122928987</v>
       </c>
       <c r="B80" t="n">
-        <v>57497</v>
+        <v>97324</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9883,35 +9887,31 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -9919,13 +9919,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>686567</v>
+        <v>686389</v>
       </c>
       <c r="R80" t="n">
-        <v>6562954</v>
+        <v>6562967</v>
       </c>
       <c r="S80" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9964,7 +9964,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10109,7 +10109,7 @@
         <v>122930205</v>
       </c>
       <c r="B82" t="n">
-        <v>94889</v>
+        <v>94891</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         <v>122930166</v>
       </c>
       <c r="B83" t="n">
-        <v>94985</v>
+        <v>94987</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -9050,7 +9050,7 @@
         <v>122781008</v>
       </c>
       <c r="B73" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9282,10 +9282,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122930294</v>
+        <v>122929342</v>
       </c>
       <c r="B75" t="n">
-        <v>97324</v>
+        <v>97333</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9298,16 +9298,16 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221945</v>
+        <v>221946</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -9326,13 +9326,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>686824</v>
+        <v>686569</v>
       </c>
       <c r="R75" t="n">
-        <v>6562778</v>
+        <v>6562949</v>
       </c>
       <c r="S75" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9398,10 +9398,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122929535</v>
+        <v>122930294</v>
       </c>
       <c r="B76" t="n">
-        <v>8441</v>
+        <v>97330</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9414,32 +9414,27 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>106545</v>
+        <v>221945</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -9447,13 +9442,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>686612</v>
+        <v>686824</v>
       </c>
       <c r="R76" t="n">
-        <v>6562882</v>
+        <v>6562778</v>
       </c>
       <c r="S76" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9482,7 +9477,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9492,7 +9487,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9519,10 +9514,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122929342</v>
+        <v>122929483</v>
       </c>
       <c r="B77" t="n">
-        <v>97327</v>
+        <v>57497</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9531,31 +9526,35 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221946</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -9563,13 +9562,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>686569</v>
+        <v>686592</v>
       </c>
       <c r="R77" t="n">
-        <v>6562949</v>
+        <v>6562918</v>
       </c>
       <c r="S77" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9598,7 +9597,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9608,7 +9607,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9635,10 +9634,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122929399</v>
+        <v>122929535</v>
       </c>
       <c r="B78" t="n">
-        <v>57497</v>
+        <v>8441</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9647,25 +9646,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -9673,6 +9672,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr"/>
@@ -9683,13 +9683,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>686567</v>
+        <v>686612</v>
       </c>
       <c r="R78" t="n">
-        <v>6562954</v>
+        <v>6562882</v>
       </c>
       <c r="S78" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9728,7 +9728,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9755,7 +9755,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122929483</v>
+        <v>122929399</v>
       </c>
       <c r="B79" t="n">
         <v>57497</v>
@@ -9803,13 +9803,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>686592</v>
+        <v>686567</v>
       </c>
       <c r="R79" t="n">
-        <v>6562918</v>
+        <v>6562954</v>
       </c>
       <c r="S79" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9838,7 +9838,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9848,7 +9848,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9878,7 +9878,7 @@
         <v>122928987</v>
       </c>
       <c r="B80" t="n">
-        <v>97324</v>
+        <v>97330</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10106,10 +10106,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122930205</v>
+        <v>122930166</v>
       </c>
       <c r="B82" t="n">
-        <v>94891</v>
+        <v>94993</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10122,21 +10122,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -10150,13 +10150,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>686779</v>
+        <v>686762</v>
       </c>
       <c r="R82" t="n">
-        <v>6562740</v>
+        <v>6562715</v>
       </c>
       <c r="S82" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10185,7 +10185,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10222,10 +10222,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122930166</v>
+        <v>122930205</v>
       </c>
       <c r="B83" t="n">
-        <v>94987</v>
+        <v>94897</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10238,21 +10238,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10266,13 +10266,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>686762</v>
+        <v>686779</v>
       </c>
       <c r="R83" t="n">
-        <v>6562715</v>
+        <v>6562740</v>
       </c>
       <c r="S83" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10301,7 +10301,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10311,7 +10311,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD83" t="b">

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -9282,10 +9282,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122929342</v>
+        <v>122928987</v>
       </c>
       <c r="B75" t="n">
-        <v>97336</v>
+        <v>97350</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9298,16 +9298,16 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -9326,13 +9326,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>686569</v>
+        <v>686389</v>
       </c>
       <c r="R75" t="n">
-        <v>6562949</v>
+        <v>6562967</v>
       </c>
       <c r="S75" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9398,10 +9398,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122929535</v>
+        <v>122929483</v>
       </c>
       <c r="B76" t="n">
-        <v>8441</v>
+        <v>57503</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9410,25 +9410,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -9436,7 +9436,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
@@ -9447,13 +9446,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>686612</v>
+        <v>686592</v>
       </c>
       <c r="R76" t="n">
-        <v>6562882</v>
+        <v>6562918</v>
       </c>
       <c r="S76" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9482,7 +9481,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9492,7 +9491,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9519,10 +9518,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122929399</v>
+        <v>122929342</v>
       </c>
       <c r="B77" t="n">
-        <v>57497</v>
+        <v>97353</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9531,35 +9530,31 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100049</v>
+        <v>221946</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -9567,13 +9562,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>686567</v>
+        <v>686569</v>
       </c>
       <c r="R77" t="n">
-        <v>6562954</v>
+        <v>6562949</v>
       </c>
       <c r="S77" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9602,7 +9597,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9612,7 +9607,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9639,10 +9634,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122929483</v>
+        <v>122929399</v>
       </c>
       <c r="B78" t="n">
-        <v>57497</v>
+        <v>57503</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9687,13 +9682,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>686592</v>
+        <v>686567</v>
       </c>
       <c r="R78" t="n">
-        <v>6562918</v>
+        <v>6562954</v>
       </c>
       <c r="S78" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9722,7 +9717,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9732,7 +9727,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9759,10 +9754,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122930294</v>
+        <v>122929535</v>
       </c>
       <c r="B79" t="n">
-        <v>97333</v>
+        <v>8445</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9775,27 +9770,32 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -9803,13 +9803,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>686824</v>
+        <v>686612</v>
       </c>
       <c r="R79" t="n">
-        <v>6562778</v>
+        <v>6562882</v>
       </c>
       <c r="S79" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9838,7 +9838,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9848,7 +9848,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9875,10 +9875,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122928987</v>
+        <v>122930294</v>
       </c>
       <c r="B80" t="n">
-        <v>97333</v>
+        <v>97350</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9919,13 +9919,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>686389</v>
+        <v>686824</v>
       </c>
       <c r="R80" t="n">
-        <v>6562967</v>
+        <v>6562778</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9964,7 +9964,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9994,7 +9994,7 @@
         <v>122988731</v>
       </c>
       <c r="B81" t="n">
-        <v>56691</v>
+        <v>56697</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10106,10 +10106,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122930166</v>
+        <v>122930205</v>
       </c>
       <c r="B82" t="n">
-        <v>94996</v>
+        <v>94917</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10122,21 +10122,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -10150,13 +10150,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>686762</v>
+        <v>686779</v>
       </c>
       <c r="R82" t="n">
-        <v>6562715</v>
+        <v>6562740</v>
       </c>
       <c r="S82" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10185,7 +10185,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10222,10 +10222,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122930205</v>
+        <v>122930166</v>
       </c>
       <c r="B83" t="n">
-        <v>94900</v>
+        <v>95013</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10238,21 +10238,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10266,13 +10266,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>686779</v>
+        <v>686762</v>
       </c>
       <c r="R83" t="n">
-        <v>6562740</v>
+        <v>6562715</v>
       </c>
       <c r="S83" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10301,7 +10301,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10311,7 +10311,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD83" t="b">

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -9398,10 +9398,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122929483</v>
+        <v>122929342</v>
       </c>
       <c r="B76" t="n">
-        <v>57503</v>
+        <v>97353</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9410,35 +9410,31 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>221946</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -9446,13 +9442,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>686592</v>
+        <v>686569</v>
       </c>
       <c r="R76" t="n">
-        <v>6562918</v>
+        <v>6562949</v>
       </c>
       <c r="S76" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9481,7 +9477,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9491,7 +9487,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9518,10 +9514,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122929342</v>
+        <v>122929483</v>
       </c>
       <c r="B77" t="n">
-        <v>97353</v>
+        <v>57503</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9530,31 +9526,35 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221946</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -9562,13 +9562,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>686569</v>
+        <v>686592</v>
       </c>
       <c r="R77" t="n">
-        <v>6562949</v>
+        <v>6562918</v>
       </c>
       <c r="S77" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9607,7 +9607,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD77" t="b">

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -10106,10 +10106,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122930205</v>
+        <v>122930166</v>
       </c>
       <c r="B82" t="n">
-        <v>94917</v>
+        <v>95019</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10122,21 +10122,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -10150,13 +10150,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>686779</v>
+        <v>686762</v>
       </c>
       <c r="R82" t="n">
-        <v>6562740</v>
+        <v>6562715</v>
       </c>
       <c r="S82" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10185,7 +10185,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10222,10 +10222,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122930166</v>
+        <v>122930205</v>
       </c>
       <c r="B83" t="n">
-        <v>95013</v>
+        <v>94923</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10238,21 +10238,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10266,13 +10266,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>686762</v>
+        <v>686779</v>
       </c>
       <c r="R83" t="n">
-        <v>6562715</v>
+        <v>6562740</v>
       </c>
       <c r="S83" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10301,7 +10301,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10311,7 +10311,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD83" t="b">

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -10109,7 +10109,7 @@
         <v>122930166</v>
       </c>
       <c r="B82" t="n">
-        <v>95019</v>
+        <v>95021</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         <v>122930205</v>
       </c>
       <c r="B83" t="n">
-        <v>94923</v>
+        <v>94925</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY83"/>
+  <dimension ref="A1:AY85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10336,6 +10336,200 @@
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>125965889</v>
+      </c>
+      <c r="B84" t="n">
+        <v>105355</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Ungfars kärr, Ungfars kärr, Srm</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>687076</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6563220</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Måns Persson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Måns Persson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>125963374</v>
+      </c>
+      <c r="B85" t="n">
+        <v>97209</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Norrby mosse, Norrby mosse, Srm</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>686873</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6562867</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Måns Persson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Måns Persson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY85"/>
+  <dimension ref="A1:AY88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10530,6 +10530,312 @@
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>126003792</v>
+      </c>
+      <c r="B86" t="n">
+        <v>98248</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>687046</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6563346</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>126005160</v>
+      </c>
+      <c r="B87" t="n">
+        <v>98248</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>687034</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6563204</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF87" t="inlineStr"/>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>126003574</v>
+      </c>
+      <c r="B88" t="n">
+        <v>105355</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>SO Norrby Mosse, Srm</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>686803</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6563098</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF88" t="inlineStr"/>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -10341,7 +10341,7 @@
         <v>125965889</v>
       </c>
       <c r="B84" t="n">
-        <v>105355</v>
+        <v>105356</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>125963374</v>
       </c>
       <c r="B85" t="n">
-        <v>97209</v>
+        <v>97210</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10535,7 +10535,7 @@
         <v>126003792</v>
       </c>
       <c r="B86" t="n">
-        <v>98248</v>
+        <v>98249</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10637,7 +10637,7 @@
         <v>126005160</v>
       </c>
       <c r="B87" t="n">
-        <v>98248</v>
+        <v>98249</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10739,7 +10739,7 @@
         <v>126003574</v>
       </c>
       <c r="B88" t="n">
-        <v>105355</v>
+        <v>105356</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY88"/>
+  <dimension ref="A1:AY110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10341,7 +10341,7 @@
         <v>125965889</v>
       </c>
       <c r="B84" t="n">
-        <v>105356</v>
+        <v>105358</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>125963374</v>
       </c>
       <c r="B85" t="n">
-        <v>97210</v>
+        <v>97212</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10535,7 +10535,7 @@
         <v>126003792</v>
       </c>
       <c r="B86" t="n">
-        <v>98249</v>
+        <v>98251</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10637,7 +10637,7 @@
         <v>126005160</v>
       </c>
       <c r="B87" t="n">
-        <v>98249</v>
+        <v>98251</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10739,7 +10739,7 @@
         <v>126003574</v>
       </c>
       <c r="B88" t="n">
-        <v>105356</v>
+        <v>105358</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10836,6 +10836,2565 @@
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>126061087</v>
+      </c>
+      <c r="B89" t="n">
+        <v>5176</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Ö Tyresta by, Srm</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>686865</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6562977</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL89" t="inlineStr">
+        <is>
+          <t>Klen torr granlåga.</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>Picea abies # Klen torr granlåga.</t>
+        </is>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>126061104</v>
+      </c>
+      <c r="B90" t="n">
+        <v>4772</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Ö Tyresta by, Srm</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>686868</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6562739</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL90" t="inlineStr">
+        <is>
+          <t>Stående död gran.</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>Picea abies # Stående död gran.</t>
+        </is>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>126061079</v>
+      </c>
+      <c r="B91" t="n">
+        <v>105358</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Ö Tyresta by, Srm</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>687082</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6563241</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>126061106</v>
+      </c>
+      <c r="B92" t="n">
+        <v>90663</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>2008</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Fyrflikig jordstjärna</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Geastrum quadrifidum</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Ö Tyresta by, Srm</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>686883</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6562742</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>126061084</v>
+      </c>
+      <c r="B93" t="n">
+        <v>98251</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Ö Tyresta by, Srm</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>687014</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6563215</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>126061094</v>
+      </c>
+      <c r="B94" t="n">
+        <v>98238</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Ö Tyresta by, Srm</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>686866</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6562874</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>126061099</v>
+      </c>
+      <c r="B95" t="n">
+        <v>98251</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Ö Tyresta by, Srm</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>686857</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6562875</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>126061081</v>
+      </c>
+      <c r="B96" t="n">
+        <v>58506</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Ö Tyresta by, Srm</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>687058</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6563228</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>126061105</v>
+      </c>
+      <c r="B97" t="n">
+        <v>8436</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Ö Tyresta by, Srm</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>686860</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6562743</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>126061113</v>
+      </c>
+      <c r="B98" t="n">
+        <v>95783</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>210</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Ö Tyresta by, Srm</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>687032</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6562726</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>126061102</v>
+      </c>
+      <c r="B99" t="n">
+        <v>98251</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Ö Tyresta by, Srm</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>686837</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6562829</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>126061086</v>
+      </c>
+      <c r="B100" t="n">
+        <v>8436</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Ö Tyresta by, Srm</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>686932</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6563067</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AL100" t="inlineStr">
+        <is>
+          <t>Barklös björklåga.</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>Betula # Barklös björklåga.</t>
+        </is>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>126061082</v>
+      </c>
+      <c r="B101" t="n">
+        <v>97212</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Ö Tyresta by, Srm</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>687079</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6563240</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>126061088</v>
+      </c>
+      <c r="B102" t="n">
+        <v>5196</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Ö Tyresta by, Srm</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>686865</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6562977</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL102" t="inlineStr">
+        <is>
+          <t>Klen torr granlåga.</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>Picea abies # Klen torr granlåga.</t>
+        </is>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>126061112</v>
+      </c>
+      <c r="B103" t="n">
+        <v>91246</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Ö Tyresta by, Srm</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>687032</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6562719</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL103" t="inlineStr">
+        <is>
+          <t>På barken och grenarna på en granlåga.</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>Picea abies # På barken och grenarna på en granlåga.</t>
+        </is>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>126061078</v>
+      </c>
+      <c r="B104" t="n">
+        <v>105358</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Ö Tyresta by, Srm</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>687085</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6563229</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>126061108</v>
+      </c>
+      <c r="B105" t="n">
+        <v>58508</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Ö Tyresta by, Srm</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>686907</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6562760</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>126061109</v>
+      </c>
+      <c r="B106" t="n">
+        <v>5196</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Ö Tyresta by, Srm</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>686946</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6562741</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL106" t="inlineStr">
+        <is>
+          <t>Klen torr granlåga.</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>Picea abies # Klen torr granlåga.</t>
+        </is>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>126061098</v>
+      </c>
+      <c r="B107" t="n">
+        <v>58480</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Ö Tyresta by, Srm</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>686857</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6562875</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>126061100</v>
+      </c>
+      <c r="B108" t="n">
+        <v>98238</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Ö Tyresta by, Srm</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>686857</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6562875</v>
+      </c>
+      <c r="S108" t="n">
+        <v>10</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>126061114</v>
+      </c>
+      <c r="B109" t="n">
+        <v>95687</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Ö Tyresta by, Srm</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>686985</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6562729</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>126061107</v>
+      </c>
+      <c r="B110" t="n">
+        <v>95687</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Ö Tyresta by, Srm</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>686880</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6562745</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -10341,7 +10341,7 @@
         <v>125965889</v>
       </c>
       <c r="B84" t="n">
-        <v>105358</v>
+        <v>105362</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>125963374</v>
       </c>
       <c r="B85" t="n">
-        <v>97212</v>
+        <v>97216</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10535,7 +10535,7 @@
         <v>126003792</v>
       </c>
       <c r="B86" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10637,7 +10637,7 @@
         <v>126005160</v>
       </c>
       <c r="B87" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10739,7 +10739,7 @@
         <v>126003574</v>
       </c>
       <c r="B88" t="n">
-        <v>105358</v>
+        <v>105362</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11092,32 +11092,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126061079</v>
+        <v>126061106</v>
       </c>
       <c r="B91" t="n">
-        <v>105358</v>
+        <v>90667</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221144</v>
+        <v>2008</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -11127,10 +11127,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>687082</v>
+        <v>686883</v>
       </c>
       <c r="R91" t="n">
-        <v>6563241</v>
+        <v>6562742</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11162,7 +11162,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11172,7 +11172,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11192,39 +11192,39 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126061106</v>
+        <v>126061079</v>
       </c>
       <c r="B92" t="n">
-        <v>90663</v>
+        <v>105362</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2008</v>
+        <v>221144</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -11234,10 +11234,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>686883</v>
+        <v>687082</v>
       </c>
       <c r="R92" t="n">
-        <v>6562742</v>
+        <v>6563241</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11269,7 +11269,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11279,7 +11279,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11299,17 +11299,17 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126061084</v>
+        <v>126061094</v>
       </c>
       <c r="B93" t="n">
-        <v>98251</v>
+        <v>98242</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11317,34 +11317,43 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>219790</v>
+        <v>220093</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>687014</v>
+        <v>686866</v>
       </c>
       <c r="R93" t="n">
-        <v>6563215</v>
+        <v>6562874</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11376,7 +11385,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11386,7 +11395,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11406,17 +11415,17 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126061094</v>
+        <v>126061084</v>
       </c>
       <c r="B94" t="n">
-        <v>98238</v>
+        <v>98255</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11424,43 +11433,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220093</v>
+        <v>219790</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>686866</v>
+        <v>687014</v>
       </c>
       <c r="R94" t="n">
-        <v>6562874</v>
+        <v>6563215</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11492,7 +11492,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11502,7 +11502,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11522,17 +11522,17 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126061099</v>
+        <v>126061081</v>
       </c>
       <c r="B95" t="n">
-        <v>98251</v>
+        <v>58506</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11540,34 +11540,48 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>219790</v>
+        <v>208250</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>686857</v>
+        <v>687058</v>
       </c>
       <c r="R95" t="n">
-        <v>6562875</v>
+        <v>6563228</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11599,7 +11613,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11609,7 +11623,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11629,17 +11643,17 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126061081</v>
+        <v>126061099</v>
       </c>
       <c r="B96" t="n">
-        <v>58506</v>
+        <v>98255</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11647,48 +11661,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>208250</v>
+        <v>219790</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>687058</v>
+        <v>686857</v>
       </c>
       <c r="R96" t="n">
-        <v>6563228</v>
+        <v>6562875</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11720,7 +11720,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11730,7 +11730,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11750,17 +11750,17 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126061105</v>
+        <v>126061113</v>
       </c>
       <c r="B97" t="n">
-        <v>8436</v>
+        <v>95787</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11768,34 +11768,43 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>106554</v>
+        <v>210</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>686860</v>
+        <v>687032</v>
       </c>
       <c r="R97" t="n">
-        <v>6562743</v>
+        <v>6562726</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11827,7 +11836,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11837,7 +11846,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11851,17 +11860,17 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -11879,10 +11888,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126061113</v>
+        <v>126061105</v>
       </c>
       <c r="B98" t="n">
-        <v>95783</v>
+        <v>8436</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11890,43 +11899,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>210</v>
+        <v>106554</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>687032</v>
+        <v>686860</v>
       </c>
       <c r="R98" t="n">
-        <v>6562726</v>
+        <v>6562743</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11958,7 +11958,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11968,7 +11968,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11982,17 +11982,17 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -12013,7 +12013,7 @@
         <v>126061102</v>
       </c>
       <c r="B99" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12247,7 +12247,7 @@
         <v>126061082</v>
       </c>
       <c r="B101" t="n">
-        <v>97212</v>
+        <v>97216</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12481,7 +12481,7 @@
         <v>126061112</v>
       </c>
       <c r="B103" t="n">
-        <v>91246</v>
+        <v>91250</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12608,7 +12608,7 @@
         <v>126061078</v>
       </c>
       <c r="B104" t="n">
-        <v>105358</v>
+        <v>105362</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12833,10 +12833,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126061109</v>
+        <v>126061098</v>
       </c>
       <c r="B106" t="n">
-        <v>5196</v>
+        <v>58480</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12844,16 +12844,16 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>105930</v>
+        <v>208245</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -12868,10 +12868,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>686946</v>
+        <v>686857</v>
       </c>
       <c r="R106" t="n">
-        <v>6562741</v>
+        <v>6562875</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12903,7 +12903,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12913,7 +12913,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12924,26 +12924,6 @@
       </c>
       <c r="AG106" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ106" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK106" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL106" t="inlineStr">
-        <is>
-          <t>Klen torr granlåga.</t>
-        </is>
-      </c>
-      <c r="AO106" t="inlineStr">
-        <is>
-          <t>Picea abies # Klen torr granlåga.</t>
-        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
@@ -12960,10 +12940,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126061098</v>
+        <v>126061100</v>
       </c>
       <c r="B107" t="n">
-        <v>58480</v>
+        <v>98242</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12971,24 +12951,33 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>208245</v>
+        <v>220093</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
@@ -13067,10 +13056,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126061100</v>
+        <v>126061109</v>
       </c>
       <c r="B108" t="n">
-        <v>98238</v>
+        <v>5196</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13078,43 +13067,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220093</v>
+        <v>105930</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>686857</v>
+        <v>686946</v>
       </c>
       <c r="R108" t="n">
-        <v>6562875</v>
+        <v>6562741</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13146,7 +13126,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -13156,7 +13136,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13167,6 +13147,26 @@
       </c>
       <c r="AG108" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL108" t="inlineStr">
+        <is>
+          <t>Klen torr granlåga.</t>
+        </is>
+      </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>Picea abies # Klen torr granlåga.</t>
+        </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
@@ -13186,7 +13186,7 @@
         <v>126061114</v>
       </c>
       <c r="B109" t="n">
-        <v>95687</v>
+        <v>95691</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         <v>126061107</v>
       </c>
       <c r="B110" t="n">
-        <v>95687</v>
+        <v>95691</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -11092,32 +11092,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126061106</v>
+        <v>126061079</v>
       </c>
       <c r="B91" t="n">
-        <v>90667</v>
+        <v>105362</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2008</v>
+        <v>221144</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -11127,10 +11127,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>686883</v>
+        <v>687082</v>
       </c>
       <c r="R91" t="n">
-        <v>6562742</v>
+        <v>6563241</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11162,7 +11162,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11172,7 +11172,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11192,39 +11192,39 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126061079</v>
+        <v>126061106</v>
       </c>
       <c r="B92" t="n">
-        <v>105362</v>
+        <v>90667</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>221144</v>
+        <v>2008</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -11234,10 +11234,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>687082</v>
+        <v>686883</v>
       </c>
       <c r="R92" t="n">
-        <v>6563241</v>
+        <v>6562742</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11269,7 +11269,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11279,7 +11279,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11299,7 +11299,7 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -12833,10 +12833,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126061098</v>
+        <v>126061100</v>
       </c>
       <c r="B106" t="n">
-        <v>58480</v>
+        <v>98242</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12844,24 +12844,33 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>208245</v>
+        <v>220093</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
@@ -12940,10 +12949,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126061100</v>
+        <v>126061098</v>
       </c>
       <c r="B107" t="n">
-        <v>98242</v>
+        <v>58480</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12951,33 +12960,24 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>220093</v>
+        <v>208245</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -10341,7 +10341,7 @@
         <v>125965889</v>
       </c>
       <c r="B84" t="n">
-        <v>105362</v>
+        <v>105363</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>125963374</v>
       </c>
       <c r="B85" t="n">
-        <v>97216</v>
+        <v>97217</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10535,7 +10535,7 @@
         <v>126003792</v>
       </c>
       <c r="B86" t="n">
-        <v>98255</v>
+        <v>98256</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10637,7 +10637,7 @@
         <v>126005160</v>
       </c>
       <c r="B87" t="n">
-        <v>98255</v>
+        <v>98256</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10739,7 +10739,7 @@
         <v>126003574</v>
       </c>
       <c r="B88" t="n">
-        <v>105362</v>
+        <v>105363</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11085,7 +11085,7 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
@@ -11095,7 +11095,7 @@
         <v>126061079</v>
       </c>
       <c r="B91" t="n">
-        <v>105362</v>
+        <v>105363</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11299,7 +11299,7 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -11309,7 +11309,7 @@
         <v>126061094</v>
       </c>
       <c r="B93" t="n">
-        <v>98242</v>
+        <v>98243</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11425,7 +11425,7 @@
         <v>126061084</v>
       </c>
       <c r="B94" t="n">
-        <v>98255</v>
+        <v>98256</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11529,10 +11529,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126061081</v>
+        <v>126061099</v>
       </c>
       <c r="B95" t="n">
-        <v>58506</v>
+        <v>98256</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11540,48 +11540,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>208250</v>
+        <v>219790</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>687058</v>
+        <v>686857</v>
       </c>
       <c r="R95" t="n">
-        <v>6563228</v>
+        <v>6562875</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11613,7 +11599,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11623,7 +11609,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11643,17 +11629,17 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126061099</v>
+        <v>126061081</v>
       </c>
       <c r="B96" t="n">
-        <v>98255</v>
+        <v>58506</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11661,34 +11647,48 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>219790</v>
+        <v>208250</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>686857</v>
+        <v>687058</v>
       </c>
       <c r="R96" t="n">
-        <v>6562875</v>
+        <v>6563228</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11720,7 +11720,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11730,7 +11730,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11750,17 +11750,17 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126061113</v>
+        <v>126061105</v>
       </c>
       <c r="B97" t="n">
-        <v>95787</v>
+        <v>8436</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11768,43 +11768,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>210</v>
+        <v>106554</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>687032</v>
+        <v>686860</v>
       </c>
       <c r="R97" t="n">
-        <v>6562726</v>
+        <v>6562743</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11836,7 +11827,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11846,7 +11837,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11860,17 +11851,17 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -11881,17 +11872,17 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126061105</v>
+        <v>126061113</v>
       </c>
       <c r="B98" t="n">
-        <v>8436</v>
+        <v>95788</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11899,34 +11890,43 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>106554</v>
+        <v>210</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>686860</v>
+        <v>687032</v>
       </c>
       <c r="R98" t="n">
-        <v>6562743</v>
+        <v>6562726</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11958,7 +11958,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11968,7 +11968,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11982,17 +11982,17 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -12003,7 +12003,7 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
@@ -12013,7 +12013,7 @@
         <v>126061102</v>
       </c>
       <c r="B99" t="n">
-        <v>98255</v>
+        <v>98256</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12110,7 +12110,7 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
@@ -12247,7 +12247,7 @@
         <v>126061082</v>
       </c>
       <c r="B101" t="n">
-        <v>97216</v>
+        <v>97217</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12351,32 +12351,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126061088</v>
+        <v>126061112</v>
       </c>
       <c r="B102" t="n">
-        <v>5196</v>
+        <v>91250</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>105930</v>
+        <v>5432</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -12386,10 +12386,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>686865</v>
+        <v>687032</v>
       </c>
       <c r="R102" t="n">
-        <v>6562977</v>
+        <v>6562719</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12421,7 +12421,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12431,7 +12431,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12455,12 +12455,12 @@
       </c>
       <c r="AL102" t="inlineStr">
         <is>
-          <t>Klen torr granlåga.</t>
+          <t>På barken och grenarna på en granlåga.</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>Picea abies # Klen torr granlåga.</t>
+          <t>Picea abies # På barken och grenarna på en granlåga.</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -12471,39 +12471,39 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126061112</v>
+        <v>126061088</v>
       </c>
       <c r="B103" t="n">
-        <v>91250</v>
+        <v>5196</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5432</v>
+        <v>105930</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12513,10 +12513,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>687032</v>
+        <v>686865</v>
       </c>
       <c r="R103" t="n">
-        <v>6562719</v>
+        <v>6562977</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12548,7 +12548,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12558,7 +12558,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12582,12 +12582,12 @@
       </c>
       <c r="AL103" t="inlineStr">
         <is>
-          <t>På barken och grenarna på en granlåga.</t>
+          <t>Klen torr granlåga.</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>Picea abies # På barken och grenarna på en granlåga.</t>
+          <t>Picea abies # Klen torr granlåga.</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>
@@ -12598,7 +12598,7 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
@@ -12608,7 +12608,7 @@
         <v>126061078</v>
       </c>
       <c r="B104" t="n">
-        <v>105362</v>
+        <v>105363</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12826,7 +12826,7 @@
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
@@ -12836,7 +12836,7 @@
         <v>126061100</v>
       </c>
       <c r="B106" t="n">
-        <v>98242</v>
+        <v>98243</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12942,17 +12942,17 @@
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126061098</v>
+        <v>126061109</v>
       </c>
       <c r="B107" t="n">
-        <v>58480</v>
+        <v>5196</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12960,16 +12960,16 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>208245</v>
+        <v>105930</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -12984,10 +12984,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>686857</v>
+        <v>686946</v>
       </c>
       <c r="R107" t="n">
-        <v>6562875</v>
+        <v>6562741</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -13019,7 +13019,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -13029,7 +13029,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13040,6 +13040,26 @@
       </c>
       <c r="AG107" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL107" t="inlineStr">
+        <is>
+          <t>Klen torr granlåga.</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>Picea abies # Klen torr granlåga.</t>
+        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
@@ -13049,17 +13069,17 @@
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126061109</v>
+        <v>126061098</v>
       </c>
       <c r="B108" t="n">
-        <v>5196</v>
+        <v>58480</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13067,16 +13087,16 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>105930</v>
+        <v>208245</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -13091,10 +13111,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>686946</v>
+        <v>686857</v>
       </c>
       <c r="R108" t="n">
-        <v>6562741</v>
+        <v>6562875</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13126,7 +13146,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -13136,7 +13156,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13147,26 +13167,6 @@
       </c>
       <c r="AG108" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ108" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK108" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL108" t="inlineStr">
-        <is>
-          <t>Klen torr granlåga.</t>
-        </is>
-      </c>
-      <c r="AO108" t="inlineStr">
-        <is>
-          <t>Picea abies # Klen torr granlåga.</t>
-        </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
@@ -13176,7 +13176,7 @@
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
@@ -13186,7 +13186,7 @@
         <v>126061114</v>
       </c>
       <c r="B109" t="n">
-        <v>95691</v>
+        <v>95692</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
@@ -13293,7 +13293,7 @@
         <v>126061107</v>
       </c>
       <c r="B110" t="n">
-        <v>95691</v>
+        <v>95692</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13390,7 +13390,7 @@
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -11092,32 +11092,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126061079</v>
+        <v>126061106</v>
       </c>
       <c r="B91" t="n">
-        <v>105363</v>
+        <v>90667</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221144</v>
+        <v>2008</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -11127,10 +11127,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>687082</v>
+        <v>686883</v>
       </c>
       <c r="R91" t="n">
-        <v>6563241</v>
+        <v>6562742</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11162,7 +11162,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11172,7 +11172,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11192,39 +11192,39 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126061106</v>
+        <v>126061079</v>
       </c>
       <c r="B92" t="n">
-        <v>90667</v>
+        <v>105363</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2008</v>
+        <v>221144</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -11234,10 +11234,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>686883</v>
+        <v>687082</v>
       </c>
       <c r="R92" t="n">
-        <v>6562742</v>
+        <v>6563241</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11269,7 +11269,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11279,7 +11279,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11299,7 +11299,7 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -11529,10 +11529,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126061099</v>
+        <v>126061081</v>
       </c>
       <c r="B95" t="n">
-        <v>98256</v>
+        <v>58506</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11540,34 +11540,48 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>219790</v>
+        <v>208250</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>686857</v>
+        <v>687058</v>
       </c>
       <c r="R95" t="n">
-        <v>6562875</v>
+        <v>6563228</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11599,7 +11613,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11609,7 +11623,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11629,17 +11643,17 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126061081</v>
+        <v>126061099</v>
       </c>
       <c r="B96" t="n">
-        <v>58506</v>
+        <v>98256</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11647,48 +11661,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>208250</v>
+        <v>219790</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>687058</v>
+        <v>686857</v>
       </c>
       <c r="R96" t="n">
-        <v>6563228</v>
+        <v>6562875</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11720,7 +11720,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11730,7 +11730,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11750,17 +11750,17 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126061105</v>
+        <v>126061113</v>
       </c>
       <c r="B97" t="n">
-        <v>8436</v>
+        <v>95788</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11768,34 +11768,43 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>106554</v>
+        <v>210</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>686860</v>
+        <v>687032</v>
       </c>
       <c r="R97" t="n">
-        <v>6562743</v>
+        <v>6562726</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11827,7 +11836,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11837,7 +11846,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11851,17 +11860,17 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -11879,10 +11888,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126061113</v>
+        <v>126061105</v>
       </c>
       <c r="B98" t="n">
-        <v>95788</v>
+        <v>8436</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11890,43 +11899,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>210</v>
+        <v>106554</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>687032</v>
+        <v>686860</v>
       </c>
       <c r="R98" t="n">
-        <v>6562726</v>
+        <v>6562743</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11958,7 +11958,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11968,7 +11968,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11982,17 +11982,17 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -12833,10 +12833,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126061100</v>
+        <v>126061109</v>
       </c>
       <c r="B106" t="n">
-        <v>98243</v>
+        <v>5196</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12844,43 +12844,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220093</v>
+        <v>105930</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>686857</v>
+        <v>686946</v>
       </c>
       <c r="R106" t="n">
-        <v>6562875</v>
+        <v>6562741</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12912,7 +12903,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12922,7 +12913,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12933,6 +12924,26 @@
       </c>
       <c r="AG106" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL106" t="inlineStr">
+        <is>
+          <t>Klen torr granlåga.</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>Picea abies # Klen torr granlåga.</t>
+        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
@@ -12949,10 +12960,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126061109</v>
+        <v>126061100</v>
       </c>
       <c r="B107" t="n">
-        <v>5196</v>
+        <v>98243</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12960,34 +12971,43 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>105930</v>
+        <v>220093</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>686946</v>
+        <v>686857</v>
       </c>
       <c r="R107" t="n">
-        <v>6562741</v>
+        <v>6562875</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -13019,7 +13039,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -13029,7 +13049,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13040,26 +13060,6 @@
       </c>
       <c r="AG107" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ107" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK107" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL107" t="inlineStr">
-        <is>
-          <t>Klen torr granlåga.</t>
-        </is>
-      </c>
-      <c r="AO107" t="inlineStr">
-        <is>
-          <t>Picea abies # Klen torr granlåga.</t>
-        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -11529,10 +11529,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126061081</v>
+        <v>126061099</v>
       </c>
       <c r="B95" t="n">
-        <v>58506</v>
+        <v>98256</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11540,48 +11540,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>208250</v>
+        <v>219790</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>687058</v>
+        <v>686857</v>
       </c>
       <c r="R95" t="n">
-        <v>6563228</v>
+        <v>6562875</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11613,7 +11599,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11623,7 +11609,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11643,17 +11629,17 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126061099</v>
+        <v>126061081</v>
       </c>
       <c r="B96" t="n">
-        <v>98256</v>
+        <v>58506</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11661,34 +11647,48 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>219790</v>
+        <v>208250</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>686857</v>
+        <v>687058</v>
       </c>
       <c r="R96" t="n">
-        <v>6562875</v>
+        <v>6563228</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11720,7 +11720,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11730,7 +11730,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11750,17 +11750,17 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126061113</v>
+        <v>126061105</v>
       </c>
       <c r="B97" t="n">
-        <v>95788</v>
+        <v>8436</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11768,43 +11768,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>210</v>
+        <v>106554</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>687032</v>
+        <v>686860</v>
       </c>
       <c r="R97" t="n">
-        <v>6562726</v>
+        <v>6562743</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11836,7 +11827,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11846,7 +11837,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11860,17 +11851,17 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -11888,10 +11879,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126061105</v>
+        <v>126061113</v>
       </c>
       <c r="B98" t="n">
-        <v>8436</v>
+        <v>95788</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11899,34 +11890,43 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>106554</v>
+        <v>210</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>686860</v>
+        <v>687032</v>
       </c>
       <c r="R98" t="n">
-        <v>6562743</v>
+        <v>6562726</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11958,7 +11958,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11968,7 +11968,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11982,17 +11982,17 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -10341,7 +10341,7 @@
         <v>125965889</v>
       </c>
       <c r="B84" t="n">
-        <v>105363</v>
+        <v>105365</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>125963374</v>
       </c>
       <c r="B85" t="n">
-        <v>97217</v>
+        <v>97219</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10535,7 +10535,7 @@
         <v>126003792</v>
       </c>
       <c r="B86" t="n">
-        <v>98256</v>
+        <v>98258</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10637,7 +10637,7 @@
         <v>126005160</v>
       </c>
       <c r="B87" t="n">
-        <v>98256</v>
+        <v>98258</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10739,7 +10739,7 @@
         <v>126003574</v>
       </c>
       <c r="B88" t="n">
-        <v>105363</v>
+        <v>105365</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11085,7 +11085,7 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
@@ -11095,7 +11095,7 @@
         <v>126061106</v>
       </c>
       <c r="B91" t="n">
-        <v>90667</v>
+        <v>90669</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11192,7 +11192,7 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -11202,7 +11202,7 @@
         <v>126061079</v>
       </c>
       <c r="B92" t="n">
-        <v>105363</v>
+        <v>105365</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11309,7 +11309,7 @@
         <v>126061094</v>
       </c>
       <c r="B93" t="n">
-        <v>98243</v>
+        <v>98245</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11425,7 +11425,7 @@
         <v>126061084</v>
       </c>
       <c r="B94" t="n">
-        <v>98256</v>
+        <v>98258</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11532,7 +11532,7 @@
         <v>126061099</v>
       </c>
       <c r="B95" t="n">
-        <v>98256</v>
+        <v>98258</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
@@ -11639,7 +11639,7 @@
         <v>126061081</v>
       </c>
       <c r="B96" t="n">
-        <v>58506</v>
+        <v>58507</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11872,7 +11872,7 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
@@ -11882,7 +11882,7 @@
         <v>126061113</v>
       </c>
       <c r="B98" t="n">
-        <v>95788</v>
+        <v>95790</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12003,7 +12003,7 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
@@ -12013,7 +12013,7 @@
         <v>126061102</v>
       </c>
       <c r="B99" t="n">
-        <v>98256</v>
+        <v>98258</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12110,7 +12110,7 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
@@ -12247,7 +12247,7 @@
         <v>126061082</v>
       </c>
       <c r="B101" t="n">
-        <v>97217</v>
+        <v>97219</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12354,7 +12354,7 @@
         <v>126061112</v>
       </c>
       <c r="B102" t="n">
-        <v>91250</v>
+        <v>91252</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12471,7 +12471,7 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
@@ -12608,7 +12608,7 @@
         <v>126061078</v>
       </c>
       <c r="B104" t="n">
-        <v>105363</v>
+        <v>105365</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12715,7 +12715,7 @@
         <v>126061108</v>
       </c>
       <c r="B105" t="n">
-        <v>58508</v>
+        <v>58509</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12826,7 +12826,7 @@
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
@@ -12953,17 +12953,17 @@
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126061100</v>
+        <v>126061098</v>
       </c>
       <c r="B107" t="n">
-        <v>98243</v>
+        <v>58481</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12971,33 +12971,24 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>220093</v>
+        <v>208245</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
@@ -13069,17 +13060,17 @@
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126061098</v>
+        <v>126061100</v>
       </c>
       <c r="B108" t="n">
-        <v>58480</v>
+        <v>98245</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13087,24 +13078,33 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>208245</v>
+        <v>220093</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
@@ -13176,7 +13176,7 @@
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
@@ -13186,7 +13186,7 @@
         <v>126061114</v>
       </c>
       <c r="B109" t="n">
-        <v>95692</v>
+        <v>95694</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
@@ -13293,7 +13293,7 @@
         <v>126061107</v>
       </c>
       <c r="B110" t="n">
-        <v>95692</v>
+        <v>95694</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13390,7 +13390,7 @@
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY110"/>
+  <dimension ref="A1:AY116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11529,10 +11529,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126061099</v>
+        <v>126061081</v>
       </c>
       <c r="B95" t="n">
-        <v>98258</v>
+        <v>58507</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11540,34 +11540,48 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>219790</v>
+        <v>208250</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>686857</v>
+        <v>687058</v>
       </c>
       <c r="R95" t="n">
-        <v>6562875</v>
+        <v>6563228</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11599,7 +11613,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11609,7 +11623,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11629,17 +11643,17 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126061081</v>
+        <v>126061099</v>
       </c>
       <c r="B96" t="n">
-        <v>58507</v>
+        <v>98258</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11647,48 +11661,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>208250</v>
+        <v>219790</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>687058</v>
+        <v>686857</v>
       </c>
       <c r="R96" t="n">
-        <v>6563228</v>
+        <v>6562875</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11720,7 +11720,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11730,7 +11730,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11750,7 +11750,7 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
@@ -13395,6 +13395,661 @@
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>126234373</v>
+      </c>
+      <c r="B111" t="n">
+        <v>105367</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Norrby mosse SO, Srm</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>686756</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6563092</v>
+      </c>
+      <c r="S111" t="n">
+        <v>10</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF111" t="inlineStr"/>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Ulf Johansson, Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>126234400</v>
+      </c>
+      <c r="B112" t="n">
+        <v>98364</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Norrby mosse SO, Srm</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>686788</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6563073</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF112" t="inlineStr"/>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Ulf Johansson, Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>126234703</v>
+      </c>
+      <c r="B113" t="n">
+        <v>91254</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Norrby mosse SO, Srm</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>687028</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6562882</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF113" t="inlineStr"/>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Ulf Johansson, Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>126234010</v>
+      </c>
+      <c r="B114" t="n">
+        <v>98260</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>687160</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6563261</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF114" t="inlineStr"/>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Bodil Ravn, Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>126234771</v>
+      </c>
+      <c r="B115" t="n">
+        <v>98260</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Norrby mosse OSO, Srm</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>686976</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6563107</v>
+      </c>
+      <c r="S115" t="n">
+        <v>10</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF115" t="inlineStr"/>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Ulf Johansson, Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>126234439</v>
+      </c>
+      <c r="B116" t="n">
+        <v>98260</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Norrby mosse SO, Srm</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>686777</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6563073</v>
+      </c>
+      <c r="S116" t="n">
+        <v>10</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF116" t="inlineStr"/>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Ulf Johansson, Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -10341,7 +10341,7 @@
         <v>125965889</v>
       </c>
       <c r="B84" t="n">
-        <v>105365</v>
+        <v>105367</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>125963374</v>
       </c>
       <c r="B85" t="n">
-        <v>97219</v>
+        <v>97221</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10535,7 +10535,7 @@
         <v>126003792</v>
       </c>
       <c r="B86" t="n">
-        <v>98258</v>
+        <v>98260</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10637,7 +10637,7 @@
         <v>126005160</v>
       </c>
       <c r="B87" t="n">
-        <v>98258</v>
+        <v>98260</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10739,7 +10739,7 @@
         <v>126003574</v>
       </c>
       <c r="B88" t="n">
-        <v>105365</v>
+        <v>105367</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10958,7 +10958,7 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
@@ -11095,7 +11095,7 @@
         <v>126061106</v>
       </c>
       <c r="B91" t="n">
-        <v>90669</v>
+        <v>90671</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11202,7 +11202,7 @@
         <v>126061079</v>
       </c>
       <c r="B92" t="n">
-        <v>105365</v>
+        <v>105367</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11299,17 +11299,17 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126061094</v>
+        <v>126061084</v>
       </c>
       <c r="B93" t="n">
-        <v>98245</v>
+        <v>98260</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11317,43 +11317,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220093</v>
+        <v>219790</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>686866</v>
+        <v>687014</v>
       </c>
       <c r="R93" t="n">
-        <v>6562874</v>
+        <v>6563215</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11385,7 +11376,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11395,7 +11386,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11415,17 +11406,17 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126061084</v>
+        <v>126061094</v>
       </c>
       <c r="B94" t="n">
-        <v>98258</v>
+        <v>98247</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11433,34 +11424,43 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>219790</v>
+        <v>220093</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>687014</v>
+        <v>686866</v>
       </c>
       <c r="R94" t="n">
-        <v>6563215</v>
+        <v>6562874</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11492,7 +11492,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11502,7 +11502,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11522,7 +11522,7 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -11643,7 +11643,7 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
@@ -11653,7 +11653,7 @@
         <v>126061099</v>
       </c>
       <c r="B96" t="n">
-        <v>98258</v>
+        <v>98260</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11757,10 +11757,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126061105</v>
+        <v>126061113</v>
       </c>
       <c r="B97" t="n">
-        <v>8436</v>
+        <v>95792</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11768,34 +11768,43 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>106554</v>
+        <v>210</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>686860</v>
+        <v>687032</v>
       </c>
       <c r="R97" t="n">
-        <v>6562743</v>
+        <v>6562726</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11827,7 +11836,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11837,7 +11846,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11851,17 +11860,17 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -11879,10 +11888,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126061113</v>
+        <v>126061105</v>
       </c>
       <c r="B98" t="n">
-        <v>95790</v>
+        <v>8436</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11890,43 +11899,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>210</v>
+        <v>106554</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>687032</v>
+        <v>686860</v>
       </c>
       <c r="R98" t="n">
-        <v>6562726</v>
+        <v>6562743</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11958,7 +11958,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11968,7 +11968,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11982,17 +11982,17 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -12013,7 +12013,7 @@
         <v>126061102</v>
       </c>
       <c r="B99" t="n">
-        <v>98258</v>
+        <v>98260</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12237,7 +12237,7 @@
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -12247,7 +12247,7 @@
         <v>126061082</v>
       </c>
       <c r="B101" t="n">
-        <v>97219</v>
+        <v>97221</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12344,7 +12344,7 @@
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
@@ -12354,7 +12354,7 @@
         <v>126061112</v>
       </c>
       <c r="B102" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12598,7 +12598,7 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
@@ -12608,7 +12608,7 @@
         <v>126061078</v>
       </c>
       <c r="B104" t="n">
-        <v>105365</v>
+        <v>105367</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12705,7 +12705,7 @@
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
@@ -12833,10 +12833,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126061109</v>
+        <v>126061098</v>
       </c>
       <c r="B106" t="n">
-        <v>5196</v>
+        <v>58481</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12844,16 +12844,16 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>105930</v>
+        <v>208245</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -12868,10 +12868,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>686946</v>
+        <v>686857</v>
       </c>
       <c r="R106" t="n">
-        <v>6562741</v>
+        <v>6562875</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12903,7 +12903,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12913,7 +12913,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12924,26 +12924,6 @@
       </c>
       <c r="AG106" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ106" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK106" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL106" t="inlineStr">
-        <is>
-          <t>Klen torr granlåga.</t>
-        </is>
-      </c>
-      <c r="AO106" t="inlineStr">
-        <is>
-          <t>Picea abies # Klen torr granlåga.</t>
-        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
@@ -12960,10 +12940,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126061098</v>
+        <v>126061109</v>
       </c>
       <c r="B107" t="n">
-        <v>58481</v>
+        <v>5196</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12971,16 +12951,16 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>208245</v>
+        <v>105930</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -12995,10 +12975,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>686857</v>
+        <v>686946</v>
       </c>
       <c r="R107" t="n">
-        <v>6562875</v>
+        <v>6562741</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -13030,7 +13010,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -13040,7 +13020,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13051,6 +13031,26 @@
       </c>
       <c r="AG107" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL107" t="inlineStr">
+        <is>
+          <t>Klen torr granlåga.</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>Picea abies # Klen torr granlåga.</t>
+        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
@@ -13070,7 +13070,7 @@
         <v>126061100</v>
       </c>
       <c r="B108" t="n">
-        <v>98245</v>
+        <v>98247</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13186,7 +13186,7 @@
         <v>126061114</v>
       </c>
       <c r="B109" t="n">
-        <v>95694</v>
+        <v>95696</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         <v>126061107</v>
       </c>
       <c r="B110" t="n">
-        <v>95694</v>
+        <v>95696</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13722,7 +13722,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126234010</v>
+        <v>126234771</v>
       </c>
       <c r="B114" t="n">
         <v>98260</v>
@@ -13750,25 +13750,29 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrby mosse OSO, Srm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>687160</v>
+        <v>686976</v>
       </c>
       <c r="R114" t="n">
-        <v>6563261</v>
+        <v>6563107</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13816,19 +13820,19 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Bodil Ravn, Ulf Johansson</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126234771</v>
+        <v>126234010</v>
       </c>
       <c r="B115" t="n">
         <v>98260</v>
@@ -13856,29 +13860,25 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr"/>
       <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Norrby mosse OSO, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>686976</v>
+        <v>687160</v>
       </c>
       <c r="R115" t="n">
-        <v>6563107</v>
+        <v>6563261</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13926,12 +13926,12 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Bodil Ravn, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -12833,10 +12833,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126061098</v>
+        <v>126061109</v>
       </c>
       <c r="B106" t="n">
-        <v>58481</v>
+        <v>5196</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12844,16 +12844,16 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>208245</v>
+        <v>105930</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -12868,10 +12868,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>686857</v>
+        <v>686946</v>
       </c>
       <c r="R106" t="n">
-        <v>6562875</v>
+        <v>6562741</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12903,7 +12903,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12913,7 +12913,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12924,6 +12924,26 @@
       </c>
       <c r="AG106" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL106" t="inlineStr">
+        <is>
+          <t>Klen torr granlåga.</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>Picea abies # Klen torr granlåga.</t>
+        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
@@ -12940,10 +12960,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126061109</v>
+        <v>126061098</v>
       </c>
       <c r="B107" t="n">
-        <v>5196</v>
+        <v>58481</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12951,16 +12971,16 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>105930</v>
+        <v>208245</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -12975,10 +12995,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>686946</v>
+        <v>686857</v>
       </c>
       <c r="R107" t="n">
-        <v>6562741</v>
+        <v>6562875</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -13010,7 +13030,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -13020,7 +13040,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13031,26 +13051,6 @@
       </c>
       <c r="AG107" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ107" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK107" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL107" t="inlineStr">
-        <is>
-          <t>Klen torr granlåga.</t>
-        </is>
-      </c>
-      <c r="AO107" t="inlineStr">
-        <is>
-          <t>Picea abies # Klen torr granlåga.</t>
-        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -10341,7 +10341,7 @@
         <v>125965889</v>
       </c>
       <c r="B84" t="n">
-        <v>105367</v>
+        <v>105371</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>125963374</v>
       </c>
       <c r="B85" t="n">
-        <v>97221</v>
+        <v>97223</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10535,7 +10535,7 @@
         <v>126003792</v>
       </c>
       <c r="B86" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10637,7 +10637,7 @@
         <v>126005160</v>
       </c>
       <c r="B87" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10739,7 +10739,7 @@
         <v>126003574</v>
       </c>
       <c r="B88" t="n">
-        <v>105367</v>
+        <v>105371</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11085,7 +11085,7 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
@@ -11095,7 +11095,7 @@
         <v>126061106</v>
       </c>
       <c r="B91" t="n">
-        <v>90671</v>
+        <v>90673</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11192,7 +11192,7 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -11202,7 +11202,7 @@
         <v>126061079</v>
       </c>
       <c r="B92" t="n">
-        <v>105367</v>
+        <v>105371</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11309,7 +11309,7 @@
         <v>126061084</v>
       </c>
       <c r="B93" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
+          <t>Bodil Ravn, Måns Persson, Klas Magnusson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
@@ -11416,7 +11416,7 @@
         <v>126061094</v>
       </c>
       <c r="B94" t="n">
-        <v>98247</v>
+        <v>98249</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11522,7 +11522,7 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -11653,7 +11653,7 @@
         <v>126061099</v>
       </c>
       <c r="B96" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11750,17 +11750,17 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126061113</v>
+        <v>126061105</v>
       </c>
       <c r="B97" t="n">
-        <v>95792</v>
+        <v>8436</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11768,43 +11768,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>210</v>
+        <v>106554</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>687032</v>
+        <v>686860</v>
       </c>
       <c r="R97" t="n">
-        <v>6562726</v>
+        <v>6562743</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11836,7 +11827,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11846,7 +11837,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11860,17 +11851,17 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -11881,17 +11872,17 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126061105</v>
+        <v>126061113</v>
       </c>
       <c r="B98" t="n">
-        <v>8436</v>
+        <v>95794</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11899,34 +11890,43 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>106554</v>
+        <v>210</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>686860</v>
+        <v>687032</v>
       </c>
       <c r="R98" t="n">
-        <v>6562743</v>
+        <v>6562726</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11958,7 +11958,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11968,7 +11968,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11982,17 +11982,17 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -12013,7 +12013,7 @@
         <v>126061102</v>
       </c>
       <c r="B99" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12110,7 +12110,7 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
@@ -12247,7 +12247,7 @@
         <v>126061082</v>
       </c>
       <c r="B101" t="n">
-        <v>97221</v>
+        <v>97223</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12354,7 +12354,7 @@
         <v>126061112</v>
       </c>
       <c r="B102" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12608,7 +12608,7 @@
         <v>126061078</v>
       </c>
       <c r="B104" t="n">
-        <v>105367</v>
+        <v>105371</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13060,7 +13060,7 @@
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
@@ -13070,7 +13070,7 @@
         <v>126061100</v>
       </c>
       <c r="B108" t="n">
-        <v>98247</v>
+        <v>98249</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13176,7 +13176,7 @@
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
@@ -13186,7 +13186,7 @@
         <v>126061114</v>
       </c>
       <c r="B109" t="n">
-        <v>95696</v>
+        <v>95698</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         <v>126061107</v>
       </c>
       <c r="B110" t="n">
-        <v>95696</v>
+        <v>95698</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13390,7 +13390,7 @@
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Måns Persson, Klas Magnusson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
@@ -13400,7 +13400,7 @@
         <v>126234373</v>
       </c>
       <c r="B111" t="n">
-        <v>105367</v>
+        <v>105371</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13510,7 +13510,7 @@
         <v>126234400</v>
       </c>
       <c r="B112" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13624,7 +13624,7 @@
         <v>126234703</v>
       </c>
       <c r="B113" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13725,7 +13725,7 @@
         <v>126234771</v>
       </c>
       <c r="B114" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13835,7 +13835,7 @@
         <v>126234010</v>
       </c>
       <c r="B115" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13941,7 +13941,7 @@
         <v>126234439</v>
       </c>
       <c r="B116" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -11306,10 +11306,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126061084</v>
+        <v>126061094</v>
       </c>
       <c r="B93" t="n">
-        <v>98262</v>
+        <v>98249</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11317,34 +11317,43 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>219790</v>
+        <v>220093</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>687014</v>
+        <v>686866</v>
       </c>
       <c r="R93" t="n">
-        <v>6563215</v>
+        <v>6562874</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11376,7 +11385,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11386,7 +11395,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11406,17 +11415,17 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Bodil Ravn, Måns Persson, Klas Magnusson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström</t>
+          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126061094</v>
+        <v>126061084</v>
       </c>
       <c r="B94" t="n">
-        <v>98249</v>
+        <v>98262</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11424,43 +11433,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220093</v>
+        <v>219790</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>686866</v>
+        <v>687014</v>
       </c>
       <c r="R94" t="n">
-        <v>6562874</v>
+        <v>6563215</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11492,7 +11492,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11502,7 +11502,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11522,7 +11522,7 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
+          <t>Bodil Ravn, Måns Persson, Klas Magnusson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -10341,7 +10341,7 @@
         <v>125965889</v>
       </c>
       <c r="B84" t="n">
-        <v>105371</v>
+        <v>105384</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>125963374</v>
       </c>
       <c r="B85" t="n">
-        <v>97223</v>
+        <v>97227</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10535,7 +10535,7 @@
         <v>126003792</v>
       </c>
       <c r="B86" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10637,7 +10637,7 @@
         <v>126005160</v>
       </c>
       <c r="B87" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10739,7 +10739,7 @@
         <v>126003574</v>
       </c>
       <c r="B88" t="n">
-        <v>105371</v>
+        <v>105384</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11095,7 +11095,7 @@
         <v>126061106</v>
       </c>
       <c r="B91" t="n">
-        <v>90673</v>
+        <v>90677</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11202,7 +11202,7 @@
         <v>126061079</v>
       </c>
       <c r="B92" t="n">
-        <v>105371</v>
+        <v>105384</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11299,7 +11299,7 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -11309,7 +11309,7 @@
         <v>126061094</v>
       </c>
       <c r="B93" t="n">
-        <v>98249</v>
+        <v>98253</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11425,7 +11425,7 @@
         <v>126061084</v>
       </c>
       <c r="B94" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11522,7 +11522,7 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Bodil Ravn, Måns Persson, Klas Magnusson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -11532,7 +11532,7 @@
         <v>126061081</v>
       </c>
       <c r="B95" t="n">
-        <v>58507</v>
+        <v>58511</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11643,7 +11643,7 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
@@ -11653,7 +11653,7 @@
         <v>126061099</v>
       </c>
       <c r="B96" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>126061113</v>
       </c>
       <c r="B98" t="n">
-        <v>95794</v>
+        <v>95798</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12003,7 +12003,7 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
@@ -12013,7 +12013,7 @@
         <v>126061102</v>
       </c>
       <c r="B99" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12247,7 +12247,7 @@
         <v>126061082</v>
       </c>
       <c r="B101" t="n">
-        <v>97223</v>
+        <v>97227</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12344,7 +12344,7 @@
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
@@ -12354,7 +12354,7 @@
         <v>126061112</v>
       </c>
       <c r="B102" t="n">
-        <v>91256</v>
+        <v>91260</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12471,7 +12471,7 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
@@ -12608,7 +12608,7 @@
         <v>126061078</v>
       </c>
       <c r="B104" t="n">
-        <v>105371</v>
+        <v>105384</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12705,7 +12705,7 @@
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
@@ -12715,7 +12715,7 @@
         <v>126061108</v>
       </c>
       <c r="B105" t="n">
-        <v>58509</v>
+        <v>58513</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12826,7 +12826,7 @@
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
@@ -12953,7 +12953,7 @@
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
@@ -12963,7 +12963,7 @@
         <v>126061098</v>
       </c>
       <c r="B107" t="n">
-        <v>58481</v>
+        <v>58485</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13070,7 +13070,7 @@
         <v>126061100</v>
       </c>
       <c r="B108" t="n">
-        <v>98249</v>
+        <v>98253</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13186,7 +13186,7 @@
         <v>126061114</v>
       </c>
       <c r="B109" t="n">
-        <v>95698</v>
+        <v>95702</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
@@ -13293,7 +13293,7 @@
         <v>126061107</v>
       </c>
       <c r="B110" t="n">
-        <v>95698</v>
+        <v>95702</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13390,7 +13390,7 @@
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Måns Persson, Klas Magnusson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
@@ -13400,7 +13400,7 @@
         <v>126234373</v>
       </c>
       <c r="B111" t="n">
-        <v>105371</v>
+        <v>105384</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13510,7 +13510,7 @@
         <v>126234400</v>
       </c>
       <c r="B112" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13624,7 +13624,7 @@
         <v>126234703</v>
       </c>
       <c r="B113" t="n">
-        <v>91256</v>
+        <v>91260</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13725,7 +13725,7 @@
         <v>126234771</v>
       </c>
       <c r="B114" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13835,7 +13835,7 @@
         <v>126234010</v>
       </c>
       <c r="B115" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13941,7 +13941,7 @@
         <v>126234439</v>
       </c>
       <c r="B116" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -11092,32 +11092,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126061106</v>
+        <v>126061079</v>
       </c>
       <c r="B91" t="n">
-        <v>90677</v>
+        <v>105384</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2008</v>
+        <v>221144</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -11127,10 +11127,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>686883</v>
+        <v>687082</v>
       </c>
       <c r="R91" t="n">
-        <v>6562742</v>
+        <v>6563241</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11162,7 +11162,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11172,7 +11172,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11192,39 +11192,39 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126061079</v>
+        <v>126061106</v>
       </c>
       <c r="B92" t="n">
-        <v>105384</v>
+        <v>90677</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>221144</v>
+        <v>2008</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -11234,10 +11234,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>687082</v>
+        <v>686883</v>
       </c>
       <c r="R92" t="n">
-        <v>6563241</v>
+        <v>6562742</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11269,7 +11269,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11279,7 +11279,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11299,7 +11299,7 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -11757,10 +11757,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126061105</v>
+        <v>126061113</v>
       </c>
       <c r="B97" t="n">
-        <v>8436</v>
+        <v>95798</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11768,34 +11768,43 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>106554</v>
+        <v>210</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>686860</v>
+        <v>687032</v>
       </c>
       <c r="R97" t="n">
-        <v>6562743</v>
+        <v>6562726</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11827,7 +11836,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11837,7 +11846,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11851,17 +11860,17 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -11879,10 +11888,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126061113</v>
+        <v>126061105</v>
       </c>
       <c r="B98" t="n">
-        <v>95798</v>
+        <v>8436</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11890,43 +11899,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>210</v>
+        <v>106554</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>687032</v>
+        <v>686860</v>
       </c>
       <c r="R98" t="n">
-        <v>6562726</v>
+        <v>6562743</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11958,7 +11958,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11968,7 +11968,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11982,17 +11982,17 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -12960,10 +12960,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126061098</v>
+        <v>126061100</v>
       </c>
       <c r="B107" t="n">
-        <v>58485</v>
+        <v>98253</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12971,24 +12971,33 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>208245</v>
+        <v>220093</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
@@ -13067,10 +13076,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126061100</v>
+        <v>126061098</v>
       </c>
       <c r="B108" t="n">
-        <v>98253</v>
+        <v>58485</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13078,33 +13087,24 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220093</v>
+        <v>208245</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -10341,7 +10341,7 @@
         <v>125965889</v>
       </c>
       <c r="B84" t="n">
-        <v>105384</v>
+        <v>105387</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>125963374</v>
       </c>
       <c r="B85" t="n">
-        <v>97227</v>
+        <v>97230</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10535,7 +10535,7 @@
         <v>126003792</v>
       </c>
       <c r="B86" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10637,7 +10637,7 @@
         <v>126005160</v>
       </c>
       <c r="B87" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10739,7 +10739,7 @@
         <v>126003574</v>
       </c>
       <c r="B88" t="n">
-        <v>105384</v>
+        <v>105387</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10958,7 +10958,7 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
@@ -11085,39 +11085,39 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126061079</v>
+        <v>126061106</v>
       </c>
       <c r="B91" t="n">
-        <v>105384</v>
+        <v>90677</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221144</v>
+        <v>2008</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -11127,10 +11127,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>687082</v>
+        <v>686883</v>
       </c>
       <c r="R91" t="n">
-        <v>6563241</v>
+        <v>6562742</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11162,7 +11162,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11172,7 +11172,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11192,39 +11192,39 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126061106</v>
+        <v>126061079</v>
       </c>
       <c r="B92" t="n">
-        <v>90677</v>
+        <v>105387</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2008</v>
+        <v>221144</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -11234,10 +11234,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>686883</v>
+        <v>687082</v>
       </c>
       <c r="R92" t="n">
-        <v>6562742</v>
+        <v>6563241</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11269,7 +11269,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11279,7 +11279,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11299,7 +11299,7 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -11309,7 +11309,7 @@
         <v>126061094</v>
       </c>
       <c r="B93" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11415,7 +11415,7 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
@@ -11425,7 +11425,7 @@
         <v>126061084</v>
       </c>
       <c r="B94" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11522,7 +11522,7 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -11653,7 +11653,7 @@
         <v>126061099</v>
       </c>
       <c r="B96" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11750,7 +11750,7 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
@@ -11760,7 +11760,7 @@
         <v>126061113</v>
       </c>
       <c r="B97" t="n">
-        <v>95798</v>
+        <v>95801</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11881,7 +11881,7 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
@@ -12003,7 +12003,7 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
@@ -12013,7 +12013,7 @@
         <v>126061102</v>
       </c>
       <c r="B99" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12110,7 +12110,7 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
@@ -12237,7 +12237,7 @@
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -12247,7 +12247,7 @@
         <v>126061082</v>
       </c>
       <c r="B101" t="n">
-        <v>97227</v>
+        <v>97230</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12351,32 +12351,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126061112</v>
+        <v>126061088</v>
       </c>
       <c r="B102" t="n">
-        <v>91260</v>
+        <v>5196</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5432</v>
+        <v>105930</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -12386,10 +12386,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>687032</v>
+        <v>686865</v>
       </c>
       <c r="R102" t="n">
-        <v>6562719</v>
+        <v>6562977</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12421,7 +12421,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12431,7 +12431,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12455,12 +12455,12 @@
       </c>
       <c r="AL102" t="inlineStr">
         <is>
-          <t>På barken och grenarna på en granlåga.</t>
+          <t>Klen torr granlåga.</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>Picea abies # På barken och grenarna på en granlåga.</t>
+          <t>Picea abies # Klen torr granlåga.</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -12471,39 +12471,39 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126061088</v>
+        <v>126061112</v>
       </c>
       <c r="B103" t="n">
-        <v>5196</v>
+        <v>91260</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>105930</v>
+        <v>5432</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12513,10 +12513,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>686865</v>
+        <v>687032</v>
       </c>
       <c r="R103" t="n">
-        <v>6562977</v>
+        <v>6562719</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12548,7 +12548,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12558,7 +12558,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12582,12 +12582,12 @@
       </c>
       <c r="AL103" t="inlineStr">
         <is>
-          <t>Klen torr granlåga.</t>
+          <t>På barken och grenarna på en granlåga.</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>Picea abies # Klen torr granlåga.</t>
+          <t>Picea abies # På barken och grenarna på en granlåga.</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>
@@ -12598,7 +12598,7 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
@@ -12608,7 +12608,7 @@
         <v>126061078</v>
       </c>
       <c r="B104" t="n">
-        <v>105384</v>
+        <v>105387</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12826,7 +12826,7 @@
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
@@ -12953,17 +12953,17 @@
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126061100</v>
+        <v>126061098</v>
       </c>
       <c r="B107" t="n">
-        <v>98253</v>
+        <v>58485</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12971,33 +12971,24 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>220093</v>
+        <v>208245</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
@@ -13069,17 +13060,17 @@
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>126061098</v>
+        <v>126061100</v>
       </c>
       <c r="B108" t="n">
-        <v>58485</v>
+        <v>98256</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13087,24 +13078,33 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>208245</v>
+        <v>220093</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
@@ -13176,7 +13176,7 @@
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
@@ -13186,7 +13186,7 @@
         <v>126061114</v>
       </c>
       <c r="B109" t="n">
-        <v>95702</v>
+        <v>95705</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
@@ -13293,7 +13293,7 @@
         <v>126061107</v>
       </c>
       <c r="B110" t="n">
-        <v>95702</v>
+        <v>95705</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13390,7 +13390,7 @@
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
@@ -13400,7 +13400,7 @@
         <v>126234373</v>
       </c>
       <c r="B111" t="n">
-        <v>105384</v>
+        <v>105387</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13510,7 +13510,7 @@
         <v>126234400</v>
       </c>
       <c r="B112" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13725,7 +13725,7 @@
         <v>126234771</v>
       </c>
       <c r="B114" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13835,7 +13835,7 @@
         <v>126234010</v>
       </c>
       <c r="B115" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13941,7 +13941,7 @@
         <v>126234439</v>
       </c>
       <c r="B116" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -12351,32 +12351,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126061088</v>
+        <v>126061112</v>
       </c>
       <c r="B102" t="n">
-        <v>5196</v>
+        <v>91260</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>105930</v>
+        <v>5432</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -12386,10 +12386,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>686865</v>
+        <v>687032</v>
       </c>
       <c r="R102" t="n">
-        <v>6562977</v>
+        <v>6562719</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12421,7 +12421,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12431,7 +12431,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12455,12 +12455,12 @@
       </c>
       <c r="AL102" t="inlineStr">
         <is>
-          <t>Klen torr granlåga.</t>
+          <t>På barken och grenarna på en granlåga.</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>Picea abies # Klen torr granlåga.</t>
+          <t>Picea abies # På barken och grenarna på en granlåga.</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -12471,39 +12471,39 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126061112</v>
+        <v>126061088</v>
       </c>
       <c r="B103" t="n">
-        <v>91260</v>
+        <v>5196</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5432</v>
+        <v>105930</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12513,10 +12513,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>687032</v>
+        <v>686865</v>
       </c>
       <c r="R103" t="n">
-        <v>6562719</v>
+        <v>6562977</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12548,7 +12548,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12558,7 +12558,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12582,12 +12582,12 @@
       </c>
       <c r="AL103" t="inlineStr">
         <is>
-          <t>På barken och grenarna på en granlåga.</t>
+          <t>Klen torr granlåga.</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>Picea abies # På barken och grenarna på en granlåga.</t>
+          <t>Picea abies # Klen torr granlåga.</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>
@@ -12598,7 +12598,7 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -10958,7 +10958,7 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
@@ -11085,7 +11085,7 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
@@ -11192,7 +11192,7 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -11299,17 +11299,17 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126061094</v>
+        <v>126061084</v>
       </c>
       <c r="B93" t="n">
-        <v>98256</v>
+        <v>98269</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11317,43 +11317,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220093</v>
+        <v>219790</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>686866</v>
+        <v>687014</v>
       </c>
       <c r="R93" t="n">
-        <v>6562874</v>
+        <v>6563215</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11385,7 +11376,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11395,7 +11386,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11415,17 +11406,17 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Bodil Ravn, Måns Persson, Klas Magnusson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126061084</v>
+        <v>126061094</v>
       </c>
       <c r="B94" t="n">
-        <v>98269</v>
+        <v>98256</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11433,34 +11424,43 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>219790</v>
+        <v>220093</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>687014</v>
+        <v>686866</v>
       </c>
       <c r="R94" t="n">
-        <v>6563215</v>
+        <v>6562874</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11492,7 +11492,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11502,7 +11502,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11522,7 +11522,7 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -11643,7 +11643,7 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
@@ -11750,7 +11750,7 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
@@ -12003,7 +12003,7 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
@@ -12110,7 +12110,7 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
@@ -12237,7 +12237,7 @@
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -12344,7 +12344,7 @@
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
@@ -12598,7 +12598,7 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
@@ -12705,7 +12705,7 @@
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
@@ -13060,7 +13060,7 @@
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
@@ -13176,7 +13176,7 @@
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
@@ -13500,7 +13500,7 @@
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Bodil Ravn, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
@@ -13722,7 +13722,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126234771</v>
+        <v>126234010</v>
       </c>
       <c r="B114" t="n">
         <v>98269</v>
@@ -13750,29 +13750,25 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Norrby mosse OSO, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>686976</v>
+        <v>687160</v>
       </c>
       <c r="R114" t="n">
-        <v>6563107</v>
+        <v>6563261</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13820,19 +13816,19 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Bodil Ravn, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126234010</v>
+        <v>126234771</v>
       </c>
       <c r="B115" t="n">
         <v>98269</v>
@@ -13860,25 +13856,29 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr"/>
       <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrby mosse OSO, Srm</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>687160</v>
+        <v>686976</v>
       </c>
       <c r="R115" t="n">
-        <v>6563261</v>
+        <v>6563107</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13926,12 +13926,12 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Bodil Ravn, Ulf Johansson</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -13722,7 +13722,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>126234010</v>
+        <v>126234771</v>
       </c>
       <c r="B114" t="n">
         <v>98269</v>
@@ -13750,25 +13750,29 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrby mosse OSO, Srm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>687160</v>
+        <v>686976</v>
       </c>
       <c r="R114" t="n">
-        <v>6563261</v>
+        <v>6563107</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13816,19 +13820,19 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Bodil Ravn, Ulf Johansson</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>126234771</v>
+        <v>126234010</v>
       </c>
       <c r="B115" t="n">
         <v>98269</v>
@@ -13856,29 +13860,25 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr"/>
       <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Norrby mosse OSO, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>686976</v>
+        <v>687160</v>
       </c>
       <c r="R115" t="n">
-        <v>6563107</v>
+        <v>6563261</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13926,12 +13926,12 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Bodil Ravn, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY116"/>
+  <dimension ref="A1:AY119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10341,7 +10341,7 @@
         <v>125965889</v>
       </c>
       <c r="B84" t="n">
-        <v>105387</v>
+        <v>105396</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>125963374</v>
       </c>
       <c r="B85" t="n">
-        <v>97230</v>
+        <v>97239</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10535,7 +10535,7 @@
         <v>126003792</v>
       </c>
       <c r="B86" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10637,7 +10637,7 @@
         <v>126005160</v>
       </c>
       <c r="B87" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10739,7 +10739,7 @@
         <v>126003574</v>
       </c>
       <c r="B88" t="n">
-        <v>105387</v>
+        <v>105396</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10958,7 +10958,7 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
@@ -11085,7 +11085,7 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
@@ -11095,7 +11095,7 @@
         <v>126061106</v>
       </c>
       <c r="B91" t="n">
-        <v>90677</v>
+        <v>90680</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11192,7 +11192,7 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -11202,7 +11202,7 @@
         <v>126061079</v>
       </c>
       <c r="B92" t="n">
-        <v>105387</v>
+        <v>105396</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11299,7 +11299,7 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -11309,7 +11309,7 @@
         <v>126061084</v>
       </c>
       <c r="B93" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Bodil Ravn, Måns Persson, Klas Magnusson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
@@ -11416,7 +11416,7 @@
         <v>126061094</v>
       </c>
       <c r="B94" t="n">
-        <v>98256</v>
+        <v>98265</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11522,17 +11522,17 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126061081</v>
+        <v>126061099</v>
       </c>
       <c r="B95" t="n">
-        <v>58511</v>
+        <v>98278</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11540,48 +11540,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>208250</v>
+        <v>219790</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>687058</v>
+        <v>686857</v>
       </c>
       <c r="R95" t="n">
-        <v>6563228</v>
+        <v>6562875</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11613,7 +11599,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11623,7 +11609,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11643,17 +11629,17 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126061099</v>
+        <v>126061081</v>
       </c>
       <c r="B96" t="n">
-        <v>98269</v>
+        <v>58514</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11661,34 +11647,48 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>219790</v>
+        <v>208250</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>686857</v>
+        <v>687058</v>
       </c>
       <c r="R96" t="n">
-        <v>6562875</v>
+        <v>6563228</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11720,7 +11720,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11730,7 +11730,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11750,17 +11750,17 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126061113</v>
+        <v>126061105</v>
       </c>
       <c r="B97" t="n">
-        <v>95801</v>
+        <v>8436</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11768,43 +11768,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>210</v>
+        <v>106554</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>687032</v>
+        <v>686860</v>
       </c>
       <c r="R97" t="n">
-        <v>6562726</v>
+        <v>6562743</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11836,7 +11827,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11846,7 +11837,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11860,17 +11851,17 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -11888,10 +11879,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126061105</v>
+        <v>126061113</v>
       </c>
       <c r="B98" t="n">
-        <v>8436</v>
+        <v>95810</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11899,34 +11890,43 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>106554</v>
+        <v>210</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>686860</v>
+        <v>687032</v>
       </c>
       <c r="R98" t="n">
-        <v>6562743</v>
+        <v>6562726</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11958,7 +11958,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11968,7 +11968,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11982,17 +11982,17 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -12003,7 +12003,7 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
@@ -12013,7 +12013,7 @@
         <v>126061102</v>
       </c>
       <c r="B99" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12110,7 +12110,7 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
@@ -12237,7 +12237,7 @@
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -12247,7 +12247,7 @@
         <v>126061082</v>
       </c>
       <c r="B101" t="n">
-        <v>97230</v>
+        <v>97239</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12344,39 +12344,39 @@
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126061112</v>
+        <v>126061088</v>
       </c>
       <c r="B102" t="n">
-        <v>91260</v>
+        <v>5196</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5432</v>
+        <v>105930</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -12386,10 +12386,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>687032</v>
+        <v>686865</v>
       </c>
       <c r="R102" t="n">
-        <v>6562719</v>
+        <v>6562977</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12421,7 +12421,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12431,7 +12431,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12455,12 +12455,12 @@
       </c>
       <c r="AL102" t="inlineStr">
         <is>
-          <t>På barken och grenarna på en granlåga.</t>
+          <t>Klen torr granlåga.</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>Picea abies # På barken och grenarna på en granlåga.</t>
+          <t>Picea abies # Klen torr granlåga.</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -12471,39 +12471,39 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126061088</v>
+        <v>126061112</v>
       </c>
       <c r="B103" t="n">
-        <v>5196</v>
+        <v>91263</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>105930</v>
+        <v>5432</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12513,10 +12513,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>686865</v>
+        <v>687032</v>
       </c>
       <c r="R103" t="n">
-        <v>6562977</v>
+        <v>6562719</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12548,7 +12548,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12558,7 +12558,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12582,12 +12582,12 @@
       </c>
       <c r="AL103" t="inlineStr">
         <is>
-          <t>Klen torr granlåga.</t>
+          <t>På barken och grenarna på en granlåga.</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>Picea abies # Klen torr granlåga.</t>
+          <t>Picea abies # På barken och grenarna på en granlåga.</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>
@@ -12598,7 +12598,7 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
@@ -12608,7 +12608,7 @@
         <v>126061078</v>
       </c>
       <c r="B104" t="n">
-        <v>105387</v>
+        <v>105396</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12705,7 +12705,7 @@
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
@@ -12715,7 +12715,7 @@
         <v>126061108</v>
       </c>
       <c r="B105" t="n">
-        <v>58513</v>
+        <v>58516</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12963,7 +12963,7 @@
         <v>126061098</v>
       </c>
       <c r="B107" t="n">
-        <v>58485</v>
+        <v>58488</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13060,7 +13060,7 @@
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
@@ -13070,7 +13070,7 @@
         <v>126061100</v>
       </c>
       <c r="B108" t="n">
-        <v>98256</v>
+        <v>98265</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13176,7 +13176,7 @@
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Viktor Munkhammar, Johan Spaedtke, Birgitta Tulin, Isak Westerström, Bodil Ravn, Måns Persson, Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
@@ -13186,7 +13186,7 @@
         <v>126061114</v>
       </c>
       <c r="B109" t="n">
-        <v>95705</v>
+        <v>95714</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         <v>126061107</v>
       </c>
       <c r="B110" t="n">
-        <v>95705</v>
+        <v>95714</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13400,7 +13400,7 @@
         <v>126234373</v>
       </c>
       <c r="B111" t="n">
-        <v>105387</v>
+        <v>105396</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13500,7 +13500,7 @@
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Bodil Ravn, Ulf Johansson</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
@@ -13510,7 +13510,7 @@
         <v>126234400</v>
       </c>
       <c r="B112" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13624,7 +13624,7 @@
         <v>126234703</v>
       </c>
       <c r="B113" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13725,7 +13725,7 @@
         <v>126234771</v>
       </c>
       <c r="B114" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13835,7 +13835,7 @@
         <v>126234010</v>
       </c>
       <c r="B115" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13941,7 +13941,7 @@
         <v>126234439</v>
       </c>
       <c r="B116" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14049,6 +14049,331 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>126491496</v>
+      </c>
+      <c r="B117" t="n">
+        <v>57817</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>687192</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6563285</v>
+      </c>
+      <c r="S117" t="n">
+        <v>25</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>126491342</v>
+      </c>
+      <c r="B118" t="n">
+        <v>95810</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>210</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>686739</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6562816</v>
+      </c>
+      <c r="S118" t="n">
+        <v>10</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Uppspruckna kapslar på björklåga.</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF118" t="inlineStr"/>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>126491267</v>
+      </c>
+      <c r="B119" t="n">
+        <v>57817</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>686828</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6562775</v>
+      </c>
+      <c r="S119" t="n">
+        <v>25</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -11306,10 +11306,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126061084</v>
+        <v>126061094</v>
       </c>
       <c r="B93" t="n">
-        <v>98278</v>
+        <v>98265</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11317,34 +11317,43 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>219790</v>
+        <v>220093</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>687014</v>
+        <v>686866</v>
       </c>
       <c r="R93" t="n">
-        <v>6563215</v>
+        <v>6562874</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11376,7 +11385,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11386,7 +11395,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11406,17 +11415,17 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126061094</v>
+        <v>126061084</v>
       </c>
       <c r="B94" t="n">
-        <v>98265</v>
+        <v>98278</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11424,43 +11433,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220093</v>
+        <v>219790</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>686866</v>
+        <v>687014</v>
       </c>
       <c r="R94" t="n">
-        <v>6562874</v>
+        <v>6563215</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11492,7 +11492,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11502,7 +11502,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11522,17 +11522,17 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126061099</v>
+        <v>126061081</v>
       </c>
       <c r="B95" t="n">
-        <v>98278</v>
+        <v>58514</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11540,34 +11540,48 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>219790</v>
+        <v>208250</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>686857</v>
+        <v>687058</v>
       </c>
       <c r="R95" t="n">
-        <v>6562875</v>
+        <v>6563228</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11599,7 +11613,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11609,7 +11623,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11629,17 +11643,17 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126061081</v>
+        <v>126061099</v>
       </c>
       <c r="B96" t="n">
-        <v>58514</v>
+        <v>98278</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11647,48 +11661,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>208250</v>
+        <v>219790</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>687058</v>
+        <v>686857</v>
       </c>
       <c r="R96" t="n">
-        <v>6563228</v>
+        <v>6562875</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11720,7 +11720,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11730,7 +11730,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11750,17 +11750,17 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126061105</v>
+        <v>126061113</v>
       </c>
       <c r="B97" t="n">
-        <v>8436</v>
+        <v>95810</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11768,34 +11768,43 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>106554</v>
+        <v>210</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>686860</v>
+        <v>687032</v>
       </c>
       <c r="R97" t="n">
-        <v>6562743</v>
+        <v>6562726</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11827,7 +11836,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11837,7 +11846,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11851,17 +11860,17 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -11879,10 +11888,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126061113</v>
+        <v>126061105</v>
       </c>
       <c r="B98" t="n">
-        <v>95810</v>
+        <v>8436</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11890,43 +11899,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>210</v>
+        <v>106554</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>687032</v>
+        <v>686860</v>
       </c>
       <c r="R98" t="n">
-        <v>6562726</v>
+        <v>6562743</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11958,7 +11958,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11968,7 +11968,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11982,17 +11982,17 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -12351,32 +12351,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>126061088</v>
+        <v>126061112</v>
       </c>
       <c r="B102" t="n">
-        <v>5196</v>
+        <v>91263</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>105930</v>
+        <v>5432</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -12386,10 +12386,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>686865</v>
+        <v>687032</v>
       </c>
       <c r="R102" t="n">
-        <v>6562977</v>
+        <v>6562719</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12421,7 +12421,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12431,7 +12431,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12455,12 +12455,12 @@
       </c>
       <c r="AL102" t="inlineStr">
         <is>
-          <t>Klen torr granlåga.</t>
+          <t>På barken och grenarna på en granlåga.</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>Picea abies # Klen torr granlåga.</t>
+          <t>Picea abies # På barken och grenarna på en granlåga.</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -12471,39 +12471,39 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>126061112</v>
+        <v>126061088</v>
       </c>
       <c r="B103" t="n">
-        <v>91263</v>
+        <v>5196</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5432</v>
+        <v>105930</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12513,10 +12513,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>687032</v>
+        <v>686865</v>
       </c>
       <c r="R103" t="n">
-        <v>6562719</v>
+        <v>6562977</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12548,7 +12548,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12558,7 +12558,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12582,12 +12582,12 @@
       </c>
       <c r="AL103" t="inlineStr">
         <is>
-          <t>På barken och grenarna på en granlåga.</t>
+          <t>Klen torr granlåga.</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>Picea abies # På barken och grenarna på en granlåga.</t>
+          <t>Picea abies # Klen torr granlåga.</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>
@@ -12598,7 +12598,7 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -11092,32 +11092,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126061106</v>
+        <v>126061079</v>
       </c>
       <c r="B91" t="n">
-        <v>90680</v>
+        <v>105396</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2008</v>
+        <v>221144</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -11127,10 +11127,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>686883</v>
+        <v>687082</v>
       </c>
       <c r="R91" t="n">
-        <v>6562742</v>
+        <v>6563241</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11162,7 +11162,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11172,7 +11172,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11192,39 +11192,39 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126061079</v>
+        <v>126061106</v>
       </c>
       <c r="B92" t="n">
-        <v>105396</v>
+        <v>90680</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>221144</v>
+        <v>2008</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -11234,10 +11234,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>687082</v>
+        <v>686883</v>
       </c>
       <c r="R92" t="n">
-        <v>6563241</v>
+        <v>6562742</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11269,7 +11269,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11279,7 +11279,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11299,7 +11299,7 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -11529,10 +11529,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126061081</v>
+        <v>126061099</v>
       </c>
       <c r="B95" t="n">
-        <v>58514</v>
+        <v>98278</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11540,48 +11540,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>208250</v>
+        <v>219790</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>687058</v>
+        <v>686857</v>
       </c>
       <c r="R95" t="n">
-        <v>6563228</v>
+        <v>6562875</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11613,7 +11599,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11623,7 +11609,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11643,17 +11629,17 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126061099</v>
+        <v>126061081</v>
       </c>
       <c r="B96" t="n">
-        <v>98278</v>
+        <v>58514</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11661,34 +11647,48 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>219790</v>
+        <v>208250</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>686857</v>
+        <v>687058</v>
       </c>
       <c r="R96" t="n">
-        <v>6562875</v>
+        <v>6563228</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11720,7 +11720,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11730,7 +11730,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11750,7 +11750,7 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -11092,32 +11092,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126061079</v>
+        <v>126061106</v>
       </c>
       <c r="B91" t="n">
-        <v>105396</v>
+        <v>90680</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>221144</v>
+        <v>2008</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -11127,10 +11127,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>687082</v>
+        <v>686883</v>
       </c>
       <c r="R91" t="n">
-        <v>6563241</v>
+        <v>6562742</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11162,7 +11162,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11172,7 +11172,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11192,39 +11192,39 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126061106</v>
+        <v>126061079</v>
       </c>
       <c r="B92" t="n">
-        <v>90680</v>
+        <v>105396</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2008</v>
+        <v>221144</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -11234,10 +11234,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>686883</v>
+        <v>687082</v>
       </c>
       <c r="R92" t="n">
-        <v>6562742</v>
+        <v>6563241</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11269,7 +11269,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11279,7 +11279,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11299,7 +11299,7 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -11529,10 +11529,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126061099</v>
+        <v>126061081</v>
       </c>
       <c r="B95" t="n">
-        <v>98278</v>
+        <v>58514</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11540,34 +11540,48 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>219790</v>
+        <v>208250</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>686857</v>
+        <v>687058</v>
       </c>
       <c r="R95" t="n">
-        <v>6562875</v>
+        <v>6563228</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11599,7 +11613,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11609,7 +11623,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11629,17 +11643,17 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126061081</v>
+        <v>126061099</v>
       </c>
       <c r="B96" t="n">
-        <v>58514</v>
+        <v>98278</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11647,48 +11661,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>208250</v>
+        <v>219790</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>687058</v>
+        <v>686857</v>
       </c>
       <c r="R96" t="n">
-        <v>6563228</v>
+        <v>6562875</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11720,7 +11720,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11730,7 +11730,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11750,7 +11750,7 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -11092,32 +11092,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126061106</v>
+        <v>126061079</v>
       </c>
       <c r="B91" t="n">
-        <v>90680</v>
+        <v>105396</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2008</v>
+        <v>221144</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -11127,10 +11127,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>686883</v>
+        <v>687082</v>
       </c>
       <c r="R91" t="n">
-        <v>6562742</v>
+        <v>6563241</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11162,7 +11162,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11172,7 +11172,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11192,39 +11192,39 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126061079</v>
+        <v>126061106</v>
       </c>
       <c r="B92" t="n">
-        <v>105396</v>
+        <v>90680</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>221144</v>
+        <v>2008</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Pers.:Pers.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -11234,10 +11234,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>687082</v>
+        <v>686883</v>
       </c>
       <c r="R92" t="n">
-        <v>6563241</v>
+        <v>6562742</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11269,7 +11269,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11279,7 +11279,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11299,17 +11299,17 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126061094</v>
+        <v>126061084</v>
       </c>
       <c r="B93" t="n">
-        <v>98265</v>
+        <v>98278</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11317,43 +11317,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220093</v>
+        <v>219790</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>686866</v>
+        <v>687014</v>
       </c>
       <c r="R93" t="n">
-        <v>6562874</v>
+        <v>6563215</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11385,7 +11376,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11395,7 +11386,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11415,17 +11406,17 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126061084</v>
+        <v>126061094</v>
       </c>
       <c r="B94" t="n">
-        <v>98278</v>
+        <v>98265</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11433,34 +11424,43 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>219790</v>
+        <v>220093</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>687014</v>
+        <v>686866</v>
       </c>
       <c r="R94" t="n">
-        <v>6563215</v>
+        <v>6562874</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11492,7 +11492,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11502,7 +11502,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11522,17 +11522,17 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>126061081</v>
+        <v>126061099</v>
       </c>
       <c r="B95" t="n">
-        <v>58514</v>
+        <v>98278</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11540,48 +11540,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>208250</v>
+        <v>219790</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>687058</v>
+        <v>686857</v>
       </c>
       <c r="R95" t="n">
-        <v>6563228</v>
+        <v>6562875</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11613,7 +11599,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11623,7 +11609,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11643,17 +11629,17 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126061099</v>
+        <v>126061081</v>
       </c>
       <c r="B96" t="n">
-        <v>98278</v>
+        <v>58514</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11661,34 +11647,48 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>219790</v>
+        <v>208250</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>686857</v>
+        <v>687058</v>
       </c>
       <c r="R96" t="n">
-        <v>6562875</v>
+        <v>6563228</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11720,7 +11720,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11730,7 +11730,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11750,17 +11750,17 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126061113</v>
+        <v>126061105</v>
       </c>
       <c r="B97" t="n">
-        <v>95810</v>
+        <v>8436</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11768,43 +11768,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>210</v>
+        <v>106554</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>687032</v>
+        <v>686860</v>
       </c>
       <c r="R97" t="n">
-        <v>6562726</v>
+        <v>6562743</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11836,7 +11827,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11846,7 +11837,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11860,17 +11851,17 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -11888,10 +11879,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>126061105</v>
+        <v>126061113</v>
       </c>
       <c r="B98" t="n">
-        <v>8436</v>
+        <v>95810</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11899,34 +11890,43 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>106554</v>
+        <v>210</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>686860</v>
+        <v>687032</v>
       </c>
       <c r="R98" t="n">
-        <v>6562743</v>
+        <v>6562726</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11958,7 +11958,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11968,7 +11968,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11982,17 +11982,17 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -11306,10 +11306,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>126061084</v>
+        <v>126061094</v>
       </c>
       <c r="B93" t="n">
-        <v>98278</v>
+        <v>98265</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11317,34 +11317,43 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>219790</v>
+        <v>220093</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>687014</v>
+        <v>686866</v>
       </c>
       <c r="R93" t="n">
-        <v>6563215</v>
+        <v>6562874</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11376,7 +11385,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11386,7 +11395,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11406,17 +11415,17 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>126061094</v>
+        <v>126061084</v>
       </c>
       <c r="B94" t="n">
-        <v>98265</v>
+        <v>98278</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11424,43 +11433,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220093</v>
+        <v>219790</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>686866</v>
+        <v>687014</v>
       </c>
       <c r="R94" t="n">
-        <v>6562874</v>
+        <v>6563215</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11492,7 +11492,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11502,7 +11502,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11522,7 +11522,7 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY119"/>
+  <dimension ref="A1:AY122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14375,6 +14375,336 @@
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>127932235</v>
+      </c>
+      <c r="B120" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>686374</v>
+      </c>
+      <c r="R120" t="n">
+        <v>6562987</v>
+      </c>
+      <c r="S120" t="n">
+        <v>25</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>127932426</v>
+      </c>
+      <c r="B121" t="n">
+        <v>98456</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>686998</v>
+      </c>
+      <c r="R121" t="n">
+        <v>6563316</v>
+      </c>
+      <c r="S121" t="n">
+        <v>10</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Återfynd, rapporterad -24 med 3 ex. Nu 5 ex.</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF121" t="inlineStr"/>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>127932257</v>
+      </c>
+      <c r="B122" t="n">
+        <v>57823</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>686696</v>
+      </c>
+      <c r="R122" t="n">
+        <v>6562934</v>
+      </c>
+      <c r="S122" t="n">
+        <v>25</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Troligen 1K.</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY122"/>
+  <dimension ref="A1:AY123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14380,7 +14380,7 @@
         <v>127932235</v>
       </c>
       <c r="B120" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14485,7 +14485,7 @@
         <v>127932426</v>
       </c>
       <c r="B121" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14600,7 +14600,7 @@
         <v>127932257</v>
       </c>
       <c r="B122" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14705,6 +14705,112 @@
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>128090282</v>
+      </c>
+      <c r="B123" t="n">
+        <v>91367</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>687014</v>
+      </c>
+      <c r="R123" t="n">
+        <v>6563225</v>
+      </c>
+      <c r="S123" t="n">
+        <v>10</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Återfynd, tidigare rapporterad -21.</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF123" t="inlineStr"/>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY123"/>
+  <dimension ref="A1:AY124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14380,7 +14380,7 @@
         <v>127932235</v>
       </c>
       <c r="B120" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14485,7 +14485,7 @@
         <v>127932426</v>
       </c>
       <c r="B121" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14600,7 +14600,7 @@
         <v>127932257</v>
       </c>
       <c r="B122" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14811,6 +14811,117 @@
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>128095464</v>
+      </c>
+      <c r="B124" t="n">
+        <v>58503</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>687155</v>
+      </c>
+      <c r="R124" t="n">
+        <v>6563193</v>
+      </c>
+      <c r="S124" t="n">
+        <v>10</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF124" t="inlineStr"/>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -14485,7 +14485,7 @@
         <v>127932426</v>
       </c>
       <c r="B121" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         <v>128090282</v>
       </c>
       <c r="B123" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -14485,7 +14485,7 @@
         <v>127932426</v>
       </c>
       <c r="B121" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         <v>128090282</v>
       </c>
       <c r="B123" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -14485,7 +14485,7 @@
         <v>127932426</v>
       </c>
       <c r="B121" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         <v>128090282</v>
       </c>
       <c r="B123" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY124"/>
+  <dimension ref="A1:AY129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14922,6 +14922,533 @@
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>128342170</v>
+      </c>
+      <c r="B125" t="n">
+        <v>92679</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>686829</v>
+      </c>
+      <c r="R125" t="n">
+        <v>6562774</v>
+      </c>
+      <c r="S125" t="n">
+        <v>10</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>Flera ex som bildade del av en cirkel.</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF125" t="inlineStr"/>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>128341941</v>
+      </c>
+      <c r="B126" t="n">
+        <v>98473</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>687244</v>
+      </c>
+      <c r="R126" t="n">
+        <v>6563404</v>
+      </c>
+      <c r="S126" t="n">
+        <v>10</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF126" t="inlineStr"/>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>128342188</v>
+      </c>
+      <c r="B127" t="n">
+        <v>92647</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>788</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Gul taggsvamp</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Hydnellum geogenium</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>686997</v>
+      </c>
+      <c r="R127" t="n">
+        <v>6562866</v>
+      </c>
+      <c r="S127" t="n">
+        <v>10</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF127" t="inlineStr"/>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>128342241</v>
+      </c>
+      <c r="B128" t="n">
+        <v>57685</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>686940</v>
+      </c>
+      <c r="R128" t="n">
+        <v>6562867</v>
+      </c>
+      <c r="S128" t="n">
+        <v>25</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>128342050</v>
+      </c>
+      <c r="B129" t="n">
+        <v>92681</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>686783</v>
+      </c>
+      <c r="R129" t="n">
+        <v>6563118</v>
+      </c>
+      <c r="S129" t="n">
+        <v>10</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AD129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF129" t="inlineStr"/>
+      <c r="AG129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY129"/>
+  <dimension ref="A1:AY133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15449,6 +15449,410 @@
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>128457646</v>
+      </c>
+      <c r="B130" t="n">
+        <v>90869</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>5741</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Tjockfotad fingersvamp</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Ramaria flavescens</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>686339</v>
+      </c>
+      <c r="R130" t="n">
+        <v>6562998</v>
+      </c>
+      <c r="S130" t="n">
+        <v>10</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AD130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF130" t="inlineStr"/>
+      <c r="AG130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT130" t="inlineStr"/>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>128457880</v>
+      </c>
+      <c r="B131" t="n">
+        <v>92684</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q131" t="n">
+        <v>686912</v>
+      </c>
+      <c r="R131" t="n">
+        <v>6563194</v>
+      </c>
+      <c r="S131" t="n">
+        <v>10</v>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AD131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF131" t="inlineStr"/>
+      <c r="AG131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT131" t="inlineStr"/>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>128457920</v>
+      </c>
+      <c r="B132" t="n">
+        <v>90869</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>5741</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Tjockfotad fingersvamp</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Ramaria flavescens</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>687131</v>
+      </c>
+      <c r="R132" t="n">
+        <v>6563365</v>
+      </c>
+      <c r="S132" t="n">
+        <v>10</v>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AD132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF132" t="inlineStr"/>
+      <c r="AG132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT132" t="inlineStr"/>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>128457904</v>
+      </c>
+      <c r="B133" t="n">
+        <v>92660</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>687015</v>
+      </c>
+      <c r="R133" t="n">
+        <v>6563271</v>
+      </c>
+      <c r="S133" t="n">
+        <v>10</v>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>2025-09-13</t>
+        </is>
+      </c>
+      <c r="AD133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF133" t="inlineStr"/>
+      <c r="AG133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT133" t="inlineStr"/>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -14380,7 +14380,7 @@
         <v>127932235</v>
       </c>
       <c r="B120" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14485,7 +14485,7 @@
         <v>127932426</v>
       </c>
       <c r="B121" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14600,7 +14600,7 @@
         <v>127932257</v>
       </c>
       <c r="B122" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         <v>128090282</v>
       </c>
       <c r="B123" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14816,7 +14816,7 @@
         <v>128095464</v>
       </c>
       <c r="B124" t="n">
-        <v>58503</v>
+        <v>58504</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14927,7 +14927,7 @@
         <v>128342170</v>
       </c>
       <c r="B125" t="n">
-        <v>92679</v>
+        <v>92684</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15033,7 +15033,7 @@
         <v>128341941</v>
       </c>
       <c r="B126" t="n">
-        <v>98473</v>
+        <v>98478</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15143,7 +15143,7 @@
         <v>128342188</v>
       </c>
       <c r="B127" t="n">
-        <v>92647</v>
+        <v>92652</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15244,7 +15244,7 @@
         <v>128342241</v>
       </c>
       <c r="B128" t="n">
-        <v>57685</v>
+        <v>57686</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15353,7 +15353,7 @@
         <v>128342050</v>
       </c>
       <c r="B129" t="n">
-        <v>92681</v>
+        <v>92686</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15555,7 +15555,7 @@
         <v>128457880</v>
       </c>
       <c r="B131" t="n">
-        <v>92684</v>
+        <v>92686</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15757,7 +15757,7 @@
         <v>128457904</v>
       </c>
       <c r="B133" t="n">
-        <v>92660</v>
+        <v>92662</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -14380,7 +14380,7 @@
         <v>127932235</v>
       </c>
       <c r="B120" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14485,7 +14485,7 @@
         <v>127932426</v>
       </c>
       <c r="B121" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14600,7 +14600,7 @@
         <v>127932257</v>
       </c>
       <c r="B122" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         <v>128090282</v>
       </c>
       <c r="B123" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14816,7 +14816,7 @@
         <v>128095464</v>
       </c>
       <c r="B124" t="n">
-        <v>58504</v>
+        <v>58516</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14927,7 +14927,7 @@
         <v>128342170</v>
       </c>
       <c r="B125" t="n">
-        <v>92684</v>
+        <v>92776</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15033,7 +15033,7 @@
         <v>128341941</v>
       </c>
       <c r="B126" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15143,7 +15143,7 @@
         <v>128342188</v>
       </c>
       <c r="B127" t="n">
-        <v>92652</v>
+        <v>92744</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15244,7 +15244,7 @@
         <v>128342241</v>
       </c>
       <c r="B128" t="n">
-        <v>57686</v>
+        <v>57698</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15353,7 +15353,7 @@
         <v>128342050</v>
       </c>
       <c r="B129" t="n">
-        <v>92686</v>
+        <v>92778</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15454,7 +15454,7 @@
         <v>128457646</v>
       </c>
       <c r="B130" t="n">
-        <v>90869</v>
+        <v>90961</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15555,7 +15555,7 @@
         <v>128457880</v>
       </c>
       <c r="B131" t="n">
-        <v>92686</v>
+        <v>92778</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15656,7 +15656,7 @@
         <v>128457920</v>
       </c>
       <c r="B132" t="n">
-        <v>90869</v>
+        <v>90961</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15757,7 +15757,7 @@
         <v>128457904</v>
       </c>
       <c r="B133" t="n">
-        <v>92662</v>
+        <v>92754</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY133"/>
+  <dimension ref="A1:AY134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15853,6 +15853,107 @@
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>128646813</v>
+      </c>
+      <c r="B134" t="n">
+        <v>92085</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>686827</v>
+      </c>
+      <c r="R134" t="n">
+        <v>6563224</v>
+      </c>
+      <c r="S134" t="n">
+        <v>10</v>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF134" t="inlineStr"/>
+      <c r="AG134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT134" t="inlineStr"/>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -15858,7 +15858,7 @@
         <v>128646813</v>
       </c>
       <c r="B134" t="n">
-        <v>92085</v>
+        <v>92090</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -14380,7 +14380,7 @@
         <v>127932235</v>
       </c>
       <c r="B120" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14485,7 +14485,7 @@
         <v>127932426</v>
       </c>
       <c r="B121" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14600,7 +14600,7 @@
         <v>127932257</v>
       </c>
       <c r="B122" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         <v>128090282</v>
       </c>
       <c r="B123" t="n">
-        <v>91470</v>
+        <v>91482</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14816,7 +14816,7 @@
         <v>128095464</v>
       </c>
       <c r="B124" t="n">
-        <v>58516</v>
+        <v>58520</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14927,7 +14927,7 @@
         <v>128342170</v>
       </c>
       <c r="B125" t="n">
-        <v>92776</v>
+        <v>92788</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15033,7 +15033,7 @@
         <v>128341941</v>
       </c>
       <c r="B126" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15143,7 +15143,7 @@
         <v>128342188</v>
       </c>
       <c r="B127" t="n">
-        <v>92744</v>
+        <v>92756</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15244,7 +15244,7 @@
         <v>128342241</v>
       </c>
       <c r="B128" t="n">
-        <v>57698</v>
+        <v>57702</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15353,7 +15353,7 @@
         <v>128342050</v>
       </c>
       <c r="B129" t="n">
-        <v>92778</v>
+        <v>92790</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15454,7 +15454,7 @@
         <v>128457646</v>
       </c>
       <c r="B130" t="n">
-        <v>90961</v>
+        <v>90973</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15555,7 +15555,7 @@
         <v>128457880</v>
       </c>
       <c r="B131" t="n">
-        <v>92778</v>
+        <v>92790</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15656,7 +15656,7 @@
         <v>128457920</v>
       </c>
       <c r="B132" t="n">
-        <v>90961</v>
+        <v>90973</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15757,7 +15757,7 @@
         <v>128457904</v>
       </c>
       <c r="B133" t="n">
-        <v>92754</v>
+        <v>92766</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
         <v>128646813</v>
       </c>
       <c r="B134" t="n">
-        <v>92090</v>
+        <v>92096</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -14927,7 +14927,7 @@
         <v>128342170</v>
       </c>
       <c r="B125" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15033,7 +15033,7 @@
         <v>128341941</v>
       </c>
       <c r="B126" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15143,7 +15143,7 @@
         <v>128342188</v>
       </c>
       <c r="B127" t="n">
-        <v>92756</v>
+        <v>92758</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15353,7 +15353,7 @@
         <v>128342050</v>
       </c>
       <c r="B129" t="n">
-        <v>92790</v>
+        <v>92792</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15454,7 +15454,7 @@
         <v>128457646</v>
       </c>
       <c r="B130" t="n">
-        <v>90973</v>
+        <v>90975</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15555,7 +15555,7 @@
         <v>128457880</v>
       </c>
       <c r="B131" t="n">
-        <v>92790</v>
+        <v>92792</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15656,7 +15656,7 @@
         <v>128457920</v>
       </c>
       <c r="B132" t="n">
-        <v>90973</v>
+        <v>90975</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15757,7 +15757,7 @@
         <v>128457904</v>
       </c>
       <c r="B133" t="n">
-        <v>92766</v>
+        <v>92768</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
         <v>128646813</v>
       </c>
       <c r="B134" t="n">
-        <v>92096</v>
+        <v>92098</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -14710,7 +14710,7 @@
         <v>128090282</v>
       </c>
       <c r="B123" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15033,7 +15033,7 @@
         <v>128341941</v>
       </c>
       <c r="B126" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15552,32 +15552,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128457880</v>
+        <v>128457920</v>
       </c>
       <c r="B131" t="n">
-        <v>92792</v>
+        <v>90975</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5966</v>
+        <v>5741</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -15590,10 +15590,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>686912</v>
+        <v>687131</v>
       </c>
       <c r="R131" t="n">
-        <v>6563194</v>
+        <v>6563365</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15653,32 +15653,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128457920</v>
+        <v>128457880</v>
       </c>
       <c r="B132" t="n">
-        <v>90975</v>
+        <v>92792</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>5741</v>
+        <v>5966</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -15691,10 +15691,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>687131</v>
+        <v>686912</v>
       </c>
       <c r="R132" t="n">
-        <v>6563365</v>
+        <v>6563194</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -14927,7 +14927,7 @@
         <v>128342170</v>
       </c>
       <c r="B125" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15033,7 +15033,7 @@
         <v>128341941</v>
       </c>
       <c r="B126" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15143,7 +15143,7 @@
         <v>128342188</v>
       </c>
       <c r="B127" t="n">
-        <v>92758</v>
+        <v>92759</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15353,7 +15353,7 @@
         <v>128342050</v>
       </c>
       <c r="B129" t="n">
-        <v>92792</v>
+        <v>92793</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15454,7 +15454,7 @@
         <v>128457646</v>
       </c>
       <c r="B130" t="n">
-        <v>90975</v>
+        <v>90976</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15552,32 +15552,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128457920</v>
+        <v>128457880</v>
       </c>
       <c r="B131" t="n">
-        <v>90975</v>
+        <v>92793</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5741</v>
+        <v>5966</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -15590,10 +15590,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>687131</v>
+        <v>686912</v>
       </c>
       <c r="R131" t="n">
-        <v>6563365</v>
+        <v>6563194</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15653,32 +15653,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128457880</v>
+        <v>128457920</v>
       </c>
       <c r="B132" t="n">
-        <v>92792</v>
+        <v>90976</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>5966</v>
+        <v>5741</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -15691,10 +15691,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>686912</v>
+        <v>687131</v>
       </c>
       <c r="R132" t="n">
-        <v>6563194</v>
+        <v>6563365</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15757,7 +15757,7 @@
         <v>128457904</v>
       </c>
       <c r="B133" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
         <v>128646813</v>
       </c>
       <c r="B134" t="n">
-        <v>92098</v>
+        <v>92099</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -15858,7 +15858,7 @@
         <v>128646813</v>
       </c>
       <c r="B134" t="n">
-        <v>92099</v>
+        <v>92126</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -14927,7 +14927,7 @@
         <v>128342170</v>
       </c>
       <c r="B125" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15033,7 +15033,7 @@
         <v>128341941</v>
       </c>
       <c r="B126" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15143,7 +15143,7 @@
         <v>128342188</v>
       </c>
       <c r="B127" t="n">
-        <v>92759</v>
+        <v>92786</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15244,7 +15244,7 @@
         <v>128342241</v>
       </c>
       <c r="B128" t="n">
-        <v>57702</v>
+        <v>57729</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15353,7 +15353,7 @@
         <v>128342050</v>
       </c>
       <c r="B129" t="n">
-        <v>92793</v>
+        <v>92820</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15454,7 +15454,7 @@
         <v>128457646</v>
       </c>
       <c r="B130" t="n">
-        <v>90976</v>
+        <v>91003</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15552,32 +15552,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128457880</v>
+        <v>128457920</v>
       </c>
       <c r="B131" t="n">
-        <v>92793</v>
+        <v>91003</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5966</v>
+        <v>5741</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -15590,10 +15590,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>686912</v>
+        <v>687131</v>
       </c>
       <c r="R131" t="n">
-        <v>6563194</v>
+        <v>6563365</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15653,32 +15653,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128457920</v>
+        <v>128457880</v>
       </c>
       <c r="B132" t="n">
-        <v>90976</v>
+        <v>92820</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>5741</v>
+        <v>5966</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -15691,10 +15691,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>687131</v>
+        <v>686912</v>
       </c>
       <c r="R132" t="n">
-        <v>6563365</v>
+        <v>6563194</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15757,7 +15757,7 @@
         <v>128457904</v>
       </c>
       <c r="B133" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -15552,32 +15552,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128457920</v>
+        <v>128457880</v>
       </c>
       <c r="B131" t="n">
-        <v>91003</v>
+        <v>92820</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5741</v>
+        <v>5966</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -15590,10 +15590,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>687131</v>
+        <v>686912</v>
       </c>
       <c r="R131" t="n">
-        <v>6563365</v>
+        <v>6563194</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15653,32 +15653,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128457880</v>
+        <v>128457920</v>
       </c>
       <c r="B132" t="n">
-        <v>92820</v>
+        <v>91003</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>5966</v>
+        <v>5741</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -15691,10 +15691,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>686912</v>
+        <v>687131</v>
       </c>
       <c r="R132" t="n">
-        <v>6563194</v>
+        <v>6563365</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15858,7 +15858,7 @@
         <v>128646813</v>
       </c>
       <c r="B134" t="n">
-        <v>92126</v>
+        <v>92131</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -14927,7 +14927,7 @@
         <v>128342170</v>
       </c>
       <c r="B125" t="n">
-        <v>92818</v>
+        <v>92830</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15033,7 +15033,7 @@
         <v>128341941</v>
       </c>
       <c r="B126" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15143,7 +15143,7 @@
         <v>128342188</v>
       </c>
       <c r="B127" t="n">
-        <v>92786</v>
+        <v>92796</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15353,7 +15353,7 @@
         <v>128342050</v>
       </c>
       <c r="B129" t="n">
-        <v>92820</v>
+        <v>92832</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15454,7 +15454,7 @@
         <v>128457646</v>
       </c>
       <c r="B130" t="n">
-        <v>91003</v>
+        <v>91013</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15555,7 +15555,7 @@
         <v>128457880</v>
       </c>
       <c r="B131" t="n">
-        <v>92820</v>
+        <v>92832</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15656,7 +15656,7 @@
         <v>128457920</v>
       </c>
       <c r="B132" t="n">
-        <v>91003</v>
+        <v>91013</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15757,7 +15757,7 @@
         <v>128457904</v>
       </c>
       <c r="B133" t="n">
-        <v>92796</v>
+        <v>92806</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
         <v>128646813</v>
       </c>
       <c r="B134" t="n">
-        <v>92131</v>
+        <v>92136</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -15552,32 +15552,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128457880</v>
+        <v>128457920</v>
       </c>
       <c r="B131" t="n">
-        <v>92832</v>
+        <v>91013</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5966</v>
+        <v>5741</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -15590,10 +15590,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>686912</v>
+        <v>687131</v>
       </c>
       <c r="R131" t="n">
-        <v>6563194</v>
+        <v>6563365</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15653,32 +15653,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128457920</v>
+        <v>128457880</v>
       </c>
       <c r="B132" t="n">
-        <v>91013</v>
+        <v>92832</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>5741</v>
+        <v>5966</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -15691,10 +15691,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>687131</v>
+        <v>686912</v>
       </c>
       <c r="R132" t="n">
-        <v>6563365</v>
+        <v>6563194</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -15552,32 +15552,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128457920</v>
+        <v>128457880</v>
       </c>
       <c r="B131" t="n">
-        <v>91013</v>
+        <v>92832</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5741</v>
+        <v>5966</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -15590,10 +15590,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>687131</v>
+        <v>686912</v>
       </c>
       <c r="R131" t="n">
-        <v>6563365</v>
+        <v>6563194</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15653,32 +15653,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128457880</v>
+        <v>128457920</v>
       </c>
       <c r="B132" t="n">
-        <v>92832</v>
+        <v>91013</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>5966</v>
+        <v>5741</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -15691,10 +15691,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>686912</v>
+        <v>687131</v>
       </c>
       <c r="R132" t="n">
-        <v>6563194</v>
+        <v>6563365</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15858,7 +15858,7 @@
         <v>128646813</v>
       </c>
       <c r="B134" t="n">
-        <v>92136</v>
+        <v>92140</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -14927,7 +14927,7 @@
         <v>128342170</v>
       </c>
       <c r="B125" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15033,7 +15033,7 @@
         <v>128341941</v>
       </c>
       <c r="B126" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15143,7 +15143,7 @@
         <v>128342188</v>
       </c>
       <c r="B127" t="n">
-        <v>92796</v>
+        <v>92800</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15244,7 +15244,7 @@
         <v>128342241</v>
       </c>
       <c r="B128" t="n">
-        <v>57729</v>
+        <v>57733</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15353,7 +15353,7 @@
         <v>128342050</v>
       </c>
       <c r="B129" t="n">
-        <v>92832</v>
+        <v>92836</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15454,7 +15454,7 @@
         <v>128457646</v>
       </c>
       <c r="B130" t="n">
-        <v>91013</v>
+        <v>91017</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15555,7 +15555,7 @@
         <v>128457880</v>
       </c>
       <c r="B131" t="n">
-        <v>92832</v>
+        <v>92836</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15656,7 +15656,7 @@
         <v>128457920</v>
       </c>
       <c r="B132" t="n">
-        <v>91013</v>
+        <v>91017</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15757,7 +15757,7 @@
         <v>128457904</v>
       </c>
       <c r="B133" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -15454,7 +15454,7 @@
         <v>128457646</v>
       </c>
       <c r="B130" t="n">
-        <v>91017</v>
+        <v>91022</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15555,7 +15555,7 @@
         <v>128457880</v>
       </c>
       <c r="B131" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15656,7 +15656,7 @@
         <v>128457920</v>
       </c>
       <c r="B132" t="n">
-        <v>91017</v>
+        <v>91022</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15757,7 +15757,7 @@
         <v>128457904</v>
       </c>
       <c r="B133" t="n">
-        <v>92810</v>
+        <v>92815</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
         <v>128646813</v>
       </c>
       <c r="B134" t="n">
-        <v>92140</v>
+        <v>92145</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -15858,7 +15858,7 @@
         <v>128646813</v>
       </c>
       <c r="B134" t="n">
-        <v>92148</v>
+        <v>92153</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY134"/>
+  <dimension ref="A1:AY135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15858,7 +15858,7 @@
         <v>128646813</v>
       </c>
       <c r="B134" t="n">
-        <v>92153</v>
+        <v>92161</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15954,6 +15954,107 @@
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>129192275</v>
+      </c>
+      <c r="B135" t="n">
+        <v>91738</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>1106</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Vågticka</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Osteina undosa</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>(Peck) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>687142</v>
+      </c>
+      <c r="R135" t="n">
+        <v>6563332</v>
+      </c>
+      <c r="S135" t="n">
+        <v>10</v>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AD135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF135" t="inlineStr"/>
+      <c r="AG135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT135" t="inlineStr"/>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY135"/>
+  <dimension ref="A1:AY143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16055,6 +16055,826 @@
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>129215511</v>
+      </c>
+      <c r="B136" t="n">
+        <v>91738</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>1106</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Vågticka</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Osteina undosa</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>(Peck) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q136" t="n">
+        <v>686884</v>
+      </c>
+      <c r="R136" t="n">
+        <v>6563284</v>
+      </c>
+      <c r="S136" t="n">
+        <v>10</v>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF136" t="inlineStr"/>
+      <c r="AG136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT136" t="inlineStr"/>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>129214830</v>
+      </c>
+      <c r="B137" t="n">
+        <v>91540</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q137" t="n">
+        <v>686505</v>
+      </c>
+      <c r="R137" t="n">
+        <v>6562950</v>
+      </c>
+      <c r="S137" t="n">
+        <v>10</v>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF137" t="inlineStr"/>
+      <c r="AG137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT137" t="inlineStr"/>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>129214713</v>
+      </c>
+      <c r="B138" t="n">
+        <v>91540</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>686402</v>
+      </c>
+      <c r="R138" t="n">
+        <v>6562993</v>
+      </c>
+      <c r="S138" t="n">
+        <v>10</v>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF138" t="inlineStr"/>
+      <c r="AG138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT138" t="inlineStr"/>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>129215212</v>
+      </c>
+      <c r="B139" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr"/>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>686971</v>
+      </c>
+      <c r="R139" t="n">
+        <v>6563132</v>
+      </c>
+      <c r="S139" t="n">
+        <v>25</v>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT139" t="inlineStr"/>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>129215334</v>
+      </c>
+      <c r="B140" t="n">
+        <v>91540</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>687145</v>
+      </c>
+      <c r="R140" t="n">
+        <v>6563332</v>
+      </c>
+      <c r="S140" t="n">
+        <v>10</v>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF140" t="inlineStr"/>
+      <c r="AG140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT140" t="inlineStr"/>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>129215416</v>
+      </c>
+      <c r="B141" t="n">
+        <v>57883</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr"/>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q141" t="n">
+        <v>687154</v>
+      </c>
+      <c r="R141" t="n">
+        <v>6563315</v>
+      </c>
+      <c r="S141" t="n">
+        <v>25</v>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT141" t="inlineStr"/>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>129214787</v>
+      </c>
+      <c r="B142" t="n">
+        <v>91526</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>686486</v>
+      </c>
+      <c r="R142" t="n">
+        <v>6562977</v>
+      </c>
+      <c r="S142" t="n">
+        <v>10</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF142" t="inlineStr"/>
+      <c r="AG142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT142" t="inlineStr"/>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>129215443</v>
+      </c>
+      <c r="B143" t="n">
+        <v>91491</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>687192</v>
+      </c>
+      <c r="R143" t="n">
+        <v>6563253</v>
+      </c>
+      <c r="S143" t="n">
+        <v>10</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF143" t="inlineStr"/>
+      <c r="AG143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT143" t="inlineStr"/>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -16158,7 +16158,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129214830</v>
+        <v>129214713</v>
       </c>
       <c r="B137" t="n">
         <v>91540</v>
@@ -16196,10 +16196,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>686505</v>
+        <v>686402</v>
       </c>
       <c r="R137" t="n">
-        <v>6562950</v>
+        <v>6562993</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16259,7 +16259,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129214713</v>
+        <v>129214830</v>
       </c>
       <c r="B138" t="n">
         <v>91540</v>
@@ -16297,10 +16297,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>686402</v>
+        <v>686505</v>
       </c>
       <c r="R138" t="n">
-        <v>6562993</v>
+        <v>6562950</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16570,10 +16570,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129215416</v>
+        <v>129214787</v>
       </c>
       <c r="B141" t="n">
-        <v>57883</v>
+        <v>91526</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16581,31 +16581,26 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
@@ -16613,13 +16608,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>687154</v>
+        <v>686486</v>
       </c>
       <c r="R141" t="n">
-        <v>6563315</v>
+        <v>6562977</v>
       </c>
       <c r="S141" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -16657,6 +16652,7 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
+      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -16675,10 +16671,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129214787</v>
+        <v>129215416</v>
       </c>
       <c r="B142" t="n">
-        <v>91526</v>
+        <v>57883</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16686,26 +16682,31 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
@@ -16713,13 +16714,13 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>686486</v>
+        <v>687154</v>
       </c>
       <c r="R142" t="n">
-        <v>6562977</v>
+        <v>6563315</v>
       </c>
       <c r="S142" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -16757,7 +16758,6 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
-      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -15858,7 +15858,7 @@
         <v>128646813</v>
       </c>
       <c r="B134" t="n">
-        <v>92161</v>
+        <v>92168</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15959,7 +15959,7 @@
         <v>129192275</v>
       </c>
       <c r="B135" t="n">
-        <v>91738</v>
+        <v>91745</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16060,7 +16060,7 @@
         <v>129215511</v>
       </c>
       <c r="B136" t="n">
-        <v>91738</v>
+        <v>91745</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16158,10 +16158,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129214713</v>
+        <v>129214830</v>
       </c>
       <c r="B137" t="n">
-        <v>91540</v>
+        <v>91547</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16196,10 +16196,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>686402</v>
+        <v>686505</v>
       </c>
       <c r="R137" t="n">
-        <v>6562993</v>
+        <v>6562950</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16259,10 +16259,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129214830</v>
+        <v>129214713</v>
       </c>
       <c r="B138" t="n">
-        <v>91540</v>
+        <v>91547</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16297,10 +16297,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>686505</v>
+        <v>686402</v>
       </c>
       <c r="R138" t="n">
-        <v>6562950</v>
+        <v>6562993</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16363,7 +16363,7 @@
         <v>129215212</v>
       </c>
       <c r="B139" t="n">
-        <v>57736</v>
+        <v>57738</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16472,7 +16472,7 @@
         <v>129215334</v>
       </c>
       <c r="B140" t="n">
-        <v>91540</v>
+        <v>91547</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16573,7 +16573,7 @@
         <v>129214787</v>
       </c>
       <c r="B141" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16674,7 +16674,7 @@
         <v>129215416</v>
       </c>
       <c r="B142" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16779,7 +16779,7 @@
         <v>129215443</v>
       </c>
       <c r="B143" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -15959,7 +15959,7 @@
         <v>129192275</v>
       </c>
       <c r="B135" t="n">
-        <v>91745</v>
+        <v>91752</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16060,7 +16060,7 @@
         <v>129215511</v>
       </c>
       <c r="B136" t="n">
-        <v>91745</v>
+        <v>91752</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16161,7 +16161,7 @@
         <v>129214830</v>
       </c>
       <c r="B137" t="n">
-        <v>91547</v>
+        <v>91554</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16262,7 +16262,7 @@
         <v>129214713</v>
       </c>
       <c r="B138" t="n">
-        <v>91547</v>
+        <v>91554</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16472,7 +16472,7 @@
         <v>129215334</v>
       </c>
       <c r="B140" t="n">
-        <v>91547</v>
+        <v>91554</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16573,7 +16573,7 @@
         <v>129214787</v>
       </c>
       <c r="B141" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16779,7 +16779,7 @@
         <v>129215443</v>
       </c>
       <c r="B143" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -15959,7 +15959,7 @@
         <v>129192275</v>
       </c>
       <c r="B135" t="n">
-        <v>91752</v>
+        <v>91754</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16060,7 +16060,7 @@
         <v>129215511</v>
       </c>
       <c r="B136" t="n">
-        <v>91752</v>
+        <v>91754</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16158,10 +16158,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129214830</v>
+        <v>129214713</v>
       </c>
       <c r="B137" t="n">
-        <v>91554</v>
+        <v>91556</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16196,10 +16196,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>686505</v>
+        <v>686402</v>
       </c>
       <c r="R137" t="n">
-        <v>6562950</v>
+        <v>6562993</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16259,10 +16259,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129214713</v>
+        <v>129214830</v>
       </c>
       <c r="B138" t="n">
-        <v>91554</v>
+        <v>91556</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16297,10 +16297,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>686402</v>
+        <v>686505</v>
       </c>
       <c r="R138" t="n">
-        <v>6562993</v>
+        <v>6562950</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16363,7 +16363,7 @@
         <v>129215212</v>
       </c>
       <c r="B139" t="n">
-        <v>57738</v>
+        <v>57740</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16472,7 +16472,7 @@
         <v>129215334</v>
       </c>
       <c r="B140" t="n">
-        <v>91554</v>
+        <v>91556</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16573,7 +16573,7 @@
         <v>129214787</v>
       </c>
       <c r="B141" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16674,7 +16674,7 @@
         <v>129215416</v>
       </c>
       <c r="B142" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16779,7 +16779,7 @@
         <v>129215443</v>
       </c>
       <c r="B143" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -16158,7 +16158,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129214713</v>
+        <v>129214830</v>
       </c>
       <c r="B137" t="n">
         <v>91556</v>
@@ -16196,10 +16196,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>686402</v>
+        <v>686505</v>
       </c>
       <c r="R137" t="n">
-        <v>6562993</v>
+        <v>6562950</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16259,7 +16259,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129214830</v>
+        <v>129214713</v>
       </c>
       <c r="B138" t="n">
         <v>91556</v>
@@ -16297,10 +16297,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>686505</v>
+        <v>686402</v>
       </c>
       <c r="R138" t="n">
-        <v>6562950</v>
+        <v>6562993</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -15959,7 +15959,7 @@
         <v>129192275</v>
       </c>
       <c r="B135" t="n">
-        <v>91754</v>
+        <v>91763</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16060,7 +16060,7 @@
         <v>129215511</v>
       </c>
       <c r="B136" t="n">
-        <v>91754</v>
+        <v>91763</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16161,7 +16161,7 @@
         <v>129214830</v>
       </c>
       <c r="B137" t="n">
-        <v>91556</v>
+        <v>91554</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16262,7 +16262,7 @@
         <v>129214713</v>
       </c>
       <c r="B138" t="n">
-        <v>91556</v>
+        <v>91554</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16472,7 +16472,7 @@
         <v>129215334</v>
       </c>
       <c r="B140" t="n">
-        <v>91556</v>
+        <v>91554</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16573,7 +16573,7 @@
         <v>129214787</v>
       </c>
       <c r="B141" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16779,7 +16779,7 @@
         <v>129215443</v>
       </c>
       <c r="B143" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -15959,7 +15959,7 @@
         <v>129192275</v>
       </c>
       <c r="B135" t="n">
-        <v>91763</v>
+        <v>91764</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16060,7 +16060,7 @@
         <v>129215511</v>
       </c>
       <c r="B136" t="n">
-        <v>91763</v>
+        <v>91764</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16158,7 +16158,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129214830</v>
+        <v>129214713</v>
       </c>
       <c r="B137" t="n">
         <v>91554</v>
@@ -16196,10 +16196,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>686505</v>
+        <v>686402</v>
       </c>
       <c r="R137" t="n">
-        <v>6562950</v>
+        <v>6562993</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16259,7 +16259,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129214713</v>
+        <v>129214830</v>
       </c>
       <c r="B138" t="n">
         <v>91554</v>
@@ -16297,10 +16297,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>686402</v>
+        <v>686505</v>
       </c>
       <c r="R138" t="n">
-        <v>6562993</v>
+        <v>6562950</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -16158,7 +16158,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129214713</v>
+        <v>129214830</v>
       </c>
       <c r="B137" t="n">
         <v>91554</v>
@@ -16196,10 +16196,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>686402</v>
+        <v>686505</v>
       </c>
       <c r="R137" t="n">
-        <v>6562993</v>
+        <v>6562950</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16259,7 +16259,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129214830</v>
+        <v>129214713</v>
       </c>
       <c r="B138" t="n">
         <v>91554</v>
@@ -16297,10 +16297,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>686505</v>
+        <v>686402</v>
       </c>
       <c r="R138" t="n">
-        <v>6562950</v>
+        <v>6562993</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -15959,7 +15959,7 @@
         <v>129192275</v>
       </c>
       <c r="B135" t="n">
-        <v>91764</v>
+        <v>91767</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16060,7 +16060,7 @@
         <v>129215511</v>
       </c>
       <c r="B136" t="n">
-        <v>91764</v>
+        <v>91767</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16158,10 +16158,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129214830</v>
+        <v>129214713</v>
       </c>
       <c r="B137" t="n">
-        <v>91554</v>
+        <v>91557</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16196,10 +16196,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>686505</v>
+        <v>686402</v>
       </c>
       <c r="R137" t="n">
-        <v>6562950</v>
+        <v>6562993</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16259,10 +16259,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129214713</v>
+        <v>129214830</v>
       </c>
       <c r="B138" t="n">
-        <v>91554</v>
+        <v>91557</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16297,10 +16297,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>686402</v>
+        <v>686505</v>
       </c>
       <c r="R138" t="n">
-        <v>6562993</v>
+        <v>6562950</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16472,7 +16472,7 @@
         <v>129215334</v>
       </c>
       <c r="B140" t="n">
-        <v>91554</v>
+        <v>91557</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16573,7 +16573,7 @@
         <v>129214787</v>
       </c>
       <c r="B141" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16779,7 +16779,7 @@
         <v>129215443</v>
       </c>
       <c r="B143" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -15959,7 +15959,7 @@
         <v>129192275</v>
       </c>
       <c r="B135" t="n">
-        <v>91767</v>
+        <v>91769</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16060,7 +16060,7 @@
         <v>129215511</v>
       </c>
       <c r="B136" t="n">
-        <v>91767</v>
+        <v>91769</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16161,7 +16161,7 @@
         <v>129214713</v>
       </c>
       <c r="B137" t="n">
-        <v>91557</v>
+        <v>91559</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16262,7 +16262,7 @@
         <v>129214830</v>
       </c>
       <c r="B138" t="n">
-        <v>91557</v>
+        <v>91559</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16472,7 +16472,7 @@
         <v>129215334</v>
       </c>
       <c r="B140" t="n">
-        <v>91557</v>
+        <v>91559</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16573,7 +16573,7 @@
         <v>129214787</v>
       </c>
       <c r="B141" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16779,7 +16779,7 @@
         <v>129215443</v>
       </c>
       <c r="B143" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -15959,7 +15959,7 @@
         <v>129192275</v>
       </c>
       <c r="B135" t="n">
-        <v>91769</v>
+        <v>91773</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16060,7 +16060,7 @@
         <v>129215511</v>
       </c>
       <c r="B136" t="n">
-        <v>91769</v>
+        <v>91773</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16158,10 +16158,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129214713</v>
+        <v>129214830</v>
       </c>
       <c r="B137" t="n">
-        <v>91559</v>
+        <v>91563</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16196,10 +16196,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>686402</v>
+        <v>686505</v>
       </c>
       <c r="R137" t="n">
-        <v>6562993</v>
+        <v>6562950</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16259,10 +16259,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129214830</v>
+        <v>129214713</v>
       </c>
       <c r="B138" t="n">
-        <v>91559</v>
+        <v>91563</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16297,10 +16297,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>686505</v>
+        <v>686402</v>
       </c>
       <c r="R138" t="n">
-        <v>6562950</v>
+        <v>6562993</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16472,7 +16472,7 @@
         <v>129215334</v>
       </c>
       <c r="B140" t="n">
-        <v>91559</v>
+        <v>91563</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16573,7 +16573,7 @@
         <v>129214787</v>
       </c>
       <c r="B141" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16779,7 +16779,7 @@
         <v>129215443</v>
       </c>
       <c r="B143" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -15959,7 +15959,7 @@
         <v>129192275</v>
       </c>
       <c r="B135" t="n">
-        <v>91773</v>
+        <v>91774</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16060,7 +16060,7 @@
         <v>129215511</v>
       </c>
       <c r="B136" t="n">
-        <v>91773</v>
+        <v>91774</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16161,7 +16161,7 @@
         <v>129214830</v>
       </c>
       <c r="B137" t="n">
-        <v>91563</v>
+        <v>91564</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16262,7 +16262,7 @@
         <v>129214713</v>
       </c>
       <c r="B138" t="n">
-        <v>91563</v>
+        <v>91564</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16472,7 +16472,7 @@
         <v>129215334</v>
       </c>
       <c r="B140" t="n">
-        <v>91563</v>
+        <v>91564</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16573,7 +16573,7 @@
         <v>129214787</v>
       </c>
       <c r="B141" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16779,7 +16779,7 @@
         <v>129215443</v>
       </c>
       <c r="B143" t="n">
-        <v>91513</v>
+        <v>91514</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY143"/>
+  <dimension ref="A1:AY147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16875,6 +16875,426 @@
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>129564502</v>
+      </c>
+      <c r="B144" t="n">
+        <v>90596</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>889</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Vintertagging</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Plicatura pendula</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>686875</v>
+      </c>
+      <c r="R144" t="n">
+        <v>6563120</v>
+      </c>
+      <c r="S144" t="n">
+        <v>10</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>På levande tall. Återfynd, rapporterad 2020.</t>
+        </is>
+      </c>
+      <c r="AD144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF144" t="inlineStr"/>
+      <c r="AG144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT144" t="inlineStr"/>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>129564176</v>
+      </c>
+      <c r="B145" t="n">
+        <v>91571</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>686792</v>
+      </c>
+      <c r="R145" t="n">
+        <v>6563037</v>
+      </c>
+      <c r="S145" t="n">
+        <v>10</v>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>Återfynd. Rapporterad 2021.</t>
+        </is>
+      </c>
+      <c r="AD145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF145" t="inlineStr"/>
+      <c r="AG145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT145" t="inlineStr"/>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>129564285</v>
+      </c>
+      <c r="B146" t="n">
+        <v>98724</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q146" t="n">
+        <v>686625</v>
+      </c>
+      <c r="R146" t="n">
+        <v>6563000</v>
+      </c>
+      <c r="S146" t="n">
+        <v>10</v>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AD146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF146" t="inlineStr"/>
+      <c r="AG146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT146" t="inlineStr"/>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>129563617</v>
+      </c>
+      <c r="B147" t="n">
+        <v>90596</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>889</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Vintertagging</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Plicatura pendula</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>686665</v>
+      </c>
+      <c r="R147" t="n">
+        <v>6563014</v>
+      </c>
+      <c r="S147" t="n">
+        <v>10</v>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>På¨levande tall.</t>
+        </is>
+      </c>
+      <c r="AD147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF147" t="inlineStr"/>
+      <c r="AG147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT147" t="inlineStr"/>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY147"/>
+  <dimension ref="A1:AY148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15959,7 +15959,7 @@
         <v>129192275</v>
       </c>
       <c r="B135" t="n">
-        <v>91774</v>
+        <v>91777</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16060,7 +16060,7 @@
         <v>129215511</v>
       </c>
       <c r="B136" t="n">
-        <v>91774</v>
+        <v>91777</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16161,7 +16161,7 @@
         <v>129214830</v>
       </c>
       <c r="B137" t="n">
-        <v>91564</v>
+        <v>91567</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16262,7 +16262,7 @@
         <v>129214713</v>
       </c>
       <c r="B138" t="n">
-        <v>91564</v>
+        <v>91567</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16472,7 +16472,7 @@
         <v>129215334</v>
       </c>
       <c r="B140" t="n">
-        <v>91564</v>
+        <v>91567</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16573,7 +16573,7 @@
         <v>129214787</v>
       </c>
       <c r="B141" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16779,7 +16779,7 @@
         <v>129215443</v>
       </c>
       <c r="B143" t="n">
-        <v>91514</v>
+        <v>91517</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16880,7 +16880,7 @@
         <v>129564502</v>
       </c>
       <c r="B144" t="n">
-        <v>90596</v>
+        <v>90599</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16986,7 +16986,7 @@
         <v>129564176</v>
       </c>
       <c r="B145" t="n">
-        <v>91571</v>
+        <v>91574</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17092,7 +17092,7 @@
         <v>129564285</v>
       </c>
       <c r="B146" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17194,7 +17194,7 @@
         <v>129563617</v>
       </c>
       <c r="B147" t="n">
-        <v>90596</v>
+        <v>90599</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17295,6 +17295,116 @@
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>129592077</v>
+      </c>
+      <c r="B148" t="n">
+        <v>79044</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr"/>
+      <c r="K148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q148" t="n">
+        <v>686804</v>
+      </c>
+      <c r="R148" t="n">
+        <v>6563019</v>
+      </c>
+      <c r="S148" t="n">
+        <v>10</v>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>Återfynd, tidigare rapporterad 2021.</t>
+        </is>
+      </c>
+      <c r="AD148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF148" t="inlineStr"/>
+      <c r="AG148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT148" t="inlineStr"/>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -16570,10 +16570,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129214787</v>
+        <v>129215416</v>
       </c>
       <c r="B141" t="n">
-        <v>91553</v>
+        <v>57887</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16581,26 +16581,31 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
@@ -16608,13 +16613,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>686486</v>
+        <v>687154</v>
       </c>
       <c r="R141" t="n">
-        <v>6562977</v>
+        <v>6563315</v>
       </c>
       <c r="S141" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -16652,7 +16657,6 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
-      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -16671,10 +16675,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129215416</v>
+        <v>129214787</v>
       </c>
       <c r="B142" t="n">
-        <v>57887</v>
+        <v>91553</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16682,31 +16686,26 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
@@ -16714,13 +16713,13 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>687154</v>
+        <v>686486</v>
       </c>
       <c r="R142" t="n">
-        <v>6563315</v>
+        <v>6562977</v>
       </c>
       <c r="S142" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -16758,6 +16757,7 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
+      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -16570,10 +16570,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129215416</v>
+        <v>129214787</v>
       </c>
       <c r="B141" t="n">
-        <v>57887</v>
+        <v>91553</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16581,31 +16581,26 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
@@ -16613,13 +16608,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>687154</v>
+        <v>686486</v>
       </c>
       <c r="R141" t="n">
-        <v>6563315</v>
+        <v>6562977</v>
       </c>
       <c r="S141" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -16657,6 +16652,7 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
+      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -16675,10 +16671,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129214787</v>
+        <v>129215416</v>
       </c>
       <c r="B142" t="n">
-        <v>91553</v>
+        <v>57887</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16686,26 +16682,31 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
@@ -16713,13 +16714,13 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>686486</v>
+        <v>687154</v>
       </c>
       <c r="R142" t="n">
-        <v>6562977</v>
+        <v>6563315</v>
       </c>
       <c r="S142" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -16757,7 +16758,6 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
-      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -15959,7 +15959,7 @@
         <v>129192275</v>
       </c>
       <c r="B135" t="n">
-        <v>91777</v>
+        <v>91805</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16060,7 +16060,7 @@
         <v>129215511</v>
       </c>
       <c r="B136" t="n">
-        <v>91777</v>
+        <v>91805</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16161,7 +16161,7 @@
         <v>129214830</v>
       </c>
       <c r="B137" t="n">
-        <v>91567</v>
+        <v>91595</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16262,7 +16262,7 @@
         <v>129214713</v>
       </c>
       <c r="B138" t="n">
-        <v>91567</v>
+        <v>91595</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16363,7 +16363,7 @@
         <v>129215212</v>
       </c>
       <c r="B139" t="n">
-        <v>57740</v>
+        <v>57743</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16472,7 +16472,7 @@
         <v>129215334</v>
       </c>
       <c r="B140" t="n">
-        <v>91567</v>
+        <v>91595</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16570,10 +16570,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129215416</v>
+        <v>129214787</v>
       </c>
       <c r="B141" t="n">
-        <v>57887</v>
+        <v>91581</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16581,31 +16581,26 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
@@ -16613,13 +16608,13 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>687154</v>
+        <v>686486</v>
       </c>
       <c r="R141" t="n">
-        <v>6563315</v>
+        <v>6562977</v>
       </c>
       <c r="S141" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -16657,6 +16652,7 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
+      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -16675,10 +16671,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129214787</v>
+        <v>129215416</v>
       </c>
       <c r="B142" t="n">
-        <v>91553</v>
+        <v>57890</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16686,26 +16682,31 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
@@ -16713,13 +16714,13 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>686486</v>
+        <v>687154</v>
       </c>
       <c r="R142" t="n">
-        <v>6562977</v>
+        <v>6563315</v>
       </c>
       <c r="S142" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -16757,7 +16758,6 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
-      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -16779,7 +16779,7 @@
         <v>129215443</v>
       </c>
       <c r="B143" t="n">
-        <v>91517</v>
+        <v>91545</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16880,7 +16880,7 @@
         <v>129564502</v>
       </c>
       <c r="B144" t="n">
-        <v>90599</v>
+        <v>90627</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16986,7 +16986,7 @@
         <v>129564176</v>
       </c>
       <c r="B145" t="n">
-        <v>91574</v>
+        <v>91602</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17092,7 +17092,7 @@
         <v>129564285</v>
       </c>
       <c r="B146" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17194,7 +17194,7 @@
         <v>129563617</v>
       </c>
       <c r="B147" t="n">
-        <v>90599</v>
+        <v>90627</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17300,7 +17300,7 @@
         <v>129592077</v>
       </c>
       <c r="B148" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -16880,7 +16880,7 @@
         <v>129564502</v>
       </c>
       <c r="B144" t="n">
-        <v>90627</v>
+        <v>90633</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16986,7 +16986,7 @@
         <v>129564176</v>
       </c>
       <c r="B145" t="n">
-        <v>91602</v>
+        <v>91608</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17092,7 +17092,7 @@
         <v>129564285</v>
       </c>
       <c r="B146" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17194,7 +17194,7 @@
         <v>129563617</v>
       </c>
       <c r="B147" t="n">
-        <v>90627</v>
+        <v>90633</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17300,7 +17300,7 @@
         <v>129592077</v>
       </c>
       <c r="B148" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -16880,7 +16880,7 @@
         <v>129564502</v>
       </c>
       <c r="B144" t="n">
-        <v>90633</v>
+        <v>90634</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16986,7 +16986,7 @@
         <v>129564176</v>
       </c>
       <c r="B145" t="n">
-        <v>91608</v>
+        <v>91609</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17092,7 +17092,7 @@
         <v>129564285</v>
       </c>
       <c r="B146" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17194,7 +17194,7 @@
         <v>129563617</v>
       </c>
       <c r="B147" t="n">
-        <v>90633</v>
+        <v>90634</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17300,7 +17300,7 @@
         <v>129592077</v>
       </c>
       <c r="B148" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -16880,7 +16880,7 @@
         <v>129564502</v>
       </c>
       <c r="B144" t="n">
-        <v>90634</v>
+        <v>90639</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16986,7 +16986,7 @@
         <v>129564176</v>
       </c>
       <c r="B145" t="n">
-        <v>91609</v>
+        <v>91614</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17092,7 +17092,7 @@
         <v>129564285</v>
       </c>
       <c r="B146" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17194,7 +17194,7 @@
         <v>129563617</v>
       </c>
       <c r="B147" t="n">
-        <v>90634</v>
+        <v>90639</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17300,7 +17300,7 @@
         <v>129592077</v>
       </c>
       <c r="B148" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -16880,7 +16880,7 @@
         <v>129564502</v>
       </c>
       <c r="B144" t="n">
-        <v>90639</v>
+        <v>90643</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16986,7 +16986,7 @@
         <v>129564176</v>
       </c>
       <c r="B145" t="n">
-        <v>91614</v>
+        <v>91618</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17092,7 +17092,7 @@
         <v>129564285</v>
       </c>
       <c r="B146" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17194,7 +17194,7 @@
         <v>129563617</v>
       </c>
       <c r="B147" t="n">
-        <v>90639</v>
+        <v>90643</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -16880,7 +16880,7 @@
         <v>129564502</v>
       </c>
       <c r="B144" t="n">
-        <v>90643</v>
+        <v>90645</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16986,7 +16986,7 @@
         <v>129564176</v>
       </c>
       <c r="B145" t="n">
-        <v>91618</v>
+        <v>91620</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17092,7 +17092,7 @@
         <v>129564285</v>
       </c>
       <c r="B146" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17194,7 +17194,7 @@
         <v>129563617</v>
       </c>
       <c r="B147" t="n">
-        <v>90643</v>
+        <v>90645</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -17092,7 +17092,7 @@
         <v>129564285</v>
       </c>
       <c r="B146" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -16880,7 +16880,7 @@
         <v>129564502</v>
       </c>
       <c r="B144" t="n">
-        <v>90645</v>
+        <v>90648</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16986,7 +16986,7 @@
         <v>129564176</v>
       </c>
       <c r="B145" t="n">
-        <v>91620</v>
+        <v>91623</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17092,7 +17092,7 @@
         <v>129564285</v>
       </c>
       <c r="B146" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17194,7 +17194,7 @@
         <v>129563617</v>
       </c>
       <c r="B147" t="n">
-        <v>90645</v>
+        <v>90648</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17300,7 +17300,7 @@
         <v>129592077</v>
       </c>
       <c r="B148" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -17300,7 +17300,7 @@
         <v>129592077</v>
       </c>
       <c r="B148" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="AE25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY211"/>
+  <dimension ref="A1:AY215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15590,10 +15590,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126061108</v>
+        <v>134488564</v>
       </c>
       <c r="B137" t="n">
-        <v>58817</v>
+        <v>58812</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15601,21 +15601,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>208249</v>
+        <v>208245</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -15623,26 +15623,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>686907</v>
+        <v>687272</v>
       </c>
       <c r="R137" t="n">
-        <v>6562760</v>
+        <v>6563263</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15669,22 +15664,17 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z137" t="inlineStr">
-        <is>
-          <t>13:17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB137" t="inlineStr">
-        <is>
-          <t>13:17</t>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>Ca 2-3 cm lång.</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15693,28 +15683,29 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
+      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126061081</v>
+        <v>126061108</v>
       </c>
       <c r="B138" t="n">
-        <v>58815</v>
+        <v>58817</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15722,21 +15713,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>208250</v>
+        <v>208249</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -15760,10 +15751,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>687058</v>
+        <v>686907</v>
       </c>
       <c r="R138" t="n">
-        <v>6563228</v>
+        <v>6562760</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15795,7 +15786,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15805,7 +15796,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15825,17 +15816,17 @@
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>117554483</v>
+        <v>126061081</v>
       </c>
       <c r="B139" t="n">
-        <v>99035</v>
+        <v>58815</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15843,41 +15834,51 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>219790</v>
+        <v>208250</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>SO Norrby Mosse, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>686878</v>
+        <v>687058</v>
       </c>
       <c r="R139" t="n">
-        <v>6562971</v>
+        <v>6563228</v>
       </c>
       <c r="S139" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -15901,12 +15902,22 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15915,26 +15926,25 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126003792</v>
+        <v>117554483</v>
       </c>
       <c r="B140" t="n">
         <v>99035</v>
@@ -15969,17 +15979,17 @@
       <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>SO Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>687046</v>
+        <v>686878</v>
       </c>
       <c r="R140" t="n">
-        <v>6563346</v>
+        <v>6562971</v>
       </c>
       <c r="S140" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -16003,12 +16013,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16036,7 +16046,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126005160</v>
+        <v>126003792</v>
       </c>
       <c r="B141" t="n">
         <v>99035</v>
@@ -16075,10 +16085,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>687034</v>
+        <v>687046</v>
       </c>
       <c r="R141" t="n">
-        <v>6563204</v>
+        <v>6563346</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16138,7 +16148,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126061084</v>
+        <v>126005160</v>
       </c>
       <c r="B142" t="n">
         <v>99035</v>
@@ -16167,16 +16177,20 @@
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>687014</v>
+        <v>687034</v>
       </c>
       <c r="R142" t="n">
-        <v>6563215</v>
+        <v>6563204</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16203,22 +16217,12 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z142" t="inlineStr">
-        <is>
-          <t>15:14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB142" t="inlineStr">
-        <is>
-          <t>15:14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16227,25 +16231,26 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
+      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126061091</v>
+        <v>126061084</v>
       </c>
       <c r="B143" t="n">
         <v>99035</v>
@@ -16280,10 +16285,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>686871</v>
+        <v>687014</v>
       </c>
       <c r="R143" t="n">
-        <v>6562972</v>
+        <v>6563215</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16315,7 +16320,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -16325,7 +16330,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16352,7 +16357,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>126061099</v>
+        <v>126061091</v>
       </c>
       <c r="B144" t="n">
         <v>99035</v>
@@ -16387,10 +16392,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>686857</v>
+        <v>686871</v>
       </c>
       <c r="R144" t="n">
-        <v>6562875</v>
+        <v>6562972</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16422,7 +16427,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16432,7 +16437,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16452,14 +16457,14 @@
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>126061102</v>
+        <v>126061099</v>
       </c>
       <c r="B145" t="n">
         <v>99035</v>
@@ -16494,10 +16499,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>686837</v>
+        <v>686857</v>
       </c>
       <c r="R145" t="n">
-        <v>6562829</v>
+        <v>6562875</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16529,7 +16534,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16539,7 +16544,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16566,7 +16571,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>126233785</v>
+        <v>126061102</v>
       </c>
       <c r="B146" t="n">
         <v>99035</v>
@@ -16595,24 +16600,16 @@
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L146" t="inlineStr"/>
-      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>686839</v>
+        <v>686837</v>
       </c>
       <c r="R146" t="n">
-        <v>6563016</v>
+        <v>6562829</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16639,12 +16636,22 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB146" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16653,26 +16660,25 @@
       <c r="AE146" t="b">
         <v>0</v>
       </c>
-      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
       </c>
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Bodil Ravn, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>126234010</v>
+        <v>126233785</v>
       </c>
       <c r="B147" t="n">
         <v>99035</v>
@@ -16715,10 +16721,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>687160</v>
+        <v>686839</v>
       </c>
       <c r="R147" t="n">
-        <v>6563261</v>
+        <v>6563016</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16771,14 +16777,14 @@
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Bodil Ravn, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126234159</v>
+        <v>126234010</v>
       </c>
       <c r="B148" t="n">
         <v>99035</v>
@@ -16806,13 +16812,13 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr"/>
       <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
@@ -16821,13 +16827,13 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>687297</v>
+        <v>687160</v>
       </c>
       <c r="R148" t="n">
-        <v>6563381</v>
+        <v>6563261</v>
       </c>
       <c r="S148" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -16857,11 +16863,6 @@
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>Ett flertal i blomning.</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16882,14 +16883,14 @@
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Bodil Ravn, Ulf Johansson</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126234439</v>
+        <v>126234159</v>
       </c>
       <c r="B149" t="n">
         <v>99035</v>
@@ -16919,34 +16920,26 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr"/>
       <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Norrby mosse SO, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>686777</v>
+        <v>687297</v>
       </c>
       <c r="R149" t="n">
-        <v>6563073</v>
+        <v>6563381</v>
       </c>
       <c r="S149" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -16976,6 +16969,11 @@
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>Ett flertal i blomning.</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16991,19 +16989,19 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Bodil Ravn, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126234644</v>
+        <v>126234439</v>
       </c>
       <c r="B150" t="n">
         <v>99035</v>
@@ -17033,7 +17031,7 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -17041,7 +17039,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr"/>
       <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
@@ -17050,10 +17052,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>686837</v>
+        <v>686777</v>
       </c>
       <c r="R150" t="n">
-        <v>6562967</v>
+        <v>6563073</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17113,7 +17115,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126234771</v>
+        <v>126234644</v>
       </c>
       <c r="B151" t="n">
         <v>99035</v>
@@ -17143,7 +17145,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -17156,14 +17158,14 @@
       <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Norrby mosse OSO, Srm</t>
+          <t>Norrby mosse SO, Srm</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>686976</v>
+        <v>686837</v>
       </c>
       <c r="R151" t="n">
-        <v>6563107</v>
+        <v>6562967</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17223,10 +17225,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>133767702</v>
+        <v>126234771</v>
       </c>
       <c r="B152" t="n">
-        <v>99112</v>
+        <v>99035</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17251,21 +17253,29 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K152" t="inlineStr"/>
       <c r="L152" t="inlineStr"/>
       <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrby mosse OSO, Srm</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>686845</v>
+        <v>686976</v>
       </c>
       <c r="R152" t="n">
-        <v>6563325</v>
+        <v>6563107</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17292,12 +17302,12 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17313,22 +17323,22 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>126061092</v>
+        <v>133767702</v>
       </c>
       <c r="B153" t="n">
-        <v>99022</v>
+        <v>99112</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17336,43 +17346,38 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>220093</v>
+        <v>219790</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>686880</v>
+        <v>686845</v>
       </c>
       <c r="R153" t="n">
-        <v>6562892</v>
+        <v>6563325</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17399,22 +17404,12 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z153" t="inlineStr">
-        <is>
-          <t>14:35</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB153" t="inlineStr">
-        <is>
-          <t>14:35</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17423,25 +17418,26 @@
       <c r="AE153" t="b">
         <v>0</v>
       </c>
+      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
       </c>
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>126061094</v>
+        <v>126061092</v>
       </c>
       <c r="B154" t="n">
         <v>99022</v>
@@ -17485,10 +17481,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>686866</v>
+        <v>686880</v>
       </c>
       <c r="R154" t="n">
-        <v>6562874</v>
+        <v>6562892</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17520,7 +17516,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17530,7 +17526,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17557,7 +17553,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>126061100</v>
+        <v>126061094</v>
       </c>
       <c r="B155" t="n">
         <v>99022</v>
@@ -17587,7 +17583,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -17601,10 +17597,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>686857</v>
+        <v>686866</v>
       </c>
       <c r="R155" t="n">
-        <v>6562875</v>
+        <v>6562874</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17636,7 +17632,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17646,7 +17642,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17673,37 +17669,37 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>86686018</v>
+        <v>126061100</v>
       </c>
       <c r="B156" t="n">
-        <v>99118</v>
+        <v>99022</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -17711,23 +17707,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L156" t="inlineStr"/>
-      <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Tyresta S Ungfars kärr, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>686831</v>
+        <v>686857</v>
       </c>
       <c r="R156" t="n">
-        <v>6563296</v>
+        <v>6562875</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17754,17 +17743,22 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2020-07-04</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2020-07-04</t>
-        </is>
-      </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>Från Ungfars kärrs södra spets och ca 200 meter österut. Ungefär hälften av skotten utanför parkens gräns. 4 blomstänglar. Området var bökat av vildsvin. Vissa skott var uppgrävda.</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17773,26 +17767,25 @@
       <c r="AE156" t="b">
         <v>0</v>
       </c>
-      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>96672256</v>
+        <v>86686018</v>
       </c>
       <c r="B157" t="n">
         <v>99118</v>
@@ -17820,24 +17813,36 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
-      <c r="K157" t="inlineStr"/>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr"/>
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>NO Norrby mosse, Srm</t>
+          <t>Tyresta S Ungfars kärr, Srm</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>686848</v>
+        <v>686831</v>
       </c>
       <c r="R157" t="n">
-        <v>6563295</v>
+        <v>6563296</v>
       </c>
       <c r="S157" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -17861,12 +17866,17 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
+          <t>2020-07-04</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
+          <t>2020-07-04</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>Från Ungfars kärrs södra spets och ca 200 meter österut. Ungefär hälften av skotten utanför parkens gräns. 4 blomstänglar. Området var bökat av vildsvin. Vissa skott var uppgrävda.</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17882,19 +17892,19 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>97242656</v>
+        <v>96672256</v>
       </c>
       <c r="B158" t="n">
         <v>99118</v>
@@ -17923,21 +17933,23 @@
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>OSO Ungfars mosse, Srm</t>
+          <t>NO Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>686846</v>
+        <v>686848</v>
       </c>
       <c r="R158" t="n">
-        <v>6563316</v>
+        <v>6563295</v>
       </c>
       <c r="S158" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -17961,22 +17973,12 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2021-11-20</t>
-        </is>
-      </c>
-      <c r="Z158" t="inlineStr">
-        <is>
-          <t>13:59</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2021-11-20</t>
-        </is>
-      </c>
-      <c r="AB158" t="inlineStr">
-        <is>
-          <t>13:59</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17985,25 +17987,26 @@
       <c r="AE158" t="b">
         <v>0</v>
       </c>
+      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
       </c>
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Thomas Strid</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Thomas Strid, Bodil Ravn, Ulf Johansson, Tiina Laantee</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>97243108</v>
+        <v>97242656</v>
       </c>
       <c r="B159" t="n">
         <v>99118</v>
@@ -18036,17 +18039,17 @@
       <c r="L159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Tyresta, Srm</t>
+          <t>OSO Ungfars mosse, Srm</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>686847</v>
+        <v>686846</v>
       </c>
       <c r="R159" t="n">
-        <v>6563308</v>
+        <v>6563316</v>
       </c>
       <c r="S159" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -18075,7 +18078,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -18085,7 +18088,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -18112,7 +18115,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>97330311</v>
+        <v>97243108</v>
       </c>
       <c r="B160" t="n">
         <v>99118</v>
@@ -18140,29 +18143,22 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J160" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Tyresta NP, SSV Bylsjön (*knärot* /stjälk/), Srm</t>
+          <t>Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q160" t="n">
         <v>686847</v>
       </c>
       <c r="R160" t="n">
-        <v>6563309</v>
+        <v>6563308</v>
       </c>
       <c r="S160" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -18184,24 +18180,24 @@
           <t>Österhaninge</t>
         </is>
       </c>
-      <c r="X160" t="inlineStr">
-        <is>
-          <t>AB-Han-0218</t>
-        </is>
-      </c>
       <c r="Y160" t="inlineStr">
         <is>
           <t>2021-11-20</t>
         </is>
       </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>2021-11-20</t>
         </is>
       </c>
-      <c r="AC160" t="inlineStr">
-        <is>
-          <t>/Ej räknad/</t>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -18216,23 +18212,19 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Tiina Laantee, Ulf Johansson, Bodil Ravn, Thomas Strid</t>
-        </is>
-      </c>
-      <c r="AY160" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Thomas Strid, Bodil Ravn, Ulf Johansson, Tiina Laantee</t>
+        </is>
+      </c>
+      <c r="AY160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>98104097</v>
+        <v>97330311</v>
       </c>
       <c r="B161" t="n">
         <v>99118</v>
@@ -18262,27 +18254,24 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K161" t="inlineStr"/>
-      <c r="L161" t="inlineStr"/>
-      <c r="N161" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Ungfars kärr SO, Srm</t>
+          <t>Tyresta NP, SSV Bylsjön (*knärot* /stjälk/), Srm</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>686934</v>
+        <v>686847</v>
       </c>
       <c r="R161" t="n">
-        <v>6563325</v>
+        <v>6563309</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18307,19 +18296,24 @@
           <t>Österhaninge</t>
         </is>
       </c>
+      <c r="X161" t="inlineStr">
+        <is>
+          <t>AB-Han-0218</t>
+        </is>
+      </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>2022-01-13</t>
+          <t>2021-11-20</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2022-01-13</t>
+          <t>2021-11-20</t>
         </is>
       </c>
       <c r="AC161" t="inlineStr">
         <is>
-          <t>Intill djurstig och granlåga</t>
+          <t>/Ej räknad/</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18328,26 +18322,29 @@
       <c r="AE161" t="b">
         <v>0</v>
       </c>
-      <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="b">
         <v>0</v>
       </c>
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
-        </is>
-      </c>
-      <c r="AY161" t="inlineStr"/>
+          <t>Tiina Laantee, Ulf Johansson, Bodil Ravn, Thomas Strid</t>
+        </is>
+      </c>
+      <c r="AY161" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>104249959</v>
+        <v>98104097</v>
       </c>
       <c r="B162" t="n">
         <v>99118</v>
@@ -18375,24 +18372,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I162" t="inlineStr"/>
-      <c r="J162" t="inlineStr"/>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr"/>
       <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>SO Norrby Mosse, Srm</t>
+          <t>Ungfars kärr SO, Srm</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>687011</v>
+        <v>686934</v>
       </c>
       <c r="R162" t="n">
-        <v>6562869</v>
+        <v>6563325</v>
       </c>
       <c r="S162" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -18416,17 +18421,17 @@
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2022-01-13</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2022-01-13</t>
         </is>
       </c>
       <c r="AC162" t="inlineStr">
         <is>
-          <t>Samma lokal som noterades 17/11-21. Ca 25 ex. Koordinaterna har varierat något vid besöken.</t>
+          <t>Intill djurstig och granlåga</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -18442,19 +18447,19 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>109890506</v>
+        <v>104249959</v>
       </c>
       <c r="B163" t="n">
         <v>99118</v>
@@ -18489,17 +18494,17 @@
       <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Ö Norrby Mosse, Srm</t>
+          <t>SO Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>686831</v>
+        <v>687011</v>
       </c>
       <c r="R163" t="n">
-        <v>6563216</v>
+        <v>6562869</v>
       </c>
       <c r="S163" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -18523,12 +18528,17 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2022-09-16</t>
+        </is>
+      </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>Samma lokal som noterades 17/11-21. Ca 25 ex. Koordinaterna har varierat något vid besöken.</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18556,7 +18566,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>119475594</v>
+        <v>109890506</v>
       </c>
       <c r="B164" t="n">
         <v>99118</v>
@@ -18584,29 +18594,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr"/>
       <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>NO Norrby  Mosse, Srm</t>
+          <t>Ö Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>686995</v>
+        <v>686831</v>
       </c>
       <c r="R164" t="n">
-        <v>6563315</v>
+        <v>6563216</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18633,12 +18635,12 @@
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -18666,7 +18668,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>121859637</v>
+        <v>119475594</v>
       </c>
       <c r="B165" t="n">
         <v>99118</v>
@@ -18694,17 +18696,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I165" t="inlineStr"/>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Öster om Tyresta by, Tyresta, Srm</t>
+          <t>NO Norrby  Mosse, Srm</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>686863</v>
+        <v>686995</v>
       </c>
       <c r="R165" t="n">
-        <v>6563252</v>
+        <v>6563315</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18731,22 +18745,12 @@
       </c>
       <c r="Y165" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="Z165" t="inlineStr">
-        <is>
-          <t>16:22</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="AB165" t="inlineStr">
-        <is>
-          <t>16:22</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18755,25 +18759,26 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
+      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121859638</v>
+        <v>121859637</v>
       </c>
       <c r="B166" t="n">
         <v>99118</v>
@@ -18808,10 +18813,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>686826</v>
+        <v>686863</v>
       </c>
       <c r="R166" t="n">
-        <v>6563286</v>
+        <v>6563252</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18843,7 +18848,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -18853,7 +18858,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18880,7 +18885,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121859639</v>
+        <v>121859638</v>
       </c>
       <c r="B167" t="n">
         <v>99118</v>
@@ -18915,10 +18920,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>686827</v>
+        <v>686826</v>
       </c>
       <c r="R167" t="n">
-        <v>6563296</v>
+        <v>6563286</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18950,7 +18955,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -18960,7 +18965,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18987,7 +18992,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>121859640</v>
+        <v>121859639</v>
       </c>
       <c r="B168" t="n">
         <v>99118</v>
@@ -19022,10 +19027,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>686837</v>
+        <v>686827</v>
       </c>
       <c r="R168" t="n">
-        <v>6563297</v>
+        <v>6563296</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19057,7 +19062,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -19067,7 +19072,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -19094,7 +19099,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>121859642</v>
+        <v>121859640</v>
       </c>
       <c r="B169" t="n">
         <v>99118</v>
@@ -19123,24 +19128,16 @@
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
-      <c r="J169" t="inlineStr"/>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L169" t="inlineStr"/>
-      <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
           <t>Öster om Tyresta by, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>686834</v>
+        <v>686837</v>
       </c>
       <c r="R169" t="n">
-        <v>6563305</v>
+        <v>6563297</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19172,7 +19169,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -19182,7 +19179,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -19191,7 +19188,6 @@
       <c r="AE169" t="b">
         <v>0</v>
       </c>
-      <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="b">
         <v>0</v>
       </c>
@@ -19210,7 +19206,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>121859643</v>
+        <v>121859642</v>
       </c>
       <c r="B170" t="n">
         <v>99118</v>
@@ -19239,6 +19235,14 @@
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
           <t>Öster om Tyresta by, Tyresta, Srm</t>
@@ -19248,7 +19252,7 @@
         <v>686834</v>
       </c>
       <c r="R170" t="n">
-        <v>6563309</v>
+        <v>6563305</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19280,7 +19284,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -19290,7 +19294,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19299,6 +19303,7 @@
       <c r="AE170" t="b">
         <v>0</v>
       </c>
+      <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
         <v>0</v>
       </c>
@@ -19317,7 +19322,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>121859644</v>
+        <v>121859643</v>
       </c>
       <c r="B171" t="n">
         <v>99118</v>
@@ -19352,10 +19357,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>686844</v>
+        <v>686834</v>
       </c>
       <c r="R171" t="n">
-        <v>6563303</v>
+        <v>6563309</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19387,7 +19392,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -19397,7 +19402,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -19424,7 +19429,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>121859646</v>
+        <v>121859644</v>
       </c>
       <c r="B172" t="n">
         <v>99118</v>
@@ -19459,7 +19464,7 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>686841</v>
+        <v>686844</v>
       </c>
       <c r="R172" t="n">
         <v>6563303</v>
@@ -19494,7 +19499,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -19504,7 +19509,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -19531,7 +19536,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>121859647</v>
+        <v>121859646</v>
       </c>
       <c r="B173" t="n">
         <v>99118</v>
@@ -19566,10 +19571,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>686854</v>
+        <v>686841</v>
       </c>
       <c r="R173" t="n">
-        <v>6563286</v>
+        <v>6563303</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19601,7 +19606,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -19611,7 +19616,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19638,7 +19643,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>121859649</v>
+        <v>121859647</v>
       </c>
       <c r="B174" t="n">
         <v>99118</v>
@@ -19673,10 +19678,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>686851</v>
+        <v>686854</v>
       </c>
       <c r="R174" t="n">
-        <v>6563299</v>
+        <v>6563286</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19708,7 +19713,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -19718,7 +19723,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19745,7 +19750,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>121859650</v>
+        <v>121859649</v>
       </c>
       <c r="B175" t="n">
         <v>99118</v>
@@ -19780,10 +19785,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>686895</v>
+        <v>686851</v>
       </c>
       <c r="R175" t="n">
-        <v>6563306</v>
+        <v>6563299</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19815,7 +19820,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -19825,7 +19830,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19852,7 +19857,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>122220583</v>
+        <v>121859650</v>
       </c>
       <c r="B176" t="n">
         <v>99118</v>
@@ -19880,29 +19885,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J176" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K176" t="inlineStr"/>
-      <c r="L176" t="inlineStr"/>
-      <c r="N176" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>SO Norrby Mosse, Srm</t>
+          <t>Öster om Tyresta by, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>686996</v>
+        <v>686895</v>
       </c>
       <c r="R176" t="n">
-        <v>6562864</v>
+        <v>6563306</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19929,17 +19922,22 @@
       </c>
       <c r="Y176" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="Z176" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
-        </is>
-      </c>
-      <c r="AC176" t="inlineStr">
-        <is>
-          <t>Samma lokal som rapporterats -21 och -22 men en ny klon. Den förra har möjligen haft lite problem med grisbök.</t>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="AB176" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19948,26 +19946,25 @@
       <c r="AE176" t="b">
         <v>0</v>
       </c>
-      <c r="AF176" t="inlineStr"/>
       <c r="AG176" t="b">
         <v>0</v>
       </c>
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>122781008</v>
+        <v>122220583</v>
       </c>
       <c r="B177" t="n">
         <v>99118</v>
@@ -19995,21 +19992,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I177" t="inlineStr"/>
-      <c r="J177" t="inlineStr"/>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr"/>
       <c r="N177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Knärot, Srm</t>
+          <t>SO Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>686833</v>
+        <v>686996</v>
       </c>
       <c r="R177" t="n">
-        <v>6563215</v>
+        <v>6562864</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -20036,17 +20041,17 @@
       </c>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="AC177" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Samma lokal som rapporterats -21 och -22 men en ny klon. Den förra har möjligen haft lite problem med grisbök.</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -20062,19 +20067,19 @@
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>126418709</v>
+        <v>122781008</v>
       </c>
       <c r="B178" t="n">
         <v>99118</v>
@@ -20102,29 +20107,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J178" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr"/>
       <c r="L178" t="inlineStr"/>
       <c r="N178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Knärot, Srm</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>686771</v>
+        <v>686833</v>
       </c>
       <c r="R178" t="n">
-        <v>6563297</v>
+        <v>6563215</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20151,17 +20148,17 @@
       </c>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>Två av dem i knopp, ca 3 m väster om de andra.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -20177,19 +20174,19 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>126418756</v>
+        <v>126418709</v>
       </c>
       <c r="B179" t="n">
         <v>99118</v>
@@ -20219,7 +20216,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
@@ -20236,10 +20233,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>686781</v>
+        <v>686771</v>
       </c>
       <c r="R179" t="n">
-        <v>6563292</v>
+        <v>6563297</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20276,7 +20273,7 @@
       </c>
       <c r="AC179" t="inlineStr">
         <is>
-          <t>En av dem i knopp.</t>
+          <t>Två av dem i knopp, ca 3 m väster om de andra.</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -20304,7 +20301,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>127932426</v>
+        <v>126418756</v>
       </c>
       <c r="B180" t="n">
         <v>99118</v>
@@ -20334,7 +20331,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -20351,10 +20348,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>686998</v>
+        <v>686781</v>
       </c>
       <c r="R180" t="n">
-        <v>6563316</v>
+        <v>6563292</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20381,17 +20378,17 @@
       </c>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AC180" t="inlineStr">
         <is>
-          <t>Återfynd, rapporterad -24 med 3 ex. Nu 5 ex.</t>
+          <t>En av dem i knopp.</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -20419,7 +20416,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128341941</v>
+        <v>127932426</v>
       </c>
       <c r="B181" t="n">
         <v>99118</v>
@@ -20449,7 +20446,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -20466,10 +20463,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>687244</v>
+        <v>686998</v>
       </c>
       <c r="R181" t="n">
-        <v>6563404</v>
+        <v>6563316</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20496,12 +20493,17 @@
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC181" t="inlineStr">
+        <is>
+          <t>Återfynd, rapporterad -24 med 3 ex. Nu 5 ex.</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -20529,7 +20531,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129564285</v>
+        <v>128341941</v>
       </c>
       <c r="B182" t="n">
         <v>99118</v>
@@ -20557,8 +20559,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I182" t="inlineStr"/>
-      <c r="J182" t="inlineStr"/>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K182" t="inlineStr"/>
       <c r="L182" t="inlineStr"/>
       <c r="N182" t="inlineStr"/>
@@ -20568,10 +20578,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>686625</v>
+        <v>687244</v>
       </c>
       <c r="R182" t="n">
-        <v>6563000</v>
+        <v>6563404</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20598,12 +20608,12 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -20631,10 +20641,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>133767721</v>
+        <v>129564285</v>
       </c>
       <c r="B183" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20670,10 +20680,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>686845</v>
+        <v>686625</v>
       </c>
       <c r="R183" t="n">
-        <v>6563325</v>
+        <v>6563000</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20700,12 +20710,12 @@
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -20733,32 +20743,32 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>96643458</v>
+        <v>133767721</v>
       </c>
       <c r="B184" t="n">
-        <v>106244</v>
+        <v>99195</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -20768,14 +20778,14 @@
       <c r="N184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Vargklåva mosse S om, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>687154</v>
+        <v>686845</v>
       </c>
       <c r="R184" t="n">
-        <v>6563329</v>
+        <v>6563325</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20802,12 +20812,12 @@
       </c>
       <c r="Y184" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -20823,19 +20833,19 @@
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>96858761</v>
+        <v>96643458</v>
       </c>
       <c r="B185" t="n">
         <v>106244</v>
@@ -20870,17 +20880,17 @@
       <c r="N185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Ungfars kärr SO, Srm</t>
+          <t>Vargklåva mosse S om, Srm</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>687064</v>
+        <v>687154</v>
       </c>
       <c r="R185" t="n">
-        <v>6563258</v>
+        <v>6563329</v>
       </c>
       <c r="S185" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -20904,17 +20914,12 @@
       </c>
       <c r="Y185" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="AC185" t="inlineStr">
-        <is>
-          <t>Två bestånd</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -20942,7 +20947,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>97204577</v>
+        <v>96858761</v>
       </c>
       <c r="B186" t="n">
         <v>106244</v>
@@ -20977,17 +20982,17 @@
       <c r="N186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>SO Norrby mosse, Srm</t>
+          <t>Ungfars kärr SO, Srm</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>687019</v>
+        <v>687064</v>
       </c>
       <c r="R186" t="n">
-        <v>6562889</v>
+        <v>6563258</v>
       </c>
       <c r="S186" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -21011,12 +21016,17 @@
       </c>
       <c r="Y186" t="inlineStr">
         <is>
-          <t>2021-11-17</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>2021-11-17</t>
+          <t>2021-10-26</t>
+        </is>
+      </c>
+      <c r="AC186" t="inlineStr">
+        <is>
+          <t>Två bestånd</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -21032,19 +21042,19 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>100252927</v>
+        <v>97204577</v>
       </c>
       <c r="B187" t="n">
         <v>106244</v>
@@ -21079,17 +21089,17 @@
       <c r="N187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>NO Norrby  Mosse, Srm</t>
+          <t>SO Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>687152</v>
+        <v>687019</v>
       </c>
       <c r="R187" t="n">
-        <v>6563326</v>
+        <v>6562889</v>
       </c>
       <c r="S187" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -21113,12 +21123,12 @@
       </c>
       <c r="Y187" t="inlineStr">
         <is>
-          <t>2022-04-26</t>
+          <t>2021-11-17</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>2022-04-26</t>
+          <t>2021-11-17</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -21146,7 +21156,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>116743172</v>
+        <v>100252927</v>
       </c>
       <c r="B188" t="n">
         <v>106244</v>
@@ -21175,16 +21185,20 @@
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="inlineStr"/>
+      <c r="N188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Ungfars kärr, Ungfars kärr, Srm</t>
+          <t>NO Norrby  Mosse, Srm</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>687088</v>
+        <v>687152</v>
       </c>
       <c r="R188" t="n">
-        <v>6563243</v>
+        <v>6563326</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21211,12 +21225,12 @@
       </c>
       <c r="Y188" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2022-04-26</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2022-04-26</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -21225,25 +21239,26 @@
       <c r="AE188" t="b">
         <v>0</v>
       </c>
+      <c r="AF188" t="inlineStr"/>
       <c r="AG188" t="b">
         <v>0</v>
       </c>
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>125965889</v>
+        <v>116743172</v>
       </c>
       <c r="B189" t="n">
         <v>106244</v>
@@ -21278,10 +21293,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>687076</v>
+        <v>687088</v>
       </c>
       <c r="R189" t="n">
-        <v>6563220</v>
+        <v>6563243</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21308,12 +21323,12 @@
       </c>
       <c r="Y189" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -21340,7 +21355,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>126003574</v>
+        <v>125965889</v>
       </c>
       <c r="B190" t="n">
         <v>106244</v>
@@ -21369,20 +21384,16 @@
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
-      <c r="J190" t="inlineStr"/>
-      <c r="K190" t="inlineStr"/>
-      <c r="L190" t="inlineStr"/>
-      <c r="N190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>SO Norrby Mosse, Srm</t>
+          <t>Ungfars kärr, Ungfars kärr, Srm</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>686803</v>
+        <v>687076</v>
       </c>
       <c r="R190" t="n">
-        <v>6563098</v>
+        <v>6563220</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21409,12 +21420,12 @@
       </c>
       <c r="Y190" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -21423,26 +21434,25 @@
       <c r="AE190" t="b">
         <v>0</v>
       </c>
-      <c r="AF190" t="inlineStr"/>
       <c r="AG190" t="b">
         <v>0</v>
       </c>
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>126061078</v>
+        <v>126003574</v>
       </c>
       <c r="B191" t="n">
         <v>106244</v>
@@ -21471,16 +21481,20 @@
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="inlineStr"/>
+      <c r="L191" t="inlineStr"/>
+      <c r="N191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>SO Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>687085</v>
+        <v>686803</v>
       </c>
       <c r="R191" t="n">
-        <v>6563229</v>
+        <v>6563098</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21507,22 +21521,12 @@
       </c>
       <c r="Y191" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z191" t="inlineStr">
-        <is>
-          <t>15:40</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB191" t="inlineStr">
-        <is>
-          <t>15:40</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -21531,25 +21535,26 @@
       <c r="AE191" t="b">
         <v>0</v>
       </c>
+      <c r="AF191" t="inlineStr"/>
       <c r="AG191" t="b">
         <v>0</v>
       </c>
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>126061079</v>
+        <v>126061078</v>
       </c>
       <c r="B192" t="n">
         <v>106244</v>
@@ -21584,10 +21589,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>687082</v>
+        <v>687085</v>
       </c>
       <c r="R192" t="n">
-        <v>6563241</v>
+        <v>6563229</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21619,7 +21624,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -21629,7 +21634,7 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -21656,7 +21661,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>126234373</v>
+        <v>126061079</v>
       </c>
       <c r="B193" t="n">
         <v>106244</v>
@@ -21684,29 +21689,17 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I193" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J193" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K193" t="inlineStr"/>
-      <c r="L193" t="inlineStr"/>
-      <c r="N193" t="inlineStr"/>
+      <c r="I193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Norrby mosse SO, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>686756</v>
+        <v>687082</v>
       </c>
       <c r="R193" t="n">
-        <v>6563092</v>
+        <v>6563241</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21733,12 +21726,22 @@
       </c>
       <c r="Y193" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z193" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB193" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -21747,26 +21750,25 @@
       <c r="AE193" t="b">
         <v>0</v>
       </c>
-      <c r="AF193" t="inlineStr"/>
       <c r="AG193" t="b">
         <v>0</v>
       </c>
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>126234937</v>
+        <v>126234373</v>
       </c>
       <c r="B194" t="n">
         <v>106244</v>
@@ -21804,23 +21806,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K194" t="inlineStr"/>
       <c r="L194" t="inlineStr"/>
       <c r="N194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Ungfars kärr SO, Srm</t>
+          <t>Norrby mosse SO, Srm</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>687103</v>
+        <v>686756</v>
       </c>
       <c r="R194" t="n">
-        <v>6563191</v>
+        <v>6563092</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21880,10 +21878,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>96643468</v>
+        <v>126234937</v>
       </c>
       <c r="B195" t="n">
-        <v>97989</v>
+        <v>106244</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -21891,46 +21889,50 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>221941</v>
+        <v>221144</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K195" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr"/>
       <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Vargklåva mosse S om, Srm</t>
+          <t>Ungfars kärr SO, Srm</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>687268</v>
+        <v>687103</v>
       </c>
       <c r="R195" t="n">
-        <v>6563319</v>
+        <v>6563191</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21957,17 +21959,12 @@
       </c>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
-        </is>
-      </c>
-      <c r="AC195" t="inlineStr">
-        <is>
-          <t>Strax nedom klippbrant</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -21995,7 +21992,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>116746465</v>
+        <v>96643468</v>
       </c>
       <c r="B196" t="n">
         <v>97989</v>
@@ -22023,17 +22020,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I196" t="inlineStr"/>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr"/>
+      <c r="L196" t="inlineStr"/>
+      <c r="N196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Norrby mosse, Norrby mosse, Srm</t>
+          <t>Vargklåva mosse S om, Srm</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>686888</v>
+        <v>687268</v>
       </c>
       <c r="R196" t="n">
-        <v>6563206</v>
+        <v>6563319</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -22060,12 +22069,17 @@
       </c>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2021-10-12</t>
+        </is>
+      </c>
+      <c r="AC196" t="inlineStr">
+        <is>
+          <t>Strax nedom klippbrant</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -22074,28 +22088,29 @@
       <c r="AE196" t="b">
         <v>0</v>
       </c>
+      <c r="AF196" t="inlineStr"/>
       <c r="AG196" t="b">
         <v>0</v>
       </c>
       <c r="AT196" t="inlineStr"/>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>121742517</v>
+        <v>116746465</v>
       </c>
       <c r="B197" t="n">
-        <v>97983</v>
+        <v>97989</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -22103,16 +22118,16 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -22127,10 +22142,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>686859</v>
+        <v>686888</v>
       </c>
       <c r="R197" t="n">
-        <v>6562875</v>
+        <v>6563206</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -22157,12 +22172,12 @@
       </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -22189,7 +22204,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>122928987</v>
+        <v>121742517</v>
       </c>
       <c r="B198" t="n">
         <v>97983</v>
@@ -22218,20 +22233,16 @@
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
-      <c r="J198" t="inlineStr"/>
-      <c r="K198" t="inlineStr"/>
-      <c r="L198" t="inlineStr"/>
-      <c r="N198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Norrby mosse, Srm</t>
+          <t>Norrby mosse, Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>686389</v>
+        <v>686859</v>
       </c>
       <c r="R198" t="n">
-        <v>6562967</v>
+        <v>6562875</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22258,22 +22269,12 @@
       </c>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="Z198" t="inlineStr">
-        <is>
-          <t>10:36</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="AB198" t="inlineStr">
-        <is>
-          <t>10:36</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -22288,19 +22289,19 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>122930294</v>
+        <v>122928987</v>
       </c>
       <c r="B199" t="n">
         <v>97983</v>
@@ -22339,13 +22340,13 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>686824</v>
+        <v>686389</v>
       </c>
       <c r="R199" t="n">
-        <v>6562778</v>
+        <v>6562967</v>
       </c>
       <c r="S199" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T199" t="inlineStr">
         <is>
@@ -22374,7 +22375,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -22384,7 +22385,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -22411,7 +22412,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>125963374</v>
+        <v>122930294</v>
       </c>
       <c r="B200" t="n">
         <v>97983</v>
@@ -22440,19 +22441,23 @@
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr"/>
+      <c r="N200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Norrby mosse, Norrby mosse, Srm</t>
+          <t>Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>686873</v>
+        <v>686824</v>
       </c>
       <c r="R200" t="n">
-        <v>6562867</v>
+        <v>6562778</v>
       </c>
       <c r="S200" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T200" t="inlineStr">
         <is>
@@ -22476,12 +22481,22 @@
       </c>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="Z200" t="inlineStr">
+        <is>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AB200" t="inlineStr">
+        <is>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -22496,19 +22511,19 @@
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>125976418</v>
+        <v>125963374</v>
       </c>
       <c r="B201" t="n">
         <v>97983</v>
@@ -22537,23 +22552,19 @@
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
-      <c r="J201" t="inlineStr"/>
-      <c r="K201" t="inlineStr"/>
-      <c r="L201" t="inlineStr"/>
-      <c r="N201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Norrby mosse Ö om, Srm</t>
+          <t>Norrby mosse, Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>686836</v>
+        <v>686873</v>
       </c>
       <c r="R201" t="n">
-        <v>6563105</v>
+        <v>6562867</v>
       </c>
       <c r="S201" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -22585,37 +22596,31 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC201" t="inlineStr">
-        <is>
-          <t>Riklig förekomst i skogskärr</t>
-        </is>
-      </c>
       <c r="AD201" t="b">
         <v>0</v>
       </c>
       <c r="AE201" t="b">
         <v>0</v>
       </c>
-      <c r="AF201" t="inlineStr"/>
       <c r="AG201" t="b">
         <v>0</v>
       </c>
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>126061082</v>
+        <v>125976418</v>
       </c>
       <c r="B202" t="n">
         <v>97983</v>
@@ -22644,19 +22649,23 @@
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
+      <c r="J202" t="inlineStr"/>
+      <c r="K202" t="inlineStr"/>
+      <c r="L202" t="inlineStr"/>
+      <c r="N202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>Norrby mosse Ö om, Srm</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>687079</v>
+        <v>686836</v>
       </c>
       <c r="R202" t="n">
-        <v>6563240</v>
+        <v>6563105</v>
       </c>
       <c r="S202" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -22683,19 +22692,14 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z202" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AA202" t="inlineStr">
         <is>
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AB202" t="inlineStr">
-        <is>
-          <t>15:22</t>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>Riklig förekomst i skogskärr</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -22704,25 +22708,26 @@
       <c r="AE202" t="b">
         <v>0</v>
       </c>
+      <c r="AF202" t="inlineStr"/>
       <c r="AG202" t="b">
         <v>0</v>
       </c>
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>126061090</v>
+        <v>126061082</v>
       </c>
       <c r="B203" t="n">
         <v>97983</v>
@@ -22757,10 +22762,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>686871</v>
+        <v>687079</v>
       </c>
       <c r="R203" t="n">
-        <v>6562972</v>
+        <v>6563240</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22792,7 +22797,7 @@
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
@@ -22802,7 +22807,7 @@
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -22829,7 +22834,7 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>126061103</v>
+        <v>126061090</v>
       </c>
       <c r="B204" t="n">
         <v>97983</v>
@@ -22864,10 +22869,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>686811</v>
+        <v>686871</v>
       </c>
       <c r="R204" t="n">
-        <v>6562803</v>
+        <v>6562972</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22899,7 +22904,7 @@
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
@@ -22909,7 +22914,7 @@
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -22929,14 +22934,14 @@
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>126061111</v>
+        <v>126061103</v>
       </c>
       <c r="B205" t="n">
         <v>97983</v>
@@ -22971,10 +22976,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>687030</v>
+        <v>686811</v>
       </c>
       <c r="R205" t="n">
-        <v>6562755</v>
+        <v>6562803</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -23006,7 +23011,7 @@
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
@@ -23016,7 +23021,7 @@
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -23043,10 +23048,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>122929342</v>
+        <v>126061111</v>
       </c>
       <c r="B206" t="n">
-        <v>97986</v>
+        <v>97983</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -23054,16 +23059,16 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -23072,23 +23077,19 @@
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
-      <c r="J206" t="inlineStr"/>
-      <c r="K206" t="inlineStr"/>
-      <c r="L206" t="inlineStr"/>
-      <c r="N206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Norrby mosse, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>686569</v>
+        <v>687030</v>
       </c>
       <c r="R206" t="n">
-        <v>6562949</v>
+        <v>6562755</v>
       </c>
       <c r="S206" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T206" t="inlineStr">
         <is>
@@ -23112,22 +23113,22 @@
       </c>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -23142,19 +23143,19 @@
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>126061110</v>
+        <v>122929342</v>
       </c>
       <c r="B207" t="n">
         <v>97986</v>
@@ -23183,19 +23184,23 @@
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
+      <c r="J207" t="inlineStr"/>
+      <c r="K207" t="inlineStr"/>
+      <c r="L207" t="inlineStr"/>
+      <c r="N207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>687029</v>
+        <v>686569</v>
       </c>
       <c r="R207" t="n">
-        <v>6562759</v>
+        <v>6562949</v>
       </c>
       <c r="S207" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T207" t="inlineStr">
         <is>
@@ -23219,22 +23224,22 @@
       </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -23249,22 +23254,22 @@
       <c r="AT207" t="inlineStr"/>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>101523203</v>
+        <v>126061110</v>
       </c>
       <c r="B208" t="n">
-        <v>99140</v>
+        <v>97986</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -23272,38 +23277,34 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>221952</v>
+        <v>221946</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
-      <c r="J208" t="inlineStr"/>
-      <c r="K208" t="inlineStr"/>
-      <c r="L208" t="inlineStr"/>
-      <c r="N208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
-          <t>NO Norrby Mosse, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>687050</v>
+        <v>687029</v>
       </c>
       <c r="R208" t="n">
-        <v>6563327</v>
+        <v>6562759</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -23330,12 +23331,22 @@
       </c>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>2022-06-08</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z208" t="inlineStr">
+        <is>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>2022-06-08</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB208" t="inlineStr">
+        <is>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -23344,26 +23355,25 @@
       <c r="AE208" t="b">
         <v>0</v>
       </c>
-      <c r="AF208" t="inlineStr"/>
       <c r="AG208" t="b">
         <v>0</v>
       </c>
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>117554655</v>
+        <v>101523203</v>
       </c>
       <c r="B209" t="n">
         <v>99140</v>
@@ -23393,23 +23403,19 @@
       </c>
       <c r="I209" t="inlineStr"/>
       <c r="J209" t="inlineStr"/>
-      <c r="K209" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K209" t="inlineStr"/>
       <c r="L209" t="inlineStr"/>
       <c r="N209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
-          <t>NO Norrby  Mosse, Srm</t>
+          <t>NO Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>687062</v>
+        <v>687050</v>
       </c>
       <c r="R209" t="n">
-        <v>6563349</v>
+        <v>6563327</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -23436,12 +23442,12 @@
       </c>
       <c r="Y209" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2022-06-08</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2022-06-08</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -23469,7 +23475,7 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>126234400</v>
+        <v>117554655</v>
       </c>
       <c r="B210" t="n">
         <v>99140</v>
@@ -23497,16 +23503,8 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I210" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J210" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I210" t="inlineStr"/>
+      <c r="J210" t="inlineStr"/>
       <c r="K210" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -23516,14 +23514,14 @@
       <c r="N210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Norrby mosse SO, Srm</t>
+          <t>NO Norrby  Mosse, Srm</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>686788</v>
+        <v>687062</v>
       </c>
       <c r="R210" t="n">
-        <v>6563073</v>
+        <v>6563349</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -23550,12 +23548,12 @@
       </c>
       <c r="Y210" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -23571,60 +23569,73 @@
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>129564006</v>
+        <v>126234400</v>
       </c>
       <c r="B211" t="n">
-        <v>79350</v>
+        <v>99140</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>260591</v>
+        <v>221952</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I211" t="inlineStr"/>
-      <c r="J211" t="inlineStr"/>
-      <c r="K211" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr"/>
       <c r="N211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrby mosse SO, Srm</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>686681</v>
+        <v>686788</v>
       </c>
       <c r="R211" t="n">
-        <v>6563025</v>
+        <v>6563073</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23651,19 +23662,19 @@
       </c>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD211" t="b">
         <v>0</v>
       </c>
       <c r="AE211" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF211" t="inlineStr"/>
       <c r="AG211" t="b">
@@ -23672,15 +23683,449 @@
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
+          <t>Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AX211" t="inlineStr">
+        <is>
+          <t>Ulf Johansson, Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>134487623</v>
+      </c>
+      <c r="B212" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E212" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr"/>
+      <c r="J212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr"/>
+      <c r="N212" t="inlineStr"/>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q212" t="n">
+        <v>687067</v>
+      </c>
+      <c r="R212" t="n">
+        <v>6563342</v>
+      </c>
+      <c r="S212" t="n">
+        <v>25</v>
+      </c>
+      <c r="T212" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V212" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W212" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y212" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AC212" t="inlineStr">
+        <is>
+          <t>Ett tiotal i blom samt flera plantor med endast blad. Kan ha varit fler. Återfynd.</t>
+        </is>
+      </c>
+      <c r="AD212" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE212" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF212" t="inlineStr"/>
+      <c r="AG212" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT212" t="inlineStr"/>
+      <c r="AW212" t="inlineStr">
+        <is>
           <t>Bodil Ravn</t>
         </is>
       </c>
-      <c r="AX211" t="inlineStr">
+      <c r="AX212" t="inlineStr">
         <is>
           <t>Bodil Ravn</t>
         </is>
       </c>
-      <c r="AY211" t="inlineStr"/>
+      <c r="AY212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>134487656</v>
+      </c>
+      <c r="B213" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E213" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr"/>
+      <c r="J213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr"/>
+      <c r="N213" t="inlineStr"/>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q213" t="n">
+        <v>686835</v>
+      </c>
+      <c r="R213" t="n">
+        <v>6563212</v>
+      </c>
+      <c r="S213" t="n">
+        <v>10</v>
+      </c>
+      <c r="T213" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V213" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W213" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y213" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AC213" t="inlineStr">
+        <is>
+          <t>2 i blom samt några plantor med endast blad.</t>
+        </is>
+      </c>
+      <c r="AD213" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE213" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF213" t="inlineStr"/>
+      <c r="AG213" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT213" t="inlineStr"/>
+      <c r="AW213" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX213" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>134488457</v>
+      </c>
+      <c r="B214" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E214" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr"/>
+      <c r="J214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr"/>
+      <c r="N214" t="inlineStr"/>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q214" t="n">
+        <v>687294</v>
+      </c>
+      <c r="R214" t="n">
+        <v>6563391</v>
+      </c>
+      <c r="S214" t="n">
+        <v>10</v>
+      </c>
+      <c r="T214" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V214" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W214" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y214" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AC214" t="inlineStr">
+        <is>
+          <t>2 i blom samt fler med endast blad.</t>
+        </is>
+      </c>
+      <c r="AD214" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE214" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF214" t="inlineStr"/>
+      <c r="AG214" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT214" t="inlineStr"/>
+      <c r="AW214" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX214" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>129564006</v>
+      </c>
+      <c r="B215" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E215" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr"/>
+      <c r="J215" t="inlineStr"/>
+      <c r="K215" t="inlineStr"/>
+      <c r="N215" t="inlineStr"/>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q215" t="n">
+        <v>686681</v>
+      </c>
+      <c r="R215" t="n">
+        <v>6563025</v>
+      </c>
+      <c r="S215" t="n">
+        <v>10</v>
+      </c>
+      <c r="T215" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V215" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W215" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y215" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AD215" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE215" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF215" t="inlineStr"/>
+      <c r="AG215" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT215" t="inlineStr"/>
+      <c r="AW215" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX215" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY215" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY215"/>
+  <dimension ref="A1:AY216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14023,45 +14023,53 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121859656</v>
+        <v>134505793</v>
       </c>
       <c r="B124" t="n">
-        <v>5199</v>
+        <v>58136</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Öster om Tyresta by, Tyresta, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>687094</v>
+        <v>687170</v>
       </c>
       <c r="R124" t="n">
-        <v>6563235</v>
+        <v>6563187</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14088,22 +14096,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>15:16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>15:16</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14114,43 +14112,23 @@
       </c>
       <c r="AG124" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ124" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK124" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL124" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO124" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>126061088</v>
+        <v>121859656</v>
       </c>
       <c r="B125" t="n">
         <v>5199</v>
@@ -14181,14 +14159,14 @@
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>Öster om Tyresta by, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>686865</v>
+        <v>687094</v>
       </c>
       <c r="R125" t="n">
-        <v>6562977</v>
+        <v>6563235</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14215,22 +14193,22 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14254,12 +14232,12 @@
       </c>
       <c r="AL125" t="inlineStr">
         <is>
-          <t>Klen torr granlåga.</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>Picea abies # Klen torr granlåga.</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT125" t="inlineStr"/>
@@ -14270,14 +14248,14 @@
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126061109</v>
+        <v>126061088</v>
       </c>
       <c r="B126" t="n">
         <v>5199</v>
@@ -14312,10 +14290,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>686946</v>
+        <v>686865</v>
       </c>
       <c r="R126" t="n">
-        <v>6562741</v>
+        <v>6562977</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14347,7 +14325,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14357,7 +14335,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14397,17 +14375,17 @@
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121859629</v>
+        <v>126061109</v>
       </c>
       <c r="B127" t="n">
-        <v>8455</v>
+        <v>5199</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14415,34 +14393,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Öster om Tyresta by, Tyresta, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>686792</v>
+        <v>686946</v>
       </c>
       <c r="R127" t="n">
-        <v>6563030</v>
+        <v>6562741</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14469,22 +14447,22 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14498,17 +14476,22 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL127" t="inlineStr">
+        <is>
+          <t>Klen torr granlåga.</t>
         </is>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies # Klen torr granlåga.</t>
         </is>
       </c>
       <c r="AT127" t="inlineStr"/>
@@ -14519,14 +14502,14 @@
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121859631</v>
+        <v>121859629</v>
       </c>
       <c r="B128" t="n">
         <v>8455</v>
@@ -14561,10 +14544,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>686934</v>
+        <v>686792</v>
       </c>
       <c r="R128" t="n">
-        <v>6563148</v>
+        <v>6563030</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14596,7 +14579,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14606,7 +14589,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14648,7 +14631,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>122929535</v>
+        <v>121859631</v>
       </c>
       <c r="B129" t="n">
         <v>8455</v>
@@ -14676,29 +14659,20 @@
           <t>(Hartig, 1834)</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Norrby mosse, Srm</t>
+          <t>Öster om Tyresta by, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>686612</v>
+        <v>686934</v>
       </c>
       <c r="R129" t="n">
-        <v>6562882</v>
+        <v>6563148</v>
       </c>
       <c r="S129" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14722,22 +14696,22 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14748,26 +14722,41 @@
       </c>
       <c r="AG129" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ129" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK129" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO129" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>125974903</v>
+        <v>122929535</v>
       </c>
       <c r="B130" t="n">
-        <v>8444</v>
+        <v>8455</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14775,50 +14764,46 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M130" t="inlineStr"/>
       <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>söder om Tyresta, Srm</t>
+          <t>Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>686838</v>
+        <v>686612</v>
       </c>
       <c r="R130" t="n">
-        <v>6562733</v>
+        <v>6562882</v>
       </c>
       <c r="S130" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14842,17 +14827,22 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>gammal björklåga med spår längs hela stammen</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14861,46 +14851,25 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
-      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ130" t="inlineStr">
-        <is>
-          <t>vårtbjörk</t>
-        </is>
-      </c>
-      <c r="AK130" t="inlineStr">
-        <is>
-          <t>Betula pendula</t>
-        </is>
-      </c>
-      <c r="AM130" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO130" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Betula pendula</t>
-        </is>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Nette Bygren</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Nette Bygren</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>126061086</v>
+        <v>125974903</v>
       </c>
       <c r="B131" t="n">
         <v>8444</v>
@@ -14928,20 +14897,33 @@
           <t>Janson, 1856</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr"/>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>söder om Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>686932</v>
+        <v>686838</v>
       </c>
       <c r="R131" t="n">
-        <v>6563067</v>
+        <v>6562733</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14968,19 +14950,14 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>15:00</t>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>gammal björklåga med spår längs hela stammen</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14989,45 +14966,46 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>vårtbjörk</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
         <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AL131" t="inlineStr">
-        <is>
-          <t>Barklös björklåga.</t>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AM131" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
         </is>
       </c>
       <c r="AO131" t="inlineStr">
         <is>
-          <t>Betula # Barklös björklåga.</t>
+          <t>Wood surface of dead wood # Betula pendula</t>
         </is>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Nette Bygren</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Nette Bygren</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126061105</v>
+        <v>126061086</v>
       </c>
       <c r="B132" t="n">
         <v>8444</v>
@@ -15062,10 +15040,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>686860</v>
+        <v>686932</v>
       </c>
       <c r="R132" t="n">
-        <v>6562743</v>
+        <v>6563067</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15097,7 +15075,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -15107,7 +15085,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15129,9 +15107,14 @@
           <t>Betula</t>
         </is>
       </c>
+      <c r="AL132" t="inlineStr">
+        <is>
+          <t>Barklös björklåga.</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Betula # Barklös björklåga.</t>
         </is>
       </c>
       <c r="AT132" t="inlineStr"/>
@@ -15142,17 +15125,17 @@
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>111182876</v>
+        <v>126061105</v>
       </c>
       <c r="B133" t="n">
-        <v>58790</v>
+        <v>8444</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15160,43 +15143,34 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>208245</v>
+        <v>106554</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>NO Norrby  Mosse, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>686971</v>
+        <v>686860</v>
       </c>
       <c r="R133" t="n">
-        <v>6563333</v>
+        <v>6562743</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15223,12 +15197,22 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2023-07-30</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2023-07-30</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15237,26 +15221,40 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ133" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK133" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO133" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>126061089</v>
+        <v>111182876</v>
       </c>
       <c r="B134" t="n">
         <v>58790</v>
@@ -15289,21 +15287,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>NO Norrby  Mosse, Srm</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>686871</v>
+        <v>686971</v>
       </c>
       <c r="R134" t="n">
-        <v>6562972</v>
+        <v>6563333</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15330,22 +15328,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z134" t="inlineStr">
-        <is>
-          <t>14:42</t>
+          <t>2023-07-30</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB134" t="inlineStr">
-        <is>
-          <t>14:42</t>
+          <t>2023-07-30</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15354,25 +15342,26 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
+      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126061098</v>
+        <v>126061089</v>
       </c>
       <c r="B135" t="n">
         <v>58790</v>
@@ -15400,17 +15389,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr"/>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>686857</v>
+        <v>686871</v>
       </c>
       <c r="R135" t="n">
-        <v>6562875</v>
+        <v>6562972</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15442,7 +15440,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15452,7 +15450,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15472,14 +15470,14 @@
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128095464</v>
+        <v>126061098</v>
       </c>
       <c r="B136" t="n">
         <v>58790</v>
@@ -15507,30 +15505,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>687155</v>
+        <v>686857</v>
       </c>
       <c r="R136" t="n">
-        <v>6563193</v>
+        <v>6562875</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15557,12 +15542,22 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15571,29 +15566,28 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
-      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>134488564</v>
+        <v>128095464</v>
       </c>
       <c r="B137" t="n">
-        <v>58812</v>
+        <v>58790</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15624,7 +15618,11 @@
         </is>
       </c>
       <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" t="inlineStr"/>
       <c r="N137" t="inlineStr"/>
@@ -15634,10 +15632,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>687272</v>
+        <v>687155</v>
       </c>
       <c r="R137" t="n">
-        <v>6563263</v>
+        <v>6563193</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15664,17 +15662,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>Ca 2-3 cm lång.</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15702,10 +15695,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126061108</v>
+        <v>134488564</v>
       </c>
       <c r="B138" t="n">
-        <v>58817</v>
+        <v>58812</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15713,21 +15706,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>208249</v>
+        <v>208245</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -15735,26 +15728,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>686907</v>
+        <v>687272</v>
       </c>
       <c r="R138" t="n">
-        <v>6562760</v>
+        <v>6563263</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15781,22 +15769,17 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z138" t="inlineStr">
-        <is>
-          <t>13:17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB138" t="inlineStr">
-        <is>
-          <t>13:17</t>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>Ca 2-3 cm lång.</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15805,28 +15788,29 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
+      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126061081</v>
+        <v>126061108</v>
       </c>
       <c r="B139" t="n">
-        <v>58815</v>
+        <v>58817</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15834,21 +15818,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>208250</v>
+        <v>208249</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -15872,10 +15856,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>687058</v>
+        <v>686907</v>
       </c>
       <c r="R139" t="n">
-        <v>6563228</v>
+        <v>6562760</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15907,7 +15891,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15917,7 +15901,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15937,17 +15921,17 @@
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>117554483</v>
+        <v>126061081</v>
       </c>
       <c r="B140" t="n">
-        <v>99035</v>
+        <v>58815</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15955,41 +15939,51 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>219790</v>
+        <v>208250</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>SO Norrby Mosse, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>686878</v>
+        <v>687058</v>
       </c>
       <c r="R140" t="n">
-        <v>6562971</v>
+        <v>6563228</v>
       </c>
       <c r="S140" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -16013,12 +16007,22 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16027,26 +16031,25 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126003792</v>
+        <v>117554483</v>
       </c>
       <c r="B141" t="n">
         <v>99035</v>
@@ -16081,17 +16084,17 @@
       <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>SO Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>687046</v>
+        <v>686878</v>
       </c>
       <c r="R141" t="n">
-        <v>6563346</v>
+        <v>6562971</v>
       </c>
       <c r="S141" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -16115,12 +16118,12 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16148,7 +16151,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126005160</v>
+        <v>126003792</v>
       </c>
       <c r="B142" t="n">
         <v>99035</v>
@@ -16187,10 +16190,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>687034</v>
+        <v>687046</v>
       </c>
       <c r="R142" t="n">
-        <v>6563204</v>
+        <v>6563346</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16250,7 +16253,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126061084</v>
+        <v>126005160</v>
       </c>
       <c r="B143" t="n">
         <v>99035</v>
@@ -16279,16 +16282,20 @@
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>687014</v>
+        <v>687034</v>
       </c>
       <c r="R143" t="n">
-        <v>6563215</v>
+        <v>6563204</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16315,22 +16322,12 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>15:14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>15:14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16339,25 +16336,26 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
+      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>126061091</v>
+        <v>126061084</v>
       </c>
       <c r="B144" t="n">
         <v>99035</v>
@@ -16392,10 +16390,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>686871</v>
+        <v>687014</v>
       </c>
       <c r="R144" t="n">
-        <v>6562972</v>
+        <v>6563215</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16427,7 +16425,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16437,7 +16435,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16464,7 +16462,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>126061099</v>
+        <v>126061091</v>
       </c>
       <c r="B145" t="n">
         <v>99035</v>
@@ -16499,10 +16497,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>686857</v>
+        <v>686871</v>
       </c>
       <c r="R145" t="n">
-        <v>6562875</v>
+        <v>6562972</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16534,7 +16532,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16544,7 +16542,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16564,14 +16562,14 @@
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>126061102</v>
+        <v>126061099</v>
       </c>
       <c r="B146" t="n">
         <v>99035</v>
@@ -16606,10 +16604,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>686837</v>
+        <v>686857</v>
       </c>
       <c r="R146" t="n">
-        <v>6562829</v>
+        <v>6562875</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16641,7 +16639,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16651,7 +16649,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16678,7 +16676,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>126233785</v>
+        <v>126061102</v>
       </c>
       <c r="B147" t="n">
         <v>99035</v>
@@ -16707,24 +16705,16 @@
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="J147" t="inlineStr"/>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L147" t="inlineStr"/>
-      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>686839</v>
+        <v>686837</v>
       </c>
       <c r="R147" t="n">
-        <v>6563016</v>
+        <v>6562829</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16751,12 +16741,22 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16765,26 +16765,25 @@
       <c r="AE147" t="b">
         <v>0</v>
       </c>
-      <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
       </c>
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Bodil Ravn, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126234010</v>
+        <v>126233785</v>
       </c>
       <c r="B148" t="n">
         <v>99035</v>
@@ -16827,10 +16826,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>687160</v>
+        <v>686839</v>
       </c>
       <c r="R148" t="n">
-        <v>6563261</v>
+        <v>6563016</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16883,14 +16882,14 @@
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Bodil Ravn, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126234159</v>
+        <v>126234010</v>
       </c>
       <c r="B149" t="n">
         <v>99035</v>
@@ -16918,13 +16917,13 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr"/>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr"/>
       <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
@@ -16933,13 +16932,13 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>687297</v>
+        <v>687160</v>
       </c>
       <c r="R149" t="n">
-        <v>6563381</v>
+        <v>6563261</v>
       </c>
       <c r="S149" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -16969,11 +16968,6 @@
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>Ett flertal i blomning.</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16994,14 +16988,14 @@
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Bodil Ravn, Ulf Johansson</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126234439</v>
+        <v>126234159</v>
       </c>
       <c r="B150" t="n">
         <v>99035</v>
@@ -17031,34 +17025,26 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J150" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
       <c r="L150" t="inlineStr"/>
       <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Norrby mosse SO, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>686777</v>
+        <v>687297</v>
       </c>
       <c r="R150" t="n">
-        <v>6563073</v>
+        <v>6563381</v>
       </c>
       <c r="S150" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -17088,6 +17074,11 @@
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>Ett flertal i blomning.</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17103,19 +17094,19 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Bodil Ravn, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126234644</v>
+        <v>126234439</v>
       </c>
       <c r="B151" t="n">
         <v>99035</v>
@@ -17145,7 +17136,7 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -17153,7 +17144,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr"/>
       <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
@@ -17162,10 +17157,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>686837</v>
+        <v>686777</v>
       </c>
       <c r="R151" t="n">
-        <v>6562967</v>
+        <v>6563073</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17225,7 +17220,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>126234771</v>
+        <v>126234644</v>
       </c>
       <c r="B152" t="n">
         <v>99035</v>
@@ -17255,7 +17250,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -17268,14 +17263,14 @@
       <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Norrby mosse OSO, Srm</t>
+          <t>Norrby mosse SO, Srm</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>686976</v>
+        <v>686837</v>
       </c>
       <c r="R152" t="n">
-        <v>6563107</v>
+        <v>6562967</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17335,10 +17330,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>133767702</v>
+        <v>126234771</v>
       </c>
       <c r="B153" t="n">
-        <v>99112</v>
+        <v>99035</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17363,21 +17358,29 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I153" t="inlineStr"/>
-      <c r="J153" t="inlineStr"/>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr"/>
       <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrby mosse OSO, Srm</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>686845</v>
+        <v>686976</v>
       </c>
       <c r="R153" t="n">
-        <v>6563325</v>
+        <v>6563107</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17404,12 +17407,12 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17425,22 +17428,22 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>126061092</v>
+        <v>133767702</v>
       </c>
       <c r="B154" t="n">
-        <v>99022</v>
+        <v>99112</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17448,43 +17451,38 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>220093</v>
+        <v>219790</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>686880</v>
+        <v>686845</v>
       </c>
       <c r="R154" t="n">
-        <v>6562892</v>
+        <v>6563325</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17511,22 +17509,12 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z154" t="inlineStr">
-        <is>
-          <t>14:35</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB154" t="inlineStr">
-        <is>
-          <t>14:35</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17535,25 +17523,26 @@
       <c r="AE154" t="b">
         <v>0</v>
       </c>
+      <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="b">
         <v>0</v>
       </c>
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>126061094</v>
+        <v>126061092</v>
       </c>
       <c r="B155" t="n">
         <v>99022</v>
@@ -17597,10 +17586,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>686866</v>
+        <v>686880</v>
       </c>
       <c r="R155" t="n">
-        <v>6562874</v>
+        <v>6562892</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17632,7 +17621,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17642,7 +17631,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17669,7 +17658,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>126061100</v>
+        <v>126061094</v>
       </c>
       <c r="B156" t="n">
         <v>99022</v>
@@ -17699,7 +17688,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -17713,10 +17702,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>686857</v>
+        <v>686866</v>
       </c>
       <c r="R156" t="n">
-        <v>6562875</v>
+        <v>6562874</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17748,7 +17737,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17758,7 +17747,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17785,37 +17774,37 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>86686018</v>
+        <v>126061100</v>
       </c>
       <c r="B157" t="n">
-        <v>99118</v>
+        <v>99022</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -17823,23 +17812,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L157" t="inlineStr"/>
-      <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Tyresta S Ungfars kärr, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>686831</v>
+        <v>686857</v>
       </c>
       <c r="R157" t="n">
-        <v>6563296</v>
+        <v>6562875</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17866,17 +17848,22 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2020-07-04</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2020-07-04</t>
-        </is>
-      </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>Från Ungfars kärrs södra spets och ca 200 meter österut. Ungefär hälften av skotten utanför parkens gräns. 4 blomstänglar. Området var bökat av vildsvin. Vissa skott var uppgrävda.</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17885,26 +17872,25 @@
       <c r="AE157" t="b">
         <v>0</v>
       </c>
-      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
       </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>96672256</v>
+        <v>86686018</v>
       </c>
       <c r="B158" t="n">
         <v>99118</v>
@@ -17932,24 +17918,36 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I158" t="inlineStr"/>
-      <c r="J158" t="inlineStr"/>
-      <c r="K158" t="inlineStr"/>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr"/>
       <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>NO Norrby mosse, Srm</t>
+          <t>Tyresta S Ungfars kärr, Srm</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>686848</v>
+        <v>686831</v>
       </c>
       <c r="R158" t="n">
-        <v>6563295</v>
+        <v>6563296</v>
       </c>
       <c r="S158" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -17973,12 +17971,17 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
+          <t>2020-07-04</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
+          <t>2020-07-04</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>Från Ungfars kärrs södra spets och ca 200 meter österut. Ungefär hälften av skotten utanför parkens gräns. 4 blomstänglar. Området var bökat av vildsvin. Vissa skott var uppgrävda.</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17994,19 +17997,19 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>97242656</v>
+        <v>96672256</v>
       </c>
       <c r="B159" t="n">
         <v>99118</v>
@@ -18035,21 +18038,23 @@
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>OSO Ungfars mosse, Srm</t>
+          <t>NO Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>686846</v>
+        <v>686848</v>
       </c>
       <c r="R159" t="n">
-        <v>6563316</v>
+        <v>6563295</v>
       </c>
       <c r="S159" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -18073,22 +18078,12 @@
       </c>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>2021-11-20</t>
-        </is>
-      </c>
-      <c r="Z159" t="inlineStr">
-        <is>
-          <t>13:59</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2021-11-20</t>
-        </is>
-      </c>
-      <c r="AB159" t="inlineStr">
-        <is>
-          <t>13:59</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -18097,25 +18092,26 @@
       <c r="AE159" t="b">
         <v>0</v>
       </c>
+      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Thomas Strid</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Thomas Strid, Bodil Ravn, Ulf Johansson, Tiina Laantee</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>97243108</v>
+        <v>97242656</v>
       </c>
       <c r="B160" t="n">
         <v>99118</v>
@@ -18148,17 +18144,17 @@
       <c r="L160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Tyresta, Srm</t>
+          <t>OSO Ungfars mosse, Srm</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>686847</v>
+        <v>686846</v>
       </c>
       <c r="R160" t="n">
-        <v>6563308</v>
+        <v>6563316</v>
       </c>
       <c r="S160" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -18187,7 +18183,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -18197,7 +18193,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -18224,7 +18220,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>97330311</v>
+        <v>97243108</v>
       </c>
       <c r="B161" t="n">
         <v>99118</v>
@@ -18252,29 +18248,22 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J161" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Tyresta NP, SSV Bylsjön (*knärot* /stjälk/), Srm</t>
+          <t>Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q161" t="n">
         <v>686847</v>
       </c>
       <c r="R161" t="n">
-        <v>6563309</v>
+        <v>6563308</v>
       </c>
       <c r="S161" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -18296,24 +18285,24 @@
           <t>Österhaninge</t>
         </is>
       </c>
-      <c r="X161" t="inlineStr">
-        <is>
-          <t>AB-Han-0218</t>
-        </is>
-      </c>
       <c r="Y161" t="inlineStr">
         <is>
           <t>2021-11-20</t>
         </is>
       </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>2021-11-20</t>
         </is>
       </c>
-      <c r="AC161" t="inlineStr">
-        <is>
-          <t>/Ej räknad/</t>
+      <c r="AB161" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18328,23 +18317,19 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Tiina Laantee, Ulf Johansson, Bodil Ravn, Thomas Strid</t>
-        </is>
-      </c>
-      <c r="AY161" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Thomas Strid, Bodil Ravn, Ulf Johansson, Tiina Laantee</t>
+        </is>
+      </c>
+      <c r="AY161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>98104097</v>
+        <v>97330311</v>
       </c>
       <c r="B162" t="n">
         <v>99118</v>
@@ -18374,27 +18359,24 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr"/>
-      <c r="L162" t="inlineStr"/>
-      <c r="N162" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Ungfars kärr SO, Srm</t>
+          <t>Tyresta NP, SSV Bylsjön (*knärot* /stjälk/), Srm</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>686934</v>
+        <v>686847</v>
       </c>
       <c r="R162" t="n">
-        <v>6563325</v>
+        <v>6563309</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18419,19 +18401,24 @@
           <t>Österhaninge</t>
         </is>
       </c>
+      <c r="X162" t="inlineStr">
+        <is>
+          <t>AB-Han-0218</t>
+        </is>
+      </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>2022-01-13</t>
+          <t>2021-11-20</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2022-01-13</t>
+          <t>2021-11-20</t>
         </is>
       </c>
       <c r="AC162" t="inlineStr">
         <is>
-          <t>Intill djurstig och granlåga</t>
+          <t>/Ej räknad/</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -18440,26 +18427,29 @@
       <c r="AE162" t="b">
         <v>0</v>
       </c>
-      <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="b">
         <v>0</v>
       </c>
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
-        </is>
-      </c>
-      <c r="AY162" t="inlineStr"/>
+          <t>Tiina Laantee, Ulf Johansson, Bodil Ravn, Thomas Strid</t>
+        </is>
+      </c>
+      <c r="AY162" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>104249959</v>
+        <v>98104097</v>
       </c>
       <c r="B163" t="n">
         <v>99118</v>
@@ -18487,24 +18477,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I163" t="inlineStr"/>
-      <c r="J163" t="inlineStr"/>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr"/>
       <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>SO Norrby Mosse, Srm</t>
+          <t>Ungfars kärr SO, Srm</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>687011</v>
+        <v>686934</v>
       </c>
       <c r="R163" t="n">
-        <v>6562869</v>
+        <v>6563325</v>
       </c>
       <c r="S163" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -18528,17 +18526,17 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2022-01-13</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2022-01-13</t>
         </is>
       </c>
       <c r="AC163" t="inlineStr">
         <is>
-          <t>Samma lokal som noterades 17/11-21. Ca 25 ex. Koordinaterna har varierat något vid besöken.</t>
+          <t>Intill djurstig och granlåga</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18554,19 +18552,19 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>109890506</v>
+        <v>104249959</v>
       </c>
       <c r="B164" t="n">
         <v>99118</v>
@@ -18601,17 +18599,17 @@
       <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Ö Norrby Mosse, Srm</t>
+          <t>SO Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>686831</v>
+        <v>687011</v>
       </c>
       <c r="R164" t="n">
-        <v>6563216</v>
+        <v>6562869</v>
       </c>
       <c r="S164" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -18635,12 +18633,17 @@
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2022-09-16</t>
+        </is>
+      </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>Samma lokal som noterades 17/11-21. Ca 25 ex. Koordinaterna har varierat något vid besöken.</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -18668,7 +18671,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>119475594</v>
+        <v>109890506</v>
       </c>
       <c r="B165" t="n">
         <v>99118</v>
@@ -18696,29 +18699,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J165" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr"/>
       <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>NO Norrby  Mosse, Srm</t>
+          <t>Ö Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>686995</v>
+        <v>686831</v>
       </c>
       <c r="R165" t="n">
-        <v>6563315</v>
+        <v>6563216</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18745,12 +18740,12 @@
       </c>
       <c r="Y165" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18778,7 +18773,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>121859637</v>
+        <v>119475594</v>
       </c>
       <c r="B166" t="n">
         <v>99118</v>
@@ -18806,17 +18801,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I166" t="inlineStr"/>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
+      <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Öster om Tyresta by, Tyresta, Srm</t>
+          <t>NO Norrby  Mosse, Srm</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>686863</v>
+        <v>686995</v>
       </c>
       <c r="R166" t="n">
-        <v>6563252</v>
+        <v>6563315</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18843,22 +18850,12 @@
       </c>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="Z166" t="inlineStr">
-        <is>
-          <t>16:22</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="AB166" t="inlineStr">
-        <is>
-          <t>16:22</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18867,25 +18864,26 @@
       <c r="AE166" t="b">
         <v>0</v>
       </c>
+      <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="b">
         <v>0</v>
       </c>
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121859638</v>
+        <v>121859637</v>
       </c>
       <c r="B167" t="n">
         <v>99118</v>
@@ -18920,10 +18918,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>686826</v>
+        <v>686863</v>
       </c>
       <c r="R167" t="n">
-        <v>6563286</v>
+        <v>6563252</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18955,7 +18953,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -18965,7 +18963,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18992,7 +18990,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>121859639</v>
+        <v>121859638</v>
       </c>
       <c r="B168" t="n">
         <v>99118</v>
@@ -19027,10 +19025,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>686827</v>
+        <v>686826</v>
       </c>
       <c r="R168" t="n">
-        <v>6563296</v>
+        <v>6563286</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19062,7 +19060,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -19072,7 +19070,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -19099,7 +19097,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>121859640</v>
+        <v>121859639</v>
       </c>
       <c r="B169" t="n">
         <v>99118</v>
@@ -19134,10 +19132,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>686837</v>
+        <v>686827</v>
       </c>
       <c r="R169" t="n">
-        <v>6563297</v>
+        <v>6563296</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19169,7 +19167,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -19179,7 +19177,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -19206,7 +19204,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>121859642</v>
+        <v>121859640</v>
       </c>
       <c r="B170" t="n">
         <v>99118</v>
@@ -19235,24 +19233,16 @@
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
-      <c r="J170" t="inlineStr"/>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L170" t="inlineStr"/>
-      <c r="N170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
           <t>Öster om Tyresta by, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>686834</v>
+        <v>686837</v>
       </c>
       <c r="R170" t="n">
-        <v>6563305</v>
+        <v>6563297</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19284,7 +19274,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -19294,7 +19284,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19303,7 +19293,6 @@
       <c r="AE170" t="b">
         <v>0</v>
       </c>
-      <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
         <v>0</v>
       </c>
@@ -19322,7 +19311,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>121859643</v>
+        <v>121859642</v>
       </c>
       <c r="B171" t="n">
         <v>99118</v>
@@ -19351,6 +19340,14 @@
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr"/>
+      <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
           <t>Öster om Tyresta by, Tyresta, Srm</t>
@@ -19360,7 +19357,7 @@
         <v>686834</v>
       </c>
       <c r="R171" t="n">
-        <v>6563309</v>
+        <v>6563305</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19392,7 +19389,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -19402,7 +19399,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -19411,6 +19408,7 @@
       <c r="AE171" t="b">
         <v>0</v>
       </c>
+      <c r="AF171" t="inlineStr"/>
       <c r="AG171" t="b">
         <v>0</v>
       </c>
@@ -19429,7 +19427,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>121859644</v>
+        <v>121859643</v>
       </c>
       <c r="B172" t="n">
         <v>99118</v>
@@ -19464,10 +19462,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>686844</v>
+        <v>686834</v>
       </c>
       <c r="R172" t="n">
-        <v>6563303</v>
+        <v>6563309</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19499,7 +19497,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -19509,7 +19507,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -19536,7 +19534,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>121859646</v>
+        <v>121859644</v>
       </c>
       <c r="B173" t="n">
         <v>99118</v>
@@ -19571,7 +19569,7 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>686841</v>
+        <v>686844</v>
       </c>
       <c r="R173" t="n">
         <v>6563303</v>
@@ -19606,7 +19604,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -19616,7 +19614,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19643,7 +19641,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>121859647</v>
+        <v>121859646</v>
       </c>
       <c r="B174" t="n">
         <v>99118</v>
@@ -19678,10 +19676,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>686854</v>
+        <v>686841</v>
       </c>
       <c r="R174" t="n">
-        <v>6563286</v>
+        <v>6563303</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19713,7 +19711,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -19723,7 +19721,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19750,7 +19748,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>121859649</v>
+        <v>121859647</v>
       </c>
       <c r="B175" t="n">
         <v>99118</v>
@@ -19785,10 +19783,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>686851</v>
+        <v>686854</v>
       </c>
       <c r="R175" t="n">
-        <v>6563299</v>
+        <v>6563286</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19820,7 +19818,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -19830,7 +19828,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19857,7 +19855,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>121859650</v>
+        <v>121859649</v>
       </c>
       <c r="B176" t="n">
         <v>99118</v>
@@ -19892,10 +19890,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>686895</v>
+        <v>686851</v>
       </c>
       <c r="R176" t="n">
-        <v>6563306</v>
+        <v>6563299</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19927,7 +19925,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -19937,7 +19935,7 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19964,7 +19962,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>122220583</v>
+        <v>121859650</v>
       </c>
       <c r="B177" t="n">
         <v>99118</v>
@@ -19992,29 +19990,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J177" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K177" t="inlineStr"/>
-      <c r="L177" t="inlineStr"/>
-      <c r="N177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>SO Norrby Mosse, Srm</t>
+          <t>Öster om Tyresta by, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>686996</v>
+        <v>686895</v>
       </c>
       <c r="R177" t="n">
-        <v>6562864</v>
+        <v>6563306</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -20041,17 +20027,22 @@
       </c>
       <c r="Y177" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="Z177" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
-        </is>
-      </c>
-      <c r="AC177" t="inlineStr">
-        <is>
-          <t>Samma lokal som rapporterats -21 och -22 men en ny klon. Den förra har möjligen haft lite problem med grisbök.</t>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="AB177" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -20060,26 +20051,25 @@
       <c r="AE177" t="b">
         <v>0</v>
       </c>
-      <c r="AF177" t="inlineStr"/>
       <c r="AG177" t="b">
         <v>0</v>
       </c>
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>122781008</v>
+        <v>122220583</v>
       </c>
       <c r="B178" t="n">
         <v>99118</v>
@@ -20107,21 +20097,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I178" t="inlineStr"/>
-      <c r="J178" t="inlineStr"/>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K178" t="inlineStr"/>
       <c r="L178" t="inlineStr"/>
       <c r="N178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Knärot, Srm</t>
+          <t>SO Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>686833</v>
+        <v>686996</v>
       </c>
       <c r="R178" t="n">
-        <v>6563215</v>
+        <v>6562864</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20148,17 +20146,17 @@
       </c>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Samma lokal som rapporterats -21 och -22 men en ny klon. Den förra har möjligen haft lite problem med grisbök.</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -20174,19 +20172,19 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>126418709</v>
+        <v>122781008</v>
       </c>
       <c r="B179" t="n">
         <v>99118</v>
@@ -20214,29 +20212,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J179" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
       <c r="K179" t="inlineStr"/>
       <c r="L179" t="inlineStr"/>
       <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Knärot, Srm</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>686771</v>
+        <v>686833</v>
       </c>
       <c r="R179" t="n">
-        <v>6563297</v>
+        <v>6563215</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20263,17 +20253,17 @@
       </c>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AC179" t="inlineStr">
         <is>
-          <t>Två av dem i knopp, ca 3 m väster om de andra.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -20289,19 +20279,19 @@
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>126418756</v>
+        <v>126418709</v>
       </c>
       <c r="B180" t="n">
         <v>99118</v>
@@ -20331,7 +20321,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
@@ -20348,10 +20338,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>686781</v>
+        <v>686771</v>
       </c>
       <c r="R180" t="n">
-        <v>6563292</v>
+        <v>6563297</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20388,7 +20378,7 @@
       </c>
       <c r="AC180" t="inlineStr">
         <is>
-          <t>En av dem i knopp.</t>
+          <t>Två av dem i knopp, ca 3 m väster om de andra.</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -20416,7 +20406,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>127932426</v>
+        <v>126418756</v>
       </c>
       <c r="B181" t="n">
         <v>99118</v>
@@ -20446,7 +20436,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -20463,10 +20453,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>686998</v>
+        <v>686781</v>
       </c>
       <c r="R181" t="n">
-        <v>6563316</v>
+        <v>6563292</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20493,17 +20483,17 @@
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AC181" t="inlineStr">
         <is>
-          <t>Återfynd, rapporterad -24 med 3 ex. Nu 5 ex.</t>
+          <t>En av dem i knopp.</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -20531,7 +20521,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>128341941</v>
+        <v>127932426</v>
       </c>
       <c r="B182" t="n">
         <v>99118</v>
@@ -20561,7 +20551,7 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -20578,10 +20568,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>687244</v>
+        <v>686998</v>
       </c>
       <c r="R182" t="n">
-        <v>6563404</v>
+        <v>6563316</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20608,12 +20598,17 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC182" t="inlineStr">
+        <is>
+          <t>Återfynd, rapporterad -24 med 3 ex. Nu 5 ex.</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -20641,7 +20636,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129564285</v>
+        <v>128341941</v>
       </c>
       <c r="B183" t="n">
         <v>99118</v>
@@ -20669,8 +20664,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I183" t="inlineStr"/>
-      <c r="J183" t="inlineStr"/>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K183" t="inlineStr"/>
       <c r="L183" t="inlineStr"/>
       <c r="N183" t="inlineStr"/>
@@ -20680,10 +20683,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>686625</v>
+        <v>687244</v>
       </c>
       <c r="R183" t="n">
-        <v>6563000</v>
+        <v>6563404</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20710,12 +20713,12 @@
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -20743,10 +20746,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>133767721</v>
+        <v>129564285</v>
       </c>
       <c r="B184" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20782,10 +20785,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>686845</v>
+        <v>686625</v>
       </c>
       <c r="R184" t="n">
-        <v>6563325</v>
+        <v>6563000</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20812,12 +20815,12 @@
       </c>
       <c r="Y184" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -20845,32 +20848,32 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>96643458</v>
+        <v>133767721</v>
       </c>
       <c r="B185" t="n">
-        <v>106244</v>
+        <v>99195</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -20880,14 +20883,14 @@
       <c r="N185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Vargklåva mosse S om, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>687154</v>
+        <v>686845</v>
       </c>
       <c r="R185" t="n">
-        <v>6563329</v>
+        <v>6563325</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20914,12 +20917,12 @@
       </c>
       <c r="Y185" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -20935,19 +20938,19 @@
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>96858761</v>
+        <v>96643458</v>
       </c>
       <c r="B186" t="n">
         <v>106244</v>
@@ -20982,17 +20985,17 @@
       <c r="N186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Ungfars kärr SO, Srm</t>
+          <t>Vargklåva mosse S om, Srm</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>687064</v>
+        <v>687154</v>
       </c>
       <c r="R186" t="n">
-        <v>6563258</v>
+        <v>6563329</v>
       </c>
       <c r="S186" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -21016,17 +21019,12 @@
       </c>
       <c r="Y186" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="AC186" t="inlineStr">
-        <is>
-          <t>Två bestånd</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -21054,7 +21052,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>97204577</v>
+        <v>96858761</v>
       </c>
       <c r="B187" t="n">
         <v>106244</v>
@@ -21089,17 +21087,17 @@
       <c r="N187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>SO Norrby mosse, Srm</t>
+          <t>Ungfars kärr SO, Srm</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>687019</v>
+        <v>687064</v>
       </c>
       <c r="R187" t="n">
-        <v>6562889</v>
+        <v>6563258</v>
       </c>
       <c r="S187" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -21123,12 +21121,17 @@
       </c>
       <c r="Y187" t="inlineStr">
         <is>
-          <t>2021-11-17</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>2021-11-17</t>
+          <t>2021-10-26</t>
+        </is>
+      </c>
+      <c r="AC187" t="inlineStr">
+        <is>
+          <t>Två bestånd</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -21144,19 +21147,19 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>100252927</v>
+        <v>97204577</v>
       </c>
       <c r="B188" t="n">
         <v>106244</v>
@@ -21191,17 +21194,17 @@
       <c r="N188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>NO Norrby  Mosse, Srm</t>
+          <t>SO Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>687152</v>
+        <v>687019</v>
       </c>
       <c r="R188" t="n">
-        <v>6563326</v>
+        <v>6562889</v>
       </c>
       <c r="S188" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -21225,12 +21228,12 @@
       </c>
       <c r="Y188" t="inlineStr">
         <is>
-          <t>2022-04-26</t>
+          <t>2021-11-17</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>2022-04-26</t>
+          <t>2021-11-17</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -21258,7 +21261,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>116743172</v>
+        <v>100252927</v>
       </c>
       <c r="B189" t="n">
         <v>106244</v>
@@ -21287,16 +21290,20 @@
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr"/>
+      <c r="N189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Ungfars kärr, Ungfars kärr, Srm</t>
+          <t>NO Norrby  Mosse, Srm</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>687088</v>
+        <v>687152</v>
       </c>
       <c r="R189" t="n">
-        <v>6563243</v>
+        <v>6563326</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21323,12 +21330,12 @@
       </c>
       <c r="Y189" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2022-04-26</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2022-04-26</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -21337,25 +21344,26 @@
       <c r="AE189" t="b">
         <v>0</v>
       </c>
+      <c r="AF189" t="inlineStr"/>
       <c r="AG189" t="b">
         <v>0</v>
       </c>
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>125965889</v>
+        <v>116743172</v>
       </c>
       <c r="B190" t="n">
         <v>106244</v>
@@ -21390,10 +21398,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>687076</v>
+        <v>687088</v>
       </c>
       <c r="R190" t="n">
-        <v>6563220</v>
+        <v>6563243</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21420,12 +21428,12 @@
       </c>
       <c r="Y190" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -21452,7 +21460,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>126003574</v>
+        <v>125965889</v>
       </c>
       <c r="B191" t="n">
         <v>106244</v>
@@ -21481,20 +21489,16 @@
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
-      <c r="J191" t="inlineStr"/>
-      <c r="K191" t="inlineStr"/>
-      <c r="L191" t="inlineStr"/>
-      <c r="N191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>SO Norrby Mosse, Srm</t>
+          <t>Ungfars kärr, Ungfars kärr, Srm</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>686803</v>
+        <v>687076</v>
       </c>
       <c r="R191" t="n">
-        <v>6563098</v>
+        <v>6563220</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21521,12 +21525,12 @@
       </c>
       <c r="Y191" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -21535,26 +21539,25 @@
       <c r="AE191" t="b">
         <v>0</v>
       </c>
-      <c r="AF191" t="inlineStr"/>
       <c r="AG191" t="b">
         <v>0</v>
       </c>
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>126061078</v>
+        <v>126003574</v>
       </c>
       <c r="B192" t="n">
         <v>106244</v>
@@ -21583,16 +21586,20 @@
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr"/>
+      <c r="L192" t="inlineStr"/>
+      <c r="N192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>SO Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>687085</v>
+        <v>686803</v>
       </c>
       <c r="R192" t="n">
-        <v>6563229</v>
+        <v>6563098</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21619,22 +21626,12 @@
       </c>
       <c r="Y192" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z192" t="inlineStr">
-        <is>
-          <t>15:40</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB192" t="inlineStr">
-        <is>
-          <t>15:40</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -21643,25 +21640,26 @@
       <c r="AE192" t="b">
         <v>0</v>
       </c>
+      <c r="AF192" t="inlineStr"/>
       <c r="AG192" t="b">
         <v>0</v>
       </c>
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>126061079</v>
+        <v>126061078</v>
       </c>
       <c r="B193" t="n">
         <v>106244</v>
@@ -21696,10 +21694,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>687082</v>
+        <v>687085</v>
       </c>
       <c r="R193" t="n">
-        <v>6563241</v>
+        <v>6563229</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21731,7 +21729,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -21741,7 +21739,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -21768,7 +21766,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>126234373</v>
+        <v>126061079</v>
       </c>
       <c r="B194" t="n">
         <v>106244</v>
@@ -21796,29 +21794,17 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J194" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K194" t="inlineStr"/>
-      <c r="L194" t="inlineStr"/>
-      <c r="N194" t="inlineStr"/>
+      <c r="I194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Norrby mosse SO, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>686756</v>
+        <v>687082</v>
       </c>
       <c r="R194" t="n">
-        <v>6563092</v>
+        <v>6563241</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21845,12 +21831,22 @@
       </c>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z194" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB194" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -21859,26 +21855,25 @@
       <c r="AE194" t="b">
         <v>0</v>
       </c>
-      <c r="AF194" t="inlineStr"/>
       <c r="AG194" t="b">
         <v>0</v>
       </c>
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>126234937</v>
+        <v>126234373</v>
       </c>
       <c r="B195" t="n">
         <v>106244</v>
@@ -21916,23 +21911,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K195" t="inlineStr"/>
       <c r="L195" t="inlineStr"/>
       <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Ungfars kärr SO, Srm</t>
+          <t>Norrby mosse SO, Srm</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>687103</v>
+        <v>686756</v>
       </c>
       <c r="R195" t="n">
-        <v>6563191</v>
+        <v>6563092</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21992,10 +21983,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>96643468</v>
+        <v>126234937</v>
       </c>
       <c r="B196" t="n">
-        <v>97989</v>
+        <v>106244</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -22003,46 +21994,50 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>221941</v>
+        <v>221144</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K196" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr"/>
       <c r="N196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Vargklåva mosse S om, Srm</t>
+          <t>Ungfars kärr SO, Srm</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>687268</v>
+        <v>687103</v>
       </c>
       <c r="R196" t="n">
-        <v>6563319</v>
+        <v>6563191</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -22069,17 +22064,12 @@
       </c>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
-        </is>
-      </c>
-      <c r="AC196" t="inlineStr">
-        <is>
-          <t>Strax nedom klippbrant</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -22107,7 +22097,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>116746465</v>
+        <v>96643468</v>
       </c>
       <c r="B197" t="n">
         <v>97989</v>
@@ -22135,17 +22125,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I197" t="inlineStr"/>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr"/>
+      <c r="N197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Norrby mosse, Norrby mosse, Srm</t>
+          <t>Vargklåva mosse S om, Srm</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>686888</v>
+        <v>687268</v>
       </c>
       <c r="R197" t="n">
-        <v>6563206</v>
+        <v>6563319</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -22172,12 +22174,17 @@
       </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2021-10-12</t>
+        </is>
+      </c>
+      <c r="AC197" t="inlineStr">
+        <is>
+          <t>Strax nedom klippbrant</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -22186,28 +22193,29 @@
       <c r="AE197" t="b">
         <v>0</v>
       </c>
+      <c r="AF197" t="inlineStr"/>
       <c r="AG197" t="b">
         <v>0</v>
       </c>
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>121742517</v>
+        <v>116746465</v>
       </c>
       <c r="B198" t="n">
-        <v>97983</v>
+        <v>97989</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -22215,16 +22223,16 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -22239,10 +22247,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>686859</v>
+        <v>686888</v>
       </c>
       <c r="R198" t="n">
-        <v>6562875</v>
+        <v>6563206</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22269,12 +22277,12 @@
       </c>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -22301,7 +22309,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>122928987</v>
+        <v>121742517</v>
       </c>
       <c r="B199" t="n">
         <v>97983</v>
@@ -22330,20 +22338,16 @@
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
-      <c r="J199" t="inlineStr"/>
-      <c r="K199" t="inlineStr"/>
-      <c r="L199" t="inlineStr"/>
-      <c r="N199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Norrby mosse, Srm</t>
+          <t>Norrby mosse, Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>686389</v>
+        <v>686859</v>
       </c>
       <c r="R199" t="n">
-        <v>6562967</v>
+        <v>6562875</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22370,22 +22374,12 @@
       </c>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="Z199" t="inlineStr">
-        <is>
-          <t>10:36</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="AB199" t="inlineStr">
-        <is>
-          <t>10:36</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -22400,19 +22394,19 @@
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>122930294</v>
+        <v>122928987</v>
       </c>
       <c r="B200" t="n">
         <v>97983</v>
@@ -22451,13 +22445,13 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>686824</v>
+        <v>686389</v>
       </c>
       <c r="R200" t="n">
-        <v>6562778</v>
+        <v>6562967</v>
       </c>
       <c r="S200" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T200" t="inlineStr">
         <is>
@@ -22486,7 +22480,7 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -22496,7 +22490,7 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -22523,7 +22517,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>125963374</v>
+        <v>122930294</v>
       </c>
       <c r="B201" t="n">
         <v>97983</v>
@@ -22552,19 +22546,23 @@
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
+      <c r="J201" t="inlineStr"/>
+      <c r="K201" t="inlineStr"/>
+      <c r="L201" t="inlineStr"/>
+      <c r="N201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Norrby mosse, Norrby mosse, Srm</t>
+          <t>Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>686873</v>
+        <v>686824</v>
       </c>
       <c r="R201" t="n">
-        <v>6562867</v>
+        <v>6562778</v>
       </c>
       <c r="S201" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -22588,12 +22586,22 @@
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="Z201" t="inlineStr">
+        <is>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AB201" t="inlineStr">
+        <is>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -22608,19 +22616,19 @@
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>125976418</v>
+        <v>125963374</v>
       </c>
       <c r="B202" t="n">
         <v>97983</v>
@@ -22649,23 +22657,19 @@
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
-      <c r="J202" t="inlineStr"/>
-      <c r="K202" t="inlineStr"/>
-      <c r="L202" t="inlineStr"/>
-      <c r="N202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Norrby mosse Ö om, Srm</t>
+          <t>Norrby mosse, Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>686836</v>
+        <v>686873</v>
       </c>
       <c r="R202" t="n">
-        <v>6563105</v>
+        <v>6562867</v>
       </c>
       <c r="S202" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -22697,37 +22701,31 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC202" t="inlineStr">
-        <is>
-          <t>Riklig förekomst i skogskärr</t>
-        </is>
-      </c>
       <c r="AD202" t="b">
         <v>0</v>
       </c>
       <c r="AE202" t="b">
         <v>0</v>
       </c>
-      <c r="AF202" t="inlineStr"/>
       <c r="AG202" t="b">
         <v>0</v>
       </c>
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>126061082</v>
+        <v>125976418</v>
       </c>
       <c r="B203" t="n">
         <v>97983</v>
@@ -22756,19 +22754,23 @@
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
+      <c r="J203" t="inlineStr"/>
+      <c r="K203" t="inlineStr"/>
+      <c r="L203" t="inlineStr"/>
+      <c r="N203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>Norrby mosse Ö om, Srm</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>687079</v>
+        <v>686836</v>
       </c>
       <c r="R203" t="n">
-        <v>6563240</v>
+        <v>6563105</v>
       </c>
       <c r="S203" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T203" t="inlineStr">
         <is>
@@ -22795,19 +22797,14 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z203" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AA203" t="inlineStr">
         <is>
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AB203" t="inlineStr">
-        <is>
-          <t>15:22</t>
+      <c r="AC203" t="inlineStr">
+        <is>
+          <t>Riklig förekomst i skogskärr</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -22816,25 +22813,26 @@
       <c r="AE203" t="b">
         <v>0</v>
       </c>
+      <c r="AF203" t="inlineStr"/>
       <c r="AG203" t="b">
         <v>0</v>
       </c>
       <c r="AT203" t="inlineStr"/>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>126061090</v>
+        <v>126061082</v>
       </c>
       <c r="B204" t="n">
         <v>97983</v>
@@ -22869,10 +22867,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>686871</v>
+        <v>687079</v>
       </c>
       <c r="R204" t="n">
-        <v>6562972</v>
+        <v>6563240</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22904,7 +22902,7 @@
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
@@ -22914,7 +22912,7 @@
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -22941,7 +22939,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>126061103</v>
+        <v>126061090</v>
       </c>
       <c r="B205" t="n">
         <v>97983</v>
@@ -22976,10 +22974,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>686811</v>
+        <v>686871</v>
       </c>
       <c r="R205" t="n">
-        <v>6562803</v>
+        <v>6562972</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -23011,7 +23009,7 @@
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
@@ -23021,7 +23019,7 @@
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -23041,14 +23039,14 @@
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>126061111</v>
+        <v>126061103</v>
       </c>
       <c r="B206" t="n">
         <v>97983</v>
@@ -23083,10 +23081,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>687030</v>
+        <v>686811</v>
       </c>
       <c r="R206" t="n">
-        <v>6562755</v>
+        <v>6562803</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -23118,7 +23116,7 @@
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
@@ -23128,7 +23126,7 @@
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -23155,10 +23153,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>122929342</v>
+        <v>126061111</v>
       </c>
       <c r="B207" t="n">
-        <v>97986</v>
+        <v>97983</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -23166,16 +23164,16 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -23184,23 +23182,19 @@
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
-      <c r="J207" t="inlineStr"/>
-      <c r="K207" t="inlineStr"/>
-      <c r="L207" t="inlineStr"/>
-      <c r="N207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Norrby mosse, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>686569</v>
+        <v>687030</v>
       </c>
       <c r="R207" t="n">
-        <v>6562949</v>
+        <v>6562755</v>
       </c>
       <c r="S207" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T207" t="inlineStr">
         <is>
@@ -23224,22 +23218,22 @@
       </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -23254,19 +23248,19 @@
       <c r="AT207" t="inlineStr"/>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>126061110</v>
+        <v>122929342</v>
       </c>
       <c r="B208" t="n">
         <v>97986</v>
@@ -23295,19 +23289,23 @@
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
+      <c r="J208" t="inlineStr"/>
+      <c r="K208" t="inlineStr"/>
+      <c r="L208" t="inlineStr"/>
+      <c r="N208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>687029</v>
+        <v>686569</v>
       </c>
       <c r="R208" t="n">
-        <v>6562759</v>
+        <v>6562949</v>
       </c>
       <c r="S208" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T208" t="inlineStr">
         <is>
@@ -23331,22 +23329,22 @@
       </c>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -23361,22 +23359,22 @@
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>101523203</v>
+        <v>126061110</v>
       </c>
       <c r="B209" t="n">
-        <v>99140</v>
+        <v>97986</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -23384,38 +23382,34 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>221952</v>
+        <v>221946</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
-      <c r="J209" t="inlineStr"/>
-      <c r="K209" t="inlineStr"/>
-      <c r="L209" t="inlineStr"/>
-      <c r="N209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
-          <t>NO Norrby Mosse, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>687050</v>
+        <v>687029</v>
       </c>
       <c r="R209" t="n">
-        <v>6563327</v>
+        <v>6562759</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -23442,12 +23436,22 @@
       </c>
       <c r="Y209" t="inlineStr">
         <is>
-          <t>2022-06-08</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>2022-06-08</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB209" t="inlineStr">
+        <is>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -23456,26 +23460,25 @@
       <c r="AE209" t="b">
         <v>0</v>
       </c>
-      <c r="AF209" t="inlineStr"/>
       <c r="AG209" t="b">
         <v>0</v>
       </c>
       <c r="AT209" t="inlineStr"/>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>117554655</v>
+        <v>101523203</v>
       </c>
       <c r="B210" t="n">
         <v>99140</v>
@@ -23505,23 +23508,19 @@
       </c>
       <c r="I210" t="inlineStr"/>
       <c r="J210" t="inlineStr"/>
-      <c r="K210" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K210" t="inlineStr"/>
       <c r="L210" t="inlineStr"/>
       <c r="N210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
-          <t>NO Norrby  Mosse, Srm</t>
+          <t>NO Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>687062</v>
+        <v>687050</v>
       </c>
       <c r="R210" t="n">
-        <v>6563349</v>
+        <v>6563327</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -23548,12 +23547,12 @@
       </c>
       <c r="Y210" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2022-06-08</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2022-06-08</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -23581,7 +23580,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>126234400</v>
+        <v>117554655</v>
       </c>
       <c r="B211" t="n">
         <v>99140</v>
@@ -23609,16 +23608,8 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I211" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J211" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I211" t="inlineStr"/>
+      <c r="J211" t="inlineStr"/>
       <c r="K211" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -23628,14 +23619,14 @@
       <c r="N211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Norrby mosse SO, Srm</t>
+          <t>NO Norrby  Mosse, Srm</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>686788</v>
+        <v>687062</v>
       </c>
       <c r="R211" t="n">
-        <v>6563073</v>
+        <v>6563349</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23662,12 +23653,12 @@
       </c>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -23683,22 +23674,22 @@
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>134487623</v>
+        <v>126234400</v>
       </c>
       <c r="B212" t="n">
-        <v>99217</v>
+        <v>99140</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -23723,8 +23714,16 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I212" t="inlineStr"/>
-      <c r="J212" t="inlineStr"/>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K212" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -23734,17 +23733,17 @@
       <c r="N212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrby mosse SO, Srm</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>687067</v>
+        <v>686788</v>
       </c>
       <c r="R212" t="n">
-        <v>6563342</v>
+        <v>6563073</v>
       </c>
       <c r="S212" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T212" t="inlineStr">
         <is>
@@ -23768,17 +23767,12 @@
       </c>
       <c r="Y212" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="AC212" t="inlineStr">
-        <is>
-          <t>Ett tiotal i blom samt flera plantor med endast blad. Kan ha varit fler. Återfynd.</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -23794,19 +23788,19 @@
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>134487656</v>
+        <v>134487623</v>
       </c>
       <c r="B213" t="n">
         <v>99217</v>
@@ -23849,13 +23843,13 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>686835</v>
+        <v>687067</v>
       </c>
       <c r="R213" t="n">
-        <v>6563212</v>
+        <v>6563342</v>
       </c>
       <c r="S213" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T213" t="inlineStr">
         <is>
@@ -23889,7 +23883,7 @@
       </c>
       <c r="AC213" t="inlineStr">
         <is>
-          <t>2 i blom samt några plantor med endast blad.</t>
+          <t>Ett tiotal i blom samt flera plantor med endast blad.  Återfynd.</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -23917,7 +23911,7 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>134488457</v>
+        <v>134487656</v>
       </c>
       <c r="B214" t="n">
         <v>99217</v>
@@ -23960,10 +23954,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>687294</v>
+        <v>686835</v>
       </c>
       <c r="R214" t="n">
-        <v>6563391</v>
+        <v>6563212</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -24000,7 +23994,7 @@
       </c>
       <c r="AC214" t="inlineStr">
         <is>
-          <t>2 i blom samt fler med endast blad.</t>
+          <t>2 i blom samt några plantor med endast blad.</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -24028,37 +24022,42 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>129564006</v>
+        <v>134488457</v>
       </c>
       <c r="B215" t="n">
-        <v>79350</v>
+        <v>99217</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>260591</v>
+        <v>221952</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
       <c r="J215" t="inlineStr"/>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr"/>
       <c r="N215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
@@ -24066,10 +24065,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>686681</v>
+        <v>687294</v>
       </c>
       <c r="R215" t="n">
-        <v>6563025</v>
+        <v>6563391</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -24096,19 +24095,24 @@
       </c>
       <c r="Y215" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AC215" t="inlineStr">
+        <is>
+          <t>2 i blom samt fler med endast blad.</t>
         </is>
       </c>
       <c r="AD215" t="b">
         <v>0</v>
       </c>
       <c r="AE215" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF215" t="inlineStr"/>
       <c r="AG215" t="b">
@@ -24126,6 +24130,107 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>129564006</v>
+      </c>
+      <c r="B216" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E216" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr"/>
+      <c r="J216" t="inlineStr"/>
+      <c r="K216" t="inlineStr"/>
+      <c r="N216" t="inlineStr"/>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q216" t="n">
+        <v>686681</v>
+      </c>
+      <c r="R216" t="n">
+        <v>6563025</v>
+      </c>
+      <c r="S216" t="n">
+        <v>10</v>
+      </c>
+      <c r="T216" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V216" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W216" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y216" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AD216" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE216" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF216" t="inlineStr"/>
+      <c r="AG216" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT216" t="inlineStr"/>
+      <c r="AW216" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX216" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY216" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY216"/>
+  <dimension ref="A1:AZ216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116757706</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859625</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859651</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,6 +1140,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859655</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1230,6 +1255,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100251895</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1340,6 +1370,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100252030</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1450,6 +1485,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100252080</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1565,6 +1605,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100252562</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1672,6 +1717,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859619</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1783,6 +1833,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122930166</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1914,6 +1969,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061113</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2029,6 +2089,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126491342</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2144,6 +2209,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126491392</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2250,6 +2320,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96672171</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2367,6 +2442,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97240952</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2483,6 +2563,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106813868</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2589,6 +2674,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112337741</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2716,6 +2806,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859633</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2830,6 +2925,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122220670</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2931,6 +3031,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128342188</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3032,6 +3137,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89470860</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3138,6 +3248,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113689593</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3244,6 +3359,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129563617</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3350,6 +3470,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129563797</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3456,6 +3581,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129563832</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3562,6 +3692,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129564096</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3663,6 +3798,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129564253</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3769,6 +3909,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129564502</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3875,6 +4020,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129564524</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3976,6 +4126,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129592095</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4077,6 +4232,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129192275</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4178,6 +4338,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215511</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4285,6 +4450,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859657</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4386,6 +4556,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129214787</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4487,6 +4662,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104247939</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4588,6 +4768,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129214713</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4689,6 +4874,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129214830</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4790,6 +4980,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215334</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4896,6 +5091,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129736615</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5003,6 +5203,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061106</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5104,6 +5309,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119060941</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5211,6 +5421,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859636</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5318,6 +5533,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859620</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5429,6 +5649,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122930205</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5536,6 +5761,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061107</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5643,6 +5873,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061114</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5744,6 +5979,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122435803</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5845,6 +6085,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128457904</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5946,6 +6191,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96672273</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6051,6 +6301,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128457812</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6152,6 +6407,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89470845</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6253,6 +6513,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96458425</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6361,6 +6626,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97240523</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6478,6 +6748,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97241458</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6605,6 +6880,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859626</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6732,6 +7012,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859630</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6859,6 +7144,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859632</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6965,6 +7255,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129564176</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7075,6 +7370,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129564462</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7176,6 +7476,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96858751</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7299,6 +7604,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97239630</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7407,6 +7717,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97242116</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7515,6 +7830,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97242271</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7623,6 +7943,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97242371</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7724,6 +8049,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215187</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7825,6 +8155,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215443</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7926,6 +8261,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129230409</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8027,6 +8367,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129564547</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8128,6 +8473,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128457646</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8229,6 +8579,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128457920</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8335,6 +8690,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128342170</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8436,6 +8796,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128342050</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8537,6 +8902,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128457671</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8638,6 +9008,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128457880</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8739,6 +9114,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128646813</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8844,6 +9224,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112337759</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8946,6 +9331,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73768473</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9052,6 +9442,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94982629</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9158,6 +9553,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96643401</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9269,6 +9669,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96643445</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9375,6 +9780,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96672230</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9498,6 +9908,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97240368</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9606,6 +10021,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97241125</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9714,6 +10134,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97241880</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9820,6 +10245,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112337965</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9942,6 +10372,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859654</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10048,6 +10483,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129591650</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10158,6 +10598,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129592077</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10259,6 +10704,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96643356</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10375,6 +10825,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97239536</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10491,6 +10946,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106813853</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10618,6 +11078,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859628</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10734,6 +11199,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106813854</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10843,6 +11313,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128342241</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10952,6 +11427,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215212</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11072,6 +11552,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859622</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11187,6 +11672,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122929399</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11302,6 +11792,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122929483</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11416,6 +11911,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131694354</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11523,6 +12023,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103903001</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11630,6 +12135,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126418797</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11737,6 +12247,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134100841</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11847,6 +12362,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97240536</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11961,6 +12481,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122779133</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12071,6 +12596,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122988731</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12198,6 +12728,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061104</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12330,6 +12865,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859623</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12457,6 +12997,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061087</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12589,6 +13134,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97239700</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12716,6 +13266,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061116</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12843,6 +13398,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859634</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12948,6 +13508,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122778162</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13066,6 +13631,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122779259</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13175,6 +13745,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126234616</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13280,6 +13855,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126491267</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13385,6 +13965,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126491426</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13490,6 +14075,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126491496</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13595,6 +14185,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126844041</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13700,6 +14295,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127932235</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13810,6 +14410,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127932257</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13915,6 +14520,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215416</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -14020,6 +14630,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129230389</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14125,6 +14740,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134505793</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14252,6 +14872,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859656</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14379,6 +15004,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061088</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14506,6 +15136,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061109</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14628,6 +15263,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859629</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14750,6 +15390,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859631</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14866,6 +15511,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122929535</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -15002,6 +15652,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125974903</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -15129,6 +15784,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061086</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -15251,6 +15911,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061105</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15358,6 +16023,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111182876</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15474,6 +16144,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061089</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15581,6 +16256,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061098</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -15692,6 +16372,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128095464</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -15804,6 +16489,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134488564</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15925,6 +16615,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061108</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -16046,6 +16741,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061081</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -16148,6 +16848,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117554483</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -16250,6 +16955,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126003792</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -16352,6 +17062,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126005160</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -16459,6 +17174,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061084</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -16566,6 +17286,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061091</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -16673,6 +17398,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061099</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -16780,6 +17510,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061102</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -16886,6 +17621,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126233785</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -16992,6 +17732,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126234010</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -17103,6 +17848,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126234159</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -17217,6 +17967,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126234439</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -17327,6 +18082,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126234644</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -17437,6 +18197,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126234771</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -17539,6 +18304,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133767702</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -17655,6 +18425,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061092</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -17771,6 +18546,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061094</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -17887,6 +18667,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061100</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -18006,6 +18791,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86686018</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -18108,6 +18898,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96672256</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -18217,6 +19012,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97242656</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -18326,6 +19126,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97243108</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -18446,6 +19251,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97330311</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -18561,6 +19371,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98104097</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -18668,6 +19483,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104249959</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -18770,6 +19590,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109890506</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -18880,6 +19705,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119475594</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -18987,6 +19817,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859637</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -19094,6 +19929,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859638</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -19201,6 +20041,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859639</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -19308,6 +20153,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859640</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -19424,6 +20274,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859642</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -19531,6 +20386,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859643</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -19638,6 +20498,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859644</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -19745,6 +20610,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859646</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -19852,6 +20722,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859647</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -19959,6 +20834,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859649</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -20066,6 +20946,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859650</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -20181,6 +21066,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122220583</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -20288,6 +21178,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122781008</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -20403,6 +21298,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126418709</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -20518,6 +21418,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126418756</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -20633,6 +21538,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127932426</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -20743,6 +21653,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128341941</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -20845,6 +21760,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129564285</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -20947,6 +21867,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133767721</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -21049,6 +21974,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96643458</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -21156,6 +22086,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96858761</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -21258,6 +22193,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97204577</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -21360,6 +22300,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100252927</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -21457,6 +22402,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116743172</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -21554,6 +22504,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125965889</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -21656,6 +22611,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126003574</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -21763,6 +22723,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061078</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -21870,6 +22835,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061079</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -21980,6 +22950,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126234373</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -22094,6 +23069,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126234937</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -22209,6 +23189,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96643468</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -22306,6 +23291,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116746465</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -22403,6 +23393,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121742517</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -22514,6 +23509,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122928987</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -22625,6 +23625,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122930294</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -22722,6 +23727,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125963374</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -22829,6 +23839,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125976418</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -22936,6 +23951,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061082</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -23043,6 +24063,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061090</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -23150,6 +24175,11 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061103</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -23257,6 +24287,11 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061111</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -23368,6 +24403,11 @@
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122929342</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -23475,6 +24515,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061110</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -23577,6 +24622,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101523203</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -23683,6 +24733,11 @@
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117554655</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -23797,6 +24852,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126234400</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -23908,6 +24968,11 @@
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134487623</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -24019,6 +25084,11 @@
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134487656</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -24130,6 +25200,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134488457</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -24231,8 +25306,230 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129564006</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ216"/>
+  <dimension ref="A1:AZ218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14748,45 +14748,53 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121859656</v>
+        <v>135827212</v>
       </c>
       <c r="B125" t="n">
-        <v>5199</v>
+        <v>58141</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Öster om Tyresta by, Tyresta, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>687094</v>
+        <v>687180</v>
       </c>
       <c r="R125" t="n">
-        <v>6563235</v>
+        <v>6563302</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14813,22 +14821,12 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="Z125" t="inlineStr">
-        <is>
-          <t>15:16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="AB125" t="inlineStr">
-        <is>
-          <t>15:16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14839,48 +14837,28 @@
       </c>
       <c r="AG125" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ125" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK125" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL125" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO125" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859656</t>
+          <t>https://artportalen.se/Sighting/135827212</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126061088</v>
+        <v>121859656</v>
       </c>
       <c r="B126" t="n">
         <v>5199</v>
@@ -14911,14 +14889,14 @@
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>Öster om Tyresta by, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>686865</v>
+        <v>687094</v>
       </c>
       <c r="R126" t="n">
-        <v>6562977</v>
+        <v>6563235</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14945,22 +14923,22 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14984,12 +14962,12 @@
       </c>
       <c r="AL126" t="inlineStr">
         <is>
-          <t>Klen torr granlåga.</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
-          <t>Picea abies # Klen torr granlåga.</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT126" t="inlineStr"/>
@@ -15000,19 +14978,19 @@
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061088</t>
+          <t>https://artportalen.se/Sighting/121859656</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126061109</v>
+        <v>126061088</v>
       </c>
       <c r="B127" t="n">
         <v>5199</v>
@@ -15047,10 +15025,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>686946</v>
+        <v>686865</v>
       </c>
       <c r="R127" t="n">
-        <v>6562741</v>
+        <v>6562977</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15082,7 +15060,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -15092,7 +15070,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -15132,22 +15110,22 @@
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061109</t>
+          <t>https://artportalen.se/Sighting/126061088</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121859629</v>
+        <v>126061109</v>
       </c>
       <c r="B128" t="n">
-        <v>8455</v>
+        <v>5199</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15155,34 +15133,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Öster om Tyresta by, Tyresta, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>686792</v>
+        <v>686946</v>
       </c>
       <c r="R128" t="n">
-        <v>6563030</v>
+        <v>6562741</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15209,22 +15187,22 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15238,17 +15216,22 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL128" t="inlineStr">
+        <is>
+          <t>Klen torr granlåga.</t>
         </is>
       </c>
       <c r="AO128" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies # Klen torr granlåga.</t>
         </is>
       </c>
       <c r="AT128" t="inlineStr"/>
@@ -15259,19 +15242,19 @@
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859629</t>
+          <t>https://artportalen.se/Sighting/126061109</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121859631</v>
+        <v>121859629</v>
       </c>
       <c r="B129" t="n">
         <v>8455</v>
@@ -15306,10 +15289,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>686934</v>
+        <v>686792</v>
       </c>
       <c r="R129" t="n">
-        <v>6563148</v>
+        <v>6563030</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15341,7 +15324,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -15351,7 +15334,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15392,13 +15375,13 @@
       <c r="AY129" t="inlineStr"/>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859631</t>
+          <t>https://artportalen.se/Sighting/121859629</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>122929535</v>
+        <v>121859631</v>
       </c>
       <c r="B130" t="n">
         <v>8455</v>
@@ -15426,29 +15409,20 @@
           <t>(Hartig, 1834)</t>
         </is>
       </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Norrby mosse, Srm</t>
+          <t>Öster om Tyresta by, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>686612</v>
+        <v>686934</v>
       </c>
       <c r="R130" t="n">
-        <v>6562882</v>
+        <v>6563148</v>
       </c>
       <c r="S130" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -15472,22 +15446,22 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15498,31 +15472,46 @@
       </c>
       <c r="AG130" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ130" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK130" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO130" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122929535</t>
+          <t>https://artportalen.se/Sighting/121859631</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125974903</v>
+        <v>122929535</v>
       </c>
       <c r="B131" t="n">
-        <v>8444</v>
+        <v>8455</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15530,50 +15519,46 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M131" t="inlineStr"/>
       <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>söder om Tyresta, Srm</t>
+          <t>Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>686838</v>
+        <v>686612</v>
       </c>
       <c r="R131" t="n">
-        <v>6562733</v>
+        <v>6562882</v>
       </c>
       <c r="S131" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15597,17 +15582,22 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>gammal björklåga med spår längs hela stammen</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15616,51 +15606,30 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
-      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ131" t="inlineStr">
-        <is>
-          <t>vårtbjörk</t>
-        </is>
-      </c>
-      <c r="AK131" t="inlineStr">
-        <is>
-          <t>Betula pendula</t>
-        </is>
-      </c>
-      <c r="AM131" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO131" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Betula pendula</t>
-        </is>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Nette Bygren</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Nette Bygren</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125974903</t>
+          <t>https://artportalen.se/Sighting/122929535</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126061086</v>
+        <v>125974903</v>
       </c>
       <c r="B132" t="n">
         <v>8444</v>
@@ -15688,20 +15657,33 @@
           <t>Janson, 1856</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr"/>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>söder om Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>686932</v>
+        <v>686838</v>
       </c>
       <c r="R132" t="n">
-        <v>6563067</v>
+        <v>6562733</v>
       </c>
       <c r="S132" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -15728,19 +15710,14 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>15:00</t>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>gammal björklåga med spår längs hela stammen</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15749,50 +15726,51 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>vårtbjörk</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
         <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AL132" t="inlineStr">
-        <is>
-          <t>Barklös björklåga.</t>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AM132" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
         </is>
       </c>
       <c r="AO132" t="inlineStr">
         <is>
-          <t>Betula # Barklös björklåga.</t>
+          <t>Wood surface of dead wood # Betula pendula</t>
         </is>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Nette Bygren</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Nette Bygren</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061086</t>
+          <t>https://artportalen.se/Sighting/125974903</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126061105</v>
+        <v>126061086</v>
       </c>
       <c r="B133" t="n">
         <v>8444</v>
@@ -15827,10 +15805,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>686860</v>
+        <v>686932</v>
       </c>
       <c r="R133" t="n">
-        <v>6562743</v>
+        <v>6563067</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15862,7 +15840,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -15872,7 +15850,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15894,9 +15872,14 @@
           <t>Betula</t>
         </is>
       </c>
+      <c r="AL133" t="inlineStr">
+        <is>
+          <t>Barklös björklåga.</t>
+        </is>
+      </c>
       <c r="AO133" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Betula # Barklös björklåga.</t>
         </is>
       </c>
       <c r="AT133" t="inlineStr"/>
@@ -15907,22 +15890,22 @@
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061105</t>
+          <t>https://artportalen.se/Sighting/126061086</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>111182876</v>
+        <v>126061105</v>
       </c>
       <c r="B134" t="n">
-        <v>58790</v>
+        <v>8444</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15930,43 +15913,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>208245</v>
+        <v>106554</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>NO Norrby  Mosse, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>686971</v>
+        <v>686860</v>
       </c>
       <c r="R134" t="n">
-        <v>6563333</v>
+        <v>6562743</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15993,12 +15967,22 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2023-07-30</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2023-07-30</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -16007,31 +15991,45 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
-      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ134" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK134" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO134" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111182876</t>
+          <t>https://artportalen.se/Sighting/126061105</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126061089</v>
+        <v>111182876</v>
       </c>
       <c r="B135" t="n">
         <v>58790</v>
@@ -16064,21 +16062,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>NO Norrby  Mosse, Srm</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>686871</v>
+        <v>686971</v>
       </c>
       <c r="R135" t="n">
-        <v>6562972</v>
+        <v>6563333</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -16105,22 +16103,12 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>14:42</t>
+          <t>2023-07-30</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>14:42</t>
+          <t>2023-07-30</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -16129,30 +16117,31 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
+      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061089</t>
+          <t>https://artportalen.se/Sighting/111182876</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126061098</v>
+        <v>126061089</v>
       </c>
       <c r="B136" t="n">
         <v>58790</v>
@@ -16180,17 +16169,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr"/>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>686857</v>
+        <v>686871</v>
       </c>
       <c r="R136" t="n">
-        <v>6562875</v>
+        <v>6562972</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -16222,7 +16220,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -16232,7 +16230,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -16252,19 +16250,19 @@
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061098</t>
+          <t>https://artportalen.se/Sighting/126061089</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128095464</v>
+        <v>126061098</v>
       </c>
       <c r="B137" t="n">
         <v>58790</v>
@@ -16292,30 +16290,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>687155</v>
+        <v>686857</v>
       </c>
       <c r="R137" t="n">
-        <v>6563193</v>
+        <v>6562875</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16342,12 +16327,22 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16356,34 +16351,33 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
-      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128095464</t>
+          <t>https://artportalen.se/Sighting/126061098</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>134488564</v>
+        <v>128095464</v>
       </c>
       <c r="B138" t="n">
-        <v>58812</v>
+        <v>58790</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16414,7 +16408,11 @@
         </is>
       </c>
       <c r="J138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" t="inlineStr"/>
       <c r="N138" t="inlineStr"/>
@@ -16424,10 +16422,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>687272</v>
+        <v>687155</v>
       </c>
       <c r="R138" t="n">
-        <v>6563263</v>
+        <v>6563193</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16454,17 +16452,12 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>Ca 2-3 cm lång.</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -16491,16 +16484,16 @@
       <c r="AY138" t="inlineStr"/>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134488564</t>
+          <t>https://artportalen.se/Sighting/128095464</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126061108</v>
+        <v>134488564</v>
       </c>
       <c r="B139" t="n">
-        <v>58817</v>
+        <v>58812</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16508,21 +16501,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>208249</v>
+        <v>208245</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -16530,26 +16523,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>686907</v>
+        <v>687272</v>
       </c>
       <c r="R139" t="n">
-        <v>6562760</v>
+        <v>6563263</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16576,22 +16564,17 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z139" t="inlineStr">
-        <is>
-          <t>13:17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB139" t="inlineStr">
-        <is>
-          <t>13:17</t>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>Ca 2-3 cm lång.</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16600,33 +16583,34 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061108</t>
+          <t>https://artportalen.se/Sighting/134488564</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126061081</v>
+        <v>126061108</v>
       </c>
       <c r="B140" t="n">
-        <v>58815</v>
+        <v>58817</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16634,21 +16618,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>208250</v>
+        <v>208249</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -16672,10 +16656,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>687058</v>
+        <v>686907</v>
       </c>
       <c r="R140" t="n">
-        <v>6563228</v>
+        <v>6562760</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -16707,7 +16691,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -16717,7 +16701,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16737,22 +16721,22 @@
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061081</t>
+          <t>https://artportalen.se/Sighting/126061108</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>117554483</v>
+        <v>126061081</v>
       </c>
       <c r="B141" t="n">
-        <v>99035</v>
+        <v>58815</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16760,41 +16744,51 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>219790</v>
+        <v>208250</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>SO Norrby Mosse, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>686878</v>
+        <v>687058</v>
       </c>
       <c r="R141" t="n">
-        <v>6562971</v>
+        <v>6563228</v>
       </c>
       <c r="S141" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -16818,12 +16812,22 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16832,31 +16836,30 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
-      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117554483</t>
+          <t>https://artportalen.se/Sighting/126061081</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126003792</v>
+        <v>117554483</v>
       </c>
       <c r="B142" t="n">
         <v>99035</v>
@@ -16891,17 +16894,17 @@
       <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>SO Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>687046</v>
+        <v>686878</v>
       </c>
       <c r="R142" t="n">
-        <v>6563346</v>
+        <v>6562971</v>
       </c>
       <c r="S142" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -16925,12 +16928,12 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16957,13 +16960,13 @@
       <c r="AY142" t="inlineStr"/>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126003792</t>
+          <t>https://artportalen.se/Sighting/117554483</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126005160</v>
+        <v>126003792</v>
       </c>
       <c r="B143" t="n">
         <v>99035</v>
@@ -17002,10 +17005,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>687034</v>
+        <v>687046</v>
       </c>
       <c r="R143" t="n">
-        <v>6563204</v>
+        <v>6563346</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -17064,13 +17067,13 @@
       <c r="AY143" t="inlineStr"/>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126005160</t>
+          <t>https://artportalen.se/Sighting/126003792</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>126061084</v>
+        <v>126005160</v>
       </c>
       <c r="B144" t="n">
         <v>99035</v>
@@ -17099,16 +17102,20 @@
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>687014</v>
+        <v>687034</v>
       </c>
       <c r="R144" t="n">
-        <v>6563215</v>
+        <v>6563204</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -17135,22 +17142,12 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z144" t="inlineStr">
-        <is>
-          <t>15:14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB144" t="inlineStr">
-        <is>
-          <t>15:14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -17159,30 +17156,31 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
+      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061084</t>
+          <t>https://artportalen.se/Sighting/126005160</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>126061091</v>
+        <v>126061084</v>
       </c>
       <c r="B145" t="n">
         <v>99035</v>
@@ -17217,10 +17215,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>686871</v>
+        <v>687014</v>
       </c>
       <c r="R145" t="n">
-        <v>6562972</v>
+        <v>6563215</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -17252,7 +17250,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -17262,7 +17260,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -17288,13 +17286,13 @@
       <c r="AY145" t="inlineStr"/>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061091</t>
+          <t>https://artportalen.se/Sighting/126061084</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>126061099</v>
+        <v>126061091</v>
       </c>
       <c r="B146" t="n">
         <v>99035</v>
@@ -17329,10 +17327,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>686857</v>
+        <v>686871</v>
       </c>
       <c r="R146" t="n">
-        <v>6562875</v>
+        <v>6562972</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -17364,7 +17362,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -17374,7 +17372,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17394,19 +17392,19 @@
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061099</t>
+          <t>https://artportalen.se/Sighting/126061091</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>126061102</v>
+        <v>126061099</v>
       </c>
       <c r="B147" t="n">
         <v>99035</v>
@@ -17441,10 +17439,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>686837</v>
+        <v>686857</v>
       </c>
       <c r="R147" t="n">
-        <v>6562829</v>
+        <v>6562875</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17476,7 +17474,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -17486,7 +17484,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17512,13 +17510,13 @@
       <c r="AY147" t="inlineStr"/>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061102</t>
+          <t>https://artportalen.se/Sighting/126061099</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126233785</v>
+        <v>126061102</v>
       </c>
       <c r="B148" t="n">
         <v>99035</v>
@@ -17547,24 +17545,16 @@
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L148" t="inlineStr"/>
-      <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>686839</v>
+        <v>686837</v>
       </c>
       <c r="R148" t="n">
-        <v>6563016</v>
+        <v>6562829</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17591,12 +17581,22 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17605,31 +17605,30 @@
       <c r="AE148" t="b">
         <v>0</v>
       </c>
-      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
       </c>
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Bodil Ravn, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126233785</t>
+          <t>https://artportalen.se/Sighting/126061102</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126234010</v>
+        <v>126233785</v>
       </c>
       <c r="B149" t="n">
         <v>99035</v>
@@ -17672,10 +17671,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>687160</v>
+        <v>686839</v>
       </c>
       <c r="R149" t="n">
-        <v>6563261</v>
+        <v>6563016</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17728,19 +17727,19 @@
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Bodil Ravn, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126234010</t>
+          <t>https://artportalen.se/Sighting/126233785</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126234159</v>
+        <v>126234010</v>
       </c>
       <c r="B150" t="n">
         <v>99035</v>
@@ -17768,13 +17767,13 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr"/>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr"/>
       <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
@@ -17783,13 +17782,13 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>687297</v>
+        <v>687160</v>
       </c>
       <c r="R150" t="n">
-        <v>6563381</v>
+        <v>6563261</v>
       </c>
       <c r="S150" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -17819,11 +17818,6 @@
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>Ett flertal i blomning.</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17844,19 +17838,19 @@
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Bodil Ravn, Ulf Johansson</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126234159</t>
+          <t>https://artportalen.se/Sighting/126234010</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126234439</v>
+        <v>126234159</v>
       </c>
       <c r="B151" t="n">
         <v>99035</v>
@@ -17886,34 +17880,26 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr"/>
       <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Norrby mosse SO, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>686777</v>
+        <v>687297</v>
       </c>
       <c r="R151" t="n">
-        <v>6563073</v>
+        <v>6563381</v>
       </c>
       <c r="S151" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -17943,6 +17929,11 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Ett flertal i blomning.</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17958,24 +17949,24 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Bodil Ravn, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126234439</t>
+          <t>https://artportalen.se/Sighting/126234159</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>126234644</v>
+        <v>126234439</v>
       </c>
       <c r="B152" t="n">
         <v>99035</v>
@@ -18005,7 +17996,7 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -18013,7 +18004,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr"/>
       <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
@@ -18022,10 +18017,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>686837</v>
+        <v>686777</v>
       </c>
       <c r="R152" t="n">
-        <v>6562967</v>
+        <v>6563073</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -18084,13 +18079,13 @@
       <c r="AY152" t="inlineStr"/>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126234644</t>
+          <t>https://artportalen.se/Sighting/126234439</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>126234771</v>
+        <v>126234644</v>
       </c>
       <c r="B153" t="n">
         <v>99035</v>
@@ -18120,7 +18115,7 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -18133,14 +18128,14 @@
       <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Norrby mosse OSO, Srm</t>
+          <t>Norrby mosse SO, Srm</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>686976</v>
+        <v>686837</v>
       </c>
       <c r="R153" t="n">
-        <v>6563107</v>
+        <v>6562967</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -18199,16 +18194,16 @@
       <c r="AY153" t="inlineStr"/>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126234771</t>
+          <t>https://artportalen.se/Sighting/126234644</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>133767702</v>
+        <v>126234771</v>
       </c>
       <c r="B154" t="n">
-        <v>99112</v>
+        <v>99035</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18233,21 +18228,29 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I154" t="inlineStr"/>
-      <c r="J154" t="inlineStr"/>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr"/>
       <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrby mosse OSO, Srm</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>686845</v>
+        <v>686976</v>
       </c>
       <c r="R154" t="n">
-        <v>6563325</v>
+        <v>6563107</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -18274,12 +18277,12 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -18295,27 +18298,27 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133767702</t>
+          <t>https://artportalen.se/Sighting/126234771</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>126061092</v>
+        <v>133767702</v>
       </c>
       <c r="B155" t="n">
-        <v>99022</v>
+        <v>99112</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18323,43 +18326,38 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>220093</v>
+        <v>219790</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>686880</v>
+        <v>686845</v>
       </c>
       <c r="R155" t="n">
-        <v>6562892</v>
+        <v>6563325</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -18386,22 +18384,12 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z155" t="inlineStr">
-        <is>
-          <t>14:35</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB155" t="inlineStr">
-        <is>
-          <t>14:35</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -18410,30 +18398,31 @@
       <c r="AE155" t="b">
         <v>0</v>
       </c>
+      <c r="AF155" t="inlineStr"/>
       <c r="AG155" t="b">
         <v>0</v>
       </c>
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061092</t>
+          <t>https://artportalen.se/Sighting/133767702</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>126061094</v>
+        <v>126061092</v>
       </c>
       <c r="B156" t="n">
         <v>99022</v>
@@ -18477,10 +18466,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>686866</v>
+        <v>686880</v>
       </c>
       <c r="R156" t="n">
-        <v>6562874</v>
+        <v>6562892</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18512,7 +18501,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -18522,7 +18511,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -18548,13 +18537,13 @@
       <c r="AY156" t="inlineStr"/>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061094</t>
+          <t>https://artportalen.se/Sighting/126061092</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>126061100</v>
+        <v>126061094</v>
       </c>
       <c r="B157" t="n">
         <v>99022</v>
@@ -18584,7 +18573,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -18598,10 +18587,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>686857</v>
+        <v>686866</v>
       </c>
       <c r="R157" t="n">
-        <v>6562875</v>
+        <v>6562874</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18633,7 +18622,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -18643,7 +18632,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -18669,43 +18658,43 @@
       <c r="AY157" t="inlineStr"/>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061100</t>
+          <t>https://artportalen.se/Sighting/126061094</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>86686018</v>
+        <v>126061100</v>
       </c>
       <c r="B158" t="n">
-        <v>99118</v>
+        <v>99022</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -18713,23 +18702,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L158" t="inlineStr"/>
-      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Tyresta S Ungfars kärr, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>686831</v>
+        <v>686857</v>
       </c>
       <c r="R158" t="n">
-        <v>6563296</v>
+        <v>6562875</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18756,17 +18738,22 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2020-07-04</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2020-07-04</t>
-        </is>
-      </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>Från Ungfars kärrs södra spets och ca 200 meter österut. Ungefär hälften av skotten utanför parkens gräns. 4 blomstänglar. Området var bökat av vildsvin. Vissa skott var uppgrävda.</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -18775,31 +18762,30 @@
       <c r="AE158" t="b">
         <v>0</v>
       </c>
-      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
       </c>
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86686018</t>
+          <t>https://artportalen.se/Sighting/126061100</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>96672256</v>
+        <v>86686018</v>
       </c>
       <c r="B159" t="n">
         <v>99118</v>
@@ -18827,24 +18813,36 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
-      <c r="K159" t="inlineStr"/>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr"/>
       <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>NO Norrby mosse, Srm</t>
+          <t>Tyresta S Ungfars kärr, Srm</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>686848</v>
+        <v>686831</v>
       </c>
       <c r="R159" t="n">
-        <v>6563295</v>
+        <v>6563296</v>
       </c>
       <c r="S159" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -18868,12 +18866,17 @@
       </c>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
+          <t>2020-07-04</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
+          <t>2020-07-04</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>Från Ungfars kärrs södra spets och ca 200 meter österut. Ungefär hälften av skotten utanför parkens gräns. 4 blomstänglar. Området var bökat av vildsvin. Vissa skott var uppgrävda.</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -18889,24 +18892,24 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96672256</t>
+          <t>https://artportalen.se/Sighting/86686018</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>97242656</v>
+        <v>96672256</v>
       </c>
       <c r="B160" t="n">
         <v>99118</v>
@@ -18935,21 +18938,23 @@
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr"/>
       <c r="L160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>OSO Ungfars mosse, Srm</t>
+          <t>NO Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>686846</v>
+        <v>686848</v>
       </c>
       <c r="R160" t="n">
-        <v>6563316</v>
+        <v>6563295</v>
       </c>
       <c r="S160" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -18973,22 +18978,12 @@
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>2021-11-20</t>
-        </is>
-      </c>
-      <c r="Z160" t="inlineStr">
-        <is>
-          <t>13:59</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2021-11-20</t>
-        </is>
-      </c>
-      <c r="AB160" t="inlineStr">
-        <is>
-          <t>13:59</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -18997,30 +18992,31 @@
       <c r="AE160" t="b">
         <v>0</v>
       </c>
+      <c r="AF160" t="inlineStr"/>
       <c r="AG160" t="b">
         <v>0</v>
       </c>
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Thomas Strid</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Thomas Strid, Bodil Ravn, Ulf Johansson, Tiina Laantee</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97242656</t>
+          <t>https://artportalen.se/Sighting/96672256</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>97243108</v>
+        <v>97242656</v>
       </c>
       <c r="B161" t="n">
         <v>99118</v>
@@ -19053,17 +19049,17 @@
       <c r="L161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Tyresta, Srm</t>
+          <t>OSO Ungfars mosse, Srm</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>686847</v>
+        <v>686846</v>
       </c>
       <c r="R161" t="n">
-        <v>6563308</v>
+        <v>6563316</v>
       </c>
       <c r="S161" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -19092,7 +19088,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -19102,7 +19098,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -19128,13 +19124,13 @@
       <c r="AY161" t="inlineStr"/>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97243108</t>
+          <t>https://artportalen.se/Sighting/97242656</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>97330311</v>
+        <v>97243108</v>
       </c>
       <c r="B162" t="n">
         <v>99118</v>
@@ -19162,29 +19158,22 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Tyresta NP, SSV Bylsjön (*knärot* /stjälk/), Srm</t>
+          <t>Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q162" t="n">
         <v>686847</v>
       </c>
       <c r="R162" t="n">
-        <v>6563309</v>
+        <v>6563308</v>
       </c>
       <c r="S162" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -19206,24 +19195,24 @@
           <t>Österhaninge</t>
         </is>
       </c>
-      <c r="X162" t="inlineStr">
-        <is>
-          <t>AB-Han-0218</t>
-        </is>
-      </c>
       <c r="Y162" t="inlineStr">
         <is>
           <t>2021-11-20</t>
         </is>
       </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>2021-11-20</t>
         </is>
       </c>
-      <c r="AC162" t="inlineStr">
-        <is>
-          <t>/Ej räknad/</t>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -19238,28 +19227,24 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Tiina Laantee, Ulf Johansson, Bodil Ravn, Thomas Strid</t>
-        </is>
-      </c>
-      <c r="AY162" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Thomas Strid, Bodil Ravn, Ulf Johansson, Tiina Laantee</t>
+        </is>
+      </c>
+      <c r="AY162" t="inlineStr"/>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97330311</t>
+          <t>https://artportalen.se/Sighting/97243108</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>98104097</v>
+        <v>97330311</v>
       </c>
       <c r="B163" t="n">
         <v>99118</v>
@@ -19289,27 +19274,24 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K163" t="inlineStr"/>
-      <c r="L163" t="inlineStr"/>
-      <c r="N163" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Ungfars kärr SO, Srm</t>
+          <t>Tyresta NP, SSV Bylsjön (*knärot* /stjälk/), Srm</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>686934</v>
+        <v>686847</v>
       </c>
       <c r="R163" t="n">
-        <v>6563325</v>
+        <v>6563309</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -19334,19 +19316,24 @@
           <t>Österhaninge</t>
         </is>
       </c>
+      <c r="X163" t="inlineStr">
+        <is>
+          <t>AB-Han-0218</t>
+        </is>
+      </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2022-01-13</t>
+          <t>2021-11-20</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2022-01-13</t>
+          <t>2021-11-20</t>
         </is>
       </c>
       <c r="AC163" t="inlineStr">
         <is>
-          <t>Intill djurstig och granlåga</t>
+          <t>/Ej räknad/</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -19355,31 +19342,34 @@
       <c r="AE163" t="b">
         <v>0</v>
       </c>
-      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
-        </is>
-      </c>
-      <c r="AY163" t="inlineStr"/>
+          <t>Tiina Laantee, Ulf Johansson, Bodil Ravn, Thomas Strid</t>
+        </is>
+      </c>
+      <c r="AY163" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98104097</t>
+          <t>https://artportalen.se/Sighting/97330311</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>104249959</v>
+        <v>98104097</v>
       </c>
       <c r="B164" t="n">
         <v>99118</v>
@@ -19407,24 +19397,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr"/>
-      <c r="J164" t="inlineStr"/>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr"/>
       <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>SO Norrby Mosse, Srm</t>
+          <t>Ungfars kärr SO, Srm</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>687011</v>
+        <v>686934</v>
       </c>
       <c r="R164" t="n">
-        <v>6562869</v>
+        <v>6563325</v>
       </c>
       <c r="S164" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -19448,17 +19446,17 @@
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2022-01-13</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2022-01-13</t>
         </is>
       </c>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>Samma lokal som noterades 17/11-21. Ca 25 ex. Koordinaterna har varierat något vid besöken.</t>
+          <t>Intill djurstig och granlåga</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -19474,24 +19472,24 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104249959</t>
+          <t>https://artportalen.se/Sighting/98104097</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>109890506</v>
+        <v>104249959</v>
       </c>
       <c r="B165" t="n">
         <v>99118</v>
@@ -19526,17 +19524,17 @@
       <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Ö Norrby Mosse, Srm</t>
+          <t>SO Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>686831</v>
+        <v>687011</v>
       </c>
       <c r="R165" t="n">
-        <v>6563216</v>
+        <v>6562869</v>
       </c>
       <c r="S165" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -19560,12 +19558,17 @@
       </c>
       <c r="Y165" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2022-09-16</t>
+        </is>
+      </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>Samma lokal som noterades 17/11-21. Ca 25 ex. Koordinaterna har varierat något vid besöken.</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -19592,13 +19595,13 @@
       <c r="AY165" t="inlineStr"/>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109890506</t>
+          <t>https://artportalen.se/Sighting/104249959</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>119475594</v>
+        <v>109890506</v>
       </c>
       <c r="B166" t="n">
         <v>99118</v>
@@ -19626,29 +19629,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J166" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr"/>
       <c r="L166" t="inlineStr"/>
       <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>NO Norrby  Mosse, Srm</t>
+          <t>Ö Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>686995</v>
+        <v>686831</v>
       </c>
       <c r="R166" t="n">
-        <v>6563315</v>
+        <v>6563216</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -19675,12 +19670,12 @@
       </c>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -19707,13 +19702,13 @@
       <c r="AY166" t="inlineStr"/>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119475594</t>
+          <t>https://artportalen.se/Sighting/109890506</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>121859637</v>
+        <v>119475594</v>
       </c>
       <c r="B167" t="n">
         <v>99118</v>
@@ -19741,17 +19736,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I167" t="inlineStr"/>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Öster om Tyresta by, Tyresta, Srm</t>
+          <t>NO Norrby  Mosse, Srm</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>686863</v>
+        <v>686995</v>
       </c>
       <c r="R167" t="n">
-        <v>6563252</v>
+        <v>6563315</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19778,22 +19785,12 @@
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="Z167" t="inlineStr">
-        <is>
-          <t>16:22</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="AB167" t="inlineStr">
-        <is>
-          <t>16:22</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -19802,30 +19799,31 @@
       <c r="AE167" t="b">
         <v>0</v>
       </c>
+      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859637</t>
+          <t>https://artportalen.se/Sighting/119475594</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>121859638</v>
+        <v>121859637</v>
       </c>
       <c r="B168" t="n">
         <v>99118</v>
@@ -19860,10 +19858,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>686826</v>
+        <v>686863</v>
       </c>
       <c r="R168" t="n">
-        <v>6563286</v>
+        <v>6563252</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19895,7 +19893,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -19905,7 +19903,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -19931,13 +19929,13 @@
       <c r="AY168" t="inlineStr"/>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859638</t>
+          <t>https://artportalen.se/Sighting/121859637</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>121859639</v>
+        <v>121859638</v>
       </c>
       <c r="B169" t="n">
         <v>99118</v>
@@ -19972,10 +19970,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>686827</v>
+        <v>686826</v>
       </c>
       <c r="R169" t="n">
-        <v>6563296</v>
+        <v>6563286</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -20007,7 +20005,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -20017,7 +20015,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -20043,13 +20041,13 @@
       <c r="AY169" t="inlineStr"/>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859639</t>
+          <t>https://artportalen.se/Sighting/121859638</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>121859640</v>
+        <v>121859639</v>
       </c>
       <c r="B170" t="n">
         <v>99118</v>
@@ -20084,10 +20082,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>686837</v>
+        <v>686827</v>
       </c>
       <c r="R170" t="n">
-        <v>6563297</v>
+        <v>6563296</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -20119,7 +20117,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -20129,7 +20127,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -20155,13 +20153,13 @@
       <c r="AY170" t="inlineStr"/>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859640</t>
+          <t>https://artportalen.se/Sighting/121859639</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>121859642</v>
+        <v>121859640</v>
       </c>
       <c r="B171" t="n">
         <v>99118</v>
@@ -20190,24 +20188,16 @@
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
-      <c r="J171" t="inlineStr"/>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L171" t="inlineStr"/>
-      <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
           <t>Öster om Tyresta by, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>686834</v>
+        <v>686837</v>
       </c>
       <c r="R171" t="n">
-        <v>6563305</v>
+        <v>6563297</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -20239,7 +20229,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -20249,7 +20239,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -20258,7 +20248,6 @@
       <c r="AE171" t="b">
         <v>0</v>
       </c>
-      <c r="AF171" t="inlineStr"/>
       <c r="AG171" t="b">
         <v>0</v>
       </c>
@@ -20276,13 +20265,13 @@
       <c r="AY171" t="inlineStr"/>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859642</t>
+          <t>https://artportalen.se/Sighting/121859640</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>121859643</v>
+        <v>121859642</v>
       </c>
       <c r="B172" t="n">
         <v>99118</v>
@@ -20311,6 +20300,14 @@
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr"/>
+      <c r="N172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
           <t>Öster om Tyresta by, Tyresta, Srm</t>
@@ -20320,7 +20317,7 @@
         <v>686834</v>
       </c>
       <c r="R172" t="n">
-        <v>6563309</v>
+        <v>6563305</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -20352,7 +20349,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -20362,7 +20359,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -20371,6 +20368,7 @@
       <c r="AE172" t="b">
         <v>0</v>
       </c>
+      <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="b">
         <v>0</v>
       </c>
@@ -20388,13 +20386,13 @@
       <c r="AY172" t="inlineStr"/>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859643</t>
+          <t>https://artportalen.se/Sighting/121859642</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>121859644</v>
+        <v>121859643</v>
       </c>
       <c r="B173" t="n">
         <v>99118</v>
@@ -20429,10 +20427,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>686844</v>
+        <v>686834</v>
       </c>
       <c r="R173" t="n">
-        <v>6563303</v>
+        <v>6563309</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -20464,7 +20462,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -20474,7 +20472,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -20500,13 +20498,13 @@
       <c r="AY173" t="inlineStr"/>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859644</t>
+          <t>https://artportalen.se/Sighting/121859643</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>121859646</v>
+        <v>121859644</v>
       </c>
       <c r="B174" t="n">
         <v>99118</v>
@@ -20541,7 +20539,7 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>686841</v>
+        <v>686844</v>
       </c>
       <c r="R174" t="n">
         <v>6563303</v>
@@ -20576,7 +20574,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -20586,7 +20584,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -20612,13 +20610,13 @@
       <c r="AY174" t="inlineStr"/>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859646</t>
+          <t>https://artportalen.se/Sighting/121859644</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>121859647</v>
+        <v>121859646</v>
       </c>
       <c r="B175" t="n">
         <v>99118</v>
@@ -20653,10 +20651,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>686854</v>
+        <v>686841</v>
       </c>
       <c r="R175" t="n">
-        <v>6563286</v>
+        <v>6563303</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -20688,7 +20686,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -20698,7 +20696,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -20724,13 +20722,13 @@
       <c r="AY175" t="inlineStr"/>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859647</t>
+          <t>https://artportalen.se/Sighting/121859646</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>121859649</v>
+        <v>121859647</v>
       </c>
       <c r="B176" t="n">
         <v>99118</v>
@@ -20765,10 +20763,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>686851</v>
+        <v>686854</v>
       </c>
       <c r="R176" t="n">
-        <v>6563299</v>
+        <v>6563286</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -20800,7 +20798,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -20810,7 +20808,7 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -20836,13 +20834,13 @@
       <c r="AY176" t="inlineStr"/>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859649</t>
+          <t>https://artportalen.se/Sighting/121859647</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>121859650</v>
+        <v>121859649</v>
       </c>
       <c r="B177" t="n">
         <v>99118</v>
@@ -20877,10 +20875,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>686895</v>
+        <v>686851</v>
       </c>
       <c r="R177" t="n">
-        <v>6563306</v>
+        <v>6563299</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -20912,7 +20910,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -20922,7 +20920,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -20948,13 +20946,13 @@
       <c r="AY177" t="inlineStr"/>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859650</t>
+          <t>https://artportalen.se/Sighting/121859649</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>122220583</v>
+        <v>121859650</v>
       </c>
       <c r="B178" t="n">
         <v>99118</v>
@@ -20982,29 +20980,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J178" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K178" t="inlineStr"/>
-      <c r="L178" t="inlineStr"/>
-      <c r="N178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>SO Norrby Mosse, Srm</t>
+          <t>Öster om Tyresta by, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>686996</v>
+        <v>686895</v>
       </c>
       <c r="R178" t="n">
-        <v>6562864</v>
+        <v>6563306</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -21031,17 +21017,22 @@
       </c>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="Z178" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
-        </is>
-      </c>
-      <c r="AC178" t="inlineStr">
-        <is>
-          <t>Samma lokal som rapporterats -21 och -22 men en ny klon. Den förra har möjligen haft lite problem med grisbök.</t>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="AB178" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -21050,31 +21041,30 @@
       <c r="AE178" t="b">
         <v>0</v>
       </c>
-      <c r="AF178" t="inlineStr"/>
       <c r="AG178" t="b">
         <v>0</v>
       </c>
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122220583</t>
+          <t>https://artportalen.se/Sighting/121859650</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>122781008</v>
+        <v>122220583</v>
       </c>
       <c r="B179" t="n">
         <v>99118</v>
@@ -21102,21 +21092,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I179" t="inlineStr"/>
-      <c r="J179" t="inlineStr"/>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K179" t="inlineStr"/>
       <c r="L179" t="inlineStr"/>
       <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Knärot, Srm</t>
+          <t>SO Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>686833</v>
+        <v>686996</v>
       </c>
       <c r="R179" t="n">
-        <v>6563215</v>
+        <v>6562864</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -21143,17 +21141,17 @@
       </c>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="AC179" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Samma lokal som rapporterats -21 och -22 men en ny klon. Den förra har möjligen haft lite problem med grisbök.</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -21169,24 +21167,24 @@
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122781008</t>
+          <t>https://artportalen.se/Sighting/122220583</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>126418709</v>
+        <v>122781008</v>
       </c>
       <c r="B180" t="n">
         <v>99118</v>
@@ -21214,29 +21212,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J180" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr"/>
       <c r="L180" t="inlineStr"/>
       <c r="N180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Knärot, Srm</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>686771</v>
+        <v>686833</v>
       </c>
       <c r="R180" t="n">
-        <v>6563297</v>
+        <v>6563215</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -21263,17 +21253,17 @@
       </c>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AC180" t="inlineStr">
         <is>
-          <t>Två av dem i knopp, ca 3 m väster om de andra.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -21289,24 +21279,24 @@
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126418709</t>
+          <t>https://artportalen.se/Sighting/122781008</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>126418756</v>
+        <v>126418709</v>
       </c>
       <c r="B181" t="n">
         <v>99118</v>
@@ -21336,7 +21326,7 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
@@ -21353,10 +21343,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>686781</v>
+        <v>686771</v>
       </c>
       <c r="R181" t="n">
-        <v>6563292</v>
+        <v>6563297</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -21393,7 +21383,7 @@
       </c>
       <c r="AC181" t="inlineStr">
         <is>
-          <t>En av dem i knopp.</t>
+          <t>Två av dem i knopp, ca 3 m väster om de andra.</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -21420,13 +21410,13 @@
       <c r="AY181" t="inlineStr"/>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126418756</t>
+          <t>https://artportalen.se/Sighting/126418709</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>127932426</v>
+        <v>126418756</v>
       </c>
       <c r="B182" t="n">
         <v>99118</v>
@@ -21456,7 +21446,7 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
@@ -21473,10 +21463,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>686998</v>
+        <v>686781</v>
       </c>
       <c r="R182" t="n">
-        <v>6563316</v>
+        <v>6563292</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -21503,17 +21493,17 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AC182" t="inlineStr">
         <is>
-          <t>Återfynd, rapporterad -24 med 3 ex. Nu 5 ex.</t>
+          <t>En av dem i knopp.</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -21540,13 +21530,13 @@
       <c r="AY182" t="inlineStr"/>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127932426</t>
+          <t>https://artportalen.se/Sighting/126418756</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>128341941</v>
+        <v>127932426</v>
       </c>
       <c r="B183" t="n">
         <v>99118</v>
@@ -21576,7 +21566,7 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
@@ -21593,10 +21583,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>687244</v>
+        <v>686998</v>
       </c>
       <c r="R183" t="n">
-        <v>6563404</v>
+        <v>6563316</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -21623,12 +21613,17 @@
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC183" t="inlineStr">
+        <is>
+          <t>Återfynd, rapporterad -24 med 3 ex. Nu 5 ex.</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -21655,13 +21650,13 @@
       <c r="AY183" t="inlineStr"/>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128341941</t>
+          <t>https://artportalen.se/Sighting/127932426</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129564285</v>
+        <v>128341941</v>
       </c>
       <c r="B184" t="n">
         <v>99118</v>
@@ -21689,8 +21684,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I184" t="inlineStr"/>
-      <c r="J184" t="inlineStr"/>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K184" t="inlineStr"/>
       <c r="L184" t="inlineStr"/>
       <c r="N184" t="inlineStr"/>
@@ -21700,10 +21703,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>686625</v>
+        <v>687244</v>
       </c>
       <c r="R184" t="n">
-        <v>6563000</v>
+        <v>6563404</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -21730,12 +21733,12 @@
       </c>
       <c r="Y184" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -21762,16 +21765,16 @@
       <c r="AY184" t="inlineStr"/>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129564285</t>
+          <t>https://artportalen.se/Sighting/128341941</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>133767721</v>
+        <v>129564285</v>
       </c>
       <c r="B185" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21807,10 +21810,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>686845</v>
+        <v>686625</v>
       </c>
       <c r="R185" t="n">
-        <v>6563325</v>
+        <v>6563000</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -21837,12 +21840,12 @@
       </c>
       <c r="Y185" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -21869,38 +21872,38 @@
       <c r="AY185" t="inlineStr"/>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133767721</t>
+          <t>https://artportalen.se/Sighting/129564285</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>96643458</v>
+        <v>133767721</v>
       </c>
       <c r="B186" t="n">
-        <v>106244</v>
+        <v>99195</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -21910,14 +21913,14 @@
       <c r="N186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Vargklåva mosse S om, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>687154</v>
+        <v>686845</v>
       </c>
       <c r="R186" t="n">
-        <v>6563329</v>
+        <v>6563325</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -21944,12 +21947,12 @@
       </c>
       <c r="Y186" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -21965,24 +21968,24 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96643458</t>
+          <t>https://artportalen.se/Sighting/133767721</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>96858761</v>
+        <v>96643458</v>
       </c>
       <c r="B187" t="n">
         <v>106244</v>
@@ -22017,17 +22020,17 @@
       <c r="N187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Ungfars kärr SO, Srm</t>
+          <t>Vargklåva mosse S om, Srm</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>687064</v>
+        <v>687154</v>
       </c>
       <c r="R187" t="n">
-        <v>6563258</v>
+        <v>6563329</v>
       </c>
       <c r="S187" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -22051,17 +22054,12 @@
       </c>
       <c r="Y187" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="AC187" t="inlineStr">
-        <is>
-          <t>Två bestånd</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -22088,13 +22086,13 @@
       <c r="AY187" t="inlineStr"/>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96858761</t>
+          <t>https://artportalen.se/Sighting/96643458</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>97204577</v>
+        <v>96858761</v>
       </c>
       <c r="B188" t="n">
         <v>106244</v>
@@ -22129,17 +22127,17 @@
       <c r="N188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>SO Norrby mosse, Srm</t>
+          <t>Ungfars kärr SO, Srm</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>687019</v>
+        <v>687064</v>
       </c>
       <c r="R188" t="n">
-        <v>6562889</v>
+        <v>6563258</v>
       </c>
       <c r="S188" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -22163,12 +22161,17 @@
       </c>
       <c r="Y188" t="inlineStr">
         <is>
-          <t>2021-11-17</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>2021-11-17</t>
+          <t>2021-10-26</t>
+        </is>
+      </c>
+      <c r="AC188" t="inlineStr">
+        <is>
+          <t>Två bestånd</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -22184,24 +22187,24 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
       <c r="AZ188" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97204577</t>
+          <t>https://artportalen.se/Sighting/96858761</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>100252927</v>
+        <v>97204577</v>
       </c>
       <c r="B189" t="n">
         <v>106244</v>
@@ -22236,17 +22239,17 @@
       <c r="N189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>NO Norrby  Mosse, Srm</t>
+          <t>SO Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>687152</v>
+        <v>687019</v>
       </c>
       <c r="R189" t="n">
-        <v>6563326</v>
+        <v>6562889</v>
       </c>
       <c r="S189" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -22270,12 +22273,12 @@
       </c>
       <c r="Y189" t="inlineStr">
         <is>
-          <t>2022-04-26</t>
+          <t>2021-11-17</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
         <is>
-          <t>2022-04-26</t>
+          <t>2021-11-17</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -22302,13 +22305,13 @@
       <c r="AY189" t="inlineStr"/>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/100252927</t>
+          <t>https://artportalen.se/Sighting/97204577</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>116743172</v>
+        <v>100252927</v>
       </c>
       <c r="B190" t="n">
         <v>106244</v>
@@ -22337,16 +22340,20 @@
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr"/>
+      <c r="L190" t="inlineStr"/>
+      <c r="N190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Ungfars kärr, Ungfars kärr, Srm</t>
+          <t>NO Norrby  Mosse, Srm</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>687088</v>
+        <v>687152</v>
       </c>
       <c r="R190" t="n">
-        <v>6563243</v>
+        <v>6563326</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -22373,12 +22380,12 @@
       </c>
       <c r="Y190" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2022-04-26</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2022-04-26</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -22387,30 +22394,31 @@
       <c r="AE190" t="b">
         <v>0</v>
       </c>
+      <c r="AF190" t="inlineStr"/>
       <c r="AG190" t="b">
         <v>0</v>
       </c>
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116743172</t>
+          <t>https://artportalen.se/Sighting/100252927</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>125965889</v>
+        <v>116743172</v>
       </c>
       <c r="B191" t="n">
         <v>106244</v>
@@ -22445,10 +22453,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>687076</v>
+        <v>687088</v>
       </c>
       <c r="R191" t="n">
-        <v>6563220</v>
+        <v>6563243</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -22475,12 +22483,12 @@
       </c>
       <c r="Y191" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -22506,13 +22514,13 @@
       <c r="AY191" t="inlineStr"/>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125965889</t>
+          <t>https://artportalen.se/Sighting/116743172</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>126003574</v>
+        <v>125965889</v>
       </c>
       <c r="B192" t="n">
         <v>106244</v>
@@ -22541,20 +22549,16 @@
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
-      <c r="J192" t="inlineStr"/>
-      <c r="K192" t="inlineStr"/>
-      <c r="L192" t="inlineStr"/>
-      <c r="N192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>SO Norrby Mosse, Srm</t>
+          <t>Ungfars kärr, Ungfars kärr, Srm</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>686803</v>
+        <v>687076</v>
       </c>
       <c r="R192" t="n">
-        <v>6563098</v>
+        <v>6563220</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -22581,12 +22585,12 @@
       </c>
       <c r="Y192" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -22595,31 +22599,30 @@
       <c r="AE192" t="b">
         <v>0</v>
       </c>
-      <c r="AF192" t="inlineStr"/>
       <c r="AG192" t="b">
         <v>0</v>
       </c>
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126003574</t>
+          <t>https://artportalen.se/Sighting/125965889</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>126061078</v>
+        <v>126003574</v>
       </c>
       <c r="B193" t="n">
         <v>106244</v>
@@ -22648,16 +22651,20 @@
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr"/>
+      <c r="L193" t="inlineStr"/>
+      <c r="N193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>SO Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>687085</v>
+        <v>686803</v>
       </c>
       <c r="R193" t="n">
-        <v>6563229</v>
+        <v>6563098</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -22684,22 +22691,12 @@
       </c>
       <c r="Y193" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z193" t="inlineStr">
-        <is>
-          <t>15:40</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB193" t="inlineStr">
-        <is>
-          <t>15:40</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -22708,30 +22705,31 @@
       <c r="AE193" t="b">
         <v>0</v>
       </c>
+      <c r="AF193" t="inlineStr"/>
       <c r="AG193" t="b">
         <v>0</v>
       </c>
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061078</t>
+          <t>https://artportalen.se/Sighting/126003574</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>126061079</v>
+        <v>126061078</v>
       </c>
       <c r="B194" t="n">
         <v>106244</v>
@@ -22766,10 +22764,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>687082</v>
+        <v>687085</v>
       </c>
       <c r="R194" t="n">
-        <v>6563241</v>
+        <v>6563229</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -22801,7 +22799,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -22811,7 +22809,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -22837,13 +22835,13 @@
       <c r="AY194" t="inlineStr"/>
       <c r="AZ194" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061079</t>
+          <t>https://artportalen.se/Sighting/126061078</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>126234373</v>
+        <v>126061079</v>
       </c>
       <c r="B195" t="n">
         <v>106244</v>
@@ -22871,29 +22869,17 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J195" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K195" t="inlineStr"/>
-      <c r="L195" t="inlineStr"/>
-      <c r="N195" t="inlineStr"/>
+      <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Norrby mosse SO, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>686756</v>
+        <v>687082</v>
       </c>
       <c r="R195" t="n">
-        <v>6563092</v>
+        <v>6563241</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -22920,12 +22906,22 @@
       </c>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z195" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB195" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -22934,31 +22930,30 @@
       <c r="AE195" t="b">
         <v>0</v>
       </c>
-      <c r="AF195" t="inlineStr"/>
       <c r="AG195" t="b">
         <v>0</v>
       </c>
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126234373</t>
+          <t>https://artportalen.se/Sighting/126061079</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>126234937</v>
+        <v>126234373</v>
       </c>
       <c r="B196" t="n">
         <v>106244</v>
@@ -22996,23 +22991,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K196" t="inlineStr"/>
       <c r="L196" t="inlineStr"/>
       <c r="N196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Ungfars kärr SO, Srm</t>
+          <t>Norrby mosse SO, Srm</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>687103</v>
+        <v>686756</v>
       </c>
       <c r="R196" t="n">
-        <v>6563191</v>
+        <v>6563092</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -23071,16 +23062,16 @@
       <c r="AY196" t="inlineStr"/>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126234937</t>
+          <t>https://artportalen.se/Sighting/126234373</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>96643468</v>
+        <v>126234937</v>
       </c>
       <c r="B197" t="n">
-        <v>97989</v>
+        <v>106244</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -23088,46 +23079,50 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>221941</v>
+        <v>221144</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K197" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr"/>
       <c r="N197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Vargklåva mosse S om, Srm</t>
+          <t>Ungfars kärr SO, Srm</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>687268</v>
+        <v>687103</v>
       </c>
       <c r="R197" t="n">
-        <v>6563319</v>
+        <v>6563191</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -23154,17 +23149,12 @@
       </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
-        </is>
-      </c>
-      <c r="AC197" t="inlineStr">
-        <is>
-          <t>Strax nedom klippbrant</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -23191,13 +23181,13 @@
       <c r="AY197" t="inlineStr"/>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96643468</t>
+          <t>https://artportalen.se/Sighting/126234937</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>116746465</v>
+        <v>96643468</v>
       </c>
       <c r="B198" t="n">
         <v>97989</v>
@@ -23225,17 +23215,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I198" t="inlineStr"/>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr"/>
+      <c r="L198" t="inlineStr"/>
+      <c r="N198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Norrby mosse, Norrby mosse, Srm</t>
+          <t>Vargklåva mosse S om, Srm</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>686888</v>
+        <v>687268</v>
       </c>
       <c r="R198" t="n">
-        <v>6563206</v>
+        <v>6563319</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -23262,12 +23264,17 @@
       </c>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2021-10-12</t>
+        </is>
+      </c>
+      <c r="AC198" t="inlineStr">
+        <is>
+          <t>Strax nedom klippbrant</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -23276,33 +23283,34 @@
       <c r="AE198" t="b">
         <v>0</v>
       </c>
+      <c r="AF198" t="inlineStr"/>
       <c r="AG198" t="b">
         <v>0</v>
       </c>
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116746465</t>
+          <t>https://artportalen.se/Sighting/96643468</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>121742517</v>
+        <v>116746465</v>
       </c>
       <c r="B199" t="n">
-        <v>97983</v>
+        <v>97989</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23310,16 +23318,16 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -23334,10 +23342,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>686859</v>
+        <v>686888</v>
       </c>
       <c r="R199" t="n">
-        <v>6562875</v>
+        <v>6563206</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -23364,12 +23372,12 @@
       </c>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -23395,16 +23403,16 @@
       <c r="AY199" t="inlineStr"/>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121742517</t>
+          <t>https://artportalen.se/Sighting/116746465</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>122928987</v>
+        <v>135827249</v>
       </c>
       <c r="B200" t="n">
-        <v>97983</v>
+        <v>98142</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23412,16 +23420,16 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -23436,14 +23444,14 @@
       <c r="N200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Norrby mosse, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>686389</v>
+        <v>687270</v>
       </c>
       <c r="R200" t="n">
-        <v>6562967</v>
+        <v>6563321</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -23470,22 +23478,17 @@
       </c>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="Z200" t="inlineStr">
-        <is>
-          <t>10:36</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="AB200" t="inlineStr">
-        <is>
-          <t>10:36</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AC200" t="inlineStr">
+        <is>
+          <t>Återfynd, tidigare rapporterad 2021.</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -23494,30 +23497,31 @@
       <c r="AE200" t="b">
         <v>0</v>
       </c>
+      <c r="AF200" t="inlineStr"/>
       <c r="AG200" t="b">
         <v>0</v>
       </c>
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122928987</t>
+          <t>https://artportalen.se/Sighting/135827249</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>122930294</v>
+        <v>121742517</v>
       </c>
       <c r="B201" t="n">
         <v>97983</v>
@@ -23546,23 +23550,19 @@
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
-      <c r="J201" t="inlineStr"/>
-      <c r="K201" t="inlineStr"/>
-      <c r="L201" t="inlineStr"/>
-      <c r="N201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Norrby mosse, Srm</t>
+          <t>Norrby mosse, Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>686824</v>
+        <v>686859</v>
       </c>
       <c r="R201" t="n">
-        <v>6562778</v>
+        <v>6562875</v>
       </c>
       <c r="S201" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -23586,22 +23586,12 @@
       </c>
       <c r="Y201" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="Z201" t="inlineStr">
-        <is>
-          <t>11:29</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="AB201" t="inlineStr">
-        <is>
-          <t>11:29</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -23616,24 +23606,24 @@
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122930294</t>
+          <t>https://artportalen.se/Sighting/121742517</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>125963374</v>
+        <v>122928987</v>
       </c>
       <c r="B202" t="n">
         <v>97983</v>
@@ -23662,16 +23652,20 @@
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
+      <c r="J202" t="inlineStr"/>
+      <c r="K202" t="inlineStr"/>
+      <c r="L202" t="inlineStr"/>
+      <c r="N202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Norrby mosse, Norrby mosse, Srm</t>
+          <t>Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>686873</v>
+        <v>686389</v>
       </c>
       <c r="R202" t="n">
-        <v>6562867</v>
+        <v>6562967</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -23698,12 +23692,22 @@
       </c>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="Z202" t="inlineStr">
+        <is>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AB202" t="inlineStr">
+        <is>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -23718,24 +23722,24 @@
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125963374</t>
+          <t>https://artportalen.se/Sighting/122928987</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>125976418</v>
+        <v>122930294</v>
       </c>
       <c r="B203" t="n">
         <v>97983</v>
@@ -23770,17 +23774,17 @@
       <c r="N203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Norrby mosse Ö om, Srm</t>
+          <t>Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>686836</v>
+        <v>686824</v>
       </c>
       <c r="R203" t="n">
-        <v>6563105</v>
+        <v>6562778</v>
       </c>
       <c r="S203" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="T203" t="inlineStr">
         <is>
@@ -23804,17 +23808,22 @@
       </c>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="Z203" t="inlineStr">
+        <is>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC203" t="inlineStr">
-        <is>
-          <t>Riklig förekomst i skogskärr</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AB203" t="inlineStr">
+        <is>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -23823,31 +23832,30 @@
       <c r="AE203" t="b">
         <v>0</v>
       </c>
-      <c r="AF203" t="inlineStr"/>
       <c r="AG203" t="b">
         <v>0</v>
       </c>
       <c r="AT203" t="inlineStr"/>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125976418</t>
+          <t>https://artportalen.se/Sighting/122930294</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>126061082</v>
+        <v>125963374</v>
       </c>
       <c r="B204" t="n">
         <v>97983</v>
@@ -23878,14 +23886,14 @@
       <c r="I204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>Norrby mosse, Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>687079</v>
+        <v>686873</v>
       </c>
       <c r="R204" t="n">
-        <v>6563240</v>
+        <v>6562867</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -23915,19 +23923,9 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z204" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AA204" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB204" t="inlineStr">
-        <is>
-          <t>15:22</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -23942,24 +23940,24 @@
       <c r="AT204" t="inlineStr"/>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061082</t>
+          <t>https://artportalen.se/Sighting/125963374</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>126061090</v>
+        <v>125976418</v>
       </c>
       <c r="B205" t="n">
         <v>97983</v>
@@ -23988,19 +23986,23 @@
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
+      <c r="J205" t="inlineStr"/>
+      <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr"/>
+      <c r="N205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>Norrby mosse Ö om, Srm</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>686871</v>
+        <v>686836</v>
       </c>
       <c r="R205" t="n">
-        <v>6562972</v>
+        <v>6563105</v>
       </c>
       <c r="S205" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T205" t="inlineStr">
         <is>
@@ -24027,19 +24029,14 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z205" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AA205" t="inlineStr">
         <is>
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AB205" t="inlineStr">
-        <is>
-          <t>14:42</t>
+      <c r="AC205" t="inlineStr">
+        <is>
+          <t>Riklig förekomst i skogskärr</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -24048,30 +24045,31 @@
       <c r="AE205" t="b">
         <v>0</v>
       </c>
+      <c r="AF205" t="inlineStr"/>
       <c r="AG205" t="b">
         <v>0</v>
       </c>
       <c r="AT205" t="inlineStr"/>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061090</t>
+          <t>https://artportalen.se/Sighting/125976418</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>126061103</v>
+        <v>126061082</v>
       </c>
       <c r="B206" t="n">
         <v>97983</v>
@@ -24106,10 +24104,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>686811</v>
+        <v>687079</v>
       </c>
       <c r="R206" t="n">
-        <v>6562803</v>
+        <v>6563240</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -24141,7 +24139,7 @@
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
@@ -24151,7 +24149,7 @@
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -24171,19 +24169,19 @@
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061103</t>
+          <t>https://artportalen.se/Sighting/126061082</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>126061111</v>
+        <v>126061090</v>
       </c>
       <c r="B207" t="n">
         <v>97983</v>
@@ -24218,10 +24216,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>687030</v>
+        <v>686871</v>
       </c>
       <c r="R207" t="n">
-        <v>6562755</v>
+        <v>6562972</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -24253,7 +24251,7 @@
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
@@ -24263,7 +24261,7 @@
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -24283,22 +24281,22 @@
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061111</t>
+          <t>https://artportalen.se/Sighting/126061090</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>122929342</v>
+        <v>126061103</v>
       </c>
       <c r="B208" t="n">
-        <v>97986</v>
+        <v>97983</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -24306,16 +24304,16 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -24324,23 +24322,19 @@
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
-      <c r="J208" t="inlineStr"/>
-      <c r="K208" t="inlineStr"/>
-      <c r="L208" t="inlineStr"/>
-      <c r="N208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Norrby mosse, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>686569</v>
+        <v>686811</v>
       </c>
       <c r="R208" t="n">
-        <v>6562949</v>
+        <v>6562803</v>
       </c>
       <c r="S208" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T208" t="inlineStr">
         <is>
@@ -24364,22 +24358,22 @@
       </c>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -24394,27 +24388,27 @@
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122929342</t>
+          <t>https://artportalen.se/Sighting/126061103</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>126061110</v>
+        <v>126061111</v>
       </c>
       <c r="B209" t="n">
-        <v>97986</v>
+        <v>97983</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -24422,16 +24416,16 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -24446,10 +24440,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>687029</v>
+        <v>687030</v>
       </c>
       <c r="R209" t="n">
-        <v>6562759</v>
+        <v>6562755</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -24481,7 +24475,7 @@
       </c>
       <c r="Z209" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
@@ -24491,7 +24485,7 @@
       </c>
       <c r="AB209" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -24517,16 +24511,16 @@
       <c r="AY209" t="inlineStr"/>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061110</t>
+          <t>https://artportalen.se/Sighting/126061111</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>101523203</v>
+        <v>122929342</v>
       </c>
       <c r="B210" t="n">
-        <v>99140</v>
+        <v>97986</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -24534,21 +24528,21 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>221952</v>
+        <v>221946</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -24558,17 +24552,17 @@
       <c r="N210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
-          <t>NO Norrby Mosse, Srm</t>
+          <t>Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>687050</v>
+        <v>686569</v>
       </c>
       <c r="R210" t="n">
-        <v>6563327</v>
+        <v>6562949</v>
       </c>
       <c r="S210" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -24592,12 +24586,22 @@
       </c>
       <c r="Y210" t="inlineStr">
         <is>
-          <t>2022-06-08</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="Z210" t="inlineStr">
+        <is>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>2022-06-08</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AB210" t="inlineStr">
+        <is>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -24606,34 +24610,33 @@
       <c r="AE210" t="b">
         <v>0</v>
       </c>
-      <c r="AF210" t="inlineStr"/>
       <c r="AG210" t="b">
         <v>0</v>
       </c>
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101523203</t>
+          <t>https://artportalen.se/Sighting/122929342</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>117554655</v>
+        <v>126061110</v>
       </c>
       <c r="B211" t="n">
-        <v>99140</v>
+        <v>97986</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -24641,42 +24644,34 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>221952</v>
+        <v>221946</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
-      <c r="J211" t="inlineStr"/>
-      <c r="K211" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L211" t="inlineStr"/>
-      <c r="N211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
-          <t>NO Norrby  Mosse, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>687062</v>
+        <v>687029</v>
       </c>
       <c r="R211" t="n">
-        <v>6563349</v>
+        <v>6562759</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -24703,12 +24698,22 @@
       </c>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z211" t="inlineStr">
+        <is>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB211" t="inlineStr">
+        <is>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -24717,31 +24722,30 @@
       <c r="AE211" t="b">
         <v>0</v>
       </c>
-      <c r="AF211" t="inlineStr"/>
       <c r="AG211" t="b">
         <v>0</v>
       </c>
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117554655</t>
+          <t>https://artportalen.se/Sighting/126061110</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>126234400</v>
+        <v>101523203</v>
       </c>
       <c r="B212" t="n">
         <v>99140</v>
@@ -24769,33 +24773,21 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I212" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J212" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K212" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I212" t="inlineStr"/>
+      <c r="J212" t="inlineStr"/>
+      <c r="K212" t="inlineStr"/>
       <c r="L212" t="inlineStr"/>
       <c r="N212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Norrby mosse SO, Srm</t>
+          <t>NO Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>686788</v>
+        <v>687050</v>
       </c>
       <c r="R212" t="n">
-        <v>6563073</v>
+        <v>6563327</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -24822,12 +24814,12 @@
       </c>
       <c r="Y212" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2022-06-08</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2022-06-08</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -24843,27 +24835,27 @@
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126234400</t>
+          <t>https://artportalen.se/Sighting/101523203</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>134487623</v>
+        <v>117554655</v>
       </c>
       <c r="B213" t="n">
-        <v>99217</v>
+        <v>99140</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -24899,17 +24891,17 @@
       <c r="N213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>NO Norrby  Mosse, Srm</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>687067</v>
+        <v>687062</v>
       </c>
       <c r="R213" t="n">
-        <v>6563342</v>
+        <v>6563349</v>
       </c>
       <c r="S213" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T213" t="inlineStr">
         <is>
@@ -24933,17 +24925,12 @@
       </c>
       <c r="Y213" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="AC213" t="inlineStr">
-        <is>
-          <t>Ett tiotal i blom samt flera plantor med endast blad.  Återfynd.</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -24970,16 +24957,16 @@
       <c r="AY213" t="inlineStr"/>
       <c r="AZ213" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134487623</t>
+          <t>https://artportalen.se/Sighting/117554655</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>134487656</v>
+        <v>126234400</v>
       </c>
       <c r="B214" t="n">
-        <v>99217</v>
+        <v>99140</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -25004,8 +24991,16 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I214" t="inlineStr"/>
-      <c r="J214" t="inlineStr"/>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K214" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -25015,14 +25010,14 @@
       <c r="N214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrby mosse SO, Srm</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>686835</v>
+        <v>686788</v>
       </c>
       <c r="R214" t="n">
-        <v>6563212</v>
+        <v>6563073</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -25049,17 +25044,12 @@
       </c>
       <c r="Y214" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="AC214" t="inlineStr">
-        <is>
-          <t>2 i blom samt några plantor med endast blad.</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -25075,24 +25065,24 @@
       <c r="AT214" t="inlineStr"/>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
       <c r="AZ214" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134487656</t>
+          <t>https://artportalen.se/Sighting/126234400</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>134488457</v>
+        <v>134487623</v>
       </c>
       <c r="B215" t="n">
         <v>99217</v>
@@ -25135,13 +25125,13 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>687294</v>
+        <v>687067</v>
       </c>
       <c r="R215" t="n">
-        <v>6563391</v>
+        <v>6563342</v>
       </c>
       <c r="S215" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T215" t="inlineStr">
         <is>
@@ -25175,7 +25165,7 @@
       </c>
       <c r="AC215" t="inlineStr">
         <is>
-          <t>2 i blom samt fler med endast blad.</t>
+          <t>Ett tiotal i blom samt flera plantor med endast blad.  Återfynd.</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -25202,43 +25192,48 @@
       <c r="AY215" t="inlineStr"/>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134488457</t>
+          <t>https://artportalen.se/Sighting/134487623</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>129564006</v>
+        <v>134487656</v>
       </c>
       <c r="B216" t="n">
-        <v>79350</v>
+        <v>99217</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>260591</v>
+        <v>221952</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
       <c r="J216" t="inlineStr"/>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr"/>
       <c r="N216" t="inlineStr"/>
       <c r="P216" t="inlineStr">
         <is>
@@ -25246,10 +25241,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>686681</v>
+        <v>686835</v>
       </c>
       <c r="R216" t="n">
-        <v>6563025</v>
+        <v>6563212</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -25276,19 +25271,24 @@
       </c>
       <c r="Y216" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AC216" t="inlineStr">
+        <is>
+          <t>2 i blom samt några plantor med endast blad.</t>
         </is>
       </c>
       <c r="AD216" t="b">
         <v>0</v>
       </c>
       <c r="AE216" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF216" t="inlineStr"/>
       <c r="AG216" t="b">
@@ -25307,6 +25307,228 @@
       </c>
       <c r="AY216" t="inlineStr"/>
       <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134487656</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>134488457</v>
+      </c>
+      <c r="B217" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E217" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr"/>
+      <c r="J217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr"/>
+      <c r="N217" t="inlineStr"/>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q217" t="n">
+        <v>687294</v>
+      </c>
+      <c r="R217" t="n">
+        <v>6563391</v>
+      </c>
+      <c r="S217" t="n">
+        <v>10</v>
+      </c>
+      <c r="T217" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V217" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W217" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y217" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AC217" t="inlineStr">
+        <is>
+          <t>2 i blom samt fler med endast blad.</t>
+        </is>
+      </c>
+      <c r="AD217" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE217" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF217" t="inlineStr"/>
+      <c r="AG217" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT217" t="inlineStr"/>
+      <c r="AW217" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX217" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134488457</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>129564006</v>
+      </c>
+      <c r="B218" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E218" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr"/>
+      <c r="J218" t="inlineStr"/>
+      <c r="K218" t="inlineStr"/>
+      <c r="N218" t="inlineStr"/>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q218" t="n">
+        <v>686681</v>
+      </c>
+      <c r="R218" t="n">
+        <v>6563025</v>
+      </c>
+      <c r="S218" t="n">
+        <v>10</v>
+      </c>
+      <c r="T218" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V218" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W218" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y218" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AD218" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE218" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF218" t="inlineStr"/>
+      <c r="AG218" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT218" t="inlineStr"/>
+      <c r="AW218" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX218" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129564006</t>
         </is>
@@ -25529,6 +25751,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -23412,7 +23412,7 @@
         <v>135827249</v>
       </c>
       <c r="B200" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -14751,7 +14751,7 @@
         <v>135827212</v>
       </c>
       <c r="B125" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -23412,7 +23412,7 @@
         <v>135827249</v>
       </c>
       <c r="B200" t="n">
-        <v>98144</v>
+        <v>98161</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -23412,7 +23412,7 @@
         <v>135827249</v>
       </c>
       <c r="B200" t="n">
-        <v>98161</v>
+        <v>98162</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -23412,7 +23412,7 @@
         <v>135827249</v>
       </c>
       <c r="B200" t="n">
-        <v>98162</v>
+        <v>98163</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -5320,7 +5320,7 @@
         <v>136261113</v>
       </c>
       <c r="B43" t="n">
-        <v>96880</v>
+        <v>96881</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>136258592</v>
       </c>
       <c r="B50" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -9352,7 +9352,7 @@
         <v>136258570</v>
       </c>
       <c r="B79" t="n">
-        <v>92744</v>
+        <v>92745</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -11547,7 +11547,7 @@
         <v>136260416</v>
       </c>
       <c r="B98" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12379,7 +12379,7 @@
         <v>136258642</v>
       </c>
       <c r="B105" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -15322,7 +15322,7 @@
         <v>135827212</v>
       </c>
       <c r="B130" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -24095,7 +24095,7 @@
         <v>135827249</v>
       </c>
       <c r="B206" t="n">
-        <v>98163</v>
+        <v>98164</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -5320,7 +5320,7 @@
         <v>136261113</v>
       </c>
       <c r="B43" t="n">
-        <v>96881</v>
+        <v>96887</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>136258592</v>
       </c>
       <c r="B50" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -9352,7 +9352,7 @@
         <v>136258570</v>
       </c>
       <c r="B79" t="n">
-        <v>92745</v>
+        <v>92751</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -11547,7 +11547,7 @@
         <v>136260416</v>
       </c>
       <c r="B98" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12379,7 +12379,7 @@
         <v>136258642</v>
       </c>
       <c r="B105" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -15322,7 +15322,7 @@
         <v>135827212</v>
       </c>
       <c r="B130" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -24095,7 +24095,7 @@
         <v>135827249</v>
       </c>
       <c r="B206" t="n">
-        <v>98164</v>
+        <v>98170</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>

--- a/artfynd/A 3151-2025 artfynd.xlsx
+++ b/artfynd/A 3151-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ224"/>
+  <dimension ref="A1:AZ226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5320,7 +5320,7 @@
         <v>136261113</v>
       </c>
       <c r="B43" t="n">
-        <v>96887</v>
+        <v>96888</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>136258592</v>
       </c>
       <c r="B50" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -9352,7 +9352,7 @@
         <v>136258570</v>
       </c>
       <c r="B79" t="n">
-        <v>92751</v>
+        <v>92752</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -11547,7 +11547,7 @@
         <v>136260416</v>
       </c>
       <c r="B98" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12379,7 +12379,7 @@
         <v>136258642</v>
       </c>
       <c r="B105" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -15322,7 +15322,7 @@
         <v>135827212</v>
       </c>
       <c r="B130" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15429,45 +15429,53 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121859656</v>
+        <v>136330004</v>
       </c>
       <c r="B131" t="n">
-        <v>5199</v>
+        <v>58149</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Öster om Tyresta by, Tyresta, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>687094</v>
+        <v>686477</v>
       </c>
       <c r="R131" t="n">
-        <v>6563235</v>
+        <v>6563053</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15494,22 +15502,12 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>15:16</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>15:16</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15520,48 +15518,28 @@
       </c>
       <c r="AG131" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ131" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK131" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL131" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO131" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859656</t>
+          <t>https://artportalen.se/Sighting/136330004</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126061088</v>
+        <v>121859656</v>
       </c>
       <c r="B132" t="n">
         <v>5199</v>
@@ -15592,14 +15570,14 @@
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>Öster om Tyresta by, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>686865</v>
+        <v>687094</v>
       </c>
       <c r="R132" t="n">
-        <v>6562977</v>
+        <v>6563235</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15626,22 +15604,22 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15665,12 +15643,12 @@
       </c>
       <c r="AL132" t="inlineStr">
         <is>
-          <t>Klen torr granlåga.</t>
+          <t>Granlåga</t>
         </is>
       </c>
       <c r="AO132" t="inlineStr">
         <is>
-          <t>Picea abies # Klen torr granlåga.</t>
+          <t>Picea abies # Granlåga</t>
         </is>
       </c>
       <c r="AT132" t="inlineStr"/>
@@ -15681,19 +15659,19 @@
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061088</t>
+          <t>https://artportalen.se/Sighting/121859656</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>126061109</v>
+        <v>126061088</v>
       </c>
       <c r="B133" t="n">
         <v>5199</v>
@@ -15728,10 +15706,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>686946</v>
+        <v>686865</v>
       </c>
       <c r="R133" t="n">
-        <v>6562741</v>
+        <v>6562977</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15763,7 +15741,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -15773,7 +15751,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15813,22 +15791,22 @@
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061109</t>
+          <t>https://artportalen.se/Sighting/126061088</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121859629</v>
+        <v>126061109</v>
       </c>
       <c r="B134" t="n">
-        <v>8455</v>
+        <v>5199</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15836,34 +15814,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Öster om Tyresta by, Tyresta, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>686792</v>
+        <v>686946</v>
       </c>
       <c r="R134" t="n">
-        <v>6563030</v>
+        <v>6562741</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15890,22 +15868,22 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15919,17 +15897,22 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK134" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL134" t="inlineStr">
+        <is>
+          <t>Klen torr granlåga.</t>
         </is>
       </c>
       <c r="AO134" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies # Klen torr granlåga.</t>
         </is>
       </c>
       <c r="AT134" t="inlineStr"/>
@@ -15940,19 +15923,19 @@
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859629</t>
+          <t>https://artportalen.se/Sighting/126061109</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121859631</v>
+        <v>121859629</v>
       </c>
       <c r="B135" t="n">
         <v>8455</v>
@@ -15987,10 +15970,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>686934</v>
+        <v>686792</v>
       </c>
       <c r="R135" t="n">
-        <v>6563148</v>
+        <v>6563030</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -16022,7 +16005,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -16032,7 +16015,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -16073,13 +16056,13 @@
       <c r="AY135" t="inlineStr"/>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859631</t>
+          <t>https://artportalen.se/Sighting/121859629</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>122929535</v>
+        <v>121859631</v>
       </c>
       <c r="B136" t="n">
         <v>8455</v>
@@ -16107,29 +16090,20 @@
           <t>(Hartig, 1834)</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Norrby mosse, Srm</t>
+          <t>Öster om Tyresta by, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>686612</v>
+        <v>686934</v>
       </c>
       <c r="R136" t="n">
-        <v>6562882</v>
+        <v>6563148</v>
       </c>
       <c r="S136" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -16153,22 +16127,22 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -16179,31 +16153,46 @@
       </c>
       <c r="AG136" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ136" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK136" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO136" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122929535</t>
+          <t>https://artportalen.se/Sighting/121859631</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>136259916</v>
+        <v>122929535</v>
       </c>
       <c r="B137" t="n">
-        <v>8463</v>
+        <v>8455</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16228,29 +16217,29 @@
           <t>(Hartig, 1834)</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr"/>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M137" t="inlineStr"/>
       <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>686457</v>
+        <v>686612</v>
       </c>
       <c r="R137" t="n">
-        <v>6563062</v>
+        <v>6562882</v>
       </c>
       <c r="S137" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -16274,12 +16263,22 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16288,34 +16287,33 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
-      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136259916</t>
+          <t>https://artportalen.se/Sighting/122929535</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>125974903</v>
+        <v>136259916</v>
       </c>
       <c r="B138" t="n">
-        <v>8444</v>
+        <v>8463</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16323,28 +16321,24 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr"/>
       <c r="L138" t="inlineStr"/>
@@ -16356,17 +16350,17 @@
       <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>söder om Tyresta, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>686838</v>
+        <v>686457</v>
       </c>
       <c r="R138" t="n">
-        <v>6562733</v>
+        <v>6563062</v>
       </c>
       <c r="S138" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -16390,17 +16384,12 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>gammal björklåga med spår längs hela stammen</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -16413,47 +16402,27 @@
       <c r="AG138" t="b">
         <v>0</v>
       </c>
-      <c r="AJ138" t="inlineStr">
-        <is>
-          <t>vårtbjörk</t>
-        </is>
-      </c>
-      <c r="AK138" t="inlineStr">
-        <is>
-          <t>Betula pendula</t>
-        </is>
-      </c>
-      <c r="AM138" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO138" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Betula pendula</t>
-        </is>
-      </c>
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Nette Bygren</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Nette Bygren</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125974903</t>
+          <t>https://artportalen.se/Sighting/136259916</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126061086</v>
+        <v>125974903</v>
       </c>
       <c r="B139" t="n">
         <v>8444</v>
@@ -16481,20 +16450,33 @@
           <t>Janson, 1856</t>
         </is>
       </c>
-      <c r="I139" t="inlineStr"/>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>söder om Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>686932</v>
+        <v>686838</v>
       </c>
       <c r="R139" t="n">
-        <v>6563067</v>
+        <v>6562733</v>
       </c>
       <c r="S139" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -16521,19 +16503,14 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z139" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AB139" t="inlineStr">
-        <is>
-          <t>15:00</t>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>gammal björklåga med spår längs hela stammen</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16542,50 +16519,51 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>vårtbjörk</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
         <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AL139" t="inlineStr">
-        <is>
-          <t>Barklös björklåga.</t>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AM139" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
         </is>
       </c>
       <c r="AO139" t="inlineStr">
         <is>
-          <t>Betula # Barklös björklåga.</t>
+          <t>Wood surface of dead wood # Betula pendula</t>
         </is>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Nette Bygren</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Nette Bygren</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061086</t>
+          <t>https://artportalen.se/Sighting/125974903</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126061105</v>
+        <v>126061086</v>
       </c>
       <c r="B140" t="n">
         <v>8444</v>
@@ -16620,10 +16598,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>686860</v>
+        <v>686932</v>
       </c>
       <c r="R140" t="n">
-        <v>6562743</v>
+        <v>6563067</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -16655,7 +16633,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -16665,7 +16643,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16687,9 +16665,14 @@
           <t>Betula</t>
         </is>
       </c>
+      <c r="AL140" t="inlineStr">
+        <is>
+          <t>Barklös björklåga.</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Betula # Barklös björklåga.</t>
         </is>
       </c>
       <c r="AT140" t="inlineStr"/>
@@ -16700,22 +16683,22 @@
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061105</t>
+          <t>https://artportalen.se/Sighting/126061086</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>111182876</v>
+        <v>126061105</v>
       </c>
       <c r="B141" t="n">
-        <v>58790</v>
+        <v>8444</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16723,43 +16706,34 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>208245</v>
+        <v>106554</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>NO Norrby  Mosse, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>686971</v>
+        <v>686860</v>
       </c>
       <c r="R141" t="n">
-        <v>6563333</v>
+        <v>6562743</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16786,12 +16760,22 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2023-07-30</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2023-07-30</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16800,31 +16784,45 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
-      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ141" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK141" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO141" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111182876</t>
+          <t>https://artportalen.se/Sighting/126061105</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126061089</v>
+        <v>111182876</v>
       </c>
       <c r="B142" t="n">
         <v>58790</v>
@@ -16857,21 +16855,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>NO Norrby  Mosse, Srm</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>686871</v>
+        <v>686971</v>
       </c>
       <c r="R142" t="n">
-        <v>6562972</v>
+        <v>6563333</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16898,22 +16896,12 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z142" t="inlineStr">
-        <is>
-          <t>14:42</t>
+          <t>2023-07-30</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB142" t="inlineStr">
-        <is>
-          <t>14:42</t>
+          <t>2023-07-30</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16922,30 +16910,31 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
+      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061089</t>
+          <t>https://artportalen.se/Sighting/111182876</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126061098</v>
+        <v>126061089</v>
       </c>
       <c r="B143" t="n">
         <v>58790</v>
@@ -16973,17 +16962,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I143" t="inlineStr"/>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="P143" t="inlineStr">
         <is>
           <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>686857</v>
+        <v>686871</v>
       </c>
       <c r="R143" t="n">
-        <v>6562875</v>
+        <v>6562972</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -17015,7 +17013,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -17025,7 +17023,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -17045,19 +17043,19 @@
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061098</t>
+          <t>https://artportalen.se/Sighting/126061089</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128095464</v>
+        <v>126061098</v>
       </c>
       <c r="B144" t="n">
         <v>58790</v>
@@ -17085,30 +17083,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
-      <c r="L144" t="inlineStr"/>
-      <c r="M144" t="inlineStr"/>
-      <c r="N144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>687155</v>
+        <v>686857</v>
       </c>
       <c r="R144" t="n">
-        <v>6563193</v>
+        <v>6562875</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -17135,12 +17120,22 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -17149,34 +17144,33 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
-      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128095464</t>
+          <t>https://artportalen.se/Sighting/126061098</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>134488564</v>
+        <v>128095464</v>
       </c>
       <c r="B145" t="n">
-        <v>58812</v>
+        <v>58790</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17207,7 +17201,11 @@
         </is>
       </c>
       <c r="J145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>årsunge</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" t="inlineStr"/>
       <c r="N145" t="inlineStr"/>
@@ -17217,10 +17215,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>687272</v>
+        <v>687155</v>
       </c>
       <c r="R145" t="n">
-        <v>6563263</v>
+        <v>6563193</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -17247,17 +17245,12 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>Ca 2-3 cm lång.</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -17284,16 +17277,16 @@
       <c r="AY145" t="inlineStr"/>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134488564</t>
+          <t>https://artportalen.se/Sighting/128095464</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>126061108</v>
+        <v>134488564</v>
       </c>
       <c r="B146" t="n">
-        <v>58817</v>
+        <v>58812</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17301,21 +17294,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>208249</v>
+        <v>208245</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -17323,26 +17316,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J146" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>686907</v>
+        <v>687272</v>
       </c>
       <c r="R146" t="n">
-        <v>6562760</v>
+        <v>6563263</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -17369,22 +17357,17 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z146" t="inlineStr">
-        <is>
-          <t>13:17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB146" t="inlineStr">
-        <is>
-          <t>13:17</t>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>Ca 2-3 cm lång.</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17393,33 +17376,34 @@
       <c r="AE146" t="b">
         <v>0</v>
       </c>
+      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
       </c>
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061108</t>
+          <t>https://artportalen.se/Sighting/134488564</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>126061081</v>
+        <v>126061108</v>
       </c>
       <c r="B147" t="n">
-        <v>58815</v>
+        <v>58817</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17427,21 +17411,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>208250</v>
+        <v>208249</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -17465,10 +17449,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>687058</v>
+        <v>686907</v>
       </c>
       <c r="R147" t="n">
-        <v>6563228</v>
+        <v>6562760</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17500,7 +17484,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -17510,7 +17494,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17530,22 +17514,22 @@
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061081</t>
+          <t>https://artportalen.se/Sighting/126061108</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>117554483</v>
+        <v>126061081</v>
       </c>
       <c r="B148" t="n">
-        <v>99035</v>
+        <v>58815</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17553,41 +17537,51 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>219790</v>
+        <v>208250</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr"/>
-      <c r="N148" t="inlineStr"/>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>SO Norrby Mosse, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>686878</v>
+        <v>687058</v>
       </c>
       <c r="R148" t="n">
-        <v>6562971</v>
+        <v>6563228</v>
       </c>
       <c r="S148" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -17611,12 +17605,22 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17625,31 +17629,30 @@
       <c r="AE148" t="b">
         <v>0</v>
       </c>
-      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
       </c>
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117554483</t>
+          <t>https://artportalen.se/Sighting/126061081</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>126003792</v>
+        <v>117554483</v>
       </c>
       <c r="B149" t="n">
         <v>99035</v>
@@ -17684,17 +17687,17 @@
       <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>SO Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>687046</v>
+        <v>686878</v>
       </c>
       <c r="R149" t="n">
-        <v>6563346</v>
+        <v>6562971</v>
       </c>
       <c r="S149" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -17718,12 +17721,12 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17750,13 +17753,13 @@
       <c r="AY149" t="inlineStr"/>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126003792</t>
+          <t>https://artportalen.se/Sighting/117554483</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>126005160</v>
+        <v>126003792</v>
       </c>
       <c r="B150" t="n">
         <v>99035</v>
@@ -17795,10 +17798,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>687034</v>
+        <v>687046</v>
       </c>
       <c r="R150" t="n">
-        <v>6563204</v>
+        <v>6563346</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17857,13 +17860,13 @@
       <c r="AY150" t="inlineStr"/>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126005160</t>
+          <t>https://artportalen.se/Sighting/126003792</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>126061084</v>
+        <v>126005160</v>
       </c>
       <c r="B151" t="n">
         <v>99035</v>
@@ -17892,16 +17895,20 @@
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>687014</v>
+        <v>687034</v>
       </c>
       <c r="R151" t="n">
-        <v>6563215</v>
+        <v>6563204</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17928,22 +17935,12 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z151" t="inlineStr">
-        <is>
-          <t>15:14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB151" t="inlineStr">
-        <is>
-          <t>15:14</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17952,30 +17949,31 @@
       <c r="AE151" t="b">
         <v>0</v>
       </c>
+      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
       </c>
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061084</t>
+          <t>https://artportalen.se/Sighting/126005160</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>126061091</v>
+        <v>126061084</v>
       </c>
       <c r="B152" t="n">
         <v>99035</v>
@@ -18010,10 +18008,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>686871</v>
+        <v>687014</v>
       </c>
       <c r="R152" t="n">
-        <v>6562972</v>
+        <v>6563215</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -18045,7 +18043,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -18055,7 +18053,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -18081,13 +18079,13 @@
       <c r="AY152" t="inlineStr"/>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061091</t>
+          <t>https://artportalen.se/Sighting/126061084</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>126061099</v>
+        <v>126061091</v>
       </c>
       <c r="B153" t="n">
         <v>99035</v>
@@ -18122,10 +18120,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>686857</v>
+        <v>686871</v>
       </c>
       <c r="R153" t="n">
-        <v>6562875</v>
+        <v>6562972</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -18157,7 +18155,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -18167,7 +18165,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -18187,19 +18185,19 @@
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061099</t>
+          <t>https://artportalen.se/Sighting/126061091</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>126061102</v>
+        <v>126061099</v>
       </c>
       <c r="B154" t="n">
         <v>99035</v>
@@ -18234,10 +18232,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>686837</v>
+        <v>686857</v>
       </c>
       <c r="R154" t="n">
-        <v>6562829</v>
+        <v>6562875</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -18269,7 +18267,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -18279,7 +18277,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -18305,13 +18303,13 @@
       <c r="AY154" t="inlineStr"/>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061102</t>
+          <t>https://artportalen.se/Sighting/126061099</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>126233785</v>
+        <v>126061102</v>
       </c>
       <c r="B155" t="n">
         <v>99035</v>
@@ -18340,24 +18338,16 @@
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
-      <c r="J155" t="inlineStr"/>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L155" t="inlineStr"/>
-      <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>686839</v>
+        <v>686837</v>
       </c>
       <c r="R155" t="n">
-        <v>6563016</v>
+        <v>6562829</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -18384,12 +18374,22 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -18398,31 +18398,30 @@
       <c r="AE155" t="b">
         <v>0</v>
       </c>
-      <c r="AF155" t="inlineStr"/>
       <c r="AG155" t="b">
         <v>0</v>
       </c>
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Bodil Ravn, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126233785</t>
+          <t>https://artportalen.se/Sighting/126061102</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>126234010</v>
+        <v>126233785</v>
       </c>
       <c r="B156" t="n">
         <v>99035</v>
@@ -18465,10 +18464,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>687160</v>
+        <v>686839</v>
       </c>
       <c r="R156" t="n">
-        <v>6563261</v>
+        <v>6563016</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18521,19 +18520,19 @@
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Bodil Ravn, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126234010</t>
+          <t>https://artportalen.se/Sighting/126233785</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>126234159</v>
+        <v>126234010</v>
       </c>
       <c r="B157" t="n">
         <v>99035</v>
@@ -18561,13 +18560,13 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr"/>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr"/>
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
@@ -18576,13 +18575,13 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>687297</v>
+        <v>687160</v>
       </c>
       <c r="R157" t="n">
-        <v>6563381</v>
+        <v>6563261</v>
       </c>
       <c r="S157" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -18612,11 +18611,6 @@
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>Ett flertal i blomning.</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -18637,19 +18631,19 @@
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Bodil Ravn, Ulf Johansson</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126234159</t>
+          <t>https://artportalen.se/Sighting/126234010</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>126234439</v>
+        <v>126234159</v>
       </c>
       <c r="B158" t="n">
         <v>99035</v>
@@ -18679,34 +18673,26 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J158" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr"/>
       <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Norrby mosse SO, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>686777</v>
+        <v>687297</v>
       </c>
       <c r="R158" t="n">
-        <v>6563073</v>
+        <v>6563381</v>
       </c>
       <c r="S158" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -18736,6 +18722,11 @@
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>Ett flertal i blomning.</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -18751,24 +18742,24 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Bodil Ravn, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126234439</t>
+          <t>https://artportalen.se/Sighting/126234159</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>126234644</v>
+        <v>126234439</v>
       </c>
       <c r="B159" t="n">
         <v>99035</v>
@@ -18798,7 +18789,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -18806,7 +18797,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr"/>
       <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
@@ -18815,10 +18810,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>686837</v>
+        <v>686777</v>
       </c>
       <c r="R159" t="n">
-        <v>6562967</v>
+        <v>6563073</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18877,13 +18872,13 @@
       <c r="AY159" t="inlineStr"/>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126234644</t>
+          <t>https://artportalen.se/Sighting/126234439</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>126234771</v>
+        <v>126234644</v>
       </c>
       <c r="B160" t="n">
         <v>99035</v>
@@ -18913,7 +18908,7 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -18926,14 +18921,14 @@
       <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Norrby mosse OSO, Srm</t>
+          <t>Norrby mosse SO, Srm</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>686976</v>
+        <v>686837</v>
       </c>
       <c r="R160" t="n">
-        <v>6563107</v>
+        <v>6562967</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18992,16 +18987,16 @@
       <c r="AY160" t="inlineStr"/>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126234771</t>
+          <t>https://artportalen.se/Sighting/126234644</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>133767702</v>
+        <v>126234771</v>
       </c>
       <c r="B161" t="n">
-        <v>99112</v>
+        <v>99035</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19026,21 +19021,29 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K161" t="inlineStr"/>
       <c r="L161" t="inlineStr"/>
       <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrby mosse OSO, Srm</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>686845</v>
+        <v>686976</v>
       </c>
       <c r="R161" t="n">
-        <v>6563325</v>
+        <v>6563107</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -19067,12 +19070,12 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -19088,27 +19091,27 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133767702</t>
+          <t>https://artportalen.se/Sighting/126234771</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>126061092</v>
+        <v>133767702</v>
       </c>
       <c r="B162" t="n">
-        <v>99022</v>
+        <v>99112</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19116,43 +19119,38 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>220093</v>
+        <v>219790</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>686880</v>
+        <v>686845</v>
       </c>
       <c r="R162" t="n">
-        <v>6562892</v>
+        <v>6563325</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -19179,22 +19177,12 @@
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z162" t="inlineStr">
-        <is>
-          <t>14:35</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB162" t="inlineStr">
-        <is>
-          <t>14:35</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -19203,30 +19191,31 @@
       <c r="AE162" t="b">
         <v>0</v>
       </c>
+      <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="b">
         <v>0</v>
       </c>
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061092</t>
+          <t>https://artportalen.se/Sighting/133767702</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>126061094</v>
+        <v>126061092</v>
       </c>
       <c r="B163" t="n">
         <v>99022</v>
@@ -19270,10 +19259,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>686866</v>
+        <v>686880</v>
       </c>
       <c r="R163" t="n">
-        <v>6562874</v>
+        <v>6562892</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -19305,7 +19294,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -19315,7 +19304,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -19341,13 +19330,13 @@
       <c r="AY163" t="inlineStr"/>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061094</t>
+          <t>https://artportalen.se/Sighting/126061092</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>126061100</v>
+        <v>126061094</v>
       </c>
       <c r="B164" t="n">
         <v>99022</v>
@@ -19377,7 +19366,7 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -19391,10 +19380,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>686857</v>
+        <v>686866</v>
       </c>
       <c r="R164" t="n">
-        <v>6562875</v>
+        <v>6562874</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -19426,7 +19415,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -19436,7 +19425,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -19462,43 +19451,43 @@
       <c r="AY164" t="inlineStr"/>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061100</t>
+          <t>https://artportalen.se/Sighting/126061094</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>86686018</v>
+        <v>126061100</v>
       </c>
       <c r="B165" t="n">
-        <v>99118</v>
+        <v>99022</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
@@ -19506,23 +19495,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L165" t="inlineStr"/>
-      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Tyresta S Ungfars kärr, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>686831</v>
+        <v>686857</v>
       </c>
       <c r="R165" t="n">
-        <v>6563296</v>
+        <v>6562875</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -19549,17 +19531,22 @@
       </c>
       <c r="Y165" t="inlineStr">
         <is>
-          <t>2020-07-04</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>2020-07-04</t>
-        </is>
-      </c>
-      <c r="AC165" t="inlineStr">
-        <is>
-          <t>Från Ungfars kärrs södra spets och ca 200 meter österut. Ungefär hälften av skotten utanför parkens gräns. 4 blomstänglar. Området var bökat av vildsvin. Vissa skott var uppgrävda.</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -19568,31 +19555,30 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
-      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/86686018</t>
+          <t>https://artportalen.se/Sighting/126061100</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>96672256</v>
+        <v>86686018</v>
       </c>
       <c r="B166" t="n">
         <v>99118</v>
@@ -19620,24 +19606,36 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I166" t="inlineStr"/>
-      <c r="J166" t="inlineStr"/>
-      <c r="K166" t="inlineStr"/>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr"/>
       <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>NO Norrby mosse, Srm</t>
+          <t>Tyresta S Ungfars kärr, Srm</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>686848</v>
+        <v>686831</v>
       </c>
       <c r="R166" t="n">
-        <v>6563295</v>
+        <v>6563296</v>
       </c>
       <c r="S166" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -19661,12 +19659,17 @@
       </c>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
+          <t>2020-07-04</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2021-10-15</t>
+          <t>2020-07-04</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>Från Ungfars kärrs södra spets och ca 200 meter österut. Ungefär hälften av skotten utanför parkens gräns. 4 blomstänglar. Området var bökat av vildsvin. Vissa skott var uppgrävda.</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -19682,24 +19685,24 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96672256</t>
+          <t>https://artportalen.se/Sighting/86686018</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>97242656</v>
+        <v>96672256</v>
       </c>
       <c r="B167" t="n">
         <v>99118</v>
@@ -19728,21 +19731,23 @@
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>OSO Ungfars mosse, Srm</t>
+          <t>NO Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>686846</v>
+        <v>686848</v>
       </c>
       <c r="R167" t="n">
-        <v>6563316</v>
+        <v>6563295</v>
       </c>
       <c r="S167" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -19766,22 +19771,12 @@
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>2021-11-20</t>
-        </is>
-      </c>
-      <c r="Z167" t="inlineStr">
-        <is>
-          <t>13:59</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2021-11-20</t>
-        </is>
-      </c>
-      <c r="AB167" t="inlineStr">
-        <is>
-          <t>13:59</t>
+          <t>2021-10-15</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -19790,30 +19785,31 @@
       <c r="AE167" t="b">
         <v>0</v>
       </c>
+      <c r="AF167" t="inlineStr"/>
       <c r="AG167" t="b">
         <v>0</v>
       </c>
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Thomas Strid</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Thomas Strid, Bodil Ravn, Ulf Johansson, Tiina Laantee</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97242656</t>
+          <t>https://artportalen.se/Sighting/96672256</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>97243108</v>
+        <v>97242656</v>
       </c>
       <c r="B168" t="n">
         <v>99118</v>
@@ -19846,17 +19842,17 @@
       <c r="L168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Tyresta, Srm</t>
+          <t>OSO Ungfars mosse, Srm</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>686847</v>
+        <v>686846</v>
       </c>
       <c r="R168" t="n">
-        <v>6563308</v>
+        <v>6563316</v>
       </c>
       <c r="S168" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -19885,7 +19881,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -19895,7 +19891,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -19921,13 +19917,13 @@
       <c r="AY168" t="inlineStr"/>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97243108</t>
+          <t>https://artportalen.se/Sighting/97242656</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>97330311</v>
+        <v>97243108</v>
       </c>
       <c r="B169" t="n">
         <v>99118</v>
@@ -19955,29 +19951,22 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J169" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Tyresta NP, SSV Bylsjön (*knärot* /stjälk/), Srm</t>
+          <t>Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q169" t="n">
         <v>686847</v>
       </c>
       <c r="R169" t="n">
-        <v>6563309</v>
+        <v>6563308</v>
       </c>
       <c r="S169" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -19999,24 +19988,24 @@
           <t>Österhaninge</t>
         </is>
       </c>
-      <c r="X169" t="inlineStr">
-        <is>
-          <t>AB-Han-0218</t>
-        </is>
-      </c>
       <c r="Y169" t="inlineStr">
         <is>
           <t>2021-11-20</t>
         </is>
       </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
       <c r="AA169" t="inlineStr">
         <is>
           <t>2021-11-20</t>
         </is>
       </c>
-      <c r="AC169" t="inlineStr">
-        <is>
-          <t>/Ej räknad/</t>
+      <c r="AB169" t="inlineStr">
+        <is>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -20031,28 +20020,24 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Tiina Laantee, Ulf Johansson, Bodil Ravn, Thomas Strid</t>
-        </is>
-      </c>
-      <c r="AY169" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Thomas Strid, Bodil Ravn, Ulf Johansson, Tiina Laantee</t>
+        </is>
+      </c>
+      <c r="AY169" t="inlineStr"/>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97330311</t>
+          <t>https://artportalen.se/Sighting/97243108</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>98104097</v>
+        <v>97330311</v>
       </c>
       <c r="B170" t="n">
         <v>99118</v>
@@ -20082,27 +20067,24 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K170" t="inlineStr"/>
-      <c r="L170" t="inlineStr"/>
-      <c r="N170" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Ungfars kärr SO, Srm</t>
+          <t>Tyresta NP, SSV Bylsjön (*knärot* /stjälk/), Srm</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>686934</v>
+        <v>686847</v>
       </c>
       <c r="R170" t="n">
-        <v>6563325</v>
+        <v>6563309</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -20127,19 +20109,24 @@
           <t>Österhaninge</t>
         </is>
       </c>
+      <c r="X170" t="inlineStr">
+        <is>
+          <t>AB-Han-0218</t>
+        </is>
+      </c>
       <c r="Y170" t="inlineStr">
         <is>
-          <t>2022-01-13</t>
+          <t>2021-11-20</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>2022-01-13</t>
+          <t>2021-11-20</t>
         </is>
       </c>
       <c r="AC170" t="inlineStr">
         <is>
-          <t>Intill djurstig och granlåga</t>
+          <t>/Ej räknad/</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -20148,31 +20135,34 @@
       <c r="AE170" t="b">
         <v>0</v>
       </c>
-      <c r="AF170" t="inlineStr"/>
       <c r="AG170" t="b">
         <v>0</v>
       </c>
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
-        </is>
-      </c>
-      <c r="AY170" t="inlineStr"/>
+          <t>Tiina Laantee, Ulf Johansson, Bodil Ravn, Thomas Strid</t>
+        </is>
+      </c>
+      <c r="AY170" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98104097</t>
+          <t>https://artportalen.se/Sighting/97330311</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>104249959</v>
+        <v>98104097</v>
       </c>
       <c r="B171" t="n">
         <v>99118</v>
@@ -20200,24 +20190,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I171" t="inlineStr"/>
-      <c r="J171" t="inlineStr"/>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K171" t="inlineStr"/>
       <c r="L171" t="inlineStr"/>
       <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>SO Norrby Mosse, Srm</t>
+          <t>Ungfars kärr SO, Srm</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>687011</v>
+        <v>686934</v>
       </c>
       <c r="R171" t="n">
-        <v>6562869</v>
+        <v>6563325</v>
       </c>
       <c r="S171" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -20241,17 +20239,17 @@
       </c>
       <c r="Y171" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2022-01-13</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
+          <t>2022-01-13</t>
         </is>
       </c>
       <c r="AC171" t="inlineStr">
         <is>
-          <t>Samma lokal som noterades 17/11-21. Ca 25 ex. Koordinaterna har varierat något vid besöken.</t>
+          <t>Intill djurstig och granlåga</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -20267,24 +20265,24 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104249959</t>
+          <t>https://artportalen.se/Sighting/98104097</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>109890506</v>
+        <v>104249959</v>
       </c>
       <c r="B172" t="n">
         <v>99118</v>
@@ -20319,17 +20317,17 @@
       <c r="N172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>Ö Norrby Mosse, Srm</t>
+          <t>SO Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>686831</v>
+        <v>687011</v>
       </c>
       <c r="R172" t="n">
-        <v>6563216</v>
+        <v>6562869</v>
       </c>
       <c r="S172" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -20353,12 +20351,17 @@
       </c>
       <c r="Y172" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2022-09-16</t>
+        </is>
+      </c>
+      <c r="AC172" t="inlineStr">
+        <is>
+          <t>Samma lokal som noterades 17/11-21. Ca 25 ex. Koordinaterna har varierat något vid besöken.</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -20385,13 +20388,13 @@
       <c r="AY172" t="inlineStr"/>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109890506</t>
+          <t>https://artportalen.se/Sighting/104249959</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>119475594</v>
+        <v>109890506</v>
       </c>
       <c r="B173" t="n">
         <v>99118</v>
@@ -20419,29 +20422,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J173" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr"/>
       <c r="L173" t="inlineStr"/>
       <c r="N173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>NO Norrby  Mosse, Srm</t>
+          <t>Ö Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>686995</v>
+        <v>686831</v>
       </c>
       <c r="R173" t="n">
-        <v>6563315</v>
+        <v>6563216</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -20468,12 +20463,12 @@
       </c>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -20500,13 +20495,13 @@
       <c r="AY173" t="inlineStr"/>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119475594</t>
+          <t>https://artportalen.se/Sighting/109890506</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>121859637</v>
+        <v>119475594</v>
       </c>
       <c r="B174" t="n">
         <v>99118</v>
@@ -20534,17 +20529,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I174" t="inlineStr"/>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr"/>
+      <c r="N174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Öster om Tyresta by, Tyresta, Srm</t>
+          <t>NO Norrby  Mosse, Srm</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>686863</v>
+        <v>686995</v>
       </c>
       <c r="R174" t="n">
-        <v>6563252</v>
+        <v>6563315</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -20571,22 +20578,12 @@
       </c>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="Z174" t="inlineStr">
-        <is>
-          <t>16:22</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="AB174" t="inlineStr">
-        <is>
-          <t>16:22</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -20595,30 +20592,31 @@
       <c r="AE174" t="b">
         <v>0</v>
       </c>
+      <c r="AF174" t="inlineStr"/>
       <c r="AG174" t="b">
         <v>0</v>
       </c>
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859637</t>
+          <t>https://artportalen.se/Sighting/119475594</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>121859638</v>
+        <v>121859637</v>
       </c>
       <c r="B175" t="n">
         <v>99118</v>
@@ -20653,10 +20651,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>686826</v>
+        <v>686863</v>
       </c>
       <c r="R175" t="n">
-        <v>6563286</v>
+        <v>6563252</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -20688,7 +20686,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -20698,7 +20696,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -20724,13 +20722,13 @@
       <c r="AY175" t="inlineStr"/>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859638</t>
+          <t>https://artportalen.se/Sighting/121859637</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>121859639</v>
+        <v>121859638</v>
       </c>
       <c r="B176" t="n">
         <v>99118</v>
@@ -20765,10 +20763,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>686827</v>
+        <v>686826</v>
       </c>
       <c r="R176" t="n">
-        <v>6563296</v>
+        <v>6563286</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -20800,7 +20798,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -20810,7 +20808,7 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -20836,13 +20834,13 @@
       <c r="AY176" t="inlineStr"/>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859639</t>
+          <t>https://artportalen.se/Sighting/121859638</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>121859640</v>
+        <v>121859639</v>
       </c>
       <c r="B177" t="n">
         <v>99118</v>
@@ -20877,10 +20875,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>686837</v>
+        <v>686827</v>
       </c>
       <c r="R177" t="n">
-        <v>6563297</v>
+        <v>6563296</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -20912,7 +20910,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -20922,7 +20920,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -20948,13 +20946,13 @@
       <c r="AY177" t="inlineStr"/>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859640</t>
+          <t>https://artportalen.se/Sighting/121859639</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>121859642</v>
+        <v>121859640</v>
       </c>
       <c r="B178" t="n">
         <v>99118</v>
@@ -20983,24 +20981,16 @@
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
-      <c r="J178" t="inlineStr"/>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L178" t="inlineStr"/>
-      <c r="N178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
           <t>Öster om Tyresta by, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>686834</v>
+        <v>686837</v>
       </c>
       <c r="R178" t="n">
-        <v>6563305</v>
+        <v>6563297</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -21032,7 +21022,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -21042,7 +21032,7 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -21051,7 +21041,6 @@
       <c r="AE178" t="b">
         <v>0</v>
       </c>
-      <c r="AF178" t="inlineStr"/>
       <c r="AG178" t="b">
         <v>0</v>
       </c>
@@ -21069,13 +21058,13 @@
       <c r="AY178" t="inlineStr"/>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859642</t>
+          <t>https://artportalen.se/Sighting/121859640</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>121859643</v>
+        <v>121859642</v>
       </c>
       <c r="B179" t="n">
         <v>99118</v>
@@ -21104,6 +21093,14 @@
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr"/>
+      <c r="N179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
           <t>Öster om Tyresta by, Tyresta, Srm</t>
@@ -21113,7 +21110,7 @@
         <v>686834</v>
       </c>
       <c r="R179" t="n">
-        <v>6563309</v>
+        <v>6563305</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -21145,7 +21142,7 @@
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -21155,7 +21152,7 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -21164,6 +21161,7 @@
       <c r="AE179" t="b">
         <v>0</v>
       </c>
+      <c r="AF179" t="inlineStr"/>
       <c r="AG179" t="b">
         <v>0</v>
       </c>
@@ -21181,13 +21179,13 @@
       <c r="AY179" t="inlineStr"/>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859643</t>
+          <t>https://artportalen.se/Sighting/121859642</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>121859644</v>
+        <v>121859643</v>
       </c>
       <c r="B180" t="n">
         <v>99118</v>
@@ -21222,10 +21220,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>686844</v>
+        <v>686834</v>
       </c>
       <c r="R180" t="n">
-        <v>6563303</v>
+        <v>6563309</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -21257,7 +21255,7 @@
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
@@ -21267,7 +21265,7 @@
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -21293,13 +21291,13 @@
       <c r="AY180" t="inlineStr"/>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859644</t>
+          <t>https://artportalen.se/Sighting/121859643</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>121859646</v>
+        <v>121859644</v>
       </c>
       <c r="B181" t="n">
         <v>99118</v>
@@ -21334,7 +21332,7 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>686841</v>
+        <v>686844</v>
       </c>
       <c r="R181" t="n">
         <v>6563303</v>
@@ -21369,7 +21367,7 @@
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
@@ -21379,7 +21377,7 @@
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -21405,13 +21403,13 @@
       <c r="AY181" t="inlineStr"/>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859646</t>
+          <t>https://artportalen.se/Sighting/121859644</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>121859647</v>
+        <v>121859646</v>
       </c>
       <c r="B182" t="n">
         <v>99118</v>
@@ -21446,10 +21444,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>686854</v>
+        <v>686841</v>
       </c>
       <c r="R182" t="n">
-        <v>6563286</v>
+        <v>6563303</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -21481,7 +21479,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -21491,7 +21489,7 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -21517,13 +21515,13 @@
       <c r="AY182" t="inlineStr"/>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859647</t>
+          <t>https://artportalen.se/Sighting/121859646</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>121859649</v>
+        <v>121859647</v>
       </c>
       <c r="B183" t="n">
         <v>99118</v>
@@ -21558,10 +21556,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>686851</v>
+        <v>686854</v>
       </c>
       <c r="R183" t="n">
-        <v>6563299</v>
+        <v>6563286</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -21593,7 +21591,7 @@
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -21603,7 +21601,7 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -21629,13 +21627,13 @@
       <c r="AY183" t="inlineStr"/>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859649</t>
+          <t>https://artportalen.se/Sighting/121859647</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>121859650</v>
+        <v>121859649</v>
       </c>
       <c r="B184" t="n">
         <v>99118</v>
@@ -21670,10 +21668,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>686895</v>
+        <v>686851</v>
       </c>
       <c r="R184" t="n">
-        <v>6563306</v>
+        <v>6563299</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -21705,7 +21703,7 @@
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
@@ -21715,7 +21713,7 @@
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -21741,13 +21739,13 @@
       <c r="AY184" t="inlineStr"/>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859650</t>
+          <t>https://artportalen.se/Sighting/121859649</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>122220583</v>
+        <v>121859650</v>
       </c>
       <c r="B185" t="n">
         <v>99118</v>
@@ -21775,29 +21773,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J185" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K185" t="inlineStr"/>
-      <c r="L185" t="inlineStr"/>
-      <c r="N185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>SO Norrby Mosse, Srm</t>
+          <t>Öster om Tyresta by, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>686996</v>
+        <v>686895</v>
       </c>
       <c r="R185" t="n">
-        <v>6562864</v>
+        <v>6563306</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -21824,17 +21810,22 @@
       </c>
       <c r="Y185" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="Z185" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
-        </is>
-      </c>
-      <c r="AC185" t="inlineStr">
-        <is>
-          <t>Samma lokal som rapporterats -21 och -22 men en ny klon. Den förra har möjligen haft lite problem med grisbök.</t>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="AB185" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -21843,31 +21834,30 @@
       <c r="AE185" t="b">
         <v>0</v>
       </c>
-      <c r="AF185" t="inlineStr"/>
       <c r="AG185" t="b">
         <v>0</v>
       </c>
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122220583</t>
+          <t>https://artportalen.se/Sighting/121859650</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>122781008</v>
+        <v>122220583</v>
       </c>
       <c r="B186" t="n">
         <v>99118</v>
@@ -21895,21 +21885,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I186" t="inlineStr"/>
-      <c r="J186" t="inlineStr"/>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K186" t="inlineStr"/>
       <c r="L186" t="inlineStr"/>
       <c r="N186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Knärot, Srm</t>
+          <t>SO Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>686833</v>
+        <v>686996</v>
       </c>
       <c r="R186" t="n">
-        <v>6563215</v>
+        <v>6562864</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -21936,17 +21934,17 @@
       </c>
       <c r="Y186" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="AC186" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Samma lokal som rapporterats -21 och -22 men en ny klon. Den förra har möjligen haft lite problem med grisbök.</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -21962,24 +21960,24 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122781008</t>
+          <t>https://artportalen.se/Sighting/122220583</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>126418709</v>
+        <v>122781008</v>
       </c>
       <c r="B187" t="n">
         <v>99118</v>
@@ -22007,29 +22005,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J187" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I187" t="inlineStr"/>
+      <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr"/>
       <c r="L187" t="inlineStr"/>
       <c r="N187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Knärot, Srm</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>686771</v>
+        <v>686833</v>
       </c>
       <c r="R187" t="n">
-        <v>6563297</v>
+        <v>6563215</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -22056,17 +22046,17 @@
       </c>
       <c r="Y187" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AC187" t="inlineStr">
         <is>
-          <t>Två av dem i knopp, ca 3 m väster om de andra.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -22082,24 +22072,24 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126418709</t>
+          <t>https://artportalen.se/Sighting/122781008</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>126418756</v>
+        <v>126418709</v>
       </c>
       <c r="B188" t="n">
         <v>99118</v>
@@ -22129,7 +22119,7 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
@@ -22146,10 +22136,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>686781</v>
+        <v>686771</v>
       </c>
       <c r="R188" t="n">
-        <v>6563292</v>
+        <v>6563297</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -22186,7 +22176,7 @@
       </c>
       <c r="AC188" t="inlineStr">
         <is>
-          <t>En av dem i knopp.</t>
+          <t>Två av dem i knopp, ca 3 m väster om de andra.</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -22213,13 +22203,13 @@
       <c r="AY188" t="inlineStr"/>
       <c r="AZ188" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126418756</t>
+          <t>https://artportalen.se/Sighting/126418709</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>127932426</v>
+        <v>126418756</v>
       </c>
       <c r="B189" t="n">
         <v>99118</v>
@@ -22249,7 +22239,7 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
@@ -22266,10 +22256,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>686998</v>
+        <v>686781</v>
       </c>
       <c r="R189" t="n">
-        <v>6563316</v>
+        <v>6563292</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -22296,17 +22286,17 @@
       </c>
       <c r="Y189" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AC189" t="inlineStr">
         <is>
-          <t>Återfynd, rapporterad -24 med 3 ex. Nu 5 ex.</t>
+          <t>En av dem i knopp.</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -22333,13 +22323,13 @@
       <c r="AY189" t="inlineStr"/>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127932426</t>
+          <t>https://artportalen.se/Sighting/126418756</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>128341941</v>
+        <v>127932426</v>
       </c>
       <c r="B190" t="n">
         <v>99118</v>
@@ -22369,7 +22359,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
@@ -22386,10 +22376,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>687244</v>
+        <v>686998</v>
       </c>
       <c r="R190" t="n">
-        <v>6563404</v>
+        <v>6563316</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -22416,12 +22406,17 @@
       </c>
       <c r="Y190" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC190" t="inlineStr">
+        <is>
+          <t>Återfynd, rapporterad -24 med 3 ex. Nu 5 ex.</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -22448,13 +22443,13 @@
       <c r="AY190" t="inlineStr"/>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128341941</t>
+          <t>https://artportalen.se/Sighting/127932426</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129564285</v>
+        <v>128341941</v>
       </c>
       <c r="B191" t="n">
         <v>99118</v>
@@ -22482,8 +22477,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I191" t="inlineStr"/>
-      <c r="J191" t="inlineStr"/>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K191" t="inlineStr"/>
       <c r="L191" t="inlineStr"/>
       <c r="N191" t="inlineStr"/>
@@ -22493,10 +22496,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>686625</v>
+        <v>687244</v>
       </c>
       <c r="R191" t="n">
-        <v>6563000</v>
+        <v>6563404</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -22523,12 +22526,12 @@
       </c>
       <c r="Y191" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -22555,16 +22558,16 @@
       <c r="AY191" t="inlineStr"/>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129564285</t>
+          <t>https://artportalen.se/Sighting/128341941</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>133767721</v>
+        <v>129564285</v>
       </c>
       <c r="B192" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -22600,10 +22603,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>686845</v>
+        <v>686625</v>
       </c>
       <c r="R192" t="n">
-        <v>6563325</v>
+        <v>6563000</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -22630,12 +22633,12 @@
       </c>
       <c r="Y192" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -22662,38 +22665,38 @@
       <c r="AY192" t="inlineStr"/>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133767721</t>
+          <t>https://artportalen.se/Sighting/129564285</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>96643458</v>
+        <v>133767721</v>
       </c>
       <c r="B193" t="n">
-        <v>106244</v>
+        <v>99195</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -22703,14 +22706,14 @@
       <c r="N193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Vargklåva mosse S om, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>687154</v>
+        <v>686845</v>
       </c>
       <c r="R193" t="n">
-        <v>6563329</v>
+        <v>6563325</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -22737,12 +22740,12 @@
       </c>
       <c r="Y193" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -22758,24 +22761,24 @@
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96643458</t>
+          <t>https://artportalen.se/Sighting/133767721</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>96858761</v>
+        <v>96643458</v>
       </c>
       <c r="B194" t="n">
         <v>106244</v>
@@ -22810,17 +22813,17 @@
       <c r="N194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Ungfars kärr SO, Srm</t>
+          <t>Vargklåva mosse S om, Srm</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>687064</v>
+        <v>687154</v>
       </c>
       <c r="R194" t="n">
-        <v>6563258</v>
+        <v>6563329</v>
       </c>
       <c r="S194" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -22844,17 +22847,12 @@
       </c>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>2021-10-26</t>
-        </is>
-      </c>
-      <c r="AC194" t="inlineStr">
-        <is>
-          <t>Två bestånd</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -22881,13 +22879,13 @@
       <c r="AY194" t="inlineStr"/>
       <c r="AZ194" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96858761</t>
+          <t>https://artportalen.se/Sighting/96643458</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>97204577</v>
+        <v>96858761</v>
       </c>
       <c r="B195" t="n">
         <v>106244</v>
@@ -22922,17 +22920,17 @@
       <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>SO Norrby mosse, Srm</t>
+          <t>Ungfars kärr SO, Srm</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>687019</v>
+        <v>687064</v>
       </c>
       <c r="R195" t="n">
-        <v>6562889</v>
+        <v>6563258</v>
       </c>
       <c r="S195" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -22956,12 +22954,17 @@
       </c>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>2021-11-17</t>
+          <t>2021-10-26</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>2021-11-17</t>
+          <t>2021-10-26</t>
+        </is>
+      </c>
+      <c r="AC195" t="inlineStr">
+        <is>
+          <t>Två bestånd</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -22977,24 +22980,24 @@
       <c r="AT195" t="inlineStr"/>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97204577</t>
+          <t>https://artportalen.se/Sighting/96858761</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>100252927</v>
+        <v>97204577</v>
       </c>
       <c r="B196" t="n">
         <v>106244</v>
@@ -23029,17 +23032,17 @@
       <c r="N196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>NO Norrby  Mosse, Srm</t>
+          <t>SO Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>687152</v>
+        <v>687019</v>
       </c>
       <c r="R196" t="n">
-        <v>6563326</v>
+        <v>6562889</v>
       </c>
       <c r="S196" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T196" t="inlineStr">
         <is>
@@ -23063,12 +23066,12 @@
       </c>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>2022-04-26</t>
+          <t>2021-11-17</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>2022-04-26</t>
+          <t>2021-11-17</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -23095,13 +23098,13 @@
       <c r="AY196" t="inlineStr"/>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/100252927</t>
+          <t>https://artportalen.se/Sighting/97204577</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>116743172</v>
+        <v>100252927</v>
       </c>
       <c r="B197" t="n">
         <v>106244</v>
@@ -23130,16 +23133,20 @@
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
+      <c r="J197" t="inlineStr"/>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr"/>
+      <c r="N197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Ungfars kärr, Ungfars kärr, Srm</t>
+          <t>NO Norrby  Mosse, Srm</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>687088</v>
+        <v>687152</v>
       </c>
       <c r="R197" t="n">
-        <v>6563243</v>
+        <v>6563326</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -23166,12 +23173,12 @@
       </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2022-04-26</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2022-04-26</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -23180,30 +23187,31 @@
       <c r="AE197" t="b">
         <v>0</v>
       </c>
+      <c r="AF197" t="inlineStr"/>
       <c r="AG197" t="b">
         <v>0</v>
       </c>
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116743172</t>
+          <t>https://artportalen.se/Sighting/100252927</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>125965889</v>
+        <v>116743172</v>
       </c>
       <c r="B198" t="n">
         <v>106244</v>
@@ -23238,10 +23246,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>687076</v>
+        <v>687088</v>
       </c>
       <c r="R198" t="n">
-        <v>6563220</v>
+        <v>6563243</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -23268,12 +23276,12 @@
       </c>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -23299,13 +23307,13 @@
       <c r="AY198" t="inlineStr"/>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125965889</t>
+          <t>https://artportalen.se/Sighting/116743172</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>126003574</v>
+        <v>125965889</v>
       </c>
       <c r="B199" t="n">
         <v>106244</v>
@@ -23334,20 +23342,16 @@
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
-      <c r="J199" t="inlineStr"/>
-      <c r="K199" t="inlineStr"/>
-      <c r="L199" t="inlineStr"/>
-      <c r="N199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
-          <t>SO Norrby Mosse, Srm</t>
+          <t>Ungfars kärr, Ungfars kärr, Srm</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>686803</v>
+        <v>687076</v>
       </c>
       <c r="R199" t="n">
-        <v>6563098</v>
+        <v>6563220</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -23374,12 +23378,12 @@
       </c>
       <c r="Y199" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -23388,31 +23392,30 @@
       <c r="AE199" t="b">
         <v>0</v>
       </c>
-      <c r="AF199" t="inlineStr"/>
       <c r="AG199" t="b">
         <v>0</v>
       </c>
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126003574</t>
+          <t>https://artportalen.se/Sighting/125965889</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>126061078</v>
+        <v>126003574</v>
       </c>
       <c r="B200" t="n">
         <v>106244</v>
@@ -23441,16 +23444,20 @@
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr"/>
+      <c r="N200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>SO Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>687085</v>
+        <v>686803</v>
       </c>
       <c r="R200" t="n">
-        <v>6563229</v>
+        <v>6563098</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -23477,22 +23484,12 @@
       </c>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z200" t="inlineStr">
-        <is>
-          <t>15:40</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB200" t="inlineStr">
-        <is>
-          <t>15:40</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -23501,30 +23498,31 @@
       <c r="AE200" t="b">
         <v>0</v>
       </c>
+      <c r="AF200" t="inlineStr"/>
       <c r="AG200" t="b">
         <v>0</v>
       </c>
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061078</t>
+          <t>https://artportalen.se/Sighting/126003574</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>126061079</v>
+        <v>126061078</v>
       </c>
       <c r="B201" t="n">
         <v>106244</v>
@@ -23559,10 +23557,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>687082</v>
+        <v>687085</v>
       </c>
       <c r="R201" t="n">
-        <v>6563241</v>
+        <v>6563229</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -23594,7 +23592,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -23604,7 +23602,7 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -23630,13 +23628,13 @@
       <c r="AY201" t="inlineStr"/>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061079</t>
+          <t>https://artportalen.se/Sighting/126061078</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>126234373</v>
+        <v>126061079</v>
       </c>
       <c r="B202" t="n">
         <v>106244</v>
@@ -23664,29 +23662,17 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I202" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J202" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K202" t="inlineStr"/>
-      <c r="L202" t="inlineStr"/>
-      <c r="N202" t="inlineStr"/>
+      <c r="I202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Norrby mosse SO, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>686756</v>
+        <v>687082</v>
       </c>
       <c r="R202" t="n">
-        <v>6563092</v>
+        <v>6563241</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -23713,12 +23699,22 @@
       </c>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z202" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB202" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -23727,31 +23723,30 @@
       <c r="AE202" t="b">
         <v>0</v>
       </c>
-      <c r="AF202" t="inlineStr"/>
       <c r="AG202" t="b">
         <v>0</v>
       </c>
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126234373</t>
+          <t>https://artportalen.se/Sighting/126061079</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>126234937</v>
+        <v>126234373</v>
       </c>
       <c r="B203" t="n">
         <v>106244</v>
@@ -23789,23 +23784,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K203" t="inlineStr"/>
       <c r="L203" t="inlineStr"/>
       <c r="N203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Ungfars kärr SO, Srm</t>
+          <t>Norrby mosse SO, Srm</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>687103</v>
+        <v>686756</v>
       </c>
       <c r="R203" t="n">
-        <v>6563191</v>
+        <v>6563092</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -23864,16 +23855,16 @@
       <c r="AY203" t="inlineStr"/>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126234937</t>
+          <t>https://artportalen.se/Sighting/126234373</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>96643468</v>
+        <v>126234937</v>
       </c>
       <c r="B204" t="n">
-        <v>97989</v>
+        <v>106244</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -23881,46 +23872,50 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>221941</v>
+        <v>221144</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K204" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr"/>
       <c r="N204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Vargklåva mosse S om, Srm</t>
+          <t>Ungfars kärr SO, Srm</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>687268</v>
+        <v>687103</v>
       </c>
       <c r="R204" t="n">
-        <v>6563319</v>
+        <v>6563191</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -23947,17 +23942,12 @@
       </c>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
-        </is>
-      </c>
-      <c r="AC204" t="inlineStr">
-        <is>
-          <t>Strax nedom klippbrant</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -23984,16 +23974,16 @@
       <c r="AY204" t="inlineStr"/>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96643468</t>
+          <t>https://artportalen.se/Sighting/126234937</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>116746465</v>
+        <v>136329900</v>
       </c>
       <c r="B205" t="n">
-        <v>97989</v>
+        <v>106444</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -24001,34 +23991,38 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>221941</v>
+        <v>221144</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
+      <c r="J205" t="inlineStr"/>
+      <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr"/>
+      <c r="N205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
-          <t>Norrby mosse, Norrby mosse, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>686888</v>
+        <v>686462</v>
       </c>
       <c r="R205" t="n">
-        <v>6563206</v>
+        <v>6563046</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -24055,12 +24049,12 @@
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -24069,33 +24063,34 @@
       <c r="AE205" t="b">
         <v>0</v>
       </c>
+      <c r="AF205" t="inlineStr"/>
       <c r="AG205" t="b">
         <v>0</v>
       </c>
       <c r="AT205" t="inlineStr"/>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
       <c r="AZ205" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116746465</t>
+          <t>https://artportalen.se/Sighting/136329900</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>135827249</v>
+        <v>96643468</v>
       </c>
       <c r="B206" t="n">
-        <v>98170</v>
+        <v>97989</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24120,21 +24115,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I206" t="inlineStr"/>
-      <c r="J206" t="inlineStr"/>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K206" t="inlineStr"/>
       <c r="L206" t="inlineStr"/>
       <c r="N206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Vargklåva mosse S om, Srm</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>687270</v>
+        <v>687268</v>
       </c>
       <c r="R206" t="n">
-        <v>6563321</v>
+        <v>6563319</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -24161,17 +24164,17 @@
       </c>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="AC206" t="inlineStr">
         <is>
-          <t>Återfynd, tidigare rapporterad 2021.</t>
+          <t>Strax nedom klippbrant</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -24187,27 +24190,27 @@
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
       <c r="AZ206" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135827249</t>
+          <t>https://artportalen.se/Sighting/96643468</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>121742517</v>
+        <v>116746465</v>
       </c>
       <c r="B207" t="n">
-        <v>97983</v>
+        <v>97989</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24215,16 +24218,16 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -24239,10 +24242,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>686859</v>
+        <v>686888</v>
       </c>
       <c r="R207" t="n">
-        <v>6562875</v>
+        <v>6563206</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -24269,12 +24272,12 @@
       </c>
       <c r="Y207" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -24300,16 +24303,16 @@
       <c r="AY207" t="inlineStr"/>
       <c r="AZ207" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121742517</t>
+          <t>https://artportalen.se/Sighting/116746465</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>122928987</v>
+        <v>135827249</v>
       </c>
       <c r="B208" t="n">
-        <v>97983</v>
+        <v>98171</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -24317,16 +24320,16 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -24341,14 +24344,14 @@
       <c r="N208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Norrby mosse, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>686389</v>
+        <v>687270</v>
       </c>
       <c r="R208" t="n">
-        <v>6562967</v>
+        <v>6563321</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -24375,22 +24378,17 @@
       </c>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="Z208" t="inlineStr">
-        <is>
-          <t>10:36</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="AB208" t="inlineStr">
-        <is>
-          <t>10:36</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AC208" t="inlineStr">
+        <is>
+          <t>Återfynd, tidigare rapporterad 2021.</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -24399,30 +24397,31 @@
       <c r="AE208" t="b">
         <v>0</v>
       </c>
+      <c r="AF208" t="inlineStr"/>
       <c r="AG208" t="b">
         <v>0</v>
       </c>
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
       <c r="AZ208" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122928987</t>
+          <t>https://artportalen.se/Sighting/135827249</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>122930294</v>
+        <v>121742517</v>
       </c>
       <c r="B209" t="n">
         <v>97983</v>
@@ -24451,23 +24450,19 @@
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
-      <c r="J209" t="inlineStr"/>
-      <c r="K209" t="inlineStr"/>
-      <c r="L209" t="inlineStr"/>
-      <c r="N209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Norrby mosse, Srm</t>
+          <t>Norrby mosse, Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>686824</v>
+        <v>686859</v>
       </c>
       <c r="R209" t="n">
-        <v>6562778</v>
+        <v>6562875</v>
       </c>
       <c r="S209" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="T209" t="inlineStr">
         <is>
@@ -24491,22 +24486,12 @@
       </c>
       <c r="Y209" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="Z209" t="inlineStr">
-        <is>
-          <t>11:29</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="AB209" t="inlineStr">
-        <is>
-          <t>11:29</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -24521,24 +24506,24 @@
       <c r="AT209" t="inlineStr"/>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
       <c r="AZ209" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122930294</t>
+          <t>https://artportalen.se/Sighting/121742517</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>125963374</v>
+        <v>122928987</v>
       </c>
       <c r="B210" t="n">
         <v>97983</v>
@@ -24567,16 +24552,20 @@
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
+      <c r="J210" t="inlineStr"/>
+      <c r="K210" t="inlineStr"/>
+      <c r="L210" t="inlineStr"/>
+      <c r="N210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Norrby mosse, Norrby mosse, Srm</t>
+          <t>Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>686873</v>
+        <v>686389</v>
       </c>
       <c r="R210" t="n">
-        <v>6562867</v>
+        <v>6562967</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -24603,12 +24592,22 @@
       </c>
       <c r="Y210" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="Z210" t="inlineStr">
+        <is>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AB210" t="inlineStr">
+        <is>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -24623,24 +24622,24 @@
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
       <c r="AZ210" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125963374</t>
+          <t>https://artportalen.se/Sighting/122928987</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>125976418</v>
+        <v>122930294</v>
       </c>
       <c r="B211" t="n">
         <v>97983</v>
@@ -24675,17 +24674,17 @@
       <c r="N211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Norrby mosse Ö om, Srm</t>
+          <t>Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>686836</v>
+        <v>686824</v>
       </c>
       <c r="R211" t="n">
-        <v>6563105</v>
+        <v>6562778</v>
       </c>
       <c r="S211" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="T211" t="inlineStr">
         <is>
@@ -24709,17 +24708,22 @@
       </c>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="Z211" t="inlineStr">
+        <is>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC211" t="inlineStr">
-        <is>
-          <t>Riklig förekomst i skogskärr</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AB211" t="inlineStr">
+        <is>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -24728,31 +24732,30 @@
       <c r="AE211" t="b">
         <v>0</v>
       </c>
-      <c r="AF211" t="inlineStr"/>
       <c r="AG211" t="b">
         <v>0</v>
       </c>
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125976418</t>
+          <t>https://artportalen.se/Sighting/122930294</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>126061082</v>
+        <v>125963374</v>
       </c>
       <c r="B212" t="n">
         <v>97983</v>
@@ -24783,14 +24786,14 @@
       <c r="I212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>Norrby mosse, Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>687079</v>
+        <v>686873</v>
       </c>
       <c r="R212" t="n">
-        <v>6563240</v>
+        <v>6562867</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -24820,19 +24823,9 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z212" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AA212" t="inlineStr">
         <is>
           <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB212" t="inlineStr">
-        <is>
-          <t>15:22</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -24847,24 +24840,24 @@
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061082</t>
+          <t>https://artportalen.se/Sighting/125963374</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>126061090</v>
+        <v>125976418</v>
       </c>
       <c r="B213" t="n">
         <v>97983</v>
@@ -24893,19 +24886,23 @@
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
+      <c r="J213" t="inlineStr"/>
+      <c r="K213" t="inlineStr"/>
+      <c r="L213" t="inlineStr"/>
+      <c r="N213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>Norrby mosse Ö om, Srm</t>
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>686871</v>
+        <v>686836</v>
       </c>
       <c r="R213" t="n">
-        <v>6562972</v>
+        <v>6563105</v>
       </c>
       <c r="S213" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T213" t="inlineStr">
         <is>
@@ -24932,19 +24929,14 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z213" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AA213" t="inlineStr">
         <is>
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AB213" t="inlineStr">
-        <is>
-          <t>14:42</t>
+      <c r="AC213" t="inlineStr">
+        <is>
+          <t>Riklig förekomst i skogskärr</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -24953,30 +24945,31 @@
       <c r="AE213" t="b">
         <v>0</v>
       </c>
+      <c r="AF213" t="inlineStr"/>
       <c r="AG213" t="b">
         <v>0</v>
       </c>
       <c r="AT213" t="inlineStr"/>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
       <c r="AZ213" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061090</t>
+          <t>https://artportalen.se/Sighting/125976418</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>126061103</v>
+        <v>126061082</v>
       </c>
       <c r="B214" t="n">
         <v>97983</v>
@@ -25011,10 +25004,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>686811</v>
+        <v>687079</v>
       </c>
       <c r="R214" t="n">
-        <v>6562803</v>
+        <v>6563240</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -25046,7 +25039,7 @@
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
@@ -25056,7 +25049,7 @@
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -25076,19 +25069,19 @@
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
       <c r="AZ214" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061103</t>
+          <t>https://artportalen.se/Sighting/126061082</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>126061111</v>
+        <v>126061090</v>
       </c>
       <c r="B215" t="n">
         <v>97983</v>
@@ -25123,10 +25116,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>687030</v>
+        <v>686871</v>
       </c>
       <c r="R215" t="n">
-        <v>6562755</v>
+        <v>6562972</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -25158,7 +25151,7 @@
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
@@ -25168,7 +25161,7 @@
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -25188,22 +25181,22 @@
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061111</t>
+          <t>https://artportalen.se/Sighting/126061090</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>122929342</v>
+        <v>126061103</v>
       </c>
       <c r="B216" t="n">
-        <v>97986</v>
+        <v>97983</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -25211,16 +25204,16 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -25229,23 +25222,19 @@
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
-      <c r="J216" t="inlineStr"/>
-      <c r="K216" t="inlineStr"/>
-      <c r="L216" t="inlineStr"/>
-      <c r="N216" t="inlineStr"/>
       <c r="P216" t="inlineStr">
         <is>
-          <t>Norrby mosse, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>686569</v>
+        <v>686811</v>
       </c>
       <c r="R216" t="n">
-        <v>6562949</v>
+        <v>6562803</v>
       </c>
       <c r="S216" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T216" t="inlineStr">
         <is>
@@ -25269,22 +25258,22 @@
       </c>
       <c r="Y216" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -25299,27 +25288,27 @@
       <c r="AT216" t="inlineStr"/>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
       <c r="AZ216" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122929342</t>
+          <t>https://artportalen.se/Sighting/126061103</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>126061110</v>
+        <v>126061111</v>
       </c>
       <c r="B217" t="n">
-        <v>97986</v>
+        <v>97983</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -25327,16 +25316,16 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -25351,10 +25340,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>687029</v>
+        <v>687030</v>
       </c>
       <c r="R217" t="n">
-        <v>6562759</v>
+        <v>6562755</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -25386,7 +25375,7 @@
       </c>
       <c r="Z217" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
@@ -25396,7 +25385,7 @@
       </c>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -25422,16 +25411,16 @@
       <c r="AY217" t="inlineStr"/>
       <c r="AZ217" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061110</t>
+          <t>https://artportalen.se/Sighting/126061111</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>101523203</v>
+        <v>122929342</v>
       </c>
       <c r="B218" t="n">
-        <v>99140</v>
+        <v>97986</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -25439,21 +25428,21 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>221952</v>
+        <v>221946</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -25463,17 +25452,17 @@
       <c r="N218" t="inlineStr"/>
       <c r="P218" t="inlineStr">
         <is>
-          <t>NO Norrby Mosse, Srm</t>
+          <t>Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>687050</v>
+        <v>686569</v>
       </c>
       <c r="R218" t="n">
-        <v>6563327</v>
+        <v>6562949</v>
       </c>
       <c r="S218" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T218" t="inlineStr">
         <is>
@@ -25497,12 +25486,22 @@
       </c>
       <c r="Y218" t="inlineStr">
         <is>
-          <t>2022-06-08</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="Z218" t="inlineStr">
+        <is>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
         <is>
-          <t>2022-06-08</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AB218" t="inlineStr">
+        <is>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -25511,34 +25510,33 @@
       <c r="AE218" t="b">
         <v>0</v>
       </c>
-      <c r="AF218" t="inlineStr"/>
       <c r="AG218" t="b">
         <v>0</v>
       </c>
       <c r="AT218" t="inlineStr"/>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101523203</t>
+          <t>https://artportalen.se/Sighting/122929342</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>117554655</v>
+        <v>126061110</v>
       </c>
       <c r="B219" t="n">
-        <v>99140</v>
+        <v>97986</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -25546,42 +25544,34 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>221952</v>
+        <v>221946</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
-      <c r="J219" t="inlineStr"/>
-      <c r="K219" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L219" t="inlineStr"/>
-      <c r="N219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
-          <t>NO Norrby  Mosse, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>687062</v>
+        <v>687029</v>
       </c>
       <c r="R219" t="n">
-        <v>6563349</v>
+        <v>6562759</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -25608,12 +25598,22 @@
       </c>
       <c r="Y219" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z219" t="inlineStr">
+        <is>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB219" t="inlineStr">
+        <is>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -25622,31 +25622,30 @@
       <c r="AE219" t="b">
         <v>0</v>
       </c>
-      <c r="AF219" t="inlineStr"/>
       <c r="AG219" t="b">
         <v>0</v>
       </c>
       <c r="AT219" t="inlineStr"/>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
       <c r="AZ219" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117554655</t>
+          <t>https://artportalen.se/Sighting/126061110</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>126234400</v>
+        <v>101523203</v>
       </c>
       <c r="B220" t="n">
         <v>99140</v>
@@ -25674,33 +25673,21 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I220" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J220" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K220" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="I220" t="inlineStr"/>
+      <c r="J220" t="inlineStr"/>
+      <c r="K220" t="inlineStr"/>
       <c r="L220" t="inlineStr"/>
       <c r="N220" t="inlineStr"/>
       <c r="P220" t="inlineStr">
         <is>
-          <t>Norrby mosse SO, Srm</t>
+          <t>NO Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>686788</v>
+        <v>687050</v>
       </c>
       <c r="R220" t="n">
-        <v>6563073</v>
+        <v>6563327</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -25727,12 +25714,12 @@
       </c>
       <c r="Y220" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2022-06-08</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2022-06-08</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -25748,27 +25735,27 @@
       <c r="AT220" t="inlineStr"/>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126234400</t>
+          <t>https://artportalen.se/Sighting/101523203</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>134487623</v>
+        <v>117554655</v>
       </c>
       <c r="B221" t="n">
-        <v>99217</v>
+        <v>99140</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -25804,17 +25791,17 @@
       <c r="N221" t="inlineStr"/>
       <c r="P221" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>NO Norrby  Mosse, Srm</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>687067</v>
+        <v>687062</v>
       </c>
       <c r="R221" t="n">
-        <v>6563342</v>
+        <v>6563349</v>
       </c>
       <c r="S221" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T221" t="inlineStr">
         <is>
@@ -25838,17 +25825,12 @@
       </c>
       <c r="Y221" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="AC221" t="inlineStr">
-        <is>
-          <t>Ett tiotal i blom samt flera plantor med endast blad.  Återfynd.</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -25875,16 +25857,16 @@
       <c r="AY221" t="inlineStr"/>
       <c r="AZ221" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134487623</t>
+          <t>https://artportalen.se/Sighting/117554655</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>134487656</v>
+        <v>126234400</v>
       </c>
       <c r="B222" t="n">
-        <v>99217</v>
+        <v>99140</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -25909,8 +25891,16 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I222" t="inlineStr"/>
-      <c r="J222" t="inlineStr"/>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K222" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -25920,14 +25910,14 @@
       <c r="N222" t="inlineStr"/>
       <c r="P222" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrby mosse SO, Srm</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>686835</v>
+        <v>686788</v>
       </c>
       <c r="R222" t="n">
-        <v>6563212</v>
+        <v>6563073</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -25954,17 +25944,12 @@
       </c>
       <c r="Y222" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="AC222" t="inlineStr">
-        <is>
-          <t>2 i blom samt några plantor med endast blad.</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -25980,24 +25965,24 @@
       <c r="AT222" t="inlineStr"/>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134487656</t>
+          <t>https://artportalen.se/Sighting/126234400</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>134488457</v>
+        <v>134487623</v>
       </c>
       <c r="B223" t="n">
         <v>99217</v>
@@ -26040,13 +26025,13 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>687294</v>
+        <v>687067</v>
       </c>
       <c r="R223" t="n">
-        <v>6563391</v>
+        <v>6563342</v>
       </c>
       <c r="S223" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T223" t="inlineStr">
         <is>
@@ -26080,7 +26065,7 @@
       </c>
       <c r="AC223" t="inlineStr">
         <is>
-          <t>2 i blom samt fler med endast blad.</t>
+          <t>Ett tiotal i blom samt flera plantor med endast blad.  Återfynd.</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -26107,43 +26092,48 @@
       <c r="AY223" t="inlineStr"/>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134488457</t>
+          <t>https://artportalen.se/Sighting/134487623</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>129564006</v>
+        <v>134487656</v>
       </c>
       <c r="B224" t="n">
-        <v>79350</v>
+        <v>99217</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>260591</v>
+        <v>221952</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
       <c r="J224" t="inlineStr"/>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr"/>
       <c r="N224" t="inlineStr"/>
       <c r="P224" t="inlineStr">
         <is>
@@ -26151,10 +26141,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>686681</v>
+        <v>686835</v>
       </c>
       <c r="R224" t="n">
-        <v>6563025</v>
+        <v>6563212</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -26181,19 +26171,24 @@
       </c>
       <c r="Y224" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AC224" t="inlineStr">
+        <is>
+          <t>2 i blom samt några plantor med endast blad.</t>
         </is>
       </c>
       <c r="AD224" t="b">
         <v>0</v>
       </c>
       <c r="AE224" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF224" t="inlineStr"/>
       <c r="AG224" t="b">
@@ -26212,6 +26207,228 @@
       </c>
       <c r="AY224" t="inlineStr"/>
       <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134487656</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>134488457</v>
+      </c>
+      <c r="B225" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E225" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr"/>
+      <c r="J225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr"/>
+      <c r="N225" t="inlineStr"/>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q225" t="n">
+        <v>687294</v>
+      </c>
+      <c r="R225" t="n">
+        <v>6563391</v>
+      </c>
+      <c r="S225" t="n">
+        <v>10</v>
+      </c>
+      <c r="T225" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V225" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W225" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y225" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AC225" t="inlineStr">
+        <is>
+          <t>2 i blom samt fler med endast blad.</t>
+        </is>
+      </c>
+      <c r="AD225" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE225" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF225" t="inlineStr"/>
+      <c r="AG225" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT225" t="inlineStr"/>
+      <c r="AW225" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX225" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134488457</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>129564006</v>
+      </c>
+      <c r="B226" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E226" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr"/>
+      <c r="J226" t="inlineStr"/>
+      <c r="K226" t="inlineStr"/>
+      <c r="N226" t="inlineStr"/>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q226" t="n">
+        <v>686681</v>
+      </c>
+      <c r="R226" t="n">
+        <v>6563025</v>
+      </c>
+      <c r="S226" t="n">
+        <v>10</v>
+      </c>
+      <c r="T226" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V226" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W226" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y226" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AD226" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE226" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF226" t="inlineStr"/>
+      <c r="AG226" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT226" t="inlineStr"/>
+      <c r="AW226" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX226" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY226" t="inlineStr"/>
+      <c r="AZ226" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129564006</t>
         </is>
@@ -26442,6 +26659,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
